--- a/data/database/shopgraph_purchase_history.xlsx
+++ b/data/database/shopgraph_purchase_history.xlsx
@@ -565,7 +565,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IMG_0253_raw_ocr.json</t>
+          <t>IMG_0250_raw_ocr.json</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -768,7 +768,7 @@
         <v>46259</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>46260.61534395623</v>
+        <v>46260.71688999394</v>
       </c>
     </row>
   </sheetData>

--- a/data/database/shopgraph_purchase_history.xlsx
+++ b/data/database/shopgraph_purchase_history.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Imported Receipts" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Purchase History'!$A$1:$J$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Purchase History'!$A$1:$O$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -61,8 +61,8 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -429,289 +429,448 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="3" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr"/>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Six-Digit SKU</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Tax Code</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Store Number</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Common Name</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Date 1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Price 1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Date 2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Price 2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Date 3</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Price 3</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="2">
+        <f>SUMPRODUCT((MOD(COLUMN(K2:XFD2)-COLUMN(K2),2)=0)*N(K2:XFD2))</f>
+        <v/>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Publix</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>Stony Yobaby Pouch Peach</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>1058</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>46259</v>
-      </c>
-      <c r="F2" s="3" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="K2" s="2" t="n">
         <v>7.85</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="2">
+        <f>SUMPRODUCT((MOD(COLUMN(K3:XFD3)-COLUMN(K3),2)=0)*N(K3:XFD3))</f>
+        <v/>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Publix</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>Stony Yobaby Pouch Banana</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>1058</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>46259</v>
-      </c>
-      <c r="F3" s="3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="K3" s="2" t="n">
         <v>7.85</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="A4" s="2">
+        <f>SUMPRODUCT((MOD(COLUMN(K4:XFD4)-COLUMN(K4),2)=0)*N(K4:XFD4))</f>
+        <v/>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Publix</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>Sweet Loren's Gf Brownie</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>1058</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>46259</v>
-      </c>
-      <c r="F4" s="3" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="K4" s="2" t="n">
         <v>6.99</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="2">
+        <f>SUMPRODUCT((MOD(COLUMN(K5:XFD5)-COLUMN(K5),2)=0)*N(K5:XFD5))</f>
+        <v/>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Publix</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>Vans Waffle Blueberry Gf</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>1058</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>46259</v>
-      </c>
-      <c r="F5" s="3" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="K5" s="2" t="n">
         <v>3.89</v>
       </c>
-      <c r="G5" s="2" t="n">
-        <v>46259</v>
-      </c>
-      <c r="H5" s="3" t="n">
+      <c r="L5" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="M5" s="2" t="n">
         <v>3.89</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="A6" s="2">
+        <f>SUMPRODUCT((MOD(COLUMN(K6:XFD6)-COLUMN(K6),2)=0)*N(K6:XFD6))</f>
+        <v/>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Publix</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>Chobani 4Pk Hero Batch</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>1058</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>46259</v>
-      </c>
-      <c r="F6" s="3" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="K6" s="2" t="n">
         <v>5.65</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="A7" s="2">
+        <f>SUMPRODUCT((MOD(COLUMN(K7:XFD7)-COLUMN(K7),2)=0)*N(K7:XFD7))</f>
+        <v/>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Publix</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>Silk Soy Organic Nsa Hg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>1058</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>46259</v>
-      </c>
-      <c r="F7" s="3" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="K7" s="2" t="n">
         <v>6.19</v>
       </c>
-      <c r="G7" s="2" t="n">
-        <v>46259</v>
-      </c>
-      <c r="H7" s="3" t="n">
+      <c r="L7" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="M7" s="2" t="n">
         <v>6.19</v>
       </c>
-      <c r="I7" s="2" t="n">
-        <v>46259</v>
-      </c>
-      <c r="J7" s="3" t="n">
+      <c r="N7" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="O7" s="2" t="n">
         <v>6.19</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+      <c r="A8" s="2">
+        <f>SUMPRODUCT((MOD(COLUMN(K8:XFD8)-COLUMN(K8),2)=0)*N(K8:XFD8))</f>
+        <v/>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Publix</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>Publix Half&amp;Half Hg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>1058</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>46259</v>
-      </c>
-      <c r="F8" s="3" t="n">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="K8" s="2" t="n">
         <v>5.89</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J8"/>
+  <autoFilter ref="A1:O8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -764,11 +923,11 @@
           <t>1058</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="3" t="n">
         <v>46259</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>46260.71688999394</v>
+        <v>46260.73270101212</v>
       </c>
     </row>
   </sheetData>

--- a/data/database/shopgraph_purchase_history.xlsx
+++ b/data/database/shopgraph_purchase_history.xlsx
@@ -19,12 +19,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
-    <numFmt numFmtId="166" formatCode="$0.00"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="168" formatCode="mm/dd/yyyy hh:mm"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="167" formatCode="mm/dd/yyyy hh:mm"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -61,9 +60,9 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -524,7 +523,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <f>SUMPRODUCT((MOD(COLUMN(K2:XFD2)-COLUMN(K2),2)=0)*N(K2:XFD2))</f>
+        <f>SUM(K2,M2,O2)</f>
         <v/>
       </c>
       <c r="C2" t="inlineStr">
@@ -571,7 +570,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2">
-        <f>SUMPRODUCT((MOD(COLUMN(K3:XFD3)-COLUMN(K3),2)=0)*N(K3:XFD3))</f>
+        <f>SUM(K3,M3,O3)</f>
         <v/>
       </c>
       <c r="C3" t="inlineStr">
@@ -618,7 +617,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <f>SUMPRODUCT((MOD(COLUMN(K4:XFD4)-COLUMN(K4),2)=0)*N(K4:XFD4))</f>
+        <f>SUM(K4,M4,O4)</f>
         <v/>
       </c>
       <c r="C4" t="inlineStr">
@@ -665,7 +664,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2">
-        <f>SUMPRODUCT((MOD(COLUMN(K5:XFD5)-COLUMN(K5),2)=0)*N(K5:XFD5))</f>
+        <f>SUM(K5,M5,O5)</f>
         <v/>
       </c>
       <c r="C5" t="inlineStr">
@@ -718,7 +717,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2">
-        <f>SUMPRODUCT((MOD(COLUMN(K6:XFD6)-COLUMN(K6),2)=0)*N(K6:XFD6))</f>
+        <f>SUM(K6,M6,O6)</f>
         <v/>
       </c>
       <c r="C6" t="inlineStr">
@@ -765,7 +764,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2">
-        <f>SUMPRODUCT((MOD(COLUMN(K7:XFD7)-COLUMN(K7),2)=0)*N(K7:XFD7))</f>
+        <f>SUM(K7,M7,O7)</f>
         <v/>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,7 +823,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2">
-        <f>SUMPRODUCT((MOD(COLUMN(K8:XFD8)-COLUMN(K8),2)=0)*N(K8:XFD8))</f>
+        <f>SUM(K8,M8,O8)</f>
         <v/>
       </c>
       <c r="C8" t="inlineStr">
@@ -927,7 +926,7 @@
         <v>46259</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>46260.73270101212</v>
+        <v>46260.75320785479</v>
       </c>
     </row>
   </sheetData>

--- a/data/database/shopgraph_purchase_history.xlsx
+++ b/data/database/shopgraph_purchase_history.xlsx
@@ -24,10 +24,10 @@
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="165" formatCode="mm/dd/yyyy\ hh:mm"/>
     <numFmt numFmtId="166" formatCode="$#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="168" formatCode="mmm yyyy"/>
+    <numFmt numFmtId="167" formatCode="mmm yyyy"/>
+    <numFmt numFmtId="168" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,8 +57,22 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -68,6 +82,71 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ED7D31"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0070AD47"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005B9BD5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C55A11"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00548235"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008064A2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00264478"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009E480E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00636363"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -83,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -102,8 +181,50 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -207,16 +328,20 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'_AnalyticsData'!B2</f>
+              <f>'_AnalyticsData'!C2</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="none"/>
+            <symbol val="circle"/>
+            <size val="7"/>
             <spPr>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
@@ -230,7 +355,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'_AnalyticsData'!$B$3</f>
+              <f>'_AnalyticsData'!$C$3</f>
             </numRef>
           </val>
         </ser>
@@ -252,7 +377,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Month</a:t>
+                  <a:t>Month Number</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -309,69 +434,6 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Spending Share by Category</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <doughnutChart>
-        <varyColors val="1"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'_AnalyticsData'!K2</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'_AnalyticsData'!$J$3:$J$10</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'_AnalyticsData'!$K$3:$K$10</f>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <showPercent val="1"/>
-          <showLeaderLines val="1"/>
-        </dLbls>
-        <firstSliceAng val="0"/>
-        <holeSize val="55"/>
-      </doughnutChart>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
               <a:t>Spending by Category</a:t>
             </a:r>
           </a:p>
@@ -387,7 +449,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'_AnalyticsData'!E2</f>
+              <f>'_AnalyticsData'!G2</f>
             </strRef>
           </tx>
           <spPr>
@@ -395,18 +457,427 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="4472C4"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="ED7D31"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="70AD47"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="A5A5A5"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="A5A5A5"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="4"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="FFC000"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="5"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="5B9BD5"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="5B9BD5"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="6"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="C55A11"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="C55A11"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="7"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="548235"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="548235"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="8"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8064A2"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="8064A2"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="9"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="264478"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="264478"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="10"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="9E480E"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="9E480E"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="11"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="636363"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="636363"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="12"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="4472C4"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="13"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="ED7D31"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="14"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="70AD47"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="15"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="A5A5A5"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="A5A5A5"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="16"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="FFC000"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="17"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="5B9BD5"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="5B9BD5"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="18"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="C55A11"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="C55A11"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="19"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="548235"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="548235"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="20"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8064A2"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="8064A2"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="21"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="264478"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="264478"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="22"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="9E480E"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="9E480E"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="23"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="636363"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="636363"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="24"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="4472C4"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="25"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="ED7D31"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="26"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="70AD47"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="27"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="A5A5A5"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="A5A5A5"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="28"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="FFC000"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
-              <f>'_AnalyticsData'!$D$3:$D$17</f>
+              <f>'_AnalyticsData'!$E$3:$E$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_AnalyticsData'!$E$3:$E$17</f>
+              <f>'_AnalyticsData'!$G$3:$G$31</f>
             </numRef>
           </val>
         </ser>
-        <gapWidth val="150"/>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="45"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -452,7 +923,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>Number</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -469,7 +940,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
@@ -497,7 +968,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'_AnalyticsData'!H2</f>
+              <f>'_AnalyticsData'!K2</f>
             </strRef>
           </tx>
           <spPr>
@@ -505,18 +976,77 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="4472C4"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="ED7D31"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="70AD47"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="A5A5A5"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="A5A5A5"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
-              <f>'_AnalyticsData'!$G$3:$G$6</f>
+              <f>'_AnalyticsData'!$I$3:$I$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_AnalyticsData'!$H$3:$H$6</f>
+              <f>'_AnalyticsData'!$K$3:$K$6</f>
             </numRef>
           </val>
         </ser>
-        <gapWidth val="150"/>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="45"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -562,7 +1092,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>Number</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -572,6 +1102,474 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Spending Share by Category</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <doughnutChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'_AnalyticsData'!O2</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="4472C4"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="ED7D31"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="70AD47"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="A5A5A5"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="A5A5A5"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="4"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="FFC000"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="5"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="5B9BD5"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="5B9BD5"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="6"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="C55A11"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="C55A11"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="7"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="548235"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="548235"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="8"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8064A2"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="8064A2"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="9"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="264478"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="264478"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="10"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="9E480E"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="9E480E"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="11"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="636363"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="636363"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="12"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="4472C4"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="13"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="ED7D31"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="14"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="70AD47"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="15"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="A5A5A5"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="A5A5A5"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="16"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="FFC000"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="17"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="5B9BD5"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="5B9BD5"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="18"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="C55A11"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="C55A11"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="19"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="548235"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="548235"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="20"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8064A2"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="8064A2"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="21"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="264478"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="264478"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="22"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="9E480E"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="9E480E"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="23"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="636363"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="636363"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="24"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="4472C4"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="25"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="ED7D31"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="26"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="70AD47"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="27"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="A5A5A5"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="A5A5A5"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="28"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="FFC000"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <cat>
+            <numRef>
+              <f>'_AnalyticsData'!$M$3:$M$31</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'_AnalyticsData'!$O$3:$O$31</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="0"/>
+          <showCatName val="1"/>
+          <showPercent val="0"/>
+          <showLeaderLines val="1"/>
+        </dLbls>
+        <firstSliceAng val="0"/>
+        <holeSize val="58"/>
+      </doughnutChart>
     </plotArea>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -607,7 +1605,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'_AnalyticsData'!N2</f>
+              <f>'_AnalyticsData'!S2</f>
             </strRef>
           </tx>
           <spPr>
@@ -615,18 +1613,161 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="4472C4"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="ED7D31"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="70AD47"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="A5A5A5"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="A5A5A5"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="4"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="FFC000"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="5"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="5B9BD5"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="5B9BD5"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="6"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="C55A11"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="C55A11"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="7"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="548235"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="548235"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="8"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8064A2"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="8064A2"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="9"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="264478"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="264478"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
-              <f>'_AnalyticsData'!$M$3:$M$12</f>
+              <f>'_AnalyticsData'!$Q$3:$Q$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_AnalyticsData'!$N$3:$N$12</f>
+              <f>'_AnalyticsData'!$S$3:$S$12</f>
             </numRef>
           </val>
         </ser>
-        <gapWidth val="150"/>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="45"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -672,7 +1813,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>Number</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -690,116 +1831,6 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Purchase Frequency by Category</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="bar"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'_AnalyticsData'!Q2</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'_AnalyticsData'!$P$3:$P$17</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'_AnalyticsData'!$Q$3:$Q$17</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Purchases</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -827,22 +1858,28 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'_AnalyticsData'!T2</f>
+              <f>'_AnalyticsData'!Z2</f>
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="4472C4"/>
+            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'_AnalyticsData'!$S$3</f>
+              <f>'_AnalyticsData'!$Y$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_AnalyticsData'!$T$3</f>
+              <f>'_AnalyticsData'!$Z$3</f>
             </numRef>
           </val>
         </ser>
@@ -851,22 +1888,28 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'_AnalyticsData'!U2</f>
+              <f>'_AnalyticsData'!AA2</f>
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="ED7D31"/>
+            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'_AnalyticsData'!$S$3</f>
+              <f>'_AnalyticsData'!$Y$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_AnalyticsData'!$U$3</f>
+              <f>'_AnalyticsData'!$AA$3</f>
             </numRef>
           </val>
         </ser>
@@ -875,22 +1918,28 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'_AnalyticsData'!V2</f>
+              <f>'_AnalyticsData'!AB2</f>
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="70AD47"/>
+            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'_AnalyticsData'!$S$3</f>
+              <f>'_AnalyticsData'!$Y$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_AnalyticsData'!$V$3</f>
+              <f>'_AnalyticsData'!$AB$3</f>
             </numRef>
           </val>
         </ser>
@@ -899,22 +1948,28 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'_AnalyticsData'!W2</f>
+              <f>'_AnalyticsData'!AC2</f>
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="A5A5A5"/>
+            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="A5A5A5"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'_AnalyticsData'!$S$3</f>
+              <f>'_AnalyticsData'!$Y$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_AnalyticsData'!$W$3</f>
+              <f>'_AnalyticsData'!$AC$3</f>
             </numRef>
           </val>
         </ser>
@@ -938,7 +1993,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Month</a:t>
+                  <a:t>Month Number</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -985,16 +2040,535 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Purchase Frequency by Category</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'_AnalyticsData'!W2</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="4472C4"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="ED7D31"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="70AD47"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="A5A5A5"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="A5A5A5"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="4"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="FFC000"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="5"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="5B9BD5"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="5B9BD5"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="6"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="C55A11"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="C55A11"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="7"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="548235"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="548235"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="8"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8064A2"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="8064A2"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="9"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="264478"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="264478"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="10"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="9E480E"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="9E480E"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="11"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="636363"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="636363"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="12"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="4472C4"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="13"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="ED7D31"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="14"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="70AD47"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="15"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="A5A5A5"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="A5A5A5"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="16"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="FFC000"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="17"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="5B9BD5"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="5B9BD5"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="18"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="C55A11"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="C55A11"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="19"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="548235"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="548235"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="20"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8064A2"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="8064A2"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="21"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="264478"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="264478"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="22"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="9E480E"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="9E480E"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="23"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="636363"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="636363"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="24"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="4472C4"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="25"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="ED7D31"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="26"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="70AD47"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="27"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="A5A5A5"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="A5A5A5"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="28"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="FFC000"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <cat>
+            <numRef>
+              <f>'_AnalyticsData'!$U$3:$U$31</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'_AnalyticsData'!$W$3:$W$31</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="45"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Purchases</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Number</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4752000" cy="2628000"/>
+    <ext cx="9180000" cy="5220000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1011,12 +2585,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4752000" cy="2628000"/>
+    <ext cx="9180000" cy="5220000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -1035,10 +2609,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>79</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4752000" cy="2628000"/>
+    <ext cx="9180000" cy="5220000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -1055,12 +2629,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>115</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4752000" cy="2628000"/>
+    <ext cx="9180000" cy="5940000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -1079,10 +2653,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>41</row>
+      <row>151</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4752000" cy="2628000"/>
+    <ext cx="9180000" cy="5220000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -1099,12 +2673,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>41</row>
+      <row>187</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4752000" cy="2628000"/>
+    <ext cx="9180000" cy="5940000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -1123,10 +2697,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>59</row>
+      <row>223</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9720000" cy="3240000"/>
+    <ext cx="9180000" cy="5220000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -3876,82 +5450,2540 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:AG254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="2" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="5" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="2" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
+    <col width="13" customWidth="1" min="32" max="32"/>
+    <col width="13" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>ShopGraph Spending Analytics</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="26" customHeight="1"/>
+    <row r="2" ht="28" customHeight="1"/>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Total Spending</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>Purchase Observations</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="M4" s="13" t="inlineStr">
         <is>
           <t>Date Range</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="T4" s="13" t="inlineStr">
         <is>
           <t>Stores</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="Z4" s="13" t="inlineStr">
         <is>
           <t>Categories</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="14" t="n">
         <v>239.76</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="G5" s="15" t="n">
         <v>56</v>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="M5" s="15" t="inlineStr">
         <is>
           <t>08/23/2026 - 08/27/2026</t>
         </is>
       </c>
-      <c r="J5" s="8" t="n">
+      <c r="T5" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="M5" s="8" t="n">
+      <c r="Z5" s="15" t="n">
         <v>29</v>
       </c>
     </row>
+    <row r="8">
+      <c r="Q8" s="16" t="inlineStr">
+        <is>
+          <t>Number / Month</t>
+        </is>
+      </c>
+      <c r="Y8" s="16" t="inlineStr">
+        <is>
+          <t>How to Read This Graph</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="Q9" s="17" t="inlineStr"/>
+      <c r="R9" s="17" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="S9" s="17" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="W9" s="17" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="Q10" s="18" t="n"/>
+      <c r="R10" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" s="20" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="W10" s="21" t="inlineStr">
+        <is>
+          <t>$239.76</t>
+        </is>
+      </c>
+      <c r="Y10" s="22" t="inlineStr">
+        <is>
+          <t>What it represents</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="Y11" s="20" t="inlineStr">
+        <is>
+          <t>Shows total household spending for each calendar month. Every valid Date N / Price N purchase observation is added to its month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="16">
+      <c r="Y16" s="22" t="inlineStr">
+        <is>
+          <t>How to read it</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="Y17" s="20" t="inlineStr">
+        <is>
+          <t>The x-axis uses month numbers instead of month names to keep the graph clear. Match each number to the month and dollar total in the key. A rising line means monthly spending increased; a falling line means it decreased.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="22">
+      <c r="Y22" s="22" t="inlineStr">
+        <is>
+          <t>What it is useful for</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="Y23" s="20" t="inlineStr">
+        <is>
+          <t>Use this to identify overall spending trends, unusually expensive months, and whether spending is gradually moving up or down over time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="28">
+      <c r="Y28" s="22" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="Y29" s="20" t="inlineStr">
+        <is>
+          <t>Months with no spending between the earliest and latest purchase dates are included as zero-spend months.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="44">
+      <c r="Q44" s="16" t="inlineStr">
+        <is>
+          <t>Number / Category</t>
+        </is>
+      </c>
+      <c r="Y44" s="16" t="inlineStr">
+        <is>
+          <t>How to Read This Graph</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="Q45" s="17" t="inlineStr"/>
+      <c r="R45" s="17" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="S45" s="17" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="W45" s="17" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="Q46" s="18" t="n"/>
+      <c r="R46" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S46" s="20" t="inlineStr">
+        <is>
+          <t>Prepared Meals</t>
+        </is>
+      </c>
+      <c r="W46" s="21" t="inlineStr">
+        <is>
+          <t>$31.20</t>
+        </is>
+      </c>
+      <c r="Y46" s="22" t="inlineStr">
+        <is>
+          <t>What it represents</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="Q47" s="23" t="n"/>
+      <c r="R47" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="S47" s="20" t="inlineStr">
+        <is>
+          <t>Yogurt</t>
+        </is>
+      </c>
+      <c r="W47" s="21" t="inlineStr">
+        <is>
+          <t>$21.35</t>
+        </is>
+      </c>
+      <c r="Y47" s="20" t="inlineStr">
+        <is>
+          <t>Compares total spending across every category in Purchase History. No categories are collapsed into an 'Other' group.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="Q48" s="24" t="n"/>
+      <c r="R48" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="S48" s="20" t="inlineStr">
+        <is>
+          <t>Fresh Vegetables</t>
+        </is>
+      </c>
+      <c r="W48" s="21" t="inlineStr">
+        <is>
+          <t>$21.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="Q49" s="25" t="n"/>
+      <c r="R49" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="S49" s="20" t="inlineStr">
+        <is>
+          <t>Plant-Based Milk</t>
+        </is>
+      </c>
+      <c r="W49" s="21" t="inlineStr">
+        <is>
+          <t>$18.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="Q50" s="26" t="n"/>
+      <c r="R50" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="S50" s="20" t="inlineStr">
+        <is>
+          <t>Fresh Fruit</t>
+        </is>
+      </c>
+      <c r="W50" s="21" t="inlineStr">
+        <is>
+          <t>$15.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="Q51" s="27" t="n"/>
+      <c r="R51" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="S51" s="20" t="inlineStr">
+        <is>
+          <t>Fresh Poultry</t>
+        </is>
+      </c>
+      <c r="W51" s="21" t="inlineStr">
+        <is>
+          <t>$13.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="Q52" s="28" t="n"/>
+      <c r="R52" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="S52" s="20" t="inlineStr">
+        <is>
+          <t>Prepared Coffee</t>
+        </is>
+      </c>
+      <c r="W52" s="21" t="inlineStr">
+        <is>
+          <t>$11.00</t>
+        </is>
+      </c>
+      <c r="Y52" s="22" t="inlineStr">
+        <is>
+          <t>How to read it</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="Q53" s="29" t="n"/>
+      <c r="R53" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="S53" s="20" t="inlineStr">
+        <is>
+          <t>Bread</t>
+        </is>
+      </c>
+      <c r="W53" s="21" t="inlineStr">
+        <is>
+          <t>$10.16</t>
+        </is>
+      </c>
+      <c r="Y53" s="20" t="inlineStr">
+        <is>
+          <t>Each horizontal bar is identified by a number and color. Use the key to map that number/color to the category name and exact spending amount. Longer bars mean more money was spent in that category.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="Q54" s="30" t="n"/>
+      <c r="R54" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="S54" s="20" t="inlineStr">
+        <is>
+          <t>Frozen Pizza</t>
+        </is>
+      </c>
+      <c r="W54" s="21" t="inlineStr">
+        <is>
+          <t>$8.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="Q55" s="31" t="n"/>
+      <c r="R55" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="S55" s="20" t="inlineStr">
+        <is>
+          <t>Frozen Breakfast</t>
+        </is>
+      </c>
+      <c r="W55" s="21" t="inlineStr">
+        <is>
+          <t>$7.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="Q56" s="32" t="n"/>
+      <c r="R56" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="S56" s="20" t="inlineStr">
+        <is>
+          <t>Refrigerated Dough</t>
+        </is>
+      </c>
+      <c r="W56" s="21" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="Q57" s="33" t="n"/>
+      <c r="R57" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="S57" s="20" t="inlineStr">
+        <is>
+          <t>Muffins &amp; Pastries</t>
+        </is>
+      </c>
+      <c r="W57" s="21" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="Q58" s="18" t="n"/>
+      <c r="R58" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="S58" s="20" t="inlineStr">
+        <is>
+          <t>Storage &amp; Organization</t>
+        </is>
+      </c>
+      <c r="W58" s="21" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
+      <c r="Y58" s="22" t="inlineStr">
+        <is>
+          <t>What it is useful for</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="Q59" s="23" t="n"/>
+      <c r="R59" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="S59" s="20" t="inlineStr">
+        <is>
+          <t>Writing Supplies</t>
+        </is>
+      </c>
+      <c r="W59" s="21" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
+      <c r="Y59" s="20" t="inlineStr">
+        <is>
+          <t>Use this to see which types of goods are the biggest drivers of household spending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="Q60" s="24" t="n"/>
+      <c r="R60" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="S60" s="20" t="inlineStr">
+        <is>
+          <t>Fees &amp; Charges</t>
+        </is>
+      </c>
+      <c r="W60" s="21" t="inlineStr">
+        <is>
+          <t>$5.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="Q61" s="25" t="n"/>
+      <c r="R61" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="S61" s="20" t="inlineStr">
+        <is>
+          <t>Cream &amp; Half-and-Half</t>
+        </is>
+      </c>
+      <c r="W61" s="21" t="inlineStr">
+        <is>
+          <t>$5.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="Q62" s="26" t="n"/>
+      <c r="R62" s="19" t="n">
+        <v>17</v>
+      </c>
+      <c r="S62" s="20" t="inlineStr">
+        <is>
+          <t>Disposable Tableware</t>
+        </is>
+      </c>
+      <c r="W62" s="21" t="inlineStr">
+        <is>
+          <t>$5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="Q63" s="27" t="n"/>
+      <c r="R63" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="S63" s="20" t="inlineStr">
+        <is>
+          <t>Specialty Cheese</t>
+        </is>
+      </c>
+      <c r="W63" s="21" t="inlineStr">
+        <is>
+          <t>$4.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="Q64" s="28" t="n"/>
+      <c r="R64" s="19" t="n">
+        <v>19</v>
+      </c>
+      <c r="S64" s="20" t="inlineStr">
+        <is>
+          <t>Snack Bars</t>
+        </is>
+      </c>
+      <c r="W64" s="21" t="inlineStr">
+        <is>
+          <t>$3.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="Q65" s="29" t="n"/>
+      <c r="R65" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="S65" s="20" t="inlineStr">
+        <is>
+          <t>Fresh-Cut Fruit</t>
+        </is>
+      </c>
+      <c r="W65" s="21" t="inlineStr">
+        <is>
+          <t>$3.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="Q66" s="30" t="n"/>
+      <c r="R66" s="19" t="n">
+        <v>21</v>
+      </c>
+      <c r="S66" s="20" t="inlineStr">
+        <is>
+          <t>Canned Beans &amp; Legumes</t>
+        </is>
+      </c>
+      <c r="W66" s="21" t="inlineStr">
+        <is>
+          <t>$3.68</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="Q67" s="31" t="n"/>
+      <c r="R67" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="S67" s="20" t="inlineStr">
+        <is>
+          <t>Dips &amp; Spreads</t>
+        </is>
+      </c>
+      <c r="W67" s="21" t="inlineStr">
+        <is>
+          <t>$3.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="Q68" s="32" t="n"/>
+      <c r="R68" s="19" t="n">
+        <v>23</v>
+      </c>
+      <c r="S68" s="20" t="inlineStr">
+        <is>
+          <t>Jarred Vegetables</t>
+        </is>
+      </c>
+      <c r="W68" s="21" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="Q69" s="33" t="n"/>
+      <c r="R69" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="S69" s="20" t="inlineStr">
+        <is>
+          <t>Pasta</t>
+        </is>
+      </c>
+      <c r="W69" s="21" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="Q70" s="18" t="n"/>
+      <c r="R70" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="S70" s="20" t="inlineStr">
+        <is>
+          <t>Salad Dressing</t>
+        </is>
+      </c>
+      <c r="W70" s="21" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="Q71" s="23" t="n"/>
+      <c r="R71" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="S71" s="20" t="inlineStr">
+        <is>
+          <t>Crackers</t>
+        </is>
+      </c>
+      <c r="W71" s="21" t="inlineStr">
+        <is>
+          <t>$2.79</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="Q72" s="24" t="n"/>
+      <c r="R72" s="19" t="n">
+        <v>27</v>
+      </c>
+      <c r="S72" s="20" t="inlineStr">
+        <is>
+          <t>Popcorn</t>
+        </is>
+      </c>
+      <c r="W72" s="21" t="inlineStr">
+        <is>
+          <t>$2.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="Q73" s="25" t="n"/>
+      <c r="R73" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="S73" s="20" t="inlineStr">
+        <is>
+          <t>Croutons</t>
+        </is>
+      </c>
+      <c r="W73" s="21" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="22" customHeight="1">
+      <c r="Q74" s="26" t="n"/>
+      <c r="R74" s="19" t="n">
+        <v>29</v>
+      </c>
+      <c r="S74" s="20" t="inlineStr">
+        <is>
+          <t>Fresh Herbs</t>
+        </is>
+      </c>
+      <c r="W74" s="21" t="inlineStr">
+        <is>
+          <t>$1.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="Q80" s="16" t="inlineStr">
+        <is>
+          <t>Number / Store</t>
+        </is>
+      </c>
+      <c r="Y80" s="16" t="inlineStr">
+        <is>
+          <t>How to Read This Graph</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="Q81" s="17" t="inlineStr"/>
+      <c r="R81" s="17" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="S81" s="17" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="W81" s="17" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="22" customHeight="1">
+      <c r="Q82" s="18" t="n"/>
+      <c r="R82" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S82" s="20" t="inlineStr">
+        <is>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="W82" s="21" t="inlineStr">
+        <is>
+          <t>$100.82</t>
+        </is>
+      </c>
+      <c r="Y82" s="22" t="inlineStr">
+        <is>
+          <t>What it represents</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="22" customHeight="1">
+      <c r="Q83" s="23" t="n"/>
+      <c r="R83" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="S83" s="20" t="inlineStr">
+        <is>
+          <t>Publix</t>
+        </is>
+      </c>
+      <c r="W83" s="21" t="inlineStr">
+        <is>
+          <t>$60.58</t>
+        </is>
+      </c>
+      <c r="Y83" s="20" t="inlineStr">
+        <is>
+          <t>Compares how much money was spent at each retailer across the entire Purchase History.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="1">
+      <c r="Q84" s="24" t="n"/>
+      <c r="R84" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="S84" s="20" t="inlineStr">
+        <is>
+          <t>Honey Pineapple</t>
+        </is>
+      </c>
+      <c r="W84" s="21" t="inlineStr">
+        <is>
+          <t>$48.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="Q85" s="25" t="n"/>
+      <c r="R85" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="S85" s="20" t="inlineStr">
+        <is>
+          <t>Trader Joe's</t>
+        </is>
+      </c>
+      <c r="W85" s="21" t="inlineStr">
+        <is>
+          <t>$30.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="86"/>
+    <row r="88">
+      <c r="Y88" s="22" t="inlineStr">
+        <is>
+          <t>How to read it</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="Y89" s="20" t="inlineStr">
+        <is>
+          <t>Each store is represented by a numbered colored bar. Match the number/color to the key. Longer bars indicate more total spending at that store.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="94">
+      <c r="Y94" s="22" t="inlineStr">
+        <is>
+          <t>What it is useful for</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="Y95" s="20" t="inlineStr">
+        <is>
+          <t>Use this to understand which retailers receive the largest share of your household shopping budget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="100">
+      <c r="Y100" s="22" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="Y101" s="20" t="inlineStr">
+        <is>
+          <t>Store Number is intentionally ignored here; purchases are grouped by the Store name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="116">
+      <c r="Q116" s="16" t="inlineStr">
+        <is>
+          <t>Number / Category</t>
+        </is>
+      </c>
+      <c r="Y116" s="16" t="inlineStr">
+        <is>
+          <t>How to Read This Graph</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="Q117" s="17" t="inlineStr"/>
+      <c r="R117" s="17" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="S117" s="17" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="W117" s="17" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="22" customHeight="1">
+      <c r="Q118" s="18" t="n"/>
+      <c r="R118" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S118" s="20" t="inlineStr">
+        <is>
+          <t>Prepared Meals</t>
+        </is>
+      </c>
+      <c r="W118" s="21" t="inlineStr">
+        <is>
+          <t>$31.20 (13.0%)</t>
+        </is>
+      </c>
+      <c r="Y118" s="22" t="inlineStr">
+        <is>
+          <t>What it represents</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="22" customHeight="1">
+      <c r="Q119" s="23" t="n"/>
+      <c r="R119" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="S119" s="20" t="inlineStr">
+        <is>
+          <t>Yogurt</t>
+        </is>
+      </c>
+      <c r="W119" s="21" t="inlineStr">
+        <is>
+          <t>$21.35 (8.9%)</t>
+        </is>
+      </c>
+      <c r="Y119" s="20" t="inlineStr">
+        <is>
+          <t>Shows each category's share of total spending as part of the whole shopping budget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="22" customHeight="1">
+      <c r="Q120" s="24" t="n"/>
+      <c r="R120" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="S120" s="20" t="inlineStr">
+        <is>
+          <t>Fresh Vegetables</t>
+        </is>
+      </c>
+      <c r="W120" s="21" t="inlineStr">
+        <is>
+          <t>$21.28 (8.9%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="22" customHeight="1">
+      <c r="Q121" s="25" t="n"/>
+      <c r="R121" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="S121" s="20" t="inlineStr">
+        <is>
+          <t>Plant-Based Milk</t>
+        </is>
+      </c>
+      <c r="W121" s="21" t="inlineStr">
+        <is>
+          <t>$18.57 (7.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="22" customHeight="1">
+      <c r="Q122" s="26" t="n"/>
+      <c r="R122" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="S122" s="20" t="inlineStr">
+        <is>
+          <t>Fresh Fruit</t>
+        </is>
+      </c>
+      <c r="W122" s="21" t="inlineStr">
+        <is>
+          <t>$15.97 (6.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="22" customHeight="1">
+      <c r="Q123" s="27" t="n"/>
+      <c r="R123" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="S123" s="20" t="inlineStr">
+        <is>
+          <t>Fresh Poultry</t>
+        </is>
+      </c>
+      <c r="W123" s="21" t="inlineStr">
+        <is>
+          <t>$13.98 (5.8%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="22" customHeight="1">
+      <c r="Q124" s="28" t="n"/>
+      <c r="R124" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="S124" s="20" t="inlineStr">
+        <is>
+          <t>Prepared Coffee</t>
+        </is>
+      </c>
+      <c r="W124" s="21" t="inlineStr">
+        <is>
+          <t>$11.00 (4.6%)</t>
+        </is>
+      </c>
+      <c r="Y124" s="22" t="inlineStr">
+        <is>
+          <t>How to read it</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="22" customHeight="1">
+      <c r="Q125" s="29" t="n"/>
+      <c r="R125" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="S125" s="20" t="inlineStr">
+        <is>
+          <t>Bread</t>
+        </is>
+      </c>
+      <c r="W125" s="21" t="inlineStr">
+        <is>
+          <t>$10.16 (4.2%)</t>
+        </is>
+      </c>
+      <c r="Y125" s="20" t="inlineStr">
+        <is>
+          <t>The doughnut itself displays only numeric category codes. Match each number/color to the key for the category name, dollar amount, and percentage of total spending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="22" customHeight="1">
+      <c r="Q126" s="30" t="n"/>
+      <c r="R126" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="S126" s="20" t="inlineStr">
+        <is>
+          <t>Frozen Pizza</t>
+        </is>
+      </c>
+      <c r="W126" s="21" t="inlineStr">
+        <is>
+          <t>$8.29 (3.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="22" customHeight="1">
+      <c r="Q127" s="31" t="n"/>
+      <c r="R127" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="S127" s="20" t="inlineStr">
+        <is>
+          <t>Frozen Breakfast</t>
+        </is>
+      </c>
+      <c r="W127" s="21" t="inlineStr">
+        <is>
+          <t>$7.78 (3.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="22" customHeight="1">
+      <c r="Q128" s="32" t="n"/>
+      <c r="R128" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="S128" s="20" t="inlineStr">
+        <is>
+          <t>Refrigerated Dough</t>
+        </is>
+      </c>
+      <c r="W128" s="21" t="inlineStr">
+        <is>
+          <t>$6.99 (2.9%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="22" customHeight="1">
+      <c r="Q129" s="33" t="n"/>
+      <c r="R129" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="S129" s="20" t="inlineStr">
+        <is>
+          <t>Muffins &amp; Pastries</t>
+        </is>
+      </c>
+      <c r="W129" s="21" t="inlineStr">
+        <is>
+          <t>$5.99 (2.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="22" customHeight="1">
+      <c r="Q130" s="18" t="n"/>
+      <c r="R130" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="S130" s="20" t="inlineStr">
+        <is>
+          <t>Storage &amp; Organization</t>
+        </is>
+      </c>
+      <c r="W130" s="21" t="inlineStr">
+        <is>
+          <t>$5.99 (2.5%)</t>
+        </is>
+      </c>
+      <c r="Y130" s="22" t="inlineStr">
+        <is>
+          <t>What it is useful for</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="22" customHeight="1">
+      <c r="Q131" s="23" t="n"/>
+      <c r="R131" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="S131" s="20" t="inlineStr">
+        <is>
+          <t>Writing Supplies</t>
+        </is>
+      </c>
+      <c r="W131" s="21" t="inlineStr">
+        <is>
+          <t>$5.99 (2.5%)</t>
+        </is>
+      </c>
+      <c r="Y131" s="20" t="inlineStr">
+        <is>
+          <t>Use this for a fast visual picture of the household spending mix—especially which categories take the largest portion of the budget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="22" customHeight="1">
+      <c r="Q132" s="24" t="n"/>
+      <c r="R132" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="S132" s="20" t="inlineStr">
+        <is>
+          <t>Fees &amp; Charges</t>
+        </is>
+      </c>
+      <c r="W132" s="21" t="inlineStr">
+        <is>
+          <t>$5.92 (2.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="22" customHeight="1">
+      <c r="Q133" s="25" t="n"/>
+      <c r="R133" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="S133" s="20" t="inlineStr">
+        <is>
+          <t>Cream &amp; Half-and-Half</t>
+        </is>
+      </c>
+      <c r="W133" s="21" t="inlineStr">
+        <is>
+          <t>$5.89 (2.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="22" customHeight="1">
+      <c r="Q134" s="26" t="n"/>
+      <c r="R134" s="19" t="n">
+        <v>17</v>
+      </c>
+      <c r="S134" s="20" t="inlineStr">
+        <is>
+          <t>Disposable Tableware</t>
+        </is>
+      </c>
+      <c r="W134" s="21" t="inlineStr">
+        <is>
+          <t>$5.25 (2.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="22" customHeight="1">
+      <c r="Q135" s="27" t="n"/>
+      <c r="R135" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="S135" s="20" t="inlineStr">
+        <is>
+          <t>Specialty Cheese</t>
+        </is>
+      </c>
+      <c r="W135" s="21" t="inlineStr">
+        <is>
+          <t>$4.88 (2.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="22" customHeight="1">
+      <c r="Q136" s="28" t="n"/>
+      <c r="R136" s="19" t="n">
+        <v>19</v>
+      </c>
+      <c r="S136" s="20" t="inlineStr">
+        <is>
+          <t>Snack Bars</t>
+        </is>
+      </c>
+      <c r="W136" s="21" t="inlineStr">
+        <is>
+          <t>$3.98 (1.7%)</t>
+        </is>
+      </c>
+      <c r="Y136" s="22" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="22" customHeight="1">
+      <c r="Q137" s="29" t="n"/>
+      <c r="R137" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="S137" s="20" t="inlineStr">
+        <is>
+          <t>Fresh-Cut Fruit</t>
+        </is>
+      </c>
+      <c r="W137" s="21" t="inlineStr">
+        <is>
+          <t>$3.89 (1.6%)</t>
+        </is>
+      </c>
+      <c r="Y137" s="20" t="inlineStr">
+        <is>
+          <t>Unlike the older dashboard, this graph does not create a large 'Other' slice. Every category receives its own numbered segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="22" customHeight="1">
+      <c r="Q138" s="30" t="n"/>
+      <c r="R138" s="19" t="n">
+        <v>21</v>
+      </c>
+      <c r="S138" s="20" t="inlineStr">
+        <is>
+          <t>Canned Beans &amp; Legumes</t>
+        </is>
+      </c>
+      <c r="W138" s="21" t="inlineStr">
+        <is>
+          <t>$3.68 (1.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="22" customHeight="1">
+      <c r="Q139" s="31" t="n"/>
+      <c r="R139" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="S139" s="20" t="inlineStr">
+        <is>
+          <t>Dips &amp; Spreads</t>
+        </is>
+      </c>
+      <c r="W139" s="21" t="inlineStr">
+        <is>
+          <t>$3.45 (1.4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="22" customHeight="1">
+      <c r="Q140" s="32" t="n"/>
+      <c r="R140" s="19" t="n">
+        <v>23</v>
+      </c>
+      <c r="S140" s="20" t="inlineStr">
+        <is>
+          <t>Jarred Vegetables</t>
+        </is>
+      </c>
+      <c r="W140" s="21" t="inlineStr">
+        <is>
+          <t>$3.29 (1.4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="22" customHeight="1">
+      <c r="Q141" s="33" t="n"/>
+      <c r="R141" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="S141" s="20" t="inlineStr">
+        <is>
+          <t>Pasta</t>
+        </is>
+      </c>
+      <c r="W141" s="21" t="inlineStr">
+        <is>
+          <t>$2.99 (1.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="22" customHeight="1">
+      <c r="Q142" s="18" t="n"/>
+      <c r="R142" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="S142" s="20" t="inlineStr">
+        <is>
+          <t>Salad Dressing</t>
+        </is>
+      </c>
+      <c r="W142" s="21" t="inlineStr">
+        <is>
+          <t>$2.99 (1.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="22" customHeight="1">
+      <c r="Q143" s="23" t="n"/>
+      <c r="R143" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="S143" s="20" t="inlineStr">
+        <is>
+          <t>Crackers</t>
+        </is>
+      </c>
+      <c r="W143" s="21" t="inlineStr">
+        <is>
+          <t>$2.79 (1.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="22" customHeight="1">
+      <c r="Q144" s="24" t="n"/>
+      <c r="R144" s="19" t="n">
+        <v>27</v>
+      </c>
+      <c r="S144" s="20" t="inlineStr">
+        <is>
+          <t>Popcorn</t>
+        </is>
+      </c>
+      <c r="W144" s="21" t="inlineStr">
+        <is>
+          <t>$2.39 (1.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="22" customHeight="1">
+      <c r="Q145" s="25" t="n"/>
+      <c r="R145" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="S145" s="20" t="inlineStr">
+        <is>
+          <t>Croutons</t>
+        </is>
+      </c>
+      <c r="W145" s="21" t="inlineStr">
+        <is>
+          <t>$1.99 (0.8%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="22" customHeight="1">
+      <c r="Q146" s="26" t="n"/>
+      <c r="R146" s="19" t="n">
+        <v>29</v>
+      </c>
+      <c r="S146" s="20" t="inlineStr">
+        <is>
+          <t>Fresh Herbs</t>
+        </is>
+      </c>
+      <c r="W146" s="21" t="inlineStr">
+        <is>
+          <t>$1.84 (0.8%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="Q152" s="16" t="inlineStr">
+        <is>
+          <t>Number / Product</t>
+        </is>
+      </c>
+      <c r="Y152" s="16" t="inlineStr">
+        <is>
+          <t>How to Read This Graph</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="Q153" s="17" t="inlineStr"/>
+      <c r="R153" s="17" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="S153" s="17" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="W153" s="17" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="22" customHeight="1">
+      <c r="Q154" s="18" t="n"/>
+      <c r="R154" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S154" s="20" t="inlineStr">
+        <is>
+          <t>Silk Organic Unsweet Soymilk, Half Gallon</t>
+        </is>
+      </c>
+      <c r="W154" s="21" t="inlineStr">
+        <is>
+          <t>$18.57</t>
+        </is>
+      </c>
+      <c r="Y154" s="22" t="inlineStr">
+        <is>
+          <t>What it represents</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="22" customHeight="1">
+      <c r="Q155" s="23" t="n"/>
+      <c r="R155" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="S155" s="20" t="inlineStr">
+        <is>
+          <t>1 Chicken N French Toast</t>
+        </is>
+      </c>
+      <c r="W155" s="21" t="inlineStr">
+        <is>
+          <t>$16.30</t>
+        </is>
+      </c>
+      <c r="Y155" s="20" t="inlineStr">
+        <is>
+          <t>Ranks the ten individual product identities with the most accumulated spending across all recorded purchases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="22" customHeight="1">
+      <c r="Q156" s="24" t="n"/>
+      <c r="R156" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="S156" s="20" t="inlineStr">
+        <is>
+          <t>1 Frenchy Plate</t>
+        </is>
+      </c>
+      <c r="W156" s="21" t="inlineStr">
+        <is>
+          <t>$14.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="22" customHeight="1">
+      <c r="Q157" s="25" t="n"/>
+      <c r="R157" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="S157" s="20" t="inlineStr">
+        <is>
+          <t>Empire Kosher Ground Turkey</t>
+        </is>
+      </c>
+      <c r="W157" s="21" t="inlineStr">
+        <is>
+          <t>$13.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="22" customHeight="1">
+      <c r="Q158" s="26" t="n"/>
+      <c r="R158" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="S158" s="20" t="inlineStr">
+        <is>
+          <t>Cauliflower Crust Pizza</t>
+        </is>
+      </c>
+      <c r="W158" s="21" t="inlineStr">
+        <is>
+          <t>$8.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="22" customHeight="1">
+      <c r="Q159" s="27" t="n"/>
+      <c r="R159" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="S159" s="20" t="inlineStr">
+        <is>
+          <t>Stonyfield Organic YoBaby Yogurt Pouch, Banana</t>
+        </is>
+      </c>
+      <c r="W159" s="21" t="inlineStr">
+        <is>
+          <t>$7.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="22" customHeight="1">
+      <c r="Q160" s="28" t="n"/>
+      <c r="R160" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="S160" s="20" t="inlineStr">
+        <is>
+          <t>Stonyfield Organic YoBaby Yogurt Pouch, Peach</t>
+        </is>
+      </c>
+      <c r="W160" s="21" t="inlineStr">
+        <is>
+          <t>$7.85</t>
+        </is>
+      </c>
+      <c r="Y160" s="22" t="inlineStr">
+        <is>
+          <t>How to read it</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="22" customHeight="1">
+      <c r="Q161" s="29" t="n"/>
+      <c r="R161" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="S161" s="20" t="inlineStr">
+        <is>
+          <t>Van's Gluten Free Blueberry Waffles</t>
+        </is>
+      </c>
+      <c r="W161" s="21" t="inlineStr">
+        <is>
+          <t>$7.78</t>
+        </is>
+      </c>
+      <c r="Y161" s="20" t="inlineStr">
+        <is>
+          <t>Each product is represented by a numbered colored bar. Use the key to see the product name and its total spending. The longest bar is the largest individual spending driver.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="22" customHeight="1">
+      <c r="Q162" s="30" t="n"/>
+      <c r="R162" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="S162" s="20" t="inlineStr">
+        <is>
+          <t>Sweet Loren's Gluten Free Brownie Cookie Dough</t>
+        </is>
+      </c>
+      <c r="W162" s="21" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="22" customHeight="1">
+      <c r="Q163" s="31" t="n"/>
+      <c r="R163" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="S163" s="20" t="inlineStr">
+        <is>
+          <t>Gluten-Free Wide Pan Bread</t>
+        </is>
+      </c>
+      <c r="W163" s="21" t="inlineStr">
+        <is>
+          <t>$6.79</t>
+        </is>
+      </c>
+    </row>
+    <row r="164"/>
+    <row r="166">
+      <c r="Y166" s="22" t="inlineStr">
+        <is>
+          <t>What it is useful for</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="Y167" s="20" t="inlineStr">
+        <is>
+          <t>Use this to identify specific products that contribute the most to total spending and may be worth price-comparing or watching over time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="172">
+      <c r="Y172" s="22" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="Y173" s="20" t="inlineStr">
+        <is>
+          <t>Product identity prefers Common Name and falls back to Product when Common Name is unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="188">
+      <c r="Q188" s="16" t="inlineStr">
+        <is>
+          <t>Store Numbers + Month Numbers</t>
+        </is>
+      </c>
+      <c r="Y188" s="16" t="inlineStr">
+        <is>
+          <t>How to Read This Graph</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="Q189" s="17" t="inlineStr"/>
+      <c r="R189" s="17" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="S189" s="17" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="W189" s="17" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="22" customHeight="1">
+      <c r="Q190" s="18" t="n"/>
+      <c r="R190" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S190" s="20" t="inlineStr">
+        <is>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="W190" s="21" t="inlineStr">
+        <is>
+          <t>$100.82</t>
+        </is>
+      </c>
+      <c r="Y190" s="22" t="inlineStr">
+        <is>
+          <t>What it represents</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="22" customHeight="1">
+      <c r="Q191" s="23" t="n"/>
+      <c r="R191" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="S191" s="20" t="inlineStr">
+        <is>
+          <t>Publix</t>
+        </is>
+      </c>
+      <c r="W191" s="21" t="inlineStr">
+        <is>
+          <t>$60.58</t>
+        </is>
+      </c>
+      <c r="Y191" s="20" t="inlineStr">
+        <is>
+          <t>Shows how monthly spending is divided among stores. Each column is one month; each colored section inside the column represents one store.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="22" customHeight="1">
+      <c r="Q192" s="24" t="n"/>
+      <c r="R192" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="S192" s="20" t="inlineStr">
+        <is>
+          <t>Honey Pineapple</t>
+        </is>
+      </c>
+      <c r="W192" s="21" t="inlineStr">
+        <is>
+          <t>$48.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="22" customHeight="1">
+      <c r="Q193" s="25" t="n"/>
+      <c r="R193" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="S193" s="20" t="inlineStr">
+        <is>
+          <t>Trader Joe's</t>
+        </is>
+      </c>
+      <c r="W193" s="21" t="inlineStr">
+        <is>
+          <t>$30.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="22" customHeight="1">
+      <c r="Q194" s="34" t="n"/>
+      <c r="R194" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S194" s="20" t="inlineStr">
+        <is>
+          <t>Month August 2026</t>
+        </is>
+      </c>
+      <c r="W194" s="21" t="inlineStr">
+        <is>
+          <t>$239.76</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="Y196" s="22" t="inlineStr">
+        <is>
+          <t>How to read it</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="Y197" s="20" t="inlineStr">
+        <is>
+          <t>Store series use the numbered color key. The x-axis uses month numbers. Match those month numbers to the month rows in the key. The total height of a column is total monthly spending; the colored portions show which stores made up that total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
+    <row r="202">
+      <c r="Y202" s="22" t="inlineStr">
+        <is>
+          <t>What it is useful for</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="Y203" s="20" t="inlineStr">
+        <is>
+          <t>Use this to see whether changes in monthly spending are connected to a particular store and how your retailer mix changes over time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204"/>
+    <row r="205"/>
+    <row r="206"/>
+    <row r="208">
+      <c r="Y208" s="22" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="Y209" s="20" t="inlineStr">
+        <is>
+          <t>All stores are retained. There is no catch-all 'Other' store series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210"/>
+    <row r="211"/>
+    <row r="212"/>
+    <row r="224">
+      <c r="Q224" s="16" t="inlineStr">
+        <is>
+          <t>Number / Category</t>
+        </is>
+      </c>
+      <c r="Y224" s="16" t="inlineStr">
+        <is>
+          <t>How to Read This Graph</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="Q225" s="17" t="inlineStr"/>
+      <c r="R225" s="17" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="S225" s="17" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="W225" s="17" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="22" customHeight="1">
+      <c r="Q226" s="18" t="n"/>
+      <c r="R226" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S226" s="20" t="inlineStr">
+        <is>
+          <t>Fresh Vegetables</t>
+        </is>
+      </c>
+      <c r="W226" s="21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y226" s="22" t="inlineStr">
+        <is>
+          <t>What it represents</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="22" customHeight="1">
+      <c r="Q227" s="23" t="n"/>
+      <c r="R227" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="S227" s="20" t="inlineStr">
+        <is>
+          <t>Fresh Fruit</t>
+        </is>
+      </c>
+      <c r="W227" s="21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y227" s="20" t="inlineStr">
+        <is>
+          <t>Counts how many valid purchase observations occurred in each category. This measures frequency, not dollars.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="22" customHeight="1">
+      <c r="Q228" s="24" t="n"/>
+      <c r="R228" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="S228" s="20" t="inlineStr">
+        <is>
+          <t>Canned Beans &amp; Legumes</t>
+        </is>
+      </c>
+      <c r="W228" s="21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="22" customHeight="1">
+      <c r="Q229" s="25" t="n"/>
+      <c r="R229" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="S229" s="20" t="inlineStr">
+        <is>
+          <t>Plant-Based Milk</t>
+        </is>
+      </c>
+      <c r="W229" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="22" customHeight="1">
+      <c r="Q230" s="26" t="n"/>
+      <c r="R230" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="S230" s="20" t="inlineStr">
+        <is>
+          <t>Yogurt</t>
+        </is>
+      </c>
+      <c r="W230" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="22" customHeight="1">
+      <c r="Q231" s="27" t="n"/>
+      <c r="R231" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="S231" s="20" t="inlineStr">
+        <is>
+          <t>Bread</t>
+        </is>
+      </c>
+      <c r="W231" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="22" customHeight="1">
+      <c r="Q232" s="28" t="n"/>
+      <c r="R232" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="S232" s="20" t="inlineStr">
+        <is>
+          <t>Fees &amp; Charges</t>
+        </is>
+      </c>
+      <c r="W232" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y232" s="22" t="inlineStr">
+        <is>
+          <t>How to read it</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="22" customHeight="1">
+      <c r="Q233" s="29" t="n"/>
+      <c r="R233" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="S233" s="20" t="inlineStr">
+        <is>
+          <t>Fresh Herbs</t>
+        </is>
+      </c>
+      <c r="W233" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y233" s="20" t="inlineStr">
+        <is>
+          <t>Each category is a numbered colored bar. Match the number and color to the key. A longer bar means the category was purchased more frequently.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="22" customHeight="1">
+      <c r="Q234" s="30" t="n"/>
+      <c r="R234" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="S234" s="20" t="inlineStr">
+        <is>
+          <t>Fresh Poultry</t>
+        </is>
+      </c>
+      <c r="W234" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="22" customHeight="1">
+      <c r="Q235" s="31" t="n"/>
+      <c r="R235" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="S235" s="20" t="inlineStr">
+        <is>
+          <t>Frozen Breakfast</t>
+        </is>
+      </c>
+      <c r="W235" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="22" customHeight="1">
+      <c r="Q236" s="32" t="n"/>
+      <c r="R236" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="S236" s="20" t="inlineStr">
+        <is>
+          <t>Prepared Coffee</t>
+        </is>
+      </c>
+      <c r="W236" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="22" customHeight="1">
+      <c r="Q237" s="33" t="n"/>
+      <c r="R237" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="S237" s="20" t="inlineStr">
+        <is>
+          <t>Prepared Meals</t>
+        </is>
+      </c>
+      <c r="W237" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="22" customHeight="1">
+      <c r="Q238" s="18" t="n"/>
+      <c r="R238" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="S238" s="20" t="inlineStr">
+        <is>
+          <t>Snack Bars</t>
+        </is>
+      </c>
+      <c r="W238" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y238" s="22" t="inlineStr">
+        <is>
+          <t>What it is useful for</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="22" customHeight="1">
+      <c r="Q239" s="23" t="n"/>
+      <c r="R239" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="S239" s="20" t="inlineStr">
+        <is>
+          <t>Specialty Cheese</t>
+        </is>
+      </c>
+      <c r="W239" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y239" s="20" t="inlineStr">
+        <is>
+          <t>Use this alongside Spending by Category to distinguish frequent routine purchases from categories that are bought less often but cost more.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="22" customHeight="1">
+      <c r="Q240" s="24" t="n"/>
+      <c r="R240" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="S240" s="20" t="inlineStr">
+        <is>
+          <t>Crackers</t>
+        </is>
+      </c>
+      <c r="W240" s="21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="22" customHeight="1">
+      <c r="Q241" s="25" t="n"/>
+      <c r="R241" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="S241" s="20" t="inlineStr">
+        <is>
+          <t>Cream &amp; Half-and-Half</t>
+        </is>
+      </c>
+      <c r="W241" s="21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="22" customHeight="1">
+      <c r="Q242" s="26" t="n"/>
+      <c r="R242" s="19" t="n">
+        <v>17</v>
+      </c>
+      <c r="S242" s="20" t="inlineStr">
+        <is>
+          <t>Croutons</t>
+        </is>
+      </c>
+      <c r="W242" s="21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="22" customHeight="1">
+      <c r="Q243" s="27" t="n"/>
+      <c r="R243" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="S243" s="20" t="inlineStr">
+        <is>
+          <t>Dips &amp; Spreads</t>
+        </is>
+      </c>
+      <c r="W243" s="21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="22" customHeight="1">
+      <c r="Q244" s="28" t="n"/>
+      <c r="R244" s="19" t="n">
+        <v>19</v>
+      </c>
+      <c r="S244" s="20" t="inlineStr">
+        <is>
+          <t>Disposable Tableware</t>
+        </is>
+      </c>
+      <c r="W244" s="21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="22" customHeight="1">
+      <c r="Q245" s="29" t="n"/>
+      <c r="R245" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="S245" s="20" t="inlineStr">
+        <is>
+          <t>Fresh-Cut Fruit</t>
+        </is>
+      </c>
+      <c r="W245" s="21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="22" customHeight="1">
+      <c r="Q246" s="30" t="n"/>
+      <c r="R246" s="19" t="n">
+        <v>21</v>
+      </c>
+      <c r="S246" s="20" t="inlineStr">
+        <is>
+          <t>Frozen Pizza</t>
+        </is>
+      </c>
+      <c r="W246" s="21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="22" customHeight="1">
+      <c r="Q247" s="31" t="n"/>
+      <c r="R247" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="S247" s="20" t="inlineStr">
+        <is>
+          <t>Jarred Vegetables</t>
+        </is>
+      </c>
+      <c r="W247" s="21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="22" customHeight="1">
+      <c r="Q248" s="32" t="n"/>
+      <c r="R248" s="19" t="n">
+        <v>23</v>
+      </c>
+      <c r="S248" s="20" t="inlineStr">
+        <is>
+          <t>Muffins &amp; Pastries</t>
+        </is>
+      </c>
+      <c r="W248" s="21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="22" customHeight="1">
+      <c r="Q249" s="33" t="n"/>
+      <c r="R249" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="S249" s="20" t="inlineStr">
+        <is>
+          <t>Pasta</t>
+        </is>
+      </c>
+      <c r="W249" s="21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="22" customHeight="1">
+      <c r="Q250" s="18" t="n"/>
+      <c r="R250" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="S250" s="20" t="inlineStr">
+        <is>
+          <t>Popcorn</t>
+        </is>
+      </c>
+      <c r="W250" s="21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="22" customHeight="1">
+      <c r="Q251" s="23" t="n"/>
+      <c r="R251" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="S251" s="20" t="inlineStr">
+        <is>
+          <t>Refrigerated Dough</t>
+        </is>
+      </c>
+      <c r="W251" s="21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="22" customHeight="1">
+      <c r="Q252" s="24" t="n"/>
+      <c r="R252" s="19" t="n">
+        <v>27</v>
+      </c>
+      <c r="S252" s="20" t="inlineStr">
+        <is>
+          <t>Salad Dressing</t>
+        </is>
+      </c>
+      <c r="W252" s="21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="22" customHeight="1">
+      <c r="Q253" s="25" t="n"/>
+      <c r="R253" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="S253" s="20" t="inlineStr">
+        <is>
+          <t>Storage &amp; Organization</t>
+        </is>
+      </c>
+      <c r="W253" s="21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="22" customHeight="1">
+      <c r="Q254" s="26" t="n"/>
+      <c r="R254" s="19" t="n">
+        <v>29</v>
+      </c>
+      <c r="S254" s="20" t="inlineStr">
+        <is>
+          <t>Writing Supplies</t>
+        </is>
+      </c>
+      <c r="W254" s="21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:N2"/>
+  <mergeCells count="174">
+    <mergeCell ref="S136:V136"/>
+    <mergeCell ref="S118:V118"/>
+    <mergeCell ref="Y82:AG82"/>
+    <mergeCell ref="S158:V158"/>
+    <mergeCell ref="Y233:AG236"/>
+    <mergeCell ref="Y10:AG10"/>
+    <mergeCell ref="Y16:AG16"/>
+    <mergeCell ref="S135:V135"/>
+    <mergeCell ref="S193:V193"/>
+    <mergeCell ref="Y52:AG52"/>
+    <mergeCell ref="S144:V144"/>
+    <mergeCell ref="S159:V159"/>
+    <mergeCell ref="S242:V242"/>
+    <mergeCell ref="S125:V125"/>
+    <mergeCell ref="S72:V72"/>
+    <mergeCell ref="Q116:W116"/>
+    <mergeCell ref="S134:V134"/>
+    <mergeCell ref="S192:V192"/>
+    <mergeCell ref="S226:V226"/>
+    <mergeCell ref="S161:V161"/>
+    <mergeCell ref="S62:V62"/>
+    <mergeCell ref="Y227:AG230"/>
+    <mergeCell ref="A1:AG2"/>
+    <mergeCell ref="S71:V71"/>
+    <mergeCell ref="Y83:AG86"/>
+    <mergeCell ref="Y100:AG100"/>
+    <mergeCell ref="S241:V241"/>
+    <mergeCell ref="S145:V145"/>
+    <mergeCell ref="S58:V58"/>
+    <mergeCell ref="Y160:AG160"/>
+    <mergeCell ref="S228:V228"/>
+    <mergeCell ref="Q224:W224"/>
+    <mergeCell ref="S120:V120"/>
+    <mergeCell ref="S191:V191"/>
+    <mergeCell ref="S73:V73"/>
+    <mergeCell ref="S243:V243"/>
+    <mergeCell ref="Y173:AG176"/>
+    <mergeCell ref="Y17:AG20"/>
+    <mergeCell ref="Y196:AG196"/>
+    <mergeCell ref="Y11:AG14"/>
+    <mergeCell ref="S57:V57"/>
+    <mergeCell ref="Y152:AG152"/>
+    <mergeCell ref="Y59:AG62"/>
+    <mergeCell ref="S229:V229"/>
+    <mergeCell ref="S146:V146"/>
+    <mergeCell ref="Y239:AG242"/>
+    <mergeCell ref="S83:V83"/>
+    <mergeCell ref="Y95:AG98"/>
+    <mergeCell ref="S141:V141"/>
+    <mergeCell ref="S154:V154"/>
+    <mergeCell ref="S254:V254"/>
+    <mergeCell ref="S163:V163"/>
+    <mergeCell ref="S124:V124"/>
+    <mergeCell ref="Y88:AG88"/>
+    <mergeCell ref="S85:V85"/>
+    <mergeCell ref="Y209:AG212"/>
+    <mergeCell ref="S140:V140"/>
+    <mergeCell ref="S246:V246"/>
+    <mergeCell ref="S47:V47"/>
+    <mergeCell ref="S233:V233"/>
+    <mergeCell ref="S59:V59"/>
+    <mergeCell ref="S119:V119"/>
+    <mergeCell ref="Y131:AG134"/>
+    <mergeCell ref="Y154:AG154"/>
+    <mergeCell ref="S46:V46"/>
+    <mergeCell ref="S248:V248"/>
+    <mergeCell ref="S61:V61"/>
+    <mergeCell ref="Y116:AG116"/>
+    <mergeCell ref="S70:V70"/>
+    <mergeCell ref="S48:V48"/>
+    <mergeCell ref="Y8:AG8"/>
+    <mergeCell ref="S194:V194"/>
+    <mergeCell ref="Y130:AG130"/>
+    <mergeCell ref="S160:V160"/>
+    <mergeCell ref="S131:V131"/>
+    <mergeCell ref="S245:V245"/>
+    <mergeCell ref="S49:V49"/>
+    <mergeCell ref="S128:V128"/>
+    <mergeCell ref="S10:V10"/>
+    <mergeCell ref="Y118:AG118"/>
+    <mergeCell ref="Y155:AG158"/>
+    <mergeCell ref="S137:V137"/>
+    <mergeCell ref="Y232:AG232"/>
+    <mergeCell ref="Q80:W80"/>
+    <mergeCell ref="S65:V65"/>
+    <mergeCell ref="S74:V74"/>
+    <mergeCell ref="Y94:AG94"/>
+    <mergeCell ref="S157:V157"/>
+    <mergeCell ref="S250:V250"/>
+    <mergeCell ref="S139:V139"/>
+    <mergeCell ref="S237:V237"/>
+    <mergeCell ref="Y22:AG22"/>
+    <mergeCell ref="Y101:AG104"/>
+    <mergeCell ref="S129:V129"/>
+    <mergeCell ref="S123:V123"/>
+    <mergeCell ref="S138:V138"/>
+    <mergeCell ref="S50:V50"/>
+    <mergeCell ref="S230:V230"/>
+    <mergeCell ref="S51:V51"/>
+    <mergeCell ref="Y125:AG128"/>
+    <mergeCell ref="S60:V60"/>
+    <mergeCell ref="Y80:AG80"/>
+    <mergeCell ref="S143:V143"/>
+    <mergeCell ref="Y208:AG208"/>
+    <mergeCell ref="S236:V236"/>
+    <mergeCell ref="Y53:AG56"/>
+    <mergeCell ref="Y47:AG50"/>
+    <mergeCell ref="S232:V232"/>
+    <mergeCell ref="Y136:AG136"/>
+    <mergeCell ref="S155:V155"/>
+    <mergeCell ref="Y167:AG170"/>
+    <mergeCell ref="S247:V247"/>
+    <mergeCell ref="S52:V52"/>
+    <mergeCell ref="Q8:W8"/>
+    <mergeCell ref="Y89:AG92"/>
+    <mergeCell ref="Y191:AG194"/>
+    <mergeCell ref="S122:V122"/>
+    <mergeCell ref="S67:V67"/>
+    <mergeCell ref="Y161:AG164"/>
+    <mergeCell ref="S69:V69"/>
+    <mergeCell ref="Y137:AG140"/>
+    <mergeCell ref="Y226:AG226"/>
+    <mergeCell ref="Y203:AG206"/>
+    <mergeCell ref="S249:V249"/>
+    <mergeCell ref="Q152:W152"/>
+    <mergeCell ref="S53:V53"/>
+    <mergeCell ref="S133:V133"/>
+    <mergeCell ref="Q44:W44"/>
+    <mergeCell ref="S127:V127"/>
+    <mergeCell ref="S142:V142"/>
+    <mergeCell ref="Y44:AG44"/>
+    <mergeCell ref="S234:V234"/>
+    <mergeCell ref="S55:V55"/>
+    <mergeCell ref="Y172:AG172"/>
+    <mergeCell ref="S64:V64"/>
+    <mergeCell ref="S235:V235"/>
+    <mergeCell ref="S162:V162"/>
+    <mergeCell ref="Y188:AG188"/>
+    <mergeCell ref="S227:V227"/>
+    <mergeCell ref="S54:V54"/>
+    <mergeCell ref="S63:V63"/>
+    <mergeCell ref="Y197:AG200"/>
+    <mergeCell ref="Y23:AG26"/>
+    <mergeCell ref="Y124:AG124"/>
+    <mergeCell ref="Y190:AG190"/>
+    <mergeCell ref="Y46:AG46"/>
+    <mergeCell ref="S252:V252"/>
+    <mergeCell ref="Y28:AG28"/>
+    <mergeCell ref="S56:V56"/>
+    <mergeCell ref="S156:V156"/>
+    <mergeCell ref="S126:V126"/>
+    <mergeCell ref="S251:V251"/>
+    <mergeCell ref="Y166:AG166"/>
+    <mergeCell ref="S238:V238"/>
+    <mergeCell ref="Y238:AG238"/>
+    <mergeCell ref="S121:V121"/>
+    <mergeCell ref="S130:V130"/>
+    <mergeCell ref="Y29:AG32"/>
+    <mergeCell ref="S244:V244"/>
+    <mergeCell ref="S82:V82"/>
+    <mergeCell ref="S253:V253"/>
+    <mergeCell ref="S231:V231"/>
+    <mergeCell ref="S240:V240"/>
+    <mergeCell ref="S66:V66"/>
+    <mergeCell ref="S132:V132"/>
+    <mergeCell ref="S190:V190"/>
+    <mergeCell ref="Y119:AG122"/>
+    <mergeCell ref="Y224:AG224"/>
+    <mergeCell ref="Y202:AG202"/>
+    <mergeCell ref="Y58:AG58"/>
+    <mergeCell ref="S68:V68"/>
+    <mergeCell ref="S239:V239"/>
+    <mergeCell ref="Q188:W188"/>
+    <mergeCell ref="S84:V84"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3964,7 +7996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W17"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3973,32 +8005,32 @@
           <t>Monthly Spending</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>Spending by Category</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Spending by Store</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>Spending Share by Category</t>
         </is>
       </c>
-      <c r="M1" s="9" t="inlineStr">
+      <c r="Q1" s="9" t="inlineStr">
         <is>
           <t>Top Products by Spending</t>
         </is>
       </c>
-      <c r="P1" s="9" t="inlineStr">
+      <c r="U1" s="9" t="inlineStr">
         <is>
           <t>Purchase Frequency by Category</t>
         </is>
       </c>
-      <c r="S1" s="9" t="inlineStr">
+      <c r="Y1" s="9" t="inlineStr">
         <is>
           <t>Monthly Spending by Store</t>
         </is>
@@ -4007,555 +8039,1311 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>Spending</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>Spending</t>
         </is>
       </c>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="I2" s="9" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="J2" s="9" t="inlineStr">
         <is>
           <t>Store</t>
         </is>
       </c>
-      <c r="H2" s="9" t="inlineStr">
+      <c r="K2" s="9" t="inlineStr">
         <is>
           <t>Spending</t>
         </is>
       </c>
-      <c r="J2" s="9" t="inlineStr">
+      <c r="M2" s="9" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N2" s="9" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="K2" s="9" t="inlineStr">
+      <c r="O2" s="9" t="inlineStr">
         <is>
           <t>Spending</t>
         </is>
       </c>
-      <c r="M2" s="9" t="inlineStr">
+      <c r="Q2" s="9" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="R2" s="9" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="N2" s="9" t="inlineStr">
+      <c r="S2" s="9" t="inlineStr">
         <is>
           <t>Spending</t>
         </is>
       </c>
-      <c r="P2" s="9" t="inlineStr">
+      <c r="U2" s="9" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="V2" s="9" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="Q2" s="9" t="inlineStr">
+      <c r="W2" s="9" t="inlineStr">
         <is>
           <t>Purchases</t>
         </is>
       </c>
-      <c r="S2" s="9" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="T2" s="9" t="inlineStr">
+      <c r="Y2" s="9" t="inlineStr">
+        <is>
+          <t>Month Number</t>
+        </is>
+      </c>
+      <c r="Z2" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA2" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC2" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="35" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C3" s="11" t="n">
+        <v>239.76</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Prepared Meals</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>Aldi</t>
         </is>
       </c>
-      <c r="U2" s="9" t="inlineStr">
+      <c r="K3" s="11" t="n">
+        <v>100.82</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Prepared Meals</t>
+        </is>
+      </c>
+      <c r="O3" s="11" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Silk Organic Unsweet Soymilk, Half Gallon</t>
+        </is>
+      </c>
+      <c r="S3" s="11" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Fresh Vegetables</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="11" t="n">
+        <v>100.82</v>
+      </c>
+      <c r="AA3" s="11" t="n">
+        <v>60.57999999999999</v>
+      </c>
+      <c r="AB3" s="11" t="n">
+        <v>48.12</v>
+      </c>
+      <c r="AC3" s="11" t="n">
+        <v>30.24</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Yogurt</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="n">
+        <v>21.35</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>Publix</t>
         </is>
       </c>
-      <c r="V2" s="9" t="inlineStr">
+      <c r="K4" s="11" t="n">
+        <v>60.57999999999999</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Yogurt</t>
+        </is>
+      </c>
+      <c r="O4" s="11" t="n">
+        <v>21.35</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1 Chicken N French Toast</t>
+        </is>
+      </c>
+      <c r="S4" s="11" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Fresh Fruit</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fresh Vegetables</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>21.28</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>Honey Pineapple</t>
         </is>
       </c>
-      <c r="W2" s="9" t="inlineStr">
+      <c r="K5" s="11" t="n">
+        <v>48.12</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Fresh Vegetables</t>
+        </is>
+      </c>
+      <c r="O5" s="11" t="n">
+        <v>21.28</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1 Frenchy Plate</t>
+        </is>
+      </c>
+      <c r="S5" s="11" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Canned Beans &amp; Legumes</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Plant-Based Milk</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>Trader Joe's</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="n">
-        <v>46235</v>
-      </c>
-      <c r="B3" s="11" t="n">
-        <v>239.76</v>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="K6" s="11" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Plant-Based Milk</t>
+        </is>
+      </c>
+      <c r="O6" s="11" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Empire Kosher Ground Turkey</t>
+        </is>
+      </c>
+      <c r="S6" s="11" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Plant-Based Milk</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fresh Fruit</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>15.97</v>
+      </c>
+      <c r="M7" t="n">
+        <v>5</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Fresh Fruit</t>
+        </is>
+      </c>
+      <c r="O7" s="11" t="n">
+        <v>15.97</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>5</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Cauliflower Crust Pizza</t>
+        </is>
+      </c>
+      <c r="S7" s="11" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="U7" t="n">
+        <v>5</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Yogurt</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="E8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fresh Poultry</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="M8" t="n">
+        <v>6</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Fresh Poultry</t>
+        </is>
+      </c>
+      <c r="O8" s="11" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>6</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Stonyfield Organic YoBaby Yogurt Pouch, Banana</t>
+        </is>
+      </c>
+      <c r="S8" s="11" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="U8" t="n">
+        <v>6</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Bread</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="E9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Prepared Coffee</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="M9" t="n">
+        <v>7</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Prepared Coffee</t>
+        </is>
+      </c>
+      <c r="O9" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>7</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Stonyfield Organic YoBaby Yogurt Pouch, Peach</t>
+        </is>
+      </c>
+      <c r="S9" s="11" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="U9" t="n">
+        <v>7</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Fees &amp; Charges</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="E10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bread</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="M10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Bread</t>
+        </is>
+      </c>
+      <c r="O10" s="11" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>8</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Van's Gluten Free Blueberry Waffles</t>
+        </is>
+      </c>
+      <c r="S10" s="11" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="U10" t="n">
+        <v>8</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Fresh Herbs</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="E11" t="n">
+        <v>9</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Frozen Pizza</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="M11" t="n">
+        <v>9</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Frozen Pizza</t>
+        </is>
+      </c>
+      <c r="O11" s="11" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>9</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Sweet Loren's Gluten Free Brownie Cookie Dough</t>
+        </is>
+      </c>
+      <c r="S11" s="11" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="U11" t="n">
+        <v>9</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Fresh Poultry</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Frozen Breakfast</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="M12" t="n">
+        <v>10</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Frozen Breakfast</t>
+        </is>
+      </c>
+      <c r="O12" s="11" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>10</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Gluten-Free Wide Pan Bread</t>
+        </is>
+      </c>
+      <c r="S12" s="11" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="U12" t="n">
+        <v>10</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Frozen Breakfast</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="E13" t="n">
+        <v>11</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Refrigerated Dough</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="M13" t="n">
+        <v>11</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Refrigerated Dough</t>
+        </is>
+      </c>
+      <c r="O13" s="11" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="U13" t="n">
+        <v>11</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Prepared Coffee</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Muffins &amp; Pastries</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="M14" t="n">
+        <v>12</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Muffins &amp; Pastries</t>
+        </is>
+      </c>
+      <c r="O14" s="11" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="U14" t="n">
+        <v>12</v>
+      </c>
+      <c r="V14" t="inlineStr">
         <is>
           <t>Prepared Meals</t>
         </is>
       </c>
-      <c r="E3" s="11" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Aldi</t>
-        </is>
-      </c>
-      <c r="H3" s="11" t="n">
-        <v>100.82</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Prepared Meals</t>
-        </is>
-      </c>
-      <c r="K3" s="11" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Silk Organic Unsweet Soymilk, Half Gallon</t>
-        </is>
-      </c>
-      <c r="N3" s="11" t="n">
-        <v>18.57</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Fresh Vegetables</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>8</v>
-      </c>
-      <c r="S3" s="10" t="n">
-        <v>46235</v>
-      </c>
-      <c r="T3" s="11" t="n">
-        <v>100.82</v>
-      </c>
-      <c r="U3" s="11" t="n">
-        <v>60.57999999999999</v>
-      </c>
-      <c r="V3" s="11" t="n">
-        <v>48.12</v>
-      </c>
-      <c r="W3" s="11" t="n">
-        <v>30.24</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Yogurt</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Publix</t>
-        </is>
-      </c>
-      <c r="H4" s="11" t="n">
-        <v>60.57999999999999</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Yogurt</t>
-        </is>
-      </c>
-      <c r="K4" s="11" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>1 Chicken N French Toast</t>
-        </is>
-      </c>
-      <c r="N4" s="11" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Fresh Fruit</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Fresh Vegetables</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Honey Pineapple</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="n">
-        <v>48.12</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Fresh Vegetables</t>
-        </is>
-      </c>
-      <c r="K5" s="11" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>1 Frenchy Plate</t>
-        </is>
-      </c>
-      <c r="N5" s="11" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="W14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="E15" t="n">
+        <v>13</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Storage &amp; Organization</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="M15" t="n">
+        <v>13</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Storage &amp; Organization</t>
+        </is>
+      </c>
+      <c r="O15" s="11" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="U15" t="n">
+        <v>13</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Snack Bars</t>
+        </is>
+      </c>
+      <c r="W15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="E16" t="n">
+        <v>14</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Writing Supplies</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="M16" t="n">
+        <v>14</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Writing Supplies</t>
+        </is>
+      </c>
+      <c r="O16" s="11" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="U16" t="n">
+        <v>14</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Specialty Cheese</t>
+        </is>
+      </c>
+      <c r="W16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="E17" t="n">
+        <v>15</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fees &amp; Charges</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="M17" t="n">
+        <v>15</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Fees &amp; Charges</t>
+        </is>
+      </c>
+      <c r="O17" s="11" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="U17" t="n">
+        <v>15</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Crackers</t>
+        </is>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="E18" t="n">
+        <v>16</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Cream &amp; Half-and-Half</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="M18" t="n">
+        <v>16</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Cream &amp; Half-and-Half</t>
+        </is>
+      </c>
+      <c r="O18" s="11" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="U18" t="n">
+        <v>16</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Cream &amp; Half-and-Half</t>
+        </is>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="E19" t="n">
+        <v>17</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Disposable Tableware</t>
+        </is>
+      </c>
+      <c r="G19" s="11" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="M19" t="n">
+        <v>17</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Disposable Tableware</t>
+        </is>
+      </c>
+      <c r="O19" s="11" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="U19" t="n">
+        <v>17</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Croutons</t>
+        </is>
+      </c>
+      <c r="W19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="E20" t="n">
+        <v>18</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Specialty Cheese</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="M20" t="n">
+        <v>18</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Specialty Cheese</t>
+        </is>
+      </c>
+      <c r="O20" s="11" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="U20" t="n">
+        <v>18</v>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dips &amp; Spreads</t>
+        </is>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="E21" t="n">
+        <v>19</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Snack Bars</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="M21" t="n">
+        <v>19</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Snack Bars</t>
+        </is>
+      </c>
+      <c r="O21" s="11" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="U21" t="n">
+        <v>19</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Disposable Tableware</t>
+        </is>
+      </c>
+      <c r="W21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="E22" t="n">
+        <v>20</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Fresh-Cut Fruit</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="M22" t="n">
+        <v>20</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Fresh-Cut Fruit</t>
+        </is>
+      </c>
+      <c r="O22" s="11" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="U22" t="n">
+        <v>20</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Fresh-Cut Fruit</t>
+        </is>
+      </c>
+      <c r="W22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="E23" t="n">
+        <v>21</v>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>Canned Beans &amp; Legumes</t>
         </is>
       </c>
-      <c r="Q5" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Plant-Based Milk</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>18.57</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Trader Joe's</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="n">
-        <v>30.24</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Plant-Based Milk</t>
-        </is>
-      </c>
-      <c r="K6" s="11" t="n">
-        <v>18.57</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Empire Kosher Ground Turkey</t>
-        </is>
-      </c>
-      <c r="N6" s="11" t="n">
-        <v>13.98</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Plant-Based Milk</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Fresh Fruit</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>15.97</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Fresh Fruit</t>
-        </is>
-      </c>
-      <c r="K7" s="11" t="n">
-        <v>15.97</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Cauliflower Crust Pizza</t>
-        </is>
-      </c>
-      <c r="N7" s="11" t="n">
-        <v>8.289999999999999</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Yogurt</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Fresh Poultry</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>13.98</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Fresh Poultry</t>
-        </is>
-      </c>
-      <c r="K8" s="11" t="n">
-        <v>13.98</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Stonyfield Organic YoBaby Yogurt Pouch, Banana</t>
-        </is>
-      </c>
-      <c r="N8" s="11" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Bread</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Prepared Coffee</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Prepared Coffee</t>
-        </is>
-      </c>
-      <c r="K9" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Stonyfield Organic YoBaby Yogurt Pouch, Peach</t>
-        </is>
-      </c>
-      <c r="N9" s="11" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Fees &amp; Charges</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Bread</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>10.16</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="K10" s="11" t="n">
-        <v>106.41</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Van's Gluten Free Blueberry Waffles</t>
-        </is>
-      </c>
-      <c r="N10" s="11" t="n">
-        <v>7.78</v>
-      </c>
-      <c r="P10" t="inlineStr">
+      <c r="G23" s="11" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="M23" t="n">
+        <v>21</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Canned Beans &amp; Legumes</t>
+        </is>
+      </c>
+      <c r="O23" s="11" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="U23" t="n">
+        <v>21</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Frozen Pizza</t>
+        </is>
+      </c>
+      <c r="W23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="E24" t="n">
+        <v>22</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Dips &amp; Spreads</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="M24" t="n">
+        <v>22</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Dips &amp; Spreads</t>
+        </is>
+      </c>
+      <c r="O24" s="11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="U24" t="n">
+        <v>22</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jarred Vegetables</t>
+        </is>
+      </c>
+      <c r="W24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="E25" t="n">
+        <v>23</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Jarred Vegetables</t>
+        </is>
+      </c>
+      <c r="G25" s="11" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="M25" t="n">
+        <v>23</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Jarred Vegetables</t>
+        </is>
+      </c>
+      <c r="O25" s="11" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="U25" t="n">
+        <v>23</v>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Muffins &amp; Pastries</t>
+        </is>
+      </c>
+      <c r="W25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="E26" t="n">
+        <v>24</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Pasta</t>
+        </is>
+      </c>
+      <c r="G26" s="11" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="M26" t="n">
+        <v>24</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Pasta</t>
+        </is>
+      </c>
+      <c r="O26" s="11" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U26" t="n">
+        <v>24</v>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Pasta</t>
+        </is>
+      </c>
+      <c r="W26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="E27" t="n">
+        <v>25</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Salad Dressing</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="M27" t="n">
+        <v>25</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Salad Dressing</t>
+        </is>
+      </c>
+      <c r="O27" s="11" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U27" t="n">
+        <v>25</v>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Popcorn</t>
+        </is>
+      </c>
+      <c r="W27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="E28" t="n">
+        <v>26</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Crackers</t>
+        </is>
+      </c>
+      <c r="G28" s="11" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="M28" t="n">
+        <v>26</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Crackers</t>
+        </is>
+      </c>
+      <c r="O28" s="11" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="U28" t="n">
+        <v>26</v>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Refrigerated Dough</t>
+        </is>
+      </c>
+      <c r="W28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="E29" t="n">
+        <v>27</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Popcorn</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="M29" t="n">
+        <v>27</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Popcorn</t>
+        </is>
+      </c>
+      <c r="O29" s="11" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="U29" t="n">
+        <v>27</v>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Salad Dressing</t>
+        </is>
+      </c>
+      <c r="W29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="E30" t="n">
+        <v>28</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Croutons</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="M30" t="n">
+        <v>28</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Croutons</t>
+        </is>
+      </c>
+      <c r="O30" s="11" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U30" t="n">
+        <v>28</v>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Storage &amp; Organization</t>
+        </is>
+      </c>
+      <c r="W30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="E31" t="n">
+        <v>29</v>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>Fresh Herbs</t>
         </is>
       </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Frozen Pizza</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="n">
-        <v>8.289999999999999</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Sweet Loren's Gluten Free Brownie Cookie Dough</t>
-        </is>
-      </c>
-      <c r="N11" s="11" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Fresh Poultry</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Frozen Breakfast</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="n">
-        <v>7.78</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Gluten-Free Wide Pan Bread</t>
-        </is>
-      </c>
-      <c r="N12" s="11" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Frozen Breakfast</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Refrigerated Dough</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Prepared Coffee</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Muffins &amp; Pastries</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Prepared Meals</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Storage &amp; Organization</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Snack Bars</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="D16" t="inlineStr">
+      <c r="G31" s="11" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="M31" t="n">
+        <v>29</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Fresh Herbs</t>
+        </is>
+      </c>
+      <c r="O31" s="11" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U31" t="n">
+        <v>29</v>
+      </c>
+      <c r="V31" t="inlineStr">
         <is>
           <t>Writing Supplies</t>
         </is>
       </c>
-      <c r="E16" s="11" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Specialty Cheese</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="n">
-        <v>55.22</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>15</v>
+      <c r="W31" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/database/shopgraph_purchase_history.xlsx
+++ b/data/database/shopgraph_purchase_history.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Imported Receipts" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Purchase History'!$A$1:$O$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Purchase History'!$A$1:$O$74</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,14 +20,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="165" formatCode="mm/dd/yyyy\ hh:mm"/>
-    <numFmt numFmtId="166" formatCode="$#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="mmm yyyy"/>
-    <numFmt numFmtId="168" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="mmm\ yyyy"/>
+    <numFmt numFmtId="167" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="168" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="169" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="170" formatCode="mmm yyyy"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,12 +41,46 @@
       <name val="Calibri"/>
       <family val="2"/>
       <b val="1"/>
+      <color rgb="FF404040"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF1F4E78"/>
       <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="20"/>
+      <sz val="22"/>
     </font>
     <font>
       <b val="1"/>
@@ -60,11 +96,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="22"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
     <font>
@@ -72,12 +103,82 @@
       <color rgb="001F4E78"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="30">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED7D31"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70AD47"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5B9BD5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC55A11"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF548235"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8064A2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF264478"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9E480E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF636363"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -162,56 +263,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -224,7 +302,55 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -863,14 +989,112 @@
               </a:ln>
             </spPr>
           </dPt>
+          <dPt>
+            <idx val="29"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="5B9BD5"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="5B9BD5"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="30"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="C55A11"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="C55A11"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="31"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="548235"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="548235"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="32"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8064A2"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="8064A2"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="33"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="264478"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="264478"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="34"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="9E480E"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="9E480E"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="35"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="636363"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="636363"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
-              <f>'_AnalyticsData'!$E$3:$E$31</f>
+              <f>'_AnalyticsData'!$E$3:$E$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_AnalyticsData'!$G$3:$G$31</f>
+              <f>'_AnalyticsData'!$G$3:$G$38</f>
             </numRef>
           </val>
         </ser>
@@ -1032,14 +1256,28 @@
               </a:ln>
             </spPr>
           </dPt>
+          <dPt>
+            <idx val="4"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="FFC000"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
-              <f>'_AnalyticsData'!$I$3:$I$6</f>
+              <f>'_AnalyticsData'!$I$3:$I$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_AnalyticsData'!$K$3:$K$6</f>
+              <f>'_AnalyticsData'!$K$3:$K$7</f>
             </numRef>
           </val>
         </ser>
@@ -1550,14 +1788,112 @@
               </a:ln>
             </spPr>
           </dPt>
+          <dPt>
+            <idx val="29"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="5B9BD5"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="5B9BD5"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="30"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="C55A11"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="C55A11"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="31"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="548235"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="548235"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="32"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8064A2"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="8064A2"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="33"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="264478"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="264478"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="34"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="9E480E"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="9E480E"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="35"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="636363"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="636363"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
-              <f>'_AnalyticsData'!$M$3:$M$31</f>
+              <f>'_AnalyticsData'!$M$3:$M$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_AnalyticsData'!$O$3:$O$31</f>
+              <f>'_AnalyticsData'!$O$3:$O$38</f>
             </numRef>
           </val>
         </ser>
@@ -1973,6 +2309,36 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'_AnalyticsData'!AD2</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="FFC000"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'_AnalyticsData'!$Y$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'_AnalyticsData'!$AD$3</f>
+            </numRef>
+          </val>
+        </ser>
         <gapWidth val="150"/>
         <overlap val="100"/>
         <axId val="10"/>
@@ -2482,14 +2848,112 @@
               </a:ln>
             </spPr>
           </dPt>
+          <dPt>
+            <idx val="29"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="5B9BD5"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="5B9BD5"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="30"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="C55A11"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="C55A11"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="31"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="548235"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="548235"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="32"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8064A2"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="8064A2"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="33"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="264478"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="264478"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="34"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="9E480E"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="9E480E"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="35"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="636363"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="636363"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
-              <f>'_AnalyticsData'!$U$3:$U$31</f>
+              <f>'_AnalyticsData'!$U$3:$U$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_AnalyticsData'!$W$3:$W$31</f>
+              <f>'_AnalyticsData'!$W$3:$W$38</f>
             </numRef>
           </val>
         </ser>
@@ -2609,7 +3073,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>79</row>
+      <row>84</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9180000" cy="5220000"/>
@@ -2631,7 +3095,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>115</row>
+      <row>120</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9180000" cy="5940000"/>
@@ -2653,7 +3117,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>151</row>
+      <row>161</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9180000" cy="5220000"/>
@@ -2675,7 +3139,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>187</row>
+      <row>197</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9180000" cy="5940000"/>
@@ -2697,7 +3161,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>223</row>
+      <row>233</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9180000" cy="5220000"/>
@@ -3007,18 +3471,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O50"/>
+  <dimension ref="A1:O76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="3" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="40.1640625" bestFit="1" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="15"/>
+    <col width="14" customWidth="1" style="27" min="1" max="1"/>
+    <col width="3" customWidth="1" style="27" min="2" max="2"/>
+    <col width="18" customWidth="1" style="27" min="3" max="4"/>
+    <col width="34" customWidth="1" style="27" min="5" max="5"/>
+    <col width="14" customWidth="1" style="27" min="6" max="6"/>
+    <col width="16" customWidth="1" style="27" min="7" max="7"/>
+    <col width="28" bestFit="1" customWidth="1" style="27" min="8" max="8"/>
+    <col width="22" customWidth="1" style="27" min="9" max="9"/>
+    <col width="14" customWidth="1" style="27" min="10" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5393,8 +5857,9 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
-        <v>6.84</v>
+      <c r="A50" s="1">
+        <f>SUM(K50,M50,O50)</f>
+        <v/>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5438,8 +5903,1230 @@
         <v>2.96</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="1">
+        <f>SUM(K51,M51,O51)</f>
+        <v/>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Safety 1 Soft Grip Brush &amp; Comb, Artic Blue</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="K51" s="1" t="n">
+        <v>4.48</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1">
+        <f>SUM(K52,M52,O52)</f>
+        <v/>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>The Honest Company Conditioning Detangler Sweet Cream Comfort 4 floz</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Dairy</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="K52" s="1" t="n">
+        <v>6.96</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1">
+        <f>SUM(K53,M53,O53)</f>
+        <v/>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Nestle Toll House Organic Allergen Free Dark Chocolate Regular Baking Chips, Morsels for Baking, 9 oz Bag</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="K53" s="1" t="n">
+        <v>8.369999999999999</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1">
+        <f>SUM(K54,M54,O54)</f>
+        <v/>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>GHIRARDELLI Gluten Free Double Chocolate Brownie Mix, Gluten Free Baking Mix, Includes Chocolate Chips, 18 oz Box 20 shopped Qty1</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="K54" s="1" t="n">
+        <v>6.67</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1">
+        <f>SUM(K55,M55,O55)</f>
+        <v/>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Purina Tidy Cats With Glade Clear Springs Scented, Odor Control, Clumping Multi-Cat Litter 20 shopped Qty2</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Pet</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="K55" s="1" t="n">
+        <v>23.94</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1">
+        <f>SUM(K56,M56,O56)</f>
+        <v/>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Lawry's Kosher Coarse Ground With Parsley Garlic Salt, 6.0 oz Bottle</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Meat &amp; Seafood</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="K56" s="1" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1">
+        <f>SUM(K57,M57,O57)</f>
+        <v/>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Huggies Natural Care Sensitive Baby Wipes, Unscented, 3 Flip-Top Packs, 168 Count 20 shopped Qty1</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Baby</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="K57" s="1" t="n">
+        <v>5.82</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1">
+        <f>SUM(K58,M58,O58)</f>
+        <v/>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Pampers Swaddlers Fragrance Free Baby Diapers Size 5, 100 Count (Select for More Options) 20 shopped Qty1</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Baby</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="K58" s="1" t="n">
+        <v>39.77</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1">
+        <f>SUM(K59,M59,O59)</f>
+        <v/>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Chobani Oatmilk Extra Creamy 52 floz Carton 20 shopped aty1</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Dairy</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="K59" s="1" t="n">
+        <v>4.17</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1">
+        <f>SUM(K60,M60,O60)</f>
+        <v/>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Desitin Maximum Strength Diaper Rash Cream, 40% Zinc Oxide, 4.8 oz</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Dairy</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="K60" s="1" t="n">
+        <v>7.97</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1">
+        <f>SUM(K61,M61,O61)</f>
+        <v/>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>fairlife Lactose Free Reduced Fat Chocolate Ultra Filtered Milk, 52 floz</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Dairy</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="K61" s="1" t="n">
+        <v>5.32</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1">
+        <f>SUM(K62,M62,O62)</f>
+        <v/>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Nestle Toll House Dark Chocolate Regular Baking Chips, 10 oz Bag 20 shopped Qty1</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="K62" s="1" t="n">
+        <v>4.96</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1">
+        <f>SUM(K63,M63,O63)</f>
+        <v/>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Dove Body Wash For 24hr Lotion-Soft Skin Sensitive Skin Moisturizing Skin Cleanser Gentle Hypoallergenic Formula With</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="K63" t="n">
+        <v>4.97</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1">
+        <f>SUM(K64,M64,O64)</f>
+        <v/>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>No Sulfates No Parabens, 11 Floz</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="K64" s="1" t="n">
+        <v>4.97</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1">
+        <f>SUM(K65,M65,O65)</f>
+        <v/>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Great Value Large White Eggs 36 Count 20 shopped Qty1</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="K65" s="1" t="n">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1">
+        <f>SUM(K66,M66,O66)</f>
+        <v/>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Chobani 20G Protein Low-Fat Greek Yogurt Drink, Strawberries and Cream 10 fl oz Bottle, 4 Pack</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="K66" s="1" t="n">
+        <v>9.67</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1">
+        <f>SUM(K67,M67,O67)</f>
+        <v/>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>McCormick Sea Salt Grinder, oz Bottle 20 shopped aty1</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="K67" s="1" t="n">
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1">
+        <f>SUM(K68,M68,O68)</f>
+        <v/>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Fresh Mandarin Oranges, 5 lb Bag 20 shopped Qty1</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="K68" s="1" t="n">
+        <v>7.96</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1">
+        <f>SUM(K69,M69,O69)</f>
+        <v/>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Fresh Pink Lady Apples, 3lb Bag 20 shopped Qty1</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="K69" s="1" t="n">
+        <v>4.97</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1">
+        <f>SUM(K70,M70,O70)</f>
+        <v/>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Fresh Banana, Each 7 weight adjusted Qty7</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="K70" s="1" t="n">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1">
+        <f>SUM(K71,M71,O71)</f>
+        <v/>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>CeraVe Baby Healing Ointment for Diaper Rash &amp; Cracked Chafed Dry Skin for Baby + Toddler 3 oz</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Baby</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="K71" s="1" t="n">
+        <v>9.98</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1">
+        <f>SUM(K72,M72,O72)</f>
+        <v/>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Fresh Banana, Each 7 weight adjusted Qty7</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="K72" s="1" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1">
+        <f>SUM(K73,M73,O73)</f>
+        <v/>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="K73" s="1" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1">
+        <f>SUM(K74,M74,O74)</f>
+        <v/>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Driver tip</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="K74" s="1" t="n">
+        <v>16.92</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1">
+        <f>SUM(K75,M75,O75)</f>
+        <v/>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>3 hours orless</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="K75" s="1" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1">
+        <f>SUM(K76,M76,O76)</f>
+        <v/>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>diff</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="K76" s="1" t="n">
+        <v>2.77</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O49"/>
+  <autoFilter ref="A1:O74"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5450,151 +7137,151 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG254"/>
+  <dimension ref="A1:AG271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="2" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
-    <col width="5" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="15" customWidth="1" min="20" max="20"/>
-    <col width="15" customWidth="1" min="21" max="21"/>
-    <col width="15" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="2" customWidth="1" min="24" max="24"/>
-    <col width="13" customWidth="1" min="25" max="25"/>
-    <col width="13" customWidth="1" min="26" max="26"/>
-    <col width="13" customWidth="1" min="27" max="27"/>
-    <col width="13" customWidth="1" min="28" max="28"/>
-    <col width="13" customWidth="1" min="29" max="29"/>
-    <col width="13" customWidth="1" min="30" max="30"/>
-    <col width="13" customWidth="1" min="31" max="31"/>
-    <col width="13" customWidth="1" min="32" max="32"/>
-    <col width="13" customWidth="1" min="33" max="33"/>
+    <col width="10" customWidth="1" style="27" min="1" max="1"/>
+    <col width="10" customWidth="1" style="27" min="2" max="2"/>
+    <col width="10" customWidth="1" style="27" min="3" max="3"/>
+    <col width="10" customWidth="1" style="27" min="4" max="4"/>
+    <col width="10" customWidth="1" style="27" min="5" max="5"/>
+    <col width="10" customWidth="1" style="27" min="6" max="6"/>
+    <col width="10" customWidth="1" style="27" min="7" max="7"/>
+    <col width="10" customWidth="1" style="27" min="8" max="8"/>
+    <col width="10" customWidth="1" style="27" min="9" max="9"/>
+    <col width="10" customWidth="1" style="27" min="10" max="10"/>
+    <col width="10" customWidth="1" style="27" min="11" max="11"/>
+    <col width="10" customWidth="1" style="27" min="12" max="12"/>
+    <col width="10" customWidth="1" style="27" min="13" max="13"/>
+    <col width="10" customWidth="1" style="27" min="14" max="14"/>
+    <col width="10" customWidth="1" style="27" min="15" max="15"/>
+    <col width="2" customWidth="1" style="27" min="16" max="16"/>
+    <col width="4" customWidth="1" style="27" min="17" max="17"/>
+    <col width="5" customWidth="1" style="27" min="18" max="18"/>
+    <col width="15" customWidth="1" style="27" min="19" max="19"/>
+    <col width="15" customWidth="1" style="27" min="20" max="20"/>
+    <col width="15" customWidth="1" style="27" min="21" max="21"/>
+    <col width="15" customWidth="1" style="27" min="22" max="22"/>
+    <col width="14" customWidth="1" style="27" min="23" max="23"/>
+    <col width="2" customWidth="1" style="27" min="24" max="24"/>
+    <col width="13" customWidth="1" style="27" min="25" max="25"/>
+    <col width="13" customWidth="1" style="27" min="26" max="26"/>
+    <col width="13" customWidth="1" style="27" min="27" max="27"/>
+    <col width="13" customWidth="1" style="27" min="28" max="28"/>
+    <col width="13" customWidth="1" style="27" min="29" max="29"/>
+    <col width="13" customWidth="1" style="27" min="30" max="30"/>
+    <col width="13" customWidth="1" style="27" min="31" max="31"/>
+    <col width="13" customWidth="1" style="27" min="32" max="32"/>
+    <col width="13" customWidth="1" style="27" min="33" max="33"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+    <row r="1" ht="28" customHeight="1" s="27">
+      <c r="A1" s="31" t="inlineStr">
         <is>
           <t>ShopGraph Spending Analytics</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1"/>
+    <row r="2" ht="28" customHeight="1" s="27"/>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="32" t="inlineStr">
         <is>
           <t>Total Spending</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="32" t="inlineStr">
         <is>
           <t>Purchase Observations</t>
         </is>
       </c>
-      <c r="M4" s="13" t="inlineStr">
+      <c r="M4" s="32" t="inlineStr">
         <is>
           <t>Date Range</t>
         </is>
       </c>
-      <c r="T4" s="13" t="inlineStr">
+      <c r="T4" s="32" t="inlineStr">
         <is>
           <t>Stores</t>
         </is>
       </c>
-      <c r="Z4" s="13" t="inlineStr">
+      <c r="Z4" s="32" t="inlineStr">
         <is>
           <t>Categories</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="n">
-        <v>239.76</v>
-      </c>
-      <c r="G5" s="15" t="n">
-        <v>56</v>
-      </c>
-      <c r="M5" s="15" t="inlineStr">
-        <is>
-          <t>08/23/2026 - 08/27/2026</t>
-        </is>
-      </c>
-      <c r="T5" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z5" s="15" t="n">
-        <v>29</v>
+      <c r="A5" s="33" t="n">
+        <v>444.77</v>
+      </c>
+      <c r="G5" s="34" t="n">
+        <v>82</v>
+      </c>
+      <c r="M5" s="34" t="inlineStr">
+        <is>
+          <t>08/06/2026 - 08/27/2026</t>
+        </is>
+      </c>
+      <c r="T5" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z5" s="34" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="8">
-      <c r="Q8" s="16" t="inlineStr">
+      <c r="Q8" s="35" t="inlineStr">
         <is>
           <t>Number / Month</t>
         </is>
       </c>
-      <c r="Y8" s="16" t="inlineStr">
+      <c r="Y8" s="35" t="inlineStr">
         <is>
           <t>How to Read This Graph</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="Q9" s="17" t="inlineStr"/>
-      <c r="R9" s="17" t="inlineStr">
+      <c r="Q9" s="36" t="inlineStr"/>
+      <c r="R9" s="36" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="S9" s="17" t="inlineStr">
+      <c r="S9" s="36" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="W9" s="17" t="inlineStr">
+      <c r="W9" s="36" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="Q10" s="18" t="n"/>
-      <c r="R10" s="19" t="n">
+    <row r="10" ht="22" customHeight="1" s="27">
+      <c r="Q10" s="37" t="n"/>
+      <c r="R10" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="S10" s="20" t="inlineStr">
+      <c r="S10" s="26" t="inlineStr">
         <is>
           <t>August 2026</t>
         </is>
       </c>
-      <c r="W10" s="21" t="inlineStr">
-        <is>
-          <t>$239.76</t>
-        </is>
-      </c>
-      <c r="Y10" s="22" t="inlineStr">
+      <c r="W10" s="13" t="inlineStr">
+        <is>
+          <t>$444.77</t>
+        </is>
+      </c>
+      <c r="Y10" s="39" t="inlineStr">
         <is>
           <t>What it represents</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="Y11" s="20" t="inlineStr">
+      <c r="Y11" s="26" t="inlineStr">
         <is>
           <t>Shows total household spending for each calendar month. Every valid Date N / Price N purchase observation is added to its month.</t>
         </is>
@@ -5604,14 +7291,14 @@
     <row r="13"/>
     <row r="14"/>
     <row r="16">
-      <c r="Y16" s="22" t="inlineStr">
+      <c r="Y16" s="39" t="inlineStr">
         <is>
           <t>How to read it</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="Y17" s="20" t="inlineStr">
+      <c r="Y17" s="26" t="inlineStr">
         <is>
           <t>The x-axis uses month numbers instead of month names to keep the graph clear. Match each number to the month and dollar total in the key. A rising line means monthly spending increased; a falling line means it decreased.</t>
         </is>
@@ -5621,14 +7308,14 @@
     <row r="19"/>
     <row r="20"/>
     <row r="22">
-      <c r="Y22" s="22" t="inlineStr">
+      <c r="Y22" s="39" t="inlineStr">
         <is>
           <t>What it is useful for</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="Y23" s="20" t="inlineStr">
+      <c r="Y23" s="26" t="inlineStr">
         <is>
           <t>Use this to identify overall spending trends, unusually expensive months, and whether spending is gradually moving up or down over time.</t>
         </is>
@@ -5638,14 +7325,14 @@
     <row r="25"/>
     <row r="26"/>
     <row r="28">
-      <c r="Y28" s="22" t="inlineStr">
+      <c r="Y28" s="39" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="Y29" s="20" t="inlineStr">
+      <c r="Y29" s="26" t="inlineStr">
         <is>
           <t>Months with no spending between the earliest and latest purchase dates are included as zero-spend months.</t>
         </is>
@@ -5655,2335 +7342,2725 @@
     <row r="31"/>
     <row r="32"/>
     <row r="44">
-      <c r="Q44" s="16" t="inlineStr">
+      <c r="Q44" s="35" t="inlineStr">
         <is>
           <t>Number / Category</t>
         </is>
       </c>
-      <c r="Y44" s="16" t="inlineStr">
+      <c r="Y44" s="35" t="inlineStr">
         <is>
           <t>How to Read This Graph</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="Q45" s="17" t="inlineStr"/>
-      <c r="R45" s="17" t="inlineStr">
+      <c r="Q45" s="36" t="inlineStr"/>
+      <c r="R45" s="36" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="S45" s="17" t="inlineStr">
+      <c r="S45" s="36" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="W45" s="17" t="inlineStr">
+      <c r="W45" s="36" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="Q46" s="18" t="n"/>
-      <c r="R46" s="19" t="n">
+    <row r="46" ht="22" customHeight="1" s="27">
+      <c r="Q46" s="37" t="n"/>
+      <c r="R46" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="S46" s="20" t="inlineStr">
+      <c r="S46" s="26" t="inlineStr">
+        <is>
+          <t>Baby</t>
+        </is>
+      </c>
+      <c r="W46" s="13" t="inlineStr">
+        <is>
+          <t>$55.57</t>
+        </is>
+      </c>
+      <c r="Y46" s="39" t="inlineStr">
+        <is>
+          <t>What it represents</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1" s="27">
+      <c r="Q47" s="40" t="n"/>
+      <c r="R47" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="S47" s="26" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="W47" s="13" t="inlineStr">
+        <is>
+          <t>$53.49</t>
+        </is>
+      </c>
+      <c r="Y47" s="26" t="inlineStr">
+        <is>
+          <t>Compares total spending across every category in Purchase History. No categories are collapsed into an 'Other' group.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1" s="27">
+      <c r="Q48" s="41" t="n"/>
+      <c r="R48" s="38" t="n">
+        <v>3</v>
+      </c>
+      <c r="S48" s="26" t="inlineStr">
         <is>
           <t>Prepared Meals</t>
         </is>
       </c>
-      <c r="W46" s="21" t="inlineStr">
+      <c r="W48" s="13" t="inlineStr">
         <is>
           <t>$31.20</t>
         </is>
       </c>
-      <c r="Y46" s="22" t="inlineStr">
+    </row>
+    <row r="49" ht="22" customHeight="1" s="27">
+      <c r="Q49" s="42" t="n"/>
+      <c r="R49" s="38" t="n">
+        <v>4</v>
+      </c>
+      <c r="S49" s="26" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="W49" s="13" t="inlineStr">
+        <is>
+          <t>$24.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1" s="27">
+      <c r="Q50" s="43" t="n"/>
+      <c r="R50" s="38" t="n">
+        <v>5</v>
+      </c>
+      <c r="S50" s="26" t="inlineStr">
+        <is>
+          <t>Dairy</t>
+        </is>
+      </c>
+      <c r="W50" s="13" t="inlineStr">
+        <is>
+          <t>$24.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1" s="27">
+      <c r="Q51" s="44" t="n"/>
+      <c r="R51" s="38" t="n">
+        <v>6</v>
+      </c>
+      <c r="S51" s="26" t="inlineStr">
+        <is>
+          <t>Pet</t>
+        </is>
+      </c>
+      <c r="W51" s="13" t="inlineStr">
+        <is>
+          <t>$23.94</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1" s="27">
+      <c r="Q52" s="45" t="n"/>
+      <c r="R52" s="38" t="n">
+        <v>7</v>
+      </c>
+      <c r="S52" s="26" t="inlineStr">
+        <is>
+          <t>Yogurt</t>
+        </is>
+      </c>
+      <c r="W52" s="13" t="inlineStr">
+        <is>
+          <t>$21.35</t>
+        </is>
+      </c>
+      <c r="Y52" s="39" t="inlineStr">
+        <is>
+          <t>How to read it</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1" s="27">
+      <c r="Q53" s="46" t="n"/>
+      <c r="R53" s="38" t="n">
+        <v>8</v>
+      </c>
+      <c r="S53" s="26" t="inlineStr">
+        <is>
+          <t>Fresh Vegetables</t>
+        </is>
+      </c>
+      <c r="W53" s="13" t="inlineStr">
+        <is>
+          <t>$21.28</t>
+        </is>
+      </c>
+      <c r="Y53" s="26" t="inlineStr">
+        <is>
+          <t>Each horizontal bar is identified by a number and color. Use the key to map that number/color to the category name and exact spending amount. Longer bars mean more money was spent in that category.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1" s="27">
+      <c r="Q54" s="47" t="n"/>
+      <c r="R54" s="38" t="n">
+        <v>9</v>
+      </c>
+      <c r="S54" s="26" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="W54" s="13" t="inlineStr">
+        <is>
+          <t>$20.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1" s="27">
+      <c r="Q55" s="48" t="n"/>
+      <c r="R55" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="S55" s="26" t="inlineStr">
+        <is>
+          <t>Plant-Based Milk</t>
+        </is>
+      </c>
+      <c r="W55" s="13" t="inlineStr">
+        <is>
+          <t>$18.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1" s="27">
+      <c r="Q56" s="49" t="n"/>
+      <c r="R56" s="38" t="n">
+        <v>11</v>
+      </c>
+      <c r="S56" s="26" t="inlineStr">
+        <is>
+          <t>Fresh Fruit</t>
+        </is>
+      </c>
+      <c r="W56" s="13" t="inlineStr">
+        <is>
+          <t>$15.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1" s="27">
+      <c r="Q57" s="50" t="n"/>
+      <c r="R57" s="38" t="n">
+        <v>12</v>
+      </c>
+      <c r="S57" s="26" t="inlineStr">
+        <is>
+          <t>Fresh Poultry</t>
+        </is>
+      </c>
+      <c r="W57" s="13" t="inlineStr">
+        <is>
+          <t>$13.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1" s="27">
+      <c r="Q58" s="37" t="n"/>
+      <c r="R58" s="38" t="n">
+        <v>13</v>
+      </c>
+      <c r="S58" s="26" t="inlineStr">
+        <is>
+          <t>Prepared Coffee</t>
+        </is>
+      </c>
+      <c r="W58" s="13" t="inlineStr">
+        <is>
+          <t>$11.00</t>
+        </is>
+      </c>
+      <c r="Y58" s="39" t="inlineStr">
+        <is>
+          <t>What it is useful for</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1" s="27">
+      <c r="Q59" s="40" t="n"/>
+      <c r="R59" s="38" t="n">
+        <v>14</v>
+      </c>
+      <c r="S59" s="26" t="inlineStr">
+        <is>
+          <t>Bread</t>
+        </is>
+      </c>
+      <c r="W59" s="13" t="inlineStr">
+        <is>
+          <t>$10.16</t>
+        </is>
+      </c>
+      <c r="Y59" s="26" t="inlineStr">
+        <is>
+          <t>Use this to see which types of goods are the biggest drivers of household spending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1" s="27">
+      <c r="Q60" s="41" t="n"/>
+      <c r="R60" s="38" t="n">
+        <v>15</v>
+      </c>
+      <c r="S60" s="26" t="inlineStr">
+        <is>
+          <t>Frozen Pizza</t>
+        </is>
+      </c>
+      <c r="W60" s="13" t="inlineStr">
+        <is>
+          <t>$8.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1" s="27">
+      <c r="Q61" s="42" t="n"/>
+      <c r="R61" s="38" t="n">
+        <v>16</v>
+      </c>
+      <c r="S61" s="26" t="inlineStr">
+        <is>
+          <t>Frozen Breakfast</t>
+        </is>
+      </c>
+      <c r="W61" s="13" t="inlineStr">
+        <is>
+          <t>$7.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1" s="27">
+      <c r="Q62" s="43" t="n"/>
+      <c r="R62" s="38" t="n">
+        <v>17</v>
+      </c>
+      <c r="S62" s="26" t="inlineStr">
+        <is>
+          <t>Refrigerated Dough</t>
+        </is>
+      </c>
+      <c r="W62" s="13" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1" s="27">
+      <c r="Q63" s="44" t="n"/>
+      <c r="R63" s="38" t="n">
+        <v>18</v>
+      </c>
+      <c r="S63" s="26" t="inlineStr">
+        <is>
+          <t>Muffins &amp; Pastries</t>
+        </is>
+      </c>
+      <c r="W63" s="13" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1" s="27">
+      <c r="Q64" s="45" t="n"/>
+      <c r="R64" s="38" t="n">
+        <v>19</v>
+      </c>
+      <c r="S64" s="26" t="inlineStr">
+        <is>
+          <t>Storage &amp; Organization</t>
+        </is>
+      </c>
+      <c r="W64" s="13" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1" s="27">
+      <c r="Q65" s="46" t="n"/>
+      <c r="R65" s="38" t="n">
+        <v>20</v>
+      </c>
+      <c r="S65" s="26" t="inlineStr">
+        <is>
+          <t>Writing Supplies</t>
+        </is>
+      </c>
+      <c r="W65" s="13" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1" s="27">
+      <c r="Q66" s="47" t="n"/>
+      <c r="R66" s="38" t="n">
+        <v>21</v>
+      </c>
+      <c r="S66" s="26" t="inlineStr">
+        <is>
+          <t>Fees &amp; Charges</t>
+        </is>
+      </c>
+      <c r="W66" s="13" t="inlineStr">
+        <is>
+          <t>$5.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1" s="27">
+      <c r="Q67" s="48" t="n"/>
+      <c r="R67" s="38" t="n">
+        <v>22</v>
+      </c>
+      <c r="S67" s="26" t="inlineStr">
+        <is>
+          <t>Cream &amp; Half-and-Half</t>
+        </is>
+      </c>
+      <c r="W67" s="13" t="inlineStr">
+        <is>
+          <t>$5.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1" s="27">
+      <c r="Q68" s="49" t="n"/>
+      <c r="R68" s="38" t="n">
+        <v>23</v>
+      </c>
+      <c r="S68" s="26" t="inlineStr">
+        <is>
+          <t>Disposable Tableware</t>
+        </is>
+      </c>
+      <c r="W68" s="13" t="inlineStr">
+        <is>
+          <t>$5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1" s="27">
+      <c r="Q69" s="50" t="n"/>
+      <c r="R69" s="38" t="n">
+        <v>24</v>
+      </c>
+      <c r="S69" s="26" t="inlineStr">
+        <is>
+          <t>Specialty Cheese</t>
+        </is>
+      </c>
+      <c r="W69" s="13" t="inlineStr">
+        <is>
+          <t>$4.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1" s="27">
+      <c r="Q70" s="37" t="n"/>
+      <c r="R70" s="38" t="n">
+        <v>25</v>
+      </c>
+      <c r="S70" s="26" t="inlineStr">
+        <is>
+          <t>Snack Bars</t>
+        </is>
+      </c>
+      <c r="W70" s="13" t="inlineStr">
+        <is>
+          <t>$3.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="22" customHeight="1" s="27">
+      <c r="Q71" s="40" t="n"/>
+      <c r="R71" s="38" t="n">
+        <v>26</v>
+      </c>
+      <c r="S71" s="26" t="inlineStr">
+        <is>
+          <t>Fresh-Cut Fruit</t>
+        </is>
+      </c>
+      <c r="W71" s="13" t="inlineStr">
+        <is>
+          <t>$3.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="22" customHeight="1" s="27">
+      <c r="Q72" s="41" t="n"/>
+      <c r="R72" s="38" t="n">
+        <v>27</v>
+      </c>
+      <c r="S72" s="26" t="inlineStr">
+        <is>
+          <t>Canned Beans &amp; Legumes</t>
+        </is>
+      </c>
+      <c r="W72" s="13" t="inlineStr">
+        <is>
+          <t>$3.68</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="1" s="27">
+      <c r="Q73" s="42" t="n"/>
+      <c r="R73" s="38" t="n">
+        <v>28</v>
+      </c>
+      <c r="S73" s="26" t="inlineStr">
+        <is>
+          <t>Dips &amp; Spreads</t>
+        </is>
+      </c>
+      <c r="W73" s="13" t="inlineStr">
+        <is>
+          <t>$3.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="22" customHeight="1" s="27">
+      <c r="Q74" s="43" t="n"/>
+      <c r="R74" s="38" t="n">
+        <v>29</v>
+      </c>
+      <c r="S74" s="26" t="inlineStr">
+        <is>
+          <t>Jarred Vegetables</t>
+        </is>
+      </c>
+      <c r="W74" s="13" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="1" s="27">
+      <c r="Q75" s="44" t="n"/>
+      <c r="R75" s="38" t="n">
+        <v>30</v>
+      </c>
+      <c r="S75" s="26" t="inlineStr">
+        <is>
+          <t>Meat &amp; Seafood</t>
+        </is>
+      </c>
+      <c r="W75" s="13" t="inlineStr">
+        <is>
+          <t>$3.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="22" customHeight="1" s="27">
+      <c r="Q76" s="45" t="n"/>
+      <c r="R76" s="38" t="n">
+        <v>31</v>
+      </c>
+      <c r="S76" s="26" t="inlineStr">
+        <is>
+          <t>Pasta</t>
+        </is>
+      </c>
+      <c r="W76" s="13" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="22" customHeight="1" s="27">
+      <c r="Q77" s="46" t="n"/>
+      <c r="R77" s="38" t="n">
+        <v>32</v>
+      </c>
+      <c r="S77" s="26" t="inlineStr">
+        <is>
+          <t>Salad Dressing</t>
+        </is>
+      </c>
+      <c r="W77" s="13" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="22" customHeight="1" s="27">
+      <c r="Q78" s="47" t="n"/>
+      <c r="R78" s="38" t="n">
+        <v>33</v>
+      </c>
+      <c r="S78" s="26" t="inlineStr">
+        <is>
+          <t>Crackers</t>
+        </is>
+      </c>
+      <c r="W78" s="13" t="inlineStr">
+        <is>
+          <t>$2.79</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="22" customHeight="1" s="27">
+      <c r="Q79" s="48" t="n"/>
+      <c r="R79" s="38" t="n">
+        <v>34</v>
+      </c>
+      <c r="S79" s="26" t="inlineStr">
+        <is>
+          <t>Popcorn</t>
+        </is>
+      </c>
+      <c r="W79" s="13" t="inlineStr">
+        <is>
+          <t>$2.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="22" customHeight="1" s="27">
+      <c r="Q80" s="49" t="n"/>
+      <c r="R80" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="S80" s="26" t="inlineStr">
+        <is>
+          <t>Croutons</t>
+        </is>
+      </c>
+      <c r="W80" s="13" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="22" customHeight="1" s="27">
+      <c r="Q81" s="50" t="n"/>
+      <c r="R81" s="38" t="n">
+        <v>36</v>
+      </c>
+      <c r="S81" s="26" t="inlineStr">
+        <is>
+          <t>Fresh Herbs</t>
+        </is>
+      </c>
+      <c r="W81" s="13" t="inlineStr">
+        <is>
+          <t>$1.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="Q85" s="35" t="inlineStr">
+        <is>
+          <t>Number / Store</t>
+        </is>
+      </c>
+      <c r="Y85" s="35" t="inlineStr">
+        <is>
+          <t>How to Read This Graph</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="Q86" s="36" t="inlineStr"/>
+      <c r="R86" s="36" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="S86" s="36" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="W86" s="36" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="22" customHeight="1" s="27">
+      <c r="Q87" s="37" t="n"/>
+      <c r="R87" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S87" s="26" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="W87" s="13" t="inlineStr">
+        <is>
+          <t>$205.01</t>
+        </is>
+      </c>
+      <c r="Y87" s="39" t="inlineStr">
         <is>
           <t>What it represents</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="Q47" s="23" t="n"/>
-      <c r="R47" s="19" t="n">
+    <row r="88" ht="22" customHeight="1" s="27">
+      <c r="Q88" s="40" t="n"/>
+      <c r="R88" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="S47" s="20" t="inlineStr">
-        <is>
-          <t>Yogurt</t>
-        </is>
-      </c>
-      <c r="W47" s="21" t="inlineStr">
-        <is>
-          <t>$21.35</t>
-        </is>
-      </c>
-      <c r="Y47" s="20" t="inlineStr">
-        <is>
-          <t>Compares total spending across every category in Purchase History. No categories are collapsed into an 'Other' group.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="Q48" s="24" t="n"/>
-      <c r="R48" s="19" t="n">
+      <c r="S88" s="26" t="inlineStr">
+        <is>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="W88" s="13" t="inlineStr">
+        <is>
+          <t>$100.82</t>
+        </is>
+      </c>
+      <c r="Y88" s="26" t="inlineStr">
+        <is>
+          <t>Compares how much money was spent at each retailer across the entire Purchase History.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="22" customHeight="1" s="27">
+      <c r="Q89" s="41" t="n"/>
+      <c r="R89" s="38" t="n">
         <v>3</v>
       </c>
-      <c r="S48" s="20" t="inlineStr">
-        <is>
-          <t>Fresh Vegetables</t>
-        </is>
-      </c>
-      <c r="W48" s="21" t="inlineStr">
-        <is>
-          <t>$21.28</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="Q49" s="25" t="n"/>
-      <c r="R49" s="19" t="n">
+      <c r="S89" s="26" t="inlineStr">
+        <is>
+          <t>Publix</t>
+        </is>
+      </c>
+      <c r="W89" s="13" t="inlineStr">
+        <is>
+          <t>$60.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="22" customHeight="1" s="27">
+      <c r="Q90" s="42" t="n"/>
+      <c r="R90" s="38" t="n">
         <v>4</v>
       </c>
-      <c r="S49" s="20" t="inlineStr">
-        <is>
-          <t>Plant-Based Milk</t>
-        </is>
-      </c>
-      <c r="W49" s="21" t="inlineStr">
-        <is>
-          <t>$18.57</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="Q50" s="26" t="n"/>
-      <c r="R50" s="19" t="n">
+      <c r="S90" s="26" t="inlineStr">
+        <is>
+          <t>Honey Pineapple</t>
+        </is>
+      </c>
+      <c r="W90" s="13" t="inlineStr">
+        <is>
+          <t>$48.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="22" customHeight="1" s="27">
+      <c r="Q91" s="43" t="n"/>
+      <c r="R91" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="S50" s="20" t="inlineStr">
-        <is>
-          <t>Fresh Fruit</t>
-        </is>
-      </c>
-      <c r="W50" s="21" t="inlineStr">
-        <is>
-          <t>$15.97</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="Q51" s="27" t="n"/>
-      <c r="R51" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="S51" s="20" t="inlineStr">
-        <is>
-          <t>Fresh Poultry</t>
-        </is>
-      </c>
-      <c r="W51" s="21" t="inlineStr">
-        <is>
-          <t>$13.98</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="Q52" s="28" t="n"/>
-      <c r="R52" s="19" t="n">
-        <v>7</v>
-      </c>
-      <c r="S52" s="20" t="inlineStr">
-        <is>
-          <t>Prepared Coffee</t>
-        </is>
-      </c>
-      <c r="W52" s="21" t="inlineStr">
-        <is>
-          <t>$11.00</t>
-        </is>
-      </c>
-      <c r="Y52" s="22" t="inlineStr">
+      <c r="S91" s="26" t="inlineStr">
+        <is>
+          <t>Trader Joe's</t>
+        </is>
+      </c>
+      <c r="W91" s="13" t="inlineStr">
+        <is>
+          <t>$30.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="Y93" s="39" t="inlineStr">
         <is>
           <t>How to read it</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="Q53" s="29" t="n"/>
-      <c r="R53" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="S53" s="20" t="inlineStr">
-        <is>
-          <t>Bread</t>
-        </is>
-      </c>
-      <c r="W53" s="21" t="inlineStr">
-        <is>
-          <t>$10.16</t>
-        </is>
-      </c>
-      <c r="Y53" s="20" t="inlineStr">
-        <is>
-          <t>Each horizontal bar is identified by a number and color. Use the key to map that number/color to the category name and exact spending amount. Longer bars mean more money was spent in that category.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="22" customHeight="1">
-      <c r="Q54" s="30" t="n"/>
-      <c r="R54" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="S54" s="20" t="inlineStr">
-        <is>
-          <t>Frozen Pizza</t>
-        </is>
-      </c>
-      <c r="W54" s="21" t="inlineStr">
-        <is>
-          <t>$8.29</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="22" customHeight="1">
-      <c r="Q55" s="31" t="n"/>
-      <c r="R55" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="S55" s="20" t="inlineStr">
-        <is>
-          <t>Frozen Breakfast</t>
-        </is>
-      </c>
-      <c r="W55" s="21" t="inlineStr">
-        <is>
-          <t>$7.78</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="22" customHeight="1">
-      <c r="Q56" s="32" t="n"/>
-      <c r="R56" s="19" t="n">
-        <v>11</v>
-      </c>
-      <c r="S56" s="20" t="inlineStr">
-        <is>
-          <t>Refrigerated Dough</t>
-        </is>
-      </c>
-      <c r="W56" s="21" t="inlineStr">
-        <is>
-          <t>$6.99</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="22" customHeight="1">
-      <c r="Q57" s="33" t="n"/>
-      <c r="R57" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="S57" s="20" t="inlineStr">
-        <is>
-          <t>Muffins &amp; Pastries</t>
-        </is>
-      </c>
-      <c r="W57" s="21" t="inlineStr">
-        <is>
-          <t>$5.99</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="22" customHeight="1">
-      <c r="Q58" s="18" t="n"/>
-      <c r="R58" s="19" t="n">
-        <v>13</v>
-      </c>
-      <c r="S58" s="20" t="inlineStr">
-        <is>
-          <t>Storage &amp; Organization</t>
-        </is>
-      </c>
-      <c r="W58" s="21" t="inlineStr">
-        <is>
-          <t>$5.99</t>
-        </is>
-      </c>
-      <c r="Y58" s="22" t="inlineStr">
-        <is>
-          <t>What it is useful for</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="22" customHeight="1">
-      <c r="Q59" s="23" t="n"/>
-      <c r="R59" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="S59" s="20" t="inlineStr">
-        <is>
-          <t>Writing Supplies</t>
-        </is>
-      </c>
-      <c r="W59" s="21" t="inlineStr">
-        <is>
-          <t>$5.99</t>
-        </is>
-      </c>
-      <c r="Y59" s="20" t="inlineStr">
-        <is>
-          <t>Use this to see which types of goods are the biggest drivers of household spending.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="22" customHeight="1">
-      <c r="Q60" s="24" t="n"/>
-      <c r="R60" s="19" t="n">
-        <v>15</v>
-      </c>
-      <c r="S60" s="20" t="inlineStr">
-        <is>
-          <t>Fees &amp; Charges</t>
-        </is>
-      </c>
-      <c r="W60" s="21" t="inlineStr">
-        <is>
-          <t>$5.92</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="Q61" s="25" t="n"/>
-      <c r="R61" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="S61" s="20" t="inlineStr">
-        <is>
-          <t>Cream &amp; Half-and-Half</t>
-        </is>
-      </c>
-      <c r="W61" s="21" t="inlineStr">
-        <is>
-          <t>$5.89</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="22" customHeight="1">
-      <c r="Q62" s="26" t="n"/>
-      <c r="R62" s="19" t="n">
-        <v>17</v>
-      </c>
-      <c r="S62" s="20" t="inlineStr">
-        <is>
-          <t>Disposable Tableware</t>
-        </is>
-      </c>
-      <c r="W62" s="21" t="inlineStr">
-        <is>
-          <t>$5.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="22" customHeight="1">
-      <c r="Q63" s="27" t="n"/>
-      <c r="R63" s="19" t="n">
-        <v>18</v>
-      </c>
-      <c r="S63" s="20" t="inlineStr">
-        <is>
-          <t>Specialty Cheese</t>
-        </is>
-      </c>
-      <c r="W63" s="21" t="inlineStr">
-        <is>
-          <t>$4.88</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="22" customHeight="1">
-      <c r="Q64" s="28" t="n"/>
-      <c r="R64" s="19" t="n">
-        <v>19</v>
-      </c>
-      <c r="S64" s="20" t="inlineStr">
-        <is>
-          <t>Snack Bars</t>
-        </is>
-      </c>
-      <c r="W64" s="21" t="inlineStr">
-        <is>
-          <t>$3.98</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="22" customHeight="1">
-      <c r="Q65" s="29" t="n"/>
-      <c r="R65" s="19" t="n">
-        <v>20</v>
-      </c>
-      <c r="S65" s="20" t="inlineStr">
-        <is>
-          <t>Fresh-Cut Fruit</t>
-        </is>
-      </c>
-      <c r="W65" s="21" t="inlineStr">
-        <is>
-          <t>$3.89</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="22" customHeight="1">
-      <c r="Q66" s="30" t="n"/>
-      <c r="R66" s="19" t="n">
-        <v>21</v>
-      </c>
-      <c r="S66" s="20" t="inlineStr">
-        <is>
-          <t>Canned Beans &amp; Legumes</t>
-        </is>
-      </c>
-      <c r="W66" s="21" t="inlineStr">
-        <is>
-          <t>$3.68</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="22" customHeight="1">
-      <c r="Q67" s="31" t="n"/>
-      <c r="R67" s="19" t="n">
-        <v>22</v>
-      </c>
-      <c r="S67" s="20" t="inlineStr">
-        <is>
-          <t>Dips &amp; Spreads</t>
-        </is>
-      </c>
-      <c r="W67" s="21" t="inlineStr">
-        <is>
-          <t>$3.45</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="22" customHeight="1">
-      <c r="Q68" s="32" t="n"/>
-      <c r="R68" s="19" t="n">
-        <v>23</v>
-      </c>
-      <c r="S68" s="20" t="inlineStr">
-        <is>
-          <t>Jarred Vegetables</t>
-        </is>
-      </c>
-      <c r="W68" s="21" t="inlineStr">
-        <is>
-          <t>$3.29</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="22" customHeight="1">
-      <c r="Q69" s="33" t="n"/>
-      <c r="R69" s="19" t="n">
-        <v>24</v>
-      </c>
-      <c r="S69" s="20" t="inlineStr">
-        <is>
-          <t>Pasta</t>
-        </is>
-      </c>
-      <c r="W69" s="21" t="inlineStr">
-        <is>
-          <t>$2.99</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="22" customHeight="1">
-      <c r="Q70" s="18" t="n"/>
-      <c r="R70" s="19" t="n">
-        <v>25</v>
-      </c>
-      <c r="S70" s="20" t="inlineStr">
-        <is>
-          <t>Salad Dressing</t>
-        </is>
-      </c>
-      <c r="W70" s="21" t="inlineStr">
-        <is>
-          <t>$2.99</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="22" customHeight="1">
-      <c r="Q71" s="23" t="n"/>
-      <c r="R71" s="19" t="n">
-        <v>26</v>
-      </c>
-      <c r="S71" s="20" t="inlineStr">
-        <is>
-          <t>Crackers</t>
-        </is>
-      </c>
-      <c r="W71" s="21" t="inlineStr">
-        <is>
-          <t>$2.79</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="22" customHeight="1">
-      <c r="Q72" s="24" t="n"/>
-      <c r="R72" s="19" t="n">
-        <v>27</v>
-      </c>
-      <c r="S72" s="20" t="inlineStr">
-        <is>
-          <t>Popcorn</t>
-        </is>
-      </c>
-      <c r="W72" s="21" t="inlineStr">
-        <is>
-          <t>$2.39</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="22" customHeight="1">
-      <c r="Q73" s="25" t="n"/>
-      <c r="R73" s="19" t="n">
-        <v>28</v>
-      </c>
-      <c r="S73" s="20" t="inlineStr">
-        <is>
-          <t>Croutons</t>
-        </is>
-      </c>
-      <c r="W73" s="21" t="inlineStr">
-        <is>
-          <t>$1.99</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="22" customHeight="1">
-      <c r="Q74" s="26" t="n"/>
-      <c r="R74" s="19" t="n">
-        <v>29</v>
-      </c>
-      <c r="S74" s="20" t="inlineStr">
-        <is>
-          <t>Fresh Herbs</t>
-        </is>
-      </c>
-      <c r="W74" s="21" t="inlineStr">
-        <is>
-          <t>$1.84</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="Q80" s="16" t="inlineStr">
-        <is>
-          <t>Number / Store</t>
-        </is>
-      </c>
-      <c r="Y80" s="16" t="inlineStr">
-        <is>
-          <t>How to Read This Graph</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="Q81" s="17" t="inlineStr"/>
-      <c r="R81" s="17" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="S81" s="17" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="W81" s="17" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="22" customHeight="1">
-      <c r="Q82" s="18" t="n"/>
-      <c r="R82" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S82" s="20" t="inlineStr">
-        <is>
-          <t>Aldi</t>
-        </is>
-      </c>
-      <c r="W82" s="21" t="inlineStr">
-        <is>
-          <t>$100.82</t>
-        </is>
-      </c>
-      <c r="Y82" s="22" t="inlineStr">
-        <is>
-          <t>What it represents</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="22" customHeight="1">
-      <c r="Q83" s="23" t="n"/>
-      <c r="R83" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="S83" s="20" t="inlineStr">
-        <is>
-          <t>Publix</t>
-        </is>
-      </c>
-      <c r="W83" s="21" t="inlineStr">
-        <is>
-          <t>$60.58</t>
-        </is>
-      </c>
-      <c r="Y83" s="20" t="inlineStr">
-        <is>
-          <t>Compares how much money was spent at each retailer across the entire Purchase History.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="22" customHeight="1">
-      <c r="Q84" s="24" t="n"/>
-      <c r="R84" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="S84" s="20" t="inlineStr">
-        <is>
-          <t>Honey Pineapple</t>
-        </is>
-      </c>
-      <c r="W84" s="21" t="inlineStr">
-        <is>
-          <t>$48.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="22" customHeight="1">
-      <c r="Q85" s="25" t="n"/>
-      <c r="R85" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="S85" s="20" t="inlineStr">
-        <is>
-          <t>Trader Joe's</t>
-        </is>
-      </c>
-      <c r="W85" s="21" t="inlineStr">
-        <is>
-          <t>$30.24</t>
-        </is>
-      </c>
-    </row>
-    <row r="86"/>
-    <row r="88">
-      <c r="Y88" s="22" t="inlineStr">
-        <is>
-          <t>How to read it</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="Y89" s="20" t="inlineStr">
+    <row r="94">
+      <c r="Y94" s="26" t="inlineStr">
         <is>
           <t>Each store is represented by a numbered colored bar. Match the number/color to the key. Longer bars indicate more total spending at that store.</t>
         </is>
       </c>
     </row>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="94">
-      <c r="Y94" s="22" t="inlineStr">
-        <is>
-          <t>What it is useful for</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="Y95" s="20" t="inlineStr">
-        <is>
-          <t>Use this to understand which retailers receive the largest share of your household shopping budget.</t>
-        </is>
-      </c>
-    </row>
+    <row r="95"/>
     <row r="96"/>
     <row r="97"/>
-    <row r="98"/>
+    <row r="99">
+      <c r="Y99" s="39" t="inlineStr">
+        <is>
+          <t>What it is useful for</t>
+        </is>
+      </c>
+    </row>
     <row r="100">
-      <c r="Y100" s="22" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="Y101" s="20" t="inlineStr">
-        <is>
-          <t>Store Number is intentionally ignored here; purchases are grouped by the Store name.</t>
-        </is>
-      </c>
-    </row>
+      <c r="Y100" s="26" t="inlineStr">
+        <is>
+          <t>Use this to understand which retailers receive the largest share of your household shopping budget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101"/>
     <row r="102"/>
     <row r="103"/>
-    <row r="104"/>
-    <row r="116">
-      <c r="Q116" s="16" t="inlineStr">
+    <row r="105">
+      <c r="Y105" s="39" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="Y106" s="26" t="inlineStr">
+        <is>
+          <t>Store Number is intentionally ignored here; purchases are grouped by the Store name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="121">
+      <c r="Q121" s="35" t="inlineStr">
         <is>
           <t>Number / Category</t>
         </is>
       </c>
-      <c r="Y116" s="16" t="inlineStr">
+      <c r="Y121" s="35" t="inlineStr">
         <is>
           <t>How to Read This Graph</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="Q117" s="17" t="inlineStr"/>
-      <c r="R117" s="17" t="inlineStr">
+    <row r="122">
+      <c r="Q122" s="36" t="inlineStr"/>
+      <c r="R122" s="36" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="S117" s="17" t="inlineStr">
+      <c r="S122" s="36" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="W117" s="17" t="inlineStr">
+      <c r="W122" s="36" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="22" customHeight="1">
-      <c r="Q118" s="18" t="n"/>
-      <c r="R118" s="19" t="n">
+    <row r="123" ht="22" customHeight="1" s="27">
+      <c r="Q123" s="37" t="n"/>
+      <c r="R123" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="S118" s="20" t="inlineStr">
+      <c r="S123" s="26" t="inlineStr">
+        <is>
+          <t>Baby</t>
+        </is>
+      </c>
+      <c r="W123" s="13" t="inlineStr">
+        <is>
+          <t>$55.57 (12.5%)</t>
+        </is>
+      </c>
+      <c r="Y123" s="39" t="inlineStr">
+        <is>
+          <t>What it represents</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="22" customHeight="1" s="27">
+      <c r="Q124" s="40" t="n"/>
+      <c r="R124" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="S124" s="26" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="W124" s="13" t="inlineStr">
+        <is>
+          <t>$53.49 (12.0%)</t>
+        </is>
+      </c>
+      <c r="Y124" s="26" t="inlineStr">
+        <is>
+          <t>Shows each category's share of total spending as part of the whole shopping budget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="22" customHeight="1" s="27">
+      <c r="Q125" s="41" t="n"/>
+      <c r="R125" s="38" t="n">
+        <v>3</v>
+      </c>
+      <c r="S125" s="26" t="inlineStr">
         <is>
           <t>Prepared Meals</t>
         </is>
       </c>
-      <c r="W118" s="21" t="inlineStr">
-        <is>
-          <t>$31.20 (13.0%)</t>
-        </is>
-      </c>
-      <c r="Y118" s="22" t="inlineStr">
+      <c r="W125" s="13" t="inlineStr">
+        <is>
+          <t>$31.20 (7.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="22" customHeight="1" s="27">
+      <c r="Q126" s="42" t="n"/>
+      <c r="R126" s="38" t="n">
+        <v>4</v>
+      </c>
+      <c r="S126" s="26" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="W126" s="13" t="inlineStr">
+        <is>
+          <t>$24.43 (5.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="22" customHeight="1" s="27">
+      <c r="Q127" s="43" t="n"/>
+      <c r="R127" s="38" t="n">
+        <v>5</v>
+      </c>
+      <c r="S127" s="26" t="inlineStr">
+        <is>
+          <t>Dairy</t>
+        </is>
+      </c>
+      <c r="W127" s="13" t="inlineStr">
+        <is>
+          <t>$24.42 (5.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="22" customHeight="1" s="27">
+      <c r="Q128" s="44" t="n"/>
+      <c r="R128" s="38" t="n">
+        <v>6</v>
+      </c>
+      <c r="S128" s="26" t="inlineStr">
+        <is>
+          <t>Pet</t>
+        </is>
+      </c>
+      <c r="W128" s="13" t="inlineStr">
+        <is>
+          <t>$23.94 (5.4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="22" customHeight="1" s="27">
+      <c r="Q129" s="45" t="n"/>
+      <c r="R129" s="38" t="n">
+        <v>7</v>
+      </c>
+      <c r="S129" s="26" t="inlineStr">
+        <is>
+          <t>Yogurt</t>
+        </is>
+      </c>
+      <c r="W129" s="13" t="inlineStr">
+        <is>
+          <t>$21.35 (4.8%)</t>
+        </is>
+      </c>
+      <c r="Y129" s="39" t="inlineStr">
+        <is>
+          <t>How to read it</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="22" customHeight="1" s="27">
+      <c r="Q130" s="46" t="n"/>
+      <c r="R130" s="38" t="n">
+        <v>8</v>
+      </c>
+      <c r="S130" s="26" t="inlineStr">
+        <is>
+          <t>Fresh Vegetables</t>
+        </is>
+      </c>
+      <c r="W130" s="13" t="inlineStr">
+        <is>
+          <t>$21.28 (4.8%)</t>
+        </is>
+      </c>
+      <c r="Y130" s="26" t="inlineStr">
+        <is>
+          <t>The doughnut itself displays only numeric category codes. Match each number/color to the key for the category name, dollar amount, and percentage of total spending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="22" customHeight="1" s="27">
+      <c r="Q131" s="47" t="n"/>
+      <c r="R131" s="38" t="n">
+        <v>9</v>
+      </c>
+      <c r="S131" s="26" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="W131" s="13" t="inlineStr">
+        <is>
+          <t>$20.00 (4.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="22" customHeight="1" s="27">
+      <c r="Q132" s="48" t="n"/>
+      <c r="R132" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="S132" s="26" t="inlineStr">
+        <is>
+          <t>Plant-Based Milk</t>
+        </is>
+      </c>
+      <c r="W132" s="13" t="inlineStr">
+        <is>
+          <t>$18.57 (4.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="22" customHeight="1" s="27">
+      <c r="Q133" s="49" t="n"/>
+      <c r="R133" s="38" t="n">
+        <v>11</v>
+      </c>
+      <c r="S133" s="26" t="inlineStr">
+        <is>
+          <t>Fresh Fruit</t>
+        </is>
+      </c>
+      <c r="W133" s="13" t="inlineStr">
+        <is>
+          <t>$15.97 (3.6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="22" customHeight="1" s="27">
+      <c r="Q134" s="50" t="n"/>
+      <c r="R134" s="38" t="n">
+        <v>12</v>
+      </c>
+      <c r="S134" s="26" t="inlineStr">
+        <is>
+          <t>Fresh Poultry</t>
+        </is>
+      </c>
+      <c r="W134" s="13" t="inlineStr">
+        <is>
+          <t>$13.98 (3.1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="22" customHeight="1" s="27">
+      <c r="Q135" s="37" t="n"/>
+      <c r="R135" s="38" t="n">
+        <v>13</v>
+      </c>
+      <c r="S135" s="26" t="inlineStr">
+        <is>
+          <t>Prepared Coffee</t>
+        </is>
+      </c>
+      <c r="W135" s="13" t="inlineStr">
+        <is>
+          <t>$11.00 (2.5%)</t>
+        </is>
+      </c>
+      <c r="Y135" s="39" t="inlineStr">
+        <is>
+          <t>What it is useful for</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="22" customHeight="1" s="27">
+      <c r="Q136" s="40" t="n"/>
+      <c r="R136" s="38" t="n">
+        <v>14</v>
+      </c>
+      <c r="S136" s="26" t="inlineStr">
+        <is>
+          <t>Bread</t>
+        </is>
+      </c>
+      <c r="W136" s="13" t="inlineStr">
+        <is>
+          <t>$10.16 (2.3%)</t>
+        </is>
+      </c>
+      <c r="Y136" s="26" t="inlineStr">
+        <is>
+          <t>Use this for a fast visual picture of the household spending mix—especially which categories take the largest portion of the budget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="22" customHeight="1" s="27">
+      <c r="Q137" s="41" t="n"/>
+      <c r="R137" s="38" t="n">
+        <v>15</v>
+      </c>
+      <c r="S137" s="26" t="inlineStr">
+        <is>
+          <t>Frozen Pizza</t>
+        </is>
+      </c>
+      <c r="W137" s="13" t="inlineStr">
+        <is>
+          <t>$8.29 (1.9%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="22" customHeight="1" s="27">
+      <c r="Q138" s="42" t="n"/>
+      <c r="R138" s="38" t="n">
+        <v>16</v>
+      </c>
+      <c r="S138" s="26" t="inlineStr">
+        <is>
+          <t>Frozen Breakfast</t>
+        </is>
+      </c>
+      <c r="W138" s="13" t="inlineStr">
+        <is>
+          <t>$7.78 (1.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="22" customHeight="1" s="27">
+      <c r="Q139" s="43" t="n"/>
+      <c r="R139" s="38" t="n">
+        <v>17</v>
+      </c>
+      <c r="S139" s="26" t="inlineStr">
+        <is>
+          <t>Refrigerated Dough</t>
+        </is>
+      </c>
+      <c r="W139" s="13" t="inlineStr">
+        <is>
+          <t>$6.99 (1.6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="22" customHeight="1" s="27">
+      <c r="Q140" s="44" t="n"/>
+      <c r="R140" s="38" t="n">
+        <v>18</v>
+      </c>
+      <c r="S140" s="26" t="inlineStr">
+        <is>
+          <t>Muffins &amp; Pastries</t>
+        </is>
+      </c>
+      <c r="W140" s="13" t="inlineStr">
+        <is>
+          <t>$5.99 (1.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="22" customHeight="1" s="27">
+      <c r="Q141" s="45" t="n"/>
+      <c r="R141" s="38" t="n">
+        <v>19</v>
+      </c>
+      <c r="S141" s="26" t="inlineStr">
+        <is>
+          <t>Storage &amp; Organization</t>
+        </is>
+      </c>
+      <c r="W141" s="13" t="inlineStr">
+        <is>
+          <t>$5.99 (1.3%)</t>
+        </is>
+      </c>
+      <c r="Y141" s="39" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="22" customHeight="1" s="27">
+      <c r="Q142" s="46" t="n"/>
+      <c r="R142" s="38" t="n">
+        <v>20</v>
+      </c>
+      <c r="S142" s="26" t="inlineStr">
+        <is>
+          <t>Writing Supplies</t>
+        </is>
+      </c>
+      <c r="W142" s="13" t="inlineStr">
+        <is>
+          <t>$5.99 (1.3%)</t>
+        </is>
+      </c>
+      <c r="Y142" s="26" t="inlineStr">
+        <is>
+          <t>Unlike the older dashboard, this graph does not create a large 'Other' slice. Every category receives its own numbered segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="22" customHeight="1" s="27">
+      <c r="Q143" s="47" t="n"/>
+      <c r="R143" s="38" t="n">
+        <v>21</v>
+      </c>
+      <c r="S143" s="26" t="inlineStr">
+        <is>
+          <t>Fees &amp; Charges</t>
+        </is>
+      </c>
+      <c r="W143" s="13" t="inlineStr">
+        <is>
+          <t>$5.92 (1.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="22" customHeight="1" s="27">
+      <c r="Q144" s="48" t="n"/>
+      <c r="R144" s="38" t="n">
+        <v>22</v>
+      </c>
+      <c r="S144" s="26" t="inlineStr">
+        <is>
+          <t>Cream &amp; Half-and-Half</t>
+        </is>
+      </c>
+      <c r="W144" s="13" t="inlineStr">
+        <is>
+          <t>$5.89 (1.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="22" customHeight="1" s="27">
+      <c r="Q145" s="49" t="n"/>
+      <c r="R145" s="38" t="n">
+        <v>23</v>
+      </c>
+      <c r="S145" s="26" t="inlineStr">
+        <is>
+          <t>Disposable Tableware</t>
+        </is>
+      </c>
+      <c r="W145" s="13" t="inlineStr">
+        <is>
+          <t>$5.25 (1.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="22" customHeight="1" s="27">
+      <c r="Q146" s="50" t="n"/>
+      <c r="R146" s="38" t="n">
+        <v>24</v>
+      </c>
+      <c r="S146" s="26" t="inlineStr">
+        <is>
+          <t>Specialty Cheese</t>
+        </is>
+      </c>
+      <c r="W146" s="13" t="inlineStr">
+        <is>
+          <t>$4.88 (1.1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="22" customHeight="1" s="27">
+      <c r="Q147" s="37" t="n"/>
+      <c r="R147" s="38" t="n">
+        <v>25</v>
+      </c>
+      <c r="S147" s="26" t="inlineStr">
+        <is>
+          <t>Snack Bars</t>
+        </is>
+      </c>
+      <c r="W147" s="13" t="inlineStr">
+        <is>
+          <t>$3.98 (0.9%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="22" customHeight="1" s="27">
+      <c r="Q148" s="40" t="n"/>
+      <c r="R148" s="38" t="n">
+        <v>26</v>
+      </c>
+      <c r="S148" s="26" t="inlineStr">
+        <is>
+          <t>Fresh-Cut Fruit</t>
+        </is>
+      </c>
+      <c r="W148" s="13" t="inlineStr">
+        <is>
+          <t>$3.89 (0.9%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="22" customHeight="1" s="27">
+      <c r="Q149" s="41" t="n"/>
+      <c r="R149" s="38" t="n">
+        <v>27</v>
+      </c>
+      <c r="S149" s="26" t="inlineStr">
+        <is>
+          <t>Canned Beans &amp; Legumes</t>
+        </is>
+      </c>
+      <c r="W149" s="13" t="inlineStr">
+        <is>
+          <t>$3.68 (0.8%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="22" customHeight="1" s="27">
+      <c r="Q150" s="42" t="n"/>
+      <c r="R150" s="38" t="n">
+        <v>28</v>
+      </c>
+      <c r="S150" s="26" t="inlineStr">
+        <is>
+          <t>Dips &amp; Spreads</t>
+        </is>
+      </c>
+      <c r="W150" s="13" t="inlineStr">
+        <is>
+          <t>$3.45 (0.8%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="22" customHeight="1" s="27">
+      <c r="Q151" s="43" t="n"/>
+      <c r="R151" s="38" t="n">
+        <v>29</v>
+      </c>
+      <c r="S151" s="26" t="inlineStr">
+        <is>
+          <t>Jarred Vegetables</t>
+        </is>
+      </c>
+      <c r="W151" s="13" t="inlineStr">
+        <is>
+          <t>$3.29 (0.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="22" customHeight="1" s="27">
+      <c r="Q152" s="44" t="n"/>
+      <c r="R152" s="38" t="n">
+        <v>30</v>
+      </c>
+      <c r="S152" s="26" t="inlineStr">
+        <is>
+          <t>Meat &amp; Seafood</t>
+        </is>
+      </c>
+      <c r="W152" s="13" t="inlineStr">
+        <is>
+          <t>$3.16 (0.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="22" customHeight="1" s="27">
+      <c r="Q153" s="45" t="n"/>
+      <c r="R153" s="38" t="n">
+        <v>31</v>
+      </c>
+      <c r="S153" s="26" t="inlineStr">
+        <is>
+          <t>Pasta</t>
+        </is>
+      </c>
+      <c r="W153" s="13" t="inlineStr">
+        <is>
+          <t>$2.99 (0.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="22" customHeight="1" s="27">
+      <c r="Q154" s="46" t="n"/>
+      <c r="R154" s="38" t="n">
+        <v>32</v>
+      </c>
+      <c r="S154" s="26" t="inlineStr">
+        <is>
+          <t>Salad Dressing</t>
+        </is>
+      </c>
+      <c r="W154" s="13" t="inlineStr">
+        <is>
+          <t>$2.99 (0.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="22" customHeight="1" s="27">
+      <c r="Q155" s="47" t="n"/>
+      <c r="R155" s="38" t="n">
+        <v>33</v>
+      </c>
+      <c r="S155" s="26" t="inlineStr">
+        <is>
+          <t>Crackers</t>
+        </is>
+      </c>
+      <c r="W155" s="13" t="inlineStr">
+        <is>
+          <t>$2.79 (0.6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="22" customHeight="1" s="27">
+      <c r="Q156" s="48" t="n"/>
+      <c r="R156" s="38" t="n">
+        <v>34</v>
+      </c>
+      <c r="S156" s="26" t="inlineStr">
+        <is>
+          <t>Popcorn</t>
+        </is>
+      </c>
+      <c r="W156" s="13" t="inlineStr">
+        <is>
+          <t>$2.39 (0.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="22" customHeight="1" s="27">
+      <c r="Q157" s="49" t="n"/>
+      <c r="R157" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="S157" s="26" t="inlineStr">
+        <is>
+          <t>Croutons</t>
+        </is>
+      </c>
+      <c r="W157" s="13" t="inlineStr">
+        <is>
+          <t>$1.99 (0.4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="22" customHeight="1" s="27">
+      <c r="Q158" s="50" t="n"/>
+      <c r="R158" s="38" t="n">
+        <v>36</v>
+      </c>
+      <c r="S158" s="26" t="inlineStr">
+        <is>
+          <t>Fresh Herbs</t>
+        </is>
+      </c>
+      <c r="W158" s="13" t="inlineStr">
+        <is>
+          <t>$1.84 (0.4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="Q162" s="35" t="inlineStr">
+        <is>
+          <t>Number / Product</t>
+        </is>
+      </c>
+      <c r="Y162" s="35" t="inlineStr">
+        <is>
+          <t>How to Read This Graph</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="Q163" s="36" t="inlineStr"/>
+      <c r="R163" s="36" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="S163" s="36" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="W163" s="36" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="22" customHeight="1" s="27">
+      <c r="Q164" s="37" t="n"/>
+      <c r="R164" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S164" s="26" t="inlineStr">
+        <is>
+          <t>Pampers Swaddlers Fragrance Free Baby Diapers Size 5, 100 Count (Select for More Options) 20 shopped Qty1</t>
+        </is>
+      </c>
+      <c r="W164" s="13" t="inlineStr">
+        <is>
+          <t>$39.77</t>
+        </is>
+      </c>
+      <c r="Y164" s="39" t="inlineStr">
         <is>
           <t>What it represents</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="22" customHeight="1">
-      <c r="Q119" s="23" t="n"/>
-      <c r="R119" s="19" t="n">
+    <row r="165" ht="22" customHeight="1" s="27">
+      <c r="Q165" s="40" t="n"/>
+      <c r="R165" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="S119" s="20" t="inlineStr">
+      <c r="S165" s="26" t="inlineStr">
+        <is>
+          <t>Purina Tidy Cats With Glade Clear Springs Scented, Odor Control, Clumping Multi-Cat Litter 20 shopped Qty2</t>
+        </is>
+      </c>
+      <c r="W165" s="13" t="inlineStr">
+        <is>
+          <t>$23.94</t>
+        </is>
+      </c>
+      <c r="Y165" s="26" t="inlineStr">
+        <is>
+          <t>Ranks the ten individual product identities with the most accumulated spending across all recorded purchases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="22" customHeight="1" s="27">
+      <c r="Q166" s="41" t="n"/>
+      <c r="R166" s="38" t="n">
+        <v>3</v>
+      </c>
+      <c r="S166" s="26" t="inlineStr">
+        <is>
+          <t>Silk Organic Unsweet Soymilk, Half Gallon</t>
+        </is>
+      </c>
+      <c r="W166" s="13" t="inlineStr">
+        <is>
+          <t>$18.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="22" customHeight="1" s="27">
+      <c r="Q167" s="42" t="n"/>
+      <c r="R167" s="38" t="n">
+        <v>4</v>
+      </c>
+      <c r="S167" s="26" t="inlineStr">
+        <is>
+          <t>Driver tip</t>
+        </is>
+      </c>
+      <c r="W167" s="13" t="inlineStr">
+        <is>
+          <t>$16.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="22" customHeight="1" s="27">
+      <c r="Q168" s="43" t="n"/>
+      <c r="R168" s="38" t="n">
+        <v>5</v>
+      </c>
+      <c r="S168" s="26" t="inlineStr">
+        <is>
+          <t>1 Chicken N French Toast</t>
+        </is>
+      </c>
+      <c r="W168" s="13" t="inlineStr">
+        <is>
+          <t>$16.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="22" customHeight="1" s="27">
+      <c r="Q169" s="44" t="n"/>
+      <c r="R169" s="38" t="n">
+        <v>6</v>
+      </c>
+      <c r="S169" s="26" t="inlineStr">
+        <is>
+          <t>1 Frenchy Plate</t>
+        </is>
+      </c>
+      <c r="W169" s="13" t="inlineStr">
+        <is>
+          <t>$14.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="22" customHeight="1" s="27">
+      <c r="Q170" s="45" t="n"/>
+      <c r="R170" s="38" t="n">
+        <v>7</v>
+      </c>
+      <c r="S170" s="26" t="inlineStr">
+        <is>
+          <t>Empire Kosher Ground Turkey</t>
+        </is>
+      </c>
+      <c r="W170" s="13" t="inlineStr">
+        <is>
+          <t>$13.98</t>
+        </is>
+      </c>
+      <c r="Y170" s="39" t="inlineStr">
+        <is>
+          <t>How to read it</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="22" customHeight="1" s="27">
+      <c r="Q171" s="46" t="n"/>
+      <c r="R171" s="38" t="n">
+        <v>8</v>
+      </c>
+      <c r="S171" s="26" t="inlineStr">
+        <is>
+          <t>CeraVe Baby Healing Ointment for Diaper Rash &amp; Cracked Chafed Dry Skin for Baby + Toddler 3 oz</t>
+        </is>
+      </c>
+      <c r="W171" s="13" t="inlineStr">
+        <is>
+          <t>$9.98</t>
+        </is>
+      </c>
+      <c r="Y171" s="26" t="inlineStr">
+        <is>
+          <t>Each product is represented by a numbered colored bar. Use the key to see the product name and its total spending. The longest bar is the largest individual spending driver.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="22" customHeight="1" s="27">
+      <c r="Q172" s="47" t="n"/>
+      <c r="R172" s="38" t="n">
+        <v>9</v>
+      </c>
+      <c r="S172" s="26" t="inlineStr">
+        <is>
+          <t>Chobani 20G Protein Low-Fat Greek Yogurt Drink, Strawberries and Cream 10 fl oz Bottle, 4 Pack</t>
+        </is>
+      </c>
+      <c r="W172" s="13" t="inlineStr">
+        <is>
+          <t>$9.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="22" customHeight="1" s="27">
+      <c r="Q173" s="48" t="n"/>
+      <c r="R173" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="S173" s="26" t="inlineStr">
+        <is>
+          <t>Nestle Toll House Organic Allergen Free Dark Chocolate Regular Baking Chips, Morsels for Baking, 9 oz Bag</t>
+        </is>
+      </c>
+      <c r="W173" s="13" t="inlineStr">
+        <is>
+          <t>$8.37</t>
+        </is>
+      </c>
+    </row>
+    <row r="174"/>
+    <row r="176">
+      <c r="Y176" s="39" t="inlineStr">
+        <is>
+          <t>What it is useful for</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="Y177" s="26" t="inlineStr">
+        <is>
+          <t>Use this to identify specific products that contribute the most to total spending and may be worth price-comparing or watching over time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="182">
+      <c r="Y182" s="39" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="Y183" s="26" t="inlineStr">
+        <is>
+          <t>Product identity prefers Common Name and falls back to Product when Common Name is unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="198">
+      <c r="Q198" s="35" t="inlineStr">
+        <is>
+          <t>Store Numbers + Month Numbers</t>
+        </is>
+      </c>
+      <c r="Y198" s="35" t="inlineStr">
+        <is>
+          <t>How to Read This Graph</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="Q199" s="36" t="inlineStr"/>
+      <c r="R199" s="36" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="S199" s="36" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="W199" s="36" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="22" customHeight="1" s="27">
+      <c r="Q200" s="37" t="n"/>
+      <c r="R200" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S200" s="26" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="W200" s="13" t="inlineStr">
+        <is>
+          <t>$205.01</t>
+        </is>
+      </c>
+      <c r="Y200" s="39" t="inlineStr">
+        <is>
+          <t>What it represents</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="22" customHeight="1" s="27">
+      <c r="Q201" s="40" t="n"/>
+      <c r="R201" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="S201" s="26" t="inlineStr">
+        <is>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="W201" s="13" t="inlineStr">
+        <is>
+          <t>$100.82</t>
+        </is>
+      </c>
+      <c r="Y201" s="26" t="inlineStr">
+        <is>
+          <t>Shows how monthly spending is divided among stores. Each column is one month; each colored section inside the column represents one store.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="22" customHeight="1" s="27">
+      <c r="Q202" s="41" t="n"/>
+      <c r="R202" s="38" t="n">
+        <v>3</v>
+      </c>
+      <c r="S202" s="26" t="inlineStr">
+        <is>
+          <t>Publix</t>
+        </is>
+      </c>
+      <c r="W202" s="13" t="inlineStr">
+        <is>
+          <t>$60.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="22" customHeight="1" s="27">
+      <c r="Q203" s="42" t="n"/>
+      <c r="R203" s="38" t="n">
+        <v>4</v>
+      </c>
+      <c r="S203" s="26" t="inlineStr">
+        <is>
+          <t>Honey Pineapple</t>
+        </is>
+      </c>
+      <c r="W203" s="13" t="inlineStr">
+        <is>
+          <t>$48.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="22" customHeight="1" s="27">
+      <c r="Q204" s="43" t="n"/>
+      <c r="R204" s="38" t="n">
+        <v>5</v>
+      </c>
+      <c r="S204" s="26" t="inlineStr">
+        <is>
+          <t>Trader Joe's</t>
+        </is>
+      </c>
+      <c r="W204" s="13" t="inlineStr">
+        <is>
+          <t>$30.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="22" customHeight="1" s="27">
+      <c r="Q205" s="51" t="n"/>
+      <c r="R205" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S205" s="26" t="inlineStr">
+        <is>
+          <t>Month August 2026</t>
+        </is>
+      </c>
+      <c r="W205" s="13" t="inlineStr">
+        <is>
+          <t>$444.77</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="Y206" s="39" t="inlineStr">
+        <is>
+          <t>How to read it</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="Y207" s="26" t="inlineStr">
+        <is>
+          <t>Store series use the numbered color key. The x-axis uses month numbers. Match those month numbers to the month rows in the key. The total height of a column is total monthly spending; the colored portions show which stores made up that total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208"/>
+    <row r="209"/>
+    <row r="210"/>
+    <row r="212">
+      <c r="Y212" s="39" t="inlineStr">
+        <is>
+          <t>What it is useful for</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="Y213" s="26" t="inlineStr">
+        <is>
+          <t>Use this to see whether changes in monthly spending are connected to a particular store and how your retailer mix changes over time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214"/>
+    <row r="215"/>
+    <row r="216"/>
+    <row r="218">
+      <c r="Y218" s="39" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="Y219" s="26" t="inlineStr">
+        <is>
+          <t>All stores are retained. There is no catch-all 'Other' store series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220"/>
+    <row r="221"/>
+    <row r="222"/>
+    <row r="234">
+      <c r="Q234" s="35" t="inlineStr">
+        <is>
+          <t>Number / Category</t>
+        </is>
+      </c>
+      <c r="Y234" s="35" t="inlineStr">
+        <is>
+          <t>How to Read This Graph</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="Q235" s="36" t="inlineStr"/>
+      <c r="R235" s="36" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="S235" s="36" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="W235" s="36" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="22" customHeight="1" s="27">
+      <c r="Q236" s="37" t="n"/>
+      <c r="R236" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S236" s="26" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="W236" s="13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y236" s="39" t="inlineStr">
+        <is>
+          <t>What it represents</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="22" customHeight="1" s="27">
+      <c r="Q237" s="40" t="n"/>
+      <c r="R237" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="S237" s="26" t="inlineStr">
+        <is>
+          <t>Fresh Vegetables</t>
+        </is>
+      </c>
+      <c r="W237" s="13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y237" s="26" t="inlineStr">
+        <is>
+          <t>Counts how many valid purchase observations occurred in each category. This measures frequency, not dollars.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="22" customHeight="1" s="27">
+      <c r="Q238" s="41" t="n"/>
+      <c r="R238" s="38" t="n">
+        <v>3</v>
+      </c>
+      <c r="S238" s="26" t="inlineStr">
+        <is>
+          <t>Fresh Fruit</t>
+        </is>
+      </c>
+      <c r="W238" s="13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="22" customHeight="1" s="27">
+      <c r="Q239" s="42" t="n"/>
+      <c r="R239" s="38" t="n">
+        <v>4</v>
+      </c>
+      <c r="S239" s="26" t="inlineStr">
+        <is>
+          <t>Canned Beans &amp; Legumes</t>
+        </is>
+      </c>
+      <c r="W239" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="22" customHeight="1" s="27">
+      <c r="Q240" s="43" t="n"/>
+      <c r="R240" s="38" t="n">
+        <v>5</v>
+      </c>
+      <c r="S240" s="26" t="inlineStr">
+        <is>
+          <t>Dairy</t>
+        </is>
+      </c>
+      <c r="W240" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="22" customHeight="1" s="27">
+      <c r="Q241" s="44" t="n"/>
+      <c r="R241" s="38" t="n">
+        <v>6</v>
+      </c>
+      <c r="S241" s="26" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="W241" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="22" customHeight="1" s="27">
+      <c r="Q242" s="45" t="n"/>
+      <c r="R242" s="38" t="n">
+        <v>7</v>
+      </c>
+      <c r="S242" s="26" t="inlineStr">
+        <is>
+          <t>Baby</t>
+        </is>
+      </c>
+      <c r="W242" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y242" s="39" t="inlineStr">
+        <is>
+          <t>How to read it</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="22" customHeight="1" s="27">
+      <c r="Q243" s="46" t="n"/>
+      <c r="R243" s="38" t="n">
+        <v>8</v>
+      </c>
+      <c r="S243" s="26" t="inlineStr">
+        <is>
+          <t>Plant-Based Milk</t>
+        </is>
+      </c>
+      <c r="W243" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y243" s="26" t="inlineStr">
+        <is>
+          <t>Each category is a numbered colored bar. Match the number and color to the key. A longer bar means the category was purchased more frequently.</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="22" customHeight="1" s="27">
+      <c r="Q244" s="47" t="n"/>
+      <c r="R244" s="38" t="n">
+        <v>9</v>
+      </c>
+      <c r="S244" s="26" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="W244" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="22" customHeight="1" s="27">
+      <c r="Q245" s="48" t="n"/>
+      <c r="R245" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="S245" s="26" t="inlineStr">
         <is>
           <t>Yogurt</t>
         </is>
       </c>
-      <c r="W119" s="21" t="inlineStr">
-        <is>
-          <t>$21.35 (8.9%)</t>
-        </is>
-      </c>
-      <c r="Y119" s="20" t="inlineStr">
-        <is>
-          <t>Shows each category's share of total spending as part of the whole shopping budget.</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="22" customHeight="1">
-      <c r="Q120" s="24" t="n"/>
-      <c r="R120" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="S120" s="20" t="inlineStr">
-        <is>
-          <t>Fresh Vegetables</t>
-        </is>
-      </c>
-      <c r="W120" s="21" t="inlineStr">
-        <is>
-          <t>$21.28 (8.9%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="22" customHeight="1">
-      <c r="Q121" s="25" t="n"/>
-      <c r="R121" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="S121" s="20" t="inlineStr">
-        <is>
-          <t>Plant-Based Milk</t>
-        </is>
-      </c>
-      <c r="W121" s="21" t="inlineStr">
-        <is>
-          <t>$18.57 (7.7%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="22" customHeight="1">
-      <c r="Q122" s="26" t="n"/>
-      <c r="R122" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="S122" s="20" t="inlineStr">
-        <is>
-          <t>Fresh Fruit</t>
-        </is>
-      </c>
-      <c r="W122" s="21" t="inlineStr">
-        <is>
-          <t>$15.97 (6.7%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="22" customHeight="1">
-      <c r="Q123" s="27" t="n"/>
-      <c r="R123" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="S123" s="20" t="inlineStr">
+      <c r="W245" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="22" customHeight="1" s="27">
+      <c r="Q246" s="49" t="n"/>
+      <c r="R246" s="38" t="n">
+        <v>11</v>
+      </c>
+      <c r="S246" s="26" t="inlineStr">
+        <is>
+          <t>Bread</t>
+        </is>
+      </c>
+      <c r="W246" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="22" customHeight="1" s="27">
+      <c r="Q247" s="50" t="n"/>
+      <c r="R247" s="38" t="n">
+        <v>12</v>
+      </c>
+      <c r="S247" s="26" t="inlineStr">
+        <is>
+          <t>Fees &amp; Charges</t>
+        </is>
+      </c>
+      <c r="W247" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="22" customHeight="1" s="27">
+      <c r="Q248" s="37" t="n"/>
+      <c r="R248" s="38" t="n">
+        <v>13</v>
+      </c>
+      <c r="S248" s="26" t="inlineStr">
+        <is>
+          <t>Fresh Herbs</t>
+        </is>
+      </c>
+      <c r="W248" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y248" s="39" t="inlineStr">
+        <is>
+          <t>What it is useful for</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="22" customHeight="1" s="27">
+      <c r="Q249" s="40" t="n"/>
+      <c r="R249" s="38" t="n">
+        <v>14</v>
+      </c>
+      <c r="S249" s="26" t="inlineStr">
         <is>
           <t>Fresh Poultry</t>
         </is>
       </c>
-      <c r="W123" s="21" t="inlineStr">
-        <is>
-          <t>$13.98 (5.8%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="22" customHeight="1">
-      <c r="Q124" s="28" t="n"/>
-      <c r="R124" s="19" t="n">
-        <v>7</v>
-      </c>
-      <c r="S124" s="20" t="inlineStr">
+      <c r="W249" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y249" s="26" t="inlineStr">
+        <is>
+          <t>Use this alongside Spending by Category to distinguish frequent routine purchases from categories that are bought less often but cost more.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="22" customHeight="1" s="27">
+      <c r="Q250" s="41" t="n"/>
+      <c r="R250" s="38" t="n">
+        <v>15</v>
+      </c>
+      <c r="S250" s="26" t="inlineStr">
+        <is>
+          <t>Frozen Breakfast</t>
+        </is>
+      </c>
+      <c r="W250" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="22" customHeight="1" s="27">
+      <c r="Q251" s="42" t="n"/>
+      <c r="R251" s="38" t="n">
+        <v>16</v>
+      </c>
+      <c r="S251" s="26" t="inlineStr">
         <is>
           <t>Prepared Coffee</t>
         </is>
       </c>
-      <c r="W124" s="21" t="inlineStr">
-        <is>
-          <t>$11.00 (4.6%)</t>
-        </is>
-      </c>
-      <c r="Y124" s="22" t="inlineStr">
-        <is>
-          <t>How to read it</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="22" customHeight="1">
-      <c r="Q125" s="29" t="n"/>
-      <c r="R125" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="S125" s="20" t="inlineStr">
-        <is>
-          <t>Bread</t>
-        </is>
-      </c>
-      <c r="W125" s="21" t="inlineStr">
-        <is>
-          <t>$10.16 (4.2%)</t>
-        </is>
-      </c>
-      <c r="Y125" s="20" t="inlineStr">
-        <is>
-          <t>The doughnut itself displays only numeric category codes. Match each number/color to the key for the category name, dollar amount, and percentage of total spending.</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="22" customHeight="1">
-      <c r="Q126" s="30" t="n"/>
-      <c r="R126" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="S126" s="20" t="inlineStr">
+      <c r="W251" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="22" customHeight="1" s="27">
+      <c r="Q252" s="43" t="n"/>
+      <c r="R252" s="38" t="n">
+        <v>17</v>
+      </c>
+      <c r="S252" s="26" t="inlineStr">
+        <is>
+          <t>Prepared Meals</t>
+        </is>
+      </c>
+      <c r="W252" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="22" customHeight="1" s="27">
+      <c r="Q253" s="44" t="n"/>
+      <c r="R253" s="38" t="n">
+        <v>18</v>
+      </c>
+      <c r="S253" s="26" t="inlineStr">
+        <is>
+          <t>Snack Bars</t>
+        </is>
+      </c>
+      <c r="W253" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="22" customHeight="1" s="27">
+      <c r="Q254" s="45" t="n"/>
+      <c r="R254" s="38" t="n">
+        <v>19</v>
+      </c>
+      <c r="S254" s="26" t="inlineStr">
+        <is>
+          <t>Specialty Cheese</t>
+        </is>
+      </c>
+      <c r="W254" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="22" customHeight="1" s="27">
+      <c r="Q255" s="46" t="n"/>
+      <c r="R255" s="38" t="n">
+        <v>20</v>
+      </c>
+      <c r="S255" s="26" t="inlineStr">
+        <is>
+          <t>Crackers</t>
+        </is>
+      </c>
+      <c r="W255" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="22" customHeight="1" s="27">
+      <c r="Q256" s="47" t="n"/>
+      <c r="R256" s="38" t="n">
+        <v>21</v>
+      </c>
+      <c r="S256" s="26" t="inlineStr">
+        <is>
+          <t>Cream &amp; Half-and-Half</t>
+        </is>
+      </c>
+      <c r="W256" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="22" customHeight="1" s="27">
+      <c r="Q257" s="48" t="n"/>
+      <c r="R257" s="38" t="n">
+        <v>22</v>
+      </c>
+      <c r="S257" s="26" t="inlineStr">
+        <is>
+          <t>Croutons</t>
+        </is>
+      </c>
+      <c r="W257" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="22" customHeight="1" s="27">
+      <c r="Q258" s="49" t="n"/>
+      <c r="R258" s="38" t="n">
+        <v>23</v>
+      </c>
+      <c r="S258" s="26" t="inlineStr">
+        <is>
+          <t>Dips &amp; Spreads</t>
+        </is>
+      </c>
+      <c r="W258" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="22" customHeight="1" s="27">
+      <c r="Q259" s="50" t="n"/>
+      <c r="R259" s="38" t="n">
+        <v>24</v>
+      </c>
+      <c r="S259" s="26" t="inlineStr">
+        <is>
+          <t>Disposable Tableware</t>
+        </is>
+      </c>
+      <c r="W259" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="22" customHeight="1" s="27">
+      <c r="Q260" s="37" t="n"/>
+      <c r="R260" s="38" t="n">
+        <v>25</v>
+      </c>
+      <c r="S260" s="26" t="inlineStr">
+        <is>
+          <t>Fresh-Cut Fruit</t>
+        </is>
+      </c>
+      <c r="W260" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="22" customHeight="1" s="27">
+      <c r="Q261" s="40" t="n"/>
+      <c r="R261" s="38" t="n">
+        <v>26</v>
+      </c>
+      <c r="S261" s="26" t="inlineStr">
         <is>
           <t>Frozen Pizza</t>
         </is>
       </c>
-      <c r="W126" s="21" t="inlineStr">
-        <is>
-          <t>$8.29 (3.5%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="22" customHeight="1">
-      <c r="Q127" s="31" t="n"/>
-      <c r="R127" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="S127" s="20" t="inlineStr">
-        <is>
-          <t>Frozen Breakfast</t>
-        </is>
-      </c>
-      <c r="W127" s="21" t="inlineStr">
-        <is>
-          <t>$7.78 (3.2%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="22" customHeight="1">
-      <c r="Q128" s="32" t="n"/>
-      <c r="R128" s="19" t="n">
-        <v>11</v>
-      </c>
-      <c r="S128" s="20" t="inlineStr">
+      <c r="W261" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="22" customHeight="1" s="27">
+      <c r="Q262" s="41" t="n"/>
+      <c r="R262" s="38" t="n">
+        <v>27</v>
+      </c>
+      <c r="S262" s="26" t="inlineStr">
+        <is>
+          <t>Jarred Vegetables</t>
+        </is>
+      </c>
+      <c r="W262" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="22" customHeight="1" s="27">
+      <c r="Q263" s="42" t="n"/>
+      <c r="R263" s="38" t="n">
+        <v>28</v>
+      </c>
+      <c r="S263" s="26" t="inlineStr">
+        <is>
+          <t>Meat &amp; Seafood</t>
+        </is>
+      </c>
+      <c r="W263" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="22" customHeight="1" s="27">
+      <c r="Q264" s="43" t="n"/>
+      <c r="R264" s="38" t="n">
+        <v>29</v>
+      </c>
+      <c r="S264" s="26" t="inlineStr">
+        <is>
+          <t>Muffins &amp; Pastries</t>
+        </is>
+      </c>
+      <c r="W264" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="22" customHeight="1" s="27">
+      <c r="Q265" s="44" t="n"/>
+      <c r="R265" s="38" t="n">
+        <v>30</v>
+      </c>
+      <c r="S265" s="26" t="inlineStr">
+        <is>
+          <t>Pasta</t>
+        </is>
+      </c>
+      <c r="W265" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="22" customHeight="1" s="27">
+      <c r="Q266" s="45" t="n"/>
+      <c r="R266" s="38" t="n">
+        <v>31</v>
+      </c>
+      <c r="S266" s="26" t="inlineStr">
+        <is>
+          <t>Pet</t>
+        </is>
+      </c>
+      <c r="W266" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="22" customHeight="1" s="27">
+      <c r="Q267" s="46" t="n"/>
+      <c r="R267" s="38" t="n">
+        <v>32</v>
+      </c>
+      <c r="S267" s="26" t="inlineStr">
+        <is>
+          <t>Popcorn</t>
+        </is>
+      </c>
+      <c r="W267" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="22" customHeight="1" s="27">
+      <c r="Q268" s="47" t="n"/>
+      <c r="R268" s="38" t="n">
+        <v>33</v>
+      </c>
+      <c r="S268" s="26" t="inlineStr">
         <is>
           <t>Refrigerated Dough</t>
         </is>
       </c>
-      <c r="W128" s="21" t="inlineStr">
-        <is>
-          <t>$6.99 (2.9%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="22" customHeight="1">
-      <c r="Q129" s="33" t="n"/>
-      <c r="R129" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="S129" s="20" t="inlineStr">
-        <is>
-          <t>Muffins &amp; Pastries</t>
-        </is>
-      </c>
-      <c r="W129" s="21" t="inlineStr">
-        <is>
-          <t>$5.99 (2.5%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="22" customHeight="1">
-      <c r="Q130" s="18" t="n"/>
-      <c r="R130" s="19" t="n">
-        <v>13</v>
-      </c>
-      <c r="S130" s="20" t="inlineStr">
+      <c r="W268" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="22" customHeight="1" s="27">
+      <c r="Q269" s="48" t="n"/>
+      <c r="R269" s="38" t="n">
+        <v>34</v>
+      </c>
+      <c r="S269" s="26" t="inlineStr">
+        <is>
+          <t>Salad Dressing</t>
+        </is>
+      </c>
+      <c r="W269" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="22" customHeight="1" s="27">
+      <c r="Q270" s="49" t="n"/>
+      <c r="R270" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="S270" s="26" t="inlineStr">
         <is>
           <t>Storage &amp; Organization</t>
         </is>
       </c>
-      <c r="W130" s="21" t="inlineStr">
-        <is>
-          <t>$5.99 (2.5%)</t>
-        </is>
-      </c>
-      <c r="Y130" s="22" t="inlineStr">
-        <is>
-          <t>What it is useful for</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="22" customHeight="1">
-      <c r="Q131" s="23" t="n"/>
-      <c r="R131" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="S131" s="20" t="inlineStr">
+      <c r="W270" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="22" customHeight="1" s="27">
+      <c r="Q271" s="50" t="n"/>
+      <c r="R271" s="38" t="n">
+        <v>36</v>
+      </c>
+      <c r="S271" s="26" t="inlineStr">
         <is>
           <t>Writing Supplies</t>
         </is>
       </c>
-      <c r="W131" s="21" t="inlineStr">
-        <is>
-          <t>$5.99 (2.5%)</t>
-        </is>
-      </c>
-      <c r="Y131" s="20" t="inlineStr">
-        <is>
-          <t>Use this for a fast visual picture of the household spending mix—especially which categories take the largest portion of the budget.</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="22" customHeight="1">
-      <c r="Q132" s="24" t="n"/>
-      <c r="R132" s="19" t="n">
-        <v>15</v>
-      </c>
-      <c r="S132" s="20" t="inlineStr">
-        <is>
-          <t>Fees &amp; Charges</t>
-        </is>
-      </c>
-      <c r="W132" s="21" t="inlineStr">
-        <is>
-          <t>$5.92 (2.5%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="22" customHeight="1">
-      <c r="Q133" s="25" t="n"/>
-      <c r="R133" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="S133" s="20" t="inlineStr">
-        <is>
-          <t>Cream &amp; Half-and-Half</t>
-        </is>
-      </c>
-      <c r="W133" s="21" t="inlineStr">
-        <is>
-          <t>$5.89 (2.5%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="22" customHeight="1">
-      <c r="Q134" s="26" t="n"/>
-      <c r="R134" s="19" t="n">
-        <v>17</v>
-      </c>
-      <c r="S134" s="20" t="inlineStr">
-        <is>
-          <t>Disposable Tableware</t>
-        </is>
-      </c>
-      <c r="W134" s="21" t="inlineStr">
-        <is>
-          <t>$5.25 (2.2%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="22" customHeight="1">
-      <c r="Q135" s="27" t="n"/>
-      <c r="R135" s="19" t="n">
-        <v>18</v>
-      </c>
-      <c r="S135" s="20" t="inlineStr">
-        <is>
-          <t>Specialty Cheese</t>
-        </is>
-      </c>
-      <c r="W135" s="21" t="inlineStr">
-        <is>
-          <t>$4.88 (2.0%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="22" customHeight="1">
-      <c r="Q136" s="28" t="n"/>
-      <c r="R136" s="19" t="n">
-        <v>19</v>
-      </c>
-      <c r="S136" s="20" t="inlineStr">
-        <is>
-          <t>Snack Bars</t>
-        </is>
-      </c>
-      <c r="W136" s="21" t="inlineStr">
-        <is>
-          <t>$3.98 (1.7%)</t>
-        </is>
-      </c>
-      <c r="Y136" s="22" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="22" customHeight="1">
-      <c r="Q137" s="29" t="n"/>
-      <c r="R137" s="19" t="n">
-        <v>20</v>
-      </c>
-      <c r="S137" s="20" t="inlineStr">
-        <is>
-          <t>Fresh-Cut Fruit</t>
-        </is>
-      </c>
-      <c r="W137" s="21" t="inlineStr">
-        <is>
-          <t>$3.89 (1.6%)</t>
-        </is>
-      </c>
-      <c r="Y137" s="20" t="inlineStr">
-        <is>
-          <t>Unlike the older dashboard, this graph does not create a large 'Other' slice. Every category receives its own numbered segment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="22" customHeight="1">
-      <c r="Q138" s="30" t="n"/>
-      <c r="R138" s="19" t="n">
-        <v>21</v>
-      </c>
-      <c r="S138" s="20" t="inlineStr">
-        <is>
-          <t>Canned Beans &amp; Legumes</t>
-        </is>
-      </c>
-      <c r="W138" s="21" t="inlineStr">
-        <is>
-          <t>$3.68 (1.5%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="22" customHeight="1">
-      <c r="Q139" s="31" t="n"/>
-      <c r="R139" s="19" t="n">
-        <v>22</v>
-      </c>
-      <c r="S139" s="20" t="inlineStr">
-        <is>
-          <t>Dips &amp; Spreads</t>
-        </is>
-      </c>
-      <c r="W139" s="21" t="inlineStr">
-        <is>
-          <t>$3.45 (1.4%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="22" customHeight="1">
-      <c r="Q140" s="32" t="n"/>
-      <c r="R140" s="19" t="n">
-        <v>23</v>
-      </c>
-      <c r="S140" s="20" t="inlineStr">
-        <is>
-          <t>Jarred Vegetables</t>
-        </is>
-      </c>
-      <c r="W140" s="21" t="inlineStr">
-        <is>
-          <t>$3.29 (1.4%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="22" customHeight="1">
-      <c r="Q141" s="33" t="n"/>
-      <c r="R141" s="19" t="n">
-        <v>24</v>
-      </c>
-      <c r="S141" s="20" t="inlineStr">
-        <is>
-          <t>Pasta</t>
-        </is>
-      </c>
-      <c r="W141" s="21" t="inlineStr">
-        <is>
-          <t>$2.99 (1.2%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="22" customHeight="1">
-      <c r="Q142" s="18" t="n"/>
-      <c r="R142" s="19" t="n">
-        <v>25</v>
-      </c>
-      <c r="S142" s="20" t="inlineStr">
-        <is>
-          <t>Salad Dressing</t>
-        </is>
-      </c>
-      <c r="W142" s="21" t="inlineStr">
-        <is>
-          <t>$2.99 (1.2%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="22" customHeight="1">
-      <c r="Q143" s="23" t="n"/>
-      <c r="R143" s="19" t="n">
-        <v>26</v>
-      </c>
-      <c r="S143" s="20" t="inlineStr">
-        <is>
-          <t>Crackers</t>
-        </is>
-      </c>
-      <c r="W143" s="21" t="inlineStr">
-        <is>
-          <t>$2.79 (1.2%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="22" customHeight="1">
-      <c r="Q144" s="24" t="n"/>
-      <c r="R144" s="19" t="n">
-        <v>27</v>
-      </c>
-      <c r="S144" s="20" t="inlineStr">
-        <is>
-          <t>Popcorn</t>
-        </is>
-      </c>
-      <c r="W144" s="21" t="inlineStr">
-        <is>
-          <t>$2.39 (1.0%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="22" customHeight="1">
-      <c r="Q145" s="25" t="n"/>
-      <c r="R145" s="19" t="n">
-        <v>28</v>
-      </c>
-      <c r="S145" s="20" t="inlineStr">
-        <is>
-          <t>Croutons</t>
-        </is>
-      </c>
-      <c r="W145" s="21" t="inlineStr">
-        <is>
-          <t>$1.99 (0.8%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="22" customHeight="1">
-      <c r="Q146" s="26" t="n"/>
-      <c r="R146" s="19" t="n">
-        <v>29</v>
-      </c>
-      <c r="S146" s="20" t="inlineStr">
-        <is>
-          <t>Fresh Herbs</t>
-        </is>
-      </c>
-      <c r="W146" s="21" t="inlineStr">
-        <is>
-          <t>$1.84 (0.8%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="Q152" s="16" t="inlineStr">
-        <is>
-          <t>Number / Product</t>
-        </is>
-      </c>
-      <c r="Y152" s="16" t="inlineStr">
-        <is>
-          <t>How to Read This Graph</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="Q153" s="17" t="inlineStr"/>
-      <c r="R153" s="17" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="S153" s="17" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="W153" s="17" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="22" customHeight="1">
-      <c r="Q154" s="18" t="n"/>
-      <c r="R154" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S154" s="20" t="inlineStr">
-        <is>
-          <t>Silk Organic Unsweet Soymilk, Half Gallon</t>
-        </is>
-      </c>
-      <c r="W154" s="21" t="inlineStr">
-        <is>
-          <t>$18.57</t>
-        </is>
-      </c>
-      <c r="Y154" s="22" t="inlineStr">
-        <is>
-          <t>What it represents</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="22" customHeight="1">
-      <c r="Q155" s="23" t="n"/>
-      <c r="R155" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="S155" s="20" t="inlineStr">
-        <is>
-          <t>1 Chicken N French Toast</t>
-        </is>
-      </c>
-      <c r="W155" s="21" t="inlineStr">
-        <is>
-          <t>$16.30</t>
-        </is>
-      </c>
-      <c r="Y155" s="20" t="inlineStr">
-        <is>
-          <t>Ranks the ten individual product identities with the most accumulated spending across all recorded purchases.</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="22" customHeight="1">
-      <c r="Q156" s="24" t="n"/>
-      <c r="R156" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="S156" s="20" t="inlineStr">
-        <is>
-          <t>1 Frenchy Plate</t>
-        </is>
-      </c>
-      <c r="W156" s="21" t="inlineStr">
-        <is>
-          <t>$14.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="22" customHeight="1">
-      <c r="Q157" s="25" t="n"/>
-      <c r="R157" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="S157" s="20" t="inlineStr">
-        <is>
-          <t>Empire Kosher Ground Turkey</t>
-        </is>
-      </c>
-      <c r="W157" s="21" t="inlineStr">
-        <is>
-          <t>$13.98</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="22" customHeight="1">
-      <c r="Q158" s="26" t="n"/>
-      <c r="R158" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="S158" s="20" t="inlineStr">
-        <is>
-          <t>Cauliflower Crust Pizza</t>
-        </is>
-      </c>
-      <c r="W158" s="21" t="inlineStr">
-        <is>
-          <t>$8.29</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="22" customHeight="1">
-      <c r="Q159" s="27" t="n"/>
-      <c r="R159" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="S159" s="20" t="inlineStr">
-        <is>
-          <t>Stonyfield Organic YoBaby Yogurt Pouch, Banana</t>
-        </is>
-      </c>
-      <c r="W159" s="21" t="inlineStr">
-        <is>
-          <t>$7.85</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="22" customHeight="1">
-      <c r="Q160" s="28" t="n"/>
-      <c r="R160" s="19" t="n">
-        <v>7</v>
-      </c>
-      <c r="S160" s="20" t="inlineStr">
-        <is>
-          <t>Stonyfield Organic YoBaby Yogurt Pouch, Peach</t>
-        </is>
-      </c>
-      <c r="W160" s="21" t="inlineStr">
-        <is>
-          <t>$7.85</t>
-        </is>
-      </c>
-      <c r="Y160" s="22" t="inlineStr">
-        <is>
-          <t>How to read it</t>
-        </is>
-      </c>
-    </row>
-    <row r="161" ht="22" customHeight="1">
-      <c r="Q161" s="29" t="n"/>
-      <c r="R161" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="S161" s="20" t="inlineStr">
-        <is>
-          <t>Van's Gluten Free Blueberry Waffles</t>
-        </is>
-      </c>
-      <c r="W161" s="21" t="inlineStr">
-        <is>
-          <t>$7.78</t>
-        </is>
-      </c>
-      <c r="Y161" s="20" t="inlineStr">
-        <is>
-          <t>Each product is represented by a numbered colored bar. Use the key to see the product name and its total spending. The longest bar is the largest individual spending driver.</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="22" customHeight="1">
-      <c r="Q162" s="30" t="n"/>
-      <c r="R162" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="S162" s="20" t="inlineStr">
-        <is>
-          <t>Sweet Loren's Gluten Free Brownie Cookie Dough</t>
-        </is>
-      </c>
-      <c r="W162" s="21" t="inlineStr">
-        <is>
-          <t>$6.99</t>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="22" customHeight="1">
-      <c r="Q163" s="31" t="n"/>
-      <c r="R163" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="S163" s="20" t="inlineStr">
-        <is>
-          <t>Gluten-Free Wide Pan Bread</t>
-        </is>
-      </c>
-      <c r="W163" s="21" t="inlineStr">
-        <is>
-          <t>$6.79</t>
-        </is>
-      </c>
-    </row>
-    <row r="164"/>
-    <row r="166">
-      <c r="Y166" s="22" t="inlineStr">
-        <is>
-          <t>What it is useful for</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="Y167" s="20" t="inlineStr">
-        <is>
-          <t>Use this to identify specific products that contribute the most to total spending and may be worth price-comparing or watching over time.</t>
-        </is>
-      </c>
-    </row>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="172">
-      <c r="Y172" s="22" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="Y173" s="20" t="inlineStr">
-        <is>
-          <t>Product identity prefers Common Name and falls back to Product when Common Name is unavailable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="188">
-      <c r="Q188" s="16" t="inlineStr">
-        <is>
-          <t>Store Numbers + Month Numbers</t>
-        </is>
-      </c>
-      <c r="Y188" s="16" t="inlineStr">
-        <is>
-          <t>How to Read This Graph</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="Q189" s="17" t="inlineStr"/>
-      <c r="R189" s="17" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="S189" s="17" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="W189" s="17" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="190" ht="22" customHeight="1">
-      <c r="Q190" s="18" t="n"/>
-      <c r="R190" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S190" s="20" t="inlineStr">
-        <is>
-          <t>Aldi</t>
-        </is>
-      </c>
-      <c r="W190" s="21" t="inlineStr">
-        <is>
-          <t>$100.82</t>
-        </is>
-      </c>
-      <c r="Y190" s="22" t="inlineStr">
-        <is>
-          <t>What it represents</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="22" customHeight="1">
-      <c r="Q191" s="23" t="n"/>
-      <c r="R191" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="S191" s="20" t="inlineStr">
-        <is>
-          <t>Publix</t>
-        </is>
-      </c>
-      <c r="W191" s="21" t="inlineStr">
-        <is>
-          <t>$60.58</t>
-        </is>
-      </c>
-      <c r="Y191" s="20" t="inlineStr">
-        <is>
-          <t>Shows how monthly spending is divided among stores. Each column is one month; each colored section inside the column represents one store.</t>
-        </is>
-      </c>
-    </row>
-    <row r="192" ht="22" customHeight="1">
-      <c r="Q192" s="24" t="n"/>
-      <c r="R192" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="S192" s="20" t="inlineStr">
-        <is>
-          <t>Honey Pineapple</t>
-        </is>
-      </c>
-      <c r="W192" s="21" t="inlineStr">
-        <is>
-          <t>$48.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="22" customHeight="1">
-      <c r="Q193" s="25" t="n"/>
-      <c r="R193" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="S193" s="20" t="inlineStr">
-        <is>
-          <t>Trader Joe's</t>
-        </is>
-      </c>
-      <c r="W193" s="21" t="inlineStr">
-        <is>
-          <t>$30.24</t>
-        </is>
-      </c>
-    </row>
-    <row r="194" ht="22" customHeight="1">
-      <c r="Q194" s="34" t="n"/>
-      <c r="R194" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S194" s="20" t="inlineStr">
-        <is>
-          <t>Month August 2026</t>
-        </is>
-      </c>
-      <c r="W194" s="21" t="inlineStr">
-        <is>
-          <t>$239.76</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="Y196" s="22" t="inlineStr">
-        <is>
-          <t>How to read it</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="Y197" s="20" t="inlineStr">
-        <is>
-          <t>Store series use the numbered color key. The x-axis uses month numbers. Match those month numbers to the month rows in the key. The total height of a column is total monthly spending; the colored portions show which stores made up that total.</t>
-        </is>
-      </c>
-    </row>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="202">
-      <c r="Y202" s="22" t="inlineStr">
-        <is>
-          <t>What it is useful for</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="Y203" s="20" t="inlineStr">
-        <is>
-          <t>Use this to see whether changes in monthly spending are connected to a particular store and how your retailer mix changes over time.</t>
-        </is>
-      </c>
-    </row>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="208">
-      <c r="Y208" s="22" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="Y209" s="20" t="inlineStr">
-        <is>
-          <t>All stores are retained. There is no catch-all 'Other' store series.</t>
-        </is>
-      </c>
-    </row>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="224">
-      <c r="Q224" s="16" t="inlineStr">
-        <is>
-          <t>Number / Category</t>
-        </is>
-      </c>
-      <c r="Y224" s="16" t="inlineStr">
-        <is>
-          <t>How to Read This Graph</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="Q225" s="17" t="inlineStr"/>
-      <c r="R225" s="17" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="S225" s="17" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="W225" s="17" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="226" ht="22" customHeight="1">
-      <c r="Q226" s="18" t="n"/>
-      <c r="R226" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S226" s="20" t="inlineStr">
-        <is>
-          <t>Fresh Vegetables</t>
-        </is>
-      </c>
-      <c r="W226" s="21" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y226" s="22" t="inlineStr">
-        <is>
-          <t>What it represents</t>
-        </is>
-      </c>
-    </row>
-    <row r="227" ht="22" customHeight="1">
-      <c r="Q227" s="23" t="n"/>
-      <c r="R227" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="S227" s="20" t="inlineStr">
-        <is>
-          <t>Fresh Fruit</t>
-        </is>
-      </c>
-      <c r="W227" s="21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y227" s="20" t="inlineStr">
-        <is>
-          <t>Counts how many valid purchase observations occurred in each category. This measures frequency, not dollars.</t>
-        </is>
-      </c>
-    </row>
-    <row r="228" ht="22" customHeight="1">
-      <c r="Q228" s="24" t="n"/>
-      <c r="R228" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="S228" s="20" t="inlineStr">
-        <is>
-          <t>Canned Beans &amp; Legumes</t>
-        </is>
-      </c>
-      <c r="W228" s="21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="229" ht="22" customHeight="1">
-      <c r="Q229" s="25" t="n"/>
-      <c r="R229" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="S229" s="20" t="inlineStr">
-        <is>
-          <t>Plant-Based Milk</t>
-        </is>
-      </c>
-      <c r="W229" s="21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="230" ht="22" customHeight="1">
-      <c r="Q230" s="26" t="n"/>
-      <c r="R230" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="S230" s="20" t="inlineStr">
-        <is>
-          <t>Yogurt</t>
-        </is>
-      </c>
-      <c r="W230" s="21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="231" ht="22" customHeight="1">
-      <c r="Q231" s="27" t="n"/>
-      <c r="R231" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="S231" s="20" t="inlineStr">
-        <is>
-          <t>Bread</t>
-        </is>
-      </c>
-      <c r="W231" s="21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="232" ht="22" customHeight="1">
-      <c r="Q232" s="28" t="n"/>
-      <c r="R232" s="19" t="n">
-        <v>7</v>
-      </c>
-      <c r="S232" s="20" t="inlineStr">
-        <is>
-          <t>Fees &amp; Charges</t>
-        </is>
-      </c>
-      <c r="W232" s="21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y232" s="22" t="inlineStr">
-        <is>
-          <t>How to read it</t>
-        </is>
-      </c>
-    </row>
-    <row r="233" ht="22" customHeight="1">
-      <c r="Q233" s="29" t="n"/>
-      <c r="R233" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="S233" s="20" t="inlineStr">
-        <is>
-          <t>Fresh Herbs</t>
-        </is>
-      </c>
-      <c r="W233" s="21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y233" s="20" t="inlineStr">
-        <is>
-          <t>Each category is a numbered colored bar. Match the number and color to the key. A longer bar means the category was purchased more frequently.</t>
-        </is>
-      </c>
-    </row>
-    <row r="234" ht="22" customHeight="1">
-      <c r="Q234" s="30" t="n"/>
-      <c r="R234" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="S234" s="20" t="inlineStr">
-        <is>
-          <t>Fresh Poultry</t>
-        </is>
-      </c>
-      <c r="W234" s="21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="235" ht="22" customHeight="1">
-      <c r="Q235" s="31" t="n"/>
-      <c r="R235" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="S235" s="20" t="inlineStr">
-        <is>
-          <t>Frozen Breakfast</t>
-        </is>
-      </c>
-      <c r="W235" s="21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="236" ht="22" customHeight="1">
-      <c r="Q236" s="32" t="n"/>
-      <c r="R236" s="19" t="n">
-        <v>11</v>
-      </c>
-      <c r="S236" s="20" t="inlineStr">
-        <is>
-          <t>Prepared Coffee</t>
-        </is>
-      </c>
-      <c r="W236" s="21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="237" ht="22" customHeight="1">
-      <c r="Q237" s="33" t="n"/>
-      <c r="R237" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="S237" s="20" t="inlineStr">
-        <is>
-          <t>Prepared Meals</t>
-        </is>
-      </c>
-      <c r="W237" s="21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="238" ht="22" customHeight="1">
-      <c r="Q238" s="18" t="n"/>
-      <c r="R238" s="19" t="n">
-        <v>13</v>
-      </c>
-      <c r="S238" s="20" t="inlineStr">
-        <is>
-          <t>Snack Bars</t>
-        </is>
-      </c>
-      <c r="W238" s="21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y238" s="22" t="inlineStr">
-        <is>
-          <t>What it is useful for</t>
-        </is>
-      </c>
-    </row>
-    <row r="239" ht="22" customHeight="1">
-      <c r="Q239" s="23" t="n"/>
-      <c r="R239" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="S239" s="20" t="inlineStr">
-        <is>
-          <t>Specialty Cheese</t>
-        </is>
-      </c>
-      <c r="W239" s="21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y239" s="20" t="inlineStr">
-        <is>
-          <t>Use this alongside Spending by Category to distinguish frequent routine purchases from categories that are bought less often but cost more.</t>
-        </is>
-      </c>
-    </row>
-    <row r="240" ht="22" customHeight="1">
-      <c r="Q240" s="24" t="n"/>
-      <c r="R240" s="19" t="n">
-        <v>15</v>
-      </c>
-      <c r="S240" s="20" t="inlineStr">
-        <is>
-          <t>Crackers</t>
-        </is>
-      </c>
-      <c r="W240" s="21" t="inlineStr">
+      <c r="W271" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="241" ht="22" customHeight="1">
-      <c r="Q241" s="25" t="n"/>
-      <c r="R241" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="S241" s="20" t="inlineStr">
-        <is>
-          <t>Cream &amp; Half-and-Half</t>
-        </is>
-      </c>
-      <c r="W241" s="21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="242" ht="22" customHeight="1">
-      <c r="Q242" s="26" t="n"/>
-      <c r="R242" s="19" t="n">
-        <v>17</v>
-      </c>
-      <c r="S242" s="20" t="inlineStr">
-        <is>
-          <t>Croutons</t>
-        </is>
-      </c>
-      <c r="W242" s="21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="243" ht="22" customHeight="1">
-      <c r="Q243" s="27" t="n"/>
-      <c r="R243" s="19" t="n">
-        <v>18</v>
-      </c>
-      <c r="S243" s="20" t="inlineStr">
-        <is>
-          <t>Dips &amp; Spreads</t>
-        </is>
-      </c>
-      <c r="W243" s="21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="244" ht="22" customHeight="1">
-      <c r="Q244" s="28" t="n"/>
-      <c r="R244" s="19" t="n">
-        <v>19</v>
-      </c>
-      <c r="S244" s="20" t="inlineStr">
-        <is>
-          <t>Disposable Tableware</t>
-        </is>
-      </c>
-      <c r="W244" s="21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="245" ht="22" customHeight="1">
-      <c r="Q245" s="29" t="n"/>
-      <c r="R245" s="19" t="n">
-        <v>20</v>
-      </c>
-      <c r="S245" s="20" t="inlineStr">
-        <is>
-          <t>Fresh-Cut Fruit</t>
-        </is>
-      </c>
-      <c r="W245" s="21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="246" ht="22" customHeight="1">
-      <c r="Q246" s="30" t="n"/>
-      <c r="R246" s="19" t="n">
-        <v>21</v>
-      </c>
-      <c r="S246" s="20" t="inlineStr">
-        <is>
-          <t>Frozen Pizza</t>
-        </is>
-      </c>
-      <c r="W246" s="21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="247" ht="22" customHeight="1">
-      <c r="Q247" s="31" t="n"/>
-      <c r="R247" s="19" t="n">
-        <v>22</v>
-      </c>
-      <c r="S247" s="20" t="inlineStr">
-        <is>
-          <t>Jarred Vegetables</t>
-        </is>
-      </c>
-      <c r="W247" s="21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="248" ht="22" customHeight="1">
-      <c r="Q248" s="32" t="n"/>
-      <c r="R248" s="19" t="n">
-        <v>23</v>
-      </c>
-      <c r="S248" s="20" t="inlineStr">
-        <is>
-          <t>Muffins &amp; Pastries</t>
-        </is>
-      </c>
-      <c r="W248" s="21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="249" ht="22" customHeight="1">
-      <c r="Q249" s="33" t="n"/>
-      <c r="R249" s="19" t="n">
-        <v>24</v>
-      </c>
-      <c r="S249" s="20" t="inlineStr">
-        <is>
-          <t>Pasta</t>
-        </is>
-      </c>
-      <c r="W249" s="21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="250" ht="22" customHeight="1">
-      <c r="Q250" s="18" t="n"/>
-      <c r="R250" s="19" t="n">
-        <v>25</v>
-      </c>
-      <c r="S250" s="20" t="inlineStr">
-        <is>
-          <t>Popcorn</t>
-        </is>
-      </c>
-      <c r="W250" s="21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="251" ht="22" customHeight="1">
-      <c r="Q251" s="23" t="n"/>
-      <c r="R251" s="19" t="n">
-        <v>26</v>
-      </c>
-      <c r="S251" s="20" t="inlineStr">
-        <is>
-          <t>Refrigerated Dough</t>
-        </is>
-      </c>
-      <c r="W251" s="21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="252" ht="22" customHeight="1">
-      <c r="Q252" s="24" t="n"/>
-      <c r="R252" s="19" t="n">
-        <v>27</v>
-      </c>
-      <c r="S252" s="20" t="inlineStr">
-        <is>
-          <t>Salad Dressing</t>
-        </is>
-      </c>
-      <c r="W252" s="21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="253" ht="22" customHeight="1">
-      <c r="Q253" s="25" t="n"/>
-      <c r="R253" s="19" t="n">
-        <v>28</v>
-      </c>
-      <c r="S253" s="20" t="inlineStr">
-        <is>
-          <t>Storage &amp; Organization</t>
-        </is>
-      </c>
-      <c r="W253" s="21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="254" ht="22" customHeight="1">
-      <c r="Q254" s="26" t="n"/>
-      <c r="R254" s="19" t="n">
-        <v>29</v>
-      </c>
-      <c r="S254" s="20" t="inlineStr">
-        <is>
-          <t>Writing Supplies</t>
-        </is>
-      </c>
-      <c r="W254" s="21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="174">
+  <mergeCells count="197">
     <mergeCell ref="S136:V136"/>
-    <mergeCell ref="S118:V118"/>
-    <mergeCell ref="Y82:AG82"/>
+    <mergeCell ref="S263:V263"/>
     <mergeCell ref="S158:V158"/>
-    <mergeCell ref="Y233:AG236"/>
+    <mergeCell ref="Y129:AG129"/>
     <mergeCell ref="Y10:AG10"/>
+    <mergeCell ref="Y123:AG123"/>
+    <mergeCell ref="S265:V265"/>
+    <mergeCell ref="S147:V147"/>
     <mergeCell ref="Y16:AG16"/>
+    <mergeCell ref="S79:V79"/>
     <mergeCell ref="S135:V135"/>
-    <mergeCell ref="S193:V193"/>
+    <mergeCell ref="S150:V150"/>
+    <mergeCell ref="S255:V255"/>
     <mergeCell ref="Y52:AG52"/>
     <mergeCell ref="S144:V144"/>
-    <mergeCell ref="S159:V159"/>
+    <mergeCell ref="S202:V202"/>
+    <mergeCell ref="S153:V153"/>
     <mergeCell ref="S242:V242"/>
+    <mergeCell ref="Y242:AG242"/>
+    <mergeCell ref="Y106:AG109"/>
     <mergeCell ref="S125:V125"/>
     <mergeCell ref="S72:V72"/>
-    <mergeCell ref="Q116:W116"/>
     <mergeCell ref="S134:V134"/>
-    <mergeCell ref="S192:V192"/>
-    <mergeCell ref="S226:V226"/>
-    <mergeCell ref="S161:V161"/>
+    <mergeCell ref="S81:V81"/>
+    <mergeCell ref="S164:V164"/>
+    <mergeCell ref="S173:V173"/>
     <mergeCell ref="S62:V62"/>
-    <mergeCell ref="Y227:AG230"/>
+    <mergeCell ref="Y130:AG133"/>
+    <mergeCell ref="Y201:AG204"/>
     <mergeCell ref="A1:AG2"/>
     <mergeCell ref="S71:V71"/>
-    <mergeCell ref="Y83:AG86"/>
-    <mergeCell ref="Y100:AG100"/>
     <mergeCell ref="S241:V241"/>
     <mergeCell ref="S145:V145"/>
     <mergeCell ref="S58:V58"/>
-    <mergeCell ref="Y160:AG160"/>
-    <mergeCell ref="S228:V228"/>
-    <mergeCell ref="Q224:W224"/>
-    <mergeCell ref="S120:V120"/>
-    <mergeCell ref="S191:V191"/>
+    <mergeCell ref="Y141:AG141"/>
+    <mergeCell ref="Y206:AG206"/>
     <mergeCell ref="S73:V73"/>
     <mergeCell ref="S243:V243"/>
-    <mergeCell ref="Y173:AG176"/>
     <mergeCell ref="Y17:AG20"/>
-    <mergeCell ref="Y196:AG196"/>
     <mergeCell ref="Y11:AG14"/>
     <mergeCell ref="S57:V57"/>
-    <mergeCell ref="Y152:AG152"/>
+    <mergeCell ref="S259:V259"/>
+    <mergeCell ref="Q162:W162"/>
     <mergeCell ref="Y59:AG62"/>
-    <mergeCell ref="S229:V229"/>
+    <mergeCell ref="Y237:AG240"/>
     <mergeCell ref="S146:V146"/>
-    <mergeCell ref="Y239:AG242"/>
-    <mergeCell ref="S83:V83"/>
-    <mergeCell ref="Y95:AG98"/>
+    <mergeCell ref="Y176:AG176"/>
+    <mergeCell ref="S204:V204"/>
+    <mergeCell ref="S270:V270"/>
+    <mergeCell ref="S151:V151"/>
+    <mergeCell ref="Y182:AG182"/>
     <mergeCell ref="S141:V141"/>
+    <mergeCell ref="S254:V254"/>
     <mergeCell ref="S154:V154"/>
-    <mergeCell ref="S254:V254"/>
-    <mergeCell ref="S163:V163"/>
     <mergeCell ref="S124:V124"/>
-    <mergeCell ref="Y88:AG88"/>
-    <mergeCell ref="S85:V85"/>
-    <mergeCell ref="Y209:AG212"/>
+    <mergeCell ref="Y136:AG139"/>
+    <mergeCell ref="S76:V76"/>
+    <mergeCell ref="S256:V256"/>
+    <mergeCell ref="S75:V75"/>
+    <mergeCell ref="Y105:AG105"/>
     <mergeCell ref="S140:V140"/>
+    <mergeCell ref="Y99:AG99"/>
+    <mergeCell ref="S167:V167"/>
+    <mergeCell ref="S47:V47"/>
+    <mergeCell ref="S149:V149"/>
+    <mergeCell ref="Y170:AG170"/>
     <mergeCell ref="S246:V246"/>
-    <mergeCell ref="S47:V47"/>
-    <mergeCell ref="S233:V233"/>
     <mergeCell ref="S59:V59"/>
-    <mergeCell ref="S119:V119"/>
-    <mergeCell ref="Y131:AG134"/>
-    <mergeCell ref="Y154:AG154"/>
     <mergeCell ref="S46:V46"/>
     <mergeCell ref="S248:V248"/>
+    <mergeCell ref="S169:V169"/>
+    <mergeCell ref="Q198:W198"/>
+    <mergeCell ref="S165:V165"/>
+    <mergeCell ref="Y177:AG180"/>
     <mergeCell ref="S61:V61"/>
-    <mergeCell ref="Y116:AG116"/>
     <mergeCell ref="S70:V70"/>
     <mergeCell ref="S48:V48"/>
     <mergeCell ref="Y8:AG8"/>
-    <mergeCell ref="S194:V194"/>
-    <mergeCell ref="Y130:AG130"/>
-    <mergeCell ref="S160:V160"/>
+    <mergeCell ref="S200:V200"/>
+    <mergeCell ref="S203:V203"/>
+    <mergeCell ref="Q85:W85"/>
+    <mergeCell ref="Y234:AG234"/>
     <mergeCell ref="S131:V131"/>
+    <mergeCell ref="Y243:AG246"/>
+    <mergeCell ref="S87:V87"/>
+    <mergeCell ref="S258:V258"/>
+    <mergeCell ref="S267:V267"/>
     <mergeCell ref="S245:V245"/>
     <mergeCell ref="S49:V49"/>
+    <mergeCell ref="Y236:AG236"/>
     <mergeCell ref="S128:V128"/>
     <mergeCell ref="S10:V10"/>
-    <mergeCell ref="Y118:AG118"/>
-    <mergeCell ref="Y155:AG158"/>
     <mergeCell ref="S137:V137"/>
-    <mergeCell ref="Y232:AG232"/>
-    <mergeCell ref="Q80:W80"/>
+    <mergeCell ref="S89:V89"/>
+    <mergeCell ref="S260:V260"/>
+    <mergeCell ref="Y124:AG127"/>
+    <mergeCell ref="S269:V269"/>
     <mergeCell ref="S65:V65"/>
     <mergeCell ref="S74:V74"/>
-    <mergeCell ref="Y94:AG94"/>
     <mergeCell ref="S157:V157"/>
+    <mergeCell ref="S201:V201"/>
+    <mergeCell ref="S139:V139"/>
+    <mergeCell ref="Y213:AG216"/>
     <mergeCell ref="S250:V250"/>
-    <mergeCell ref="S139:V139"/>
     <mergeCell ref="S237:V237"/>
     <mergeCell ref="Y22:AG22"/>
-    <mergeCell ref="Y101:AG104"/>
     <mergeCell ref="S129:V129"/>
     <mergeCell ref="S123:V123"/>
     <mergeCell ref="S138:V138"/>
     <mergeCell ref="S50:V50"/>
-    <mergeCell ref="S230:V230"/>
+    <mergeCell ref="Y218:AG218"/>
+    <mergeCell ref="S168:V168"/>
     <mergeCell ref="S51:V51"/>
-    <mergeCell ref="Y125:AG128"/>
     <mergeCell ref="S60:V60"/>
-    <mergeCell ref="Y80:AG80"/>
+    <mergeCell ref="S91:V91"/>
     <mergeCell ref="S143:V143"/>
-    <mergeCell ref="Y208:AG208"/>
     <mergeCell ref="S236:V236"/>
+    <mergeCell ref="S271:V271"/>
     <mergeCell ref="Y53:AG56"/>
     <mergeCell ref="Y47:AG50"/>
-    <mergeCell ref="S232:V232"/>
-    <mergeCell ref="Y136:AG136"/>
     <mergeCell ref="S155:V155"/>
-    <mergeCell ref="Y167:AG170"/>
+    <mergeCell ref="S264:V264"/>
     <mergeCell ref="S247:V247"/>
+    <mergeCell ref="S77:V77"/>
     <mergeCell ref="S52:V52"/>
     <mergeCell ref="Q8:W8"/>
-    <mergeCell ref="Y89:AG92"/>
-    <mergeCell ref="Y191:AG194"/>
-    <mergeCell ref="S122:V122"/>
+    <mergeCell ref="Q121:W121"/>
+    <mergeCell ref="S170:V170"/>
+    <mergeCell ref="S257:V257"/>
+    <mergeCell ref="S262:V262"/>
+    <mergeCell ref="S166:V166"/>
     <mergeCell ref="S67:V67"/>
-    <mergeCell ref="Y161:AG164"/>
+    <mergeCell ref="Y88:AG91"/>
+    <mergeCell ref="Y162:AG162"/>
+    <mergeCell ref="Y219:AG222"/>
+    <mergeCell ref="Y121:AG121"/>
     <mergeCell ref="S69:V69"/>
-    <mergeCell ref="Y137:AG140"/>
-    <mergeCell ref="Y226:AG226"/>
-    <mergeCell ref="Y203:AG206"/>
+    <mergeCell ref="Y212:AG212"/>
+    <mergeCell ref="Y93:AG93"/>
+    <mergeCell ref="S78:V78"/>
+    <mergeCell ref="Y164:AG164"/>
     <mergeCell ref="S249:V249"/>
-    <mergeCell ref="Q152:W152"/>
+    <mergeCell ref="S205:V205"/>
     <mergeCell ref="S53:V53"/>
+    <mergeCell ref="Y249:AG252"/>
     <mergeCell ref="S133:V133"/>
     <mergeCell ref="Q44:W44"/>
     <mergeCell ref="S127:V127"/>
     <mergeCell ref="S142:V142"/>
+    <mergeCell ref="S80:V80"/>
     <mergeCell ref="Y44:AG44"/>
-    <mergeCell ref="S234:V234"/>
+    <mergeCell ref="S172:V172"/>
     <mergeCell ref="S55:V55"/>
-    <mergeCell ref="Y172:AG172"/>
     <mergeCell ref="S64:V64"/>
-    <mergeCell ref="S235:V235"/>
-    <mergeCell ref="S162:V162"/>
-    <mergeCell ref="Y188:AG188"/>
-    <mergeCell ref="S227:V227"/>
+    <mergeCell ref="Y85:AG85"/>
+    <mergeCell ref="S148:V148"/>
+    <mergeCell ref="S266:V266"/>
     <mergeCell ref="S54:V54"/>
+    <mergeCell ref="S88:V88"/>
     <mergeCell ref="S63:V63"/>
-    <mergeCell ref="Y197:AG200"/>
+    <mergeCell ref="S268:V268"/>
     <mergeCell ref="Y23:AG26"/>
-    <mergeCell ref="Y124:AG124"/>
-    <mergeCell ref="Y190:AG190"/>
     <mergeCell ref="Y46:AG46"/>
     <mergeCell ref="S252:V252"/>
     <mergeCell ref="Y28:AG28"/>
     <mergeCell ref="S56:V56"/>
+    <mergeCell ref="Y198:AG198"/>
+    <mergeCell ref="S90:V90"/>
+    <mergeCell ref="S261:V261"/>
     <mergeCell ref="S156:V156"/>
+    <mergeCell ref="Y100:AG103"/>
     <mergeCell ref="S126:V126"/>
+    <mergeCell ref="Y171:AG174"/>
+    <mergeCell ref="Y165:AG168"/>
     <mergeCell ref="S251:V251"/>
-    <mergeCell ref="Y166:AG166"/>
+    <mergeCell ref="Y135:AG135"/>
+    <mergeCell ref="Y248:AG248"/>
     <mergeCell ref="S238:V238"/>
-    <mergeCell ref="Y238:AG238"/>
-    <mergeCell ref="S121:V121"/>
+    <mergeCell ref="Q234:W234"/>
+    <mergeCell ref="Y29:AG32"/>
     <mergeCell ref="S130:V130"/>
-    <mergeCell ref="Y29:AG32"/>
+    <mergeCell ref="Y142:AG145"/>
+    <mergeCell ref="Y207:AG210"/>
     <mergeCell ref="S244:V244"/>
-    <mergeCell ref="S82:V82"/>
+    <mergeCell ref="Y94:AG97"/>
     <mergeCell ref="S253:V253"/>
-    <mergeCell ref="S231:V231"/>
     <mergeCell ref="S240:V240"/>
+    <mergeCell ref="Y200:AG200"/>
     <mergeCell ref="S66:V66"/>
+    <mergeCell ref="Y87:AG87"/>
     <mergeCell ref="S132:V132"/>
-    <mergeCell ref="S190:V190"/>
-    <mergeCell ref="Y119:AG122"/>
-    <mergeCell ref="Y224:AG224"/>
-    <mergeCell ref="Y202:AG202"/>
+    <mergeCell ref="Y183:AG186"/>
     <mergeCell ref="Y58:AG58"/>
     <mergeCell ref="S68:V68"/>
+    <mergeCell ref="S152:V152"/>
     <mergeCell ref="S239:V239"/>
-    <mergeCell ref="Q188:W188"/>
-    <mergeCell ref="S84:V84"/>
+    <mergeCell ref="S171:V171"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7996,160 +10073,165 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AD38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Monthly Spending</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="52" t="inlineStr">
         <is>
           <t>Spending by Category</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="52" t="inlineStr">
         <is>
           <t>Spending by Store</t>
         </is>
       </c>
-      <c r="M1" s="9" t="inlineStr">
+      <c r="M1" s="52" t="inlineStr">
         <is>
           <t>Spending Share by Category</t>
         </is>
       </c>
-      <c r="Q1" s="9" t="inlineStr">
+      <c r="Q1" s="52" t="inlineStr">
         <is>
           <t>Top Products by Spending</t>
         </is>
       </c>
-      <c r="U1" s="9" t="inlineStr">
+      <c r="U1" s="52" t="inlineStr">
         <is>
           <t>Purchase Frequency by Category</t>
         </is>
       </c>
-      <c r="Y1" s="9" t="inlineStr">
+      <c r="Y1" s="52" t="inlineStr">
         <is>
           <t>Monthly Spending by Store</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="52" t="inlineStr">
         <is>
           <t>Number</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="52" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="52" t="inlineStr">
         <is>
           <t>Spending</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="E2" s="52" t="inlineStr">
         <is>
           <t>Number</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="F2" s="52" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="G2" s="52" t="inlineStr">
         <is>
           <t>Spending</t>
         </is>
       </c>
-      <c r="I2" s="9" t="inlineStr">
+      <c r="I2" s="52" t="inlineStr">
         <is>
           <t>Number</t>
         </is>
       </c>
-      <c r="J2" s="9" t="inlineStr">
+      <c r="J2" s="52" t="inlineStr">
         <is>
           <t>Store</t>
         </is>
       </c>
-      <c r="K2" s="9" t="inlineStr">
+      <c r="K2" s="52" t="inlineStr">
         <is>
           <t>Spending</t>
         </is>
       </c>
-      <c r="M2" s="9" t="inlineStr">
+      <c r="M2" s="52" t="inlineStr">
         <is>
           <t>Number</t>
         </is>
       </c>
-      <c r="N2" s="9" t="inlineStr">
+      <c r="N2" s="52" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="O2" s="9" t="inlineStr">
+      <c r="O2" s="52" t="inlineStr">
         <is>
           <t>Spending</t>
         </is>
       </c>
-      <c r="Q2" s="9" t="inlineStr">
+      <c r="Q2" s="52" t="inlineStr">
         <is>
           <t>Number</t>
         </is>
       </c>
-      <c r="R2" s="9" t="inlineStr">
+      <c r="R2" s="52" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="S2" s="9" t="inlineStr">
+      <c r="S2" s="52" t="inlineStr">
         <is>
           <t>Spending</t>
         </is>
       </c>
-      <c r="U2" s="9" t="inlineStr">
+      <c r="U2" s="52" t="inlineStr">
         <is>
           <t>Number</t>
         </is>
       </c>
-      <c r="V2" s="9" t="inlineStr">
+      <c r="V2" s="52" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="W2" s="9" t="inlineStr">
+      <c r="W2" s="52" t="inlineStr">
         <is>
           <t>Purchases</t>
         </is>
       </c>
-      <c r="Y2" s="9" t="inlineStr">
+      <c r="Y2" s="52" t="inlineStr">
         <is>
           <t>Month Number</t>
         </is>
       </c>
-      <c r="Z2" s="9" t="inlineStr">
+      <c r="Z2" s="52" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="9" t="inlineStr">
+      <c r="AA2" s="52" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB2" s="9" t="inlineStr">
+      <c r="AB2" s="52" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AC2" s="9" t="inlineStr">
+      <c r="AC2" s="52" t="inlineStr">
         <is>
           <t>4</t>
+        </is>
+      </c>
+      <c r="AD2" s="52" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -8157,80 +10239,83 @@
       <c r="A3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="35" t="n">
+      <c r="B3" s="53" t="n">
         <v>46235</v>
       </c>
-      <c r="C3" s="11" t="n">
-        <v>239.76</v>
+      <c r="C3" s="54" t="n">
+        <v>444.7700000000002</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Prepared Meals</t>
-        </is>
-      </c>
-      <c r="G3" s="11" t="n">
-        <v>31.2</v>
+          <t>Baby</t>
+        </is>
+      </c>
+      <c r="G3" s="54" t="n">
+        <v>55.57000000000001</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Aldi</t>
-        </is>
-      </c>
-      <c r="K3" s="11" t="n">
-        <v>100.82</v>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="K3" s="54" t="n">
+        <v>205.01</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Prepared Meals</t>
-        </is>
-      </c>
-      <c r="O3" s="11" t="n">
-        <v>31.2</v>
+          <t>Baby</t>
+        </is>
+      </c>
+      <c r="O3" s="54" t="n">
+        <v>55.57000000000001</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Silk Organic Unsweet Soymilk, Half Gallon</t>
-        </is>
-      </c>
-      <c r="S3" s="11" t="n">
-        <v>18.57</v>
+          <t>Pampers Swaddlers Fragrance Free Baby Diapers Size 5, 100 Count (Select for More Options) 20 shopped Qty1</t>
+        </is>
+      </c>
+      <c r="S3" s="54" t="n">
+        <v>39.77</v>
       </c>
       <c r="U3" t="n">
         <v>1</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Fresh Vegetables</t>
+          <t>Uncategorized</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y3" t="n">
         <v>1</v>
       </c>
-      <c r="Z3" s="11" t="n">
+      <c r="Z3" s="54" t="n">
+        <v>205.01</v>
+      </c>
+      <c r="AA3" s="54" t="n">
         <v>100.82</v>
       </c>
-      <c r="AA3" s="11" t="n">
+      <c r="AB3" s="54" t="n">
         <v>60.57999999999999</v>
       </c>
-      <c r="AB3" s="11" t="n">
+      <c r="AC3" s="54" t="n">
         <v>48.12</v>
       </c>
-      <c r="AC3" s="11" t="n">
+      <c r="AD3" s="54" t="n">
         <v>30.24</v>
       </c>
     </row>
@@ -8240,55 +10325,55 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Yogurt</t>
-        </is>
-      </c>
-      <c r="G4" s="11" t="n">
-        <v>21.35</v>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="G4" s="54" t="n">
+        <v>53.49</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Publix</t>
-        </is>
-      </c>
-      <c r="K4" s="11" t="n">
-        <v>60.57999999999999</v>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="K4" s="54" t="n">
+        <v>100.82</v>
       </c>
       <c r="M4" t="n">
         <v>2</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Yogurt</t>
-        </is>
-      </c>
-      <c r="O4" s="11" t="n">
-        <v>21.35</v>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="O4" s="54" t="n">
+        <v>53.49</v>
       </c>
       <c r="Q4" t="n">
         <v>2</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1 Chicken N French Toast</t>
-        </is>
-      </c>
-      <c r="S4" s="11" t="n">
-        <v>16.3</v>
+          <t>Purina Tidy Cats With Glade Clear Springs Scented, Odor Control, Clumping Multi-Cat Litter 20 shopped Qty2</t>
+        </is>
+      </c>
+      <c r="S4" s="54" t="n">
+        <v>23.94</v>
       </c>
       <c r="U4" t="n">
         <v>2</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Fresh Fruit</t>
+          <t>Fresh Vegetables</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -8297,55 +10382,55 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fresh Vegetables</t>
-        </is>
-      </c>
-      <c r="G5" s="11" t="n">
-        <v>21.28</v>
+          <t>Prepared Meals</t>
+        </is>
+      </c>
+      <c r="G5" s="54" t="n">
+        <v>31.2</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Honey Pineapple</t>
-        </is>
-      </c>
-      <c r="K5" s="11" t="n">
-        <v>48.12</v>
+          <t>Publix</t>
+        </is>
+      </c>
+      <c r="K5" s="54" t="n">
+        <v>60.57999999999999</v>
       </c>
       <c r="M5" t="n">
         <v>3</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Fresh Vegetables</t>
-        </is>
-      </c>
-      <c r="O5" s="11" t="n">
-        <v>21.28</v>
+          <t>Prepared Meals</t>
+        </is>
+      </c>
+      <c r="O5" s="54" t="n">
+        <v>31.2</v>
       </c>
       <c r="Q5" t="n">
         <v>3</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1 Frenchy Plate</t>
-        </is>
-      </c>
-      <c r="S5" s="11" t="n">
-        <v>14.9</v>
+          <t>Silk Organic Unsweet Soymilk, Half Gallon</t>
+        </is>
+      </c>
+      <c r="S5" s="54" t="n">
+        <v>18.57</v>
       </c>
       <c r="U5" t="n">
         <v>3</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Canned Beans &amp; Legumes</t>
+          <t>Fresh Fruit</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -8354,55 +10439,55 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plant-Based Milk</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>18.57</v>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="G6" s="54" t="n">
+        <v>24.43</v>
       </c>
       <c r="I6" t="n">
         <v>4</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Trader Joe's</t>
-        </is>
-      </c>
-      <c r="K6" s="11" t="n">
-        <v>30.24</v>
+          <t>Honey Pineapple</t>
+        </is>
+      </c>
+      <c r="K6" s="54" t="n">
+        <v>48.12</v>
       </c>
       <c r="M6" t="n">
         <v>4</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Plant-Based Milk</t>
-        </is>
-      </c>
-      <c r="O6" s="11" t="n">
-        <v>18.57</v>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="O6" s="54" t="n">
+        <v>24.43</v>
       </c>
       <c r="Q6" t="n">
         <v>4</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Empire Kosher Ground Turkey</t>
-        </is>
-      </c>
-      <c r="S6" s="11" t="n">
-        <v>13.98</v>
+          <t>Driver tip</t>
+        </is>
+      </c>
+      <c r="S6" s="54" t="n">
+        <v>16.92</v>
       </c>
       <c r="U6" t="n">
         <v>4</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Plant-Based Milk</t>
+          <t>Canned Beans &amp; Legumes</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -8411,44 +10496,55 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fresh Fruit</t>
-        </is>
-      </c>
-      <c r="G7" s="11" t="n">
-        <v>15.97</v>
+          <t>Dairy</t>
+        </is>
+      </c>
+      <c r="G7" s="54" t="n">
+        <v>24.42</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Trader Joe's</t>
+        </is>
+      </c>
+      <c r="K7" s="54" t="n">
+        <v>30.24</v>
       </c>
       <c r="M7" t="n">
         <v>5</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Fresh Fruit</t>
-        </is>
-      </c>
-      <c r="O7" s="11" t="n">
-        <v>15.97</v>
+          <t>Dairy</t>
+        </is>
+      </c>
+      <c r="O7" s="54" t="n">
+        <v>24.42</v>
       </c>
       <c r="Q7" t="n">
         <v>5</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Cauliflower Crust Pizza</t>
-        </is>
-      </c>
-      <c r="S7" s="11" t="n">
-        <v>8.289999999999999</v>
+          <t>1 Chicken N French Toast</t>
+        </is>
+      </c>
+      <c r="S7" s="54" t="n">
+        <v>16.3</v>
       </c>
       <c r="U7" t="n">
         <v>5</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Yogurt</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -8457,44 +10553,44 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fresh Poultry</t>
-        </is>
-      </c>
-      <c r="G8" s="11" t="n">
-        <v>13.98</v>
+          <t>Pet</t>
+        </is>
+      </c>
+      <c r="G8" s="54" t="n">
+        <v>23.94</v>
       </c>
       <c r="M8" t="n">
         <v>6</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Fresh Poultry</t>
-        </is>
-      </c>
-      <c r="O8" s="11" t="n">
-        <v>13.98</v>
+          <t>Pet</t>
+        </is>
+      </c>
+      <c r="O8" s="54" t="n">
+        <v>23.94</v>
       </c>
       <c r="Q8" t="n">
         <v>6</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Stonyfield Organic YoBaby Yogurt Pouch, Banana</t>
-        </is>
-      </c>
-      <c r="S8" s="11" t="n">
-        <v>7.85</v>
+          <t>1 Frenchy Plate</t>
+        </is>
+      </c>
+      <c r="S8" s="54" t="n">
+        <v>14.9</v>
       </c>
       <c r="U8" t="n">
         <v>6</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Bread</t>
+          <t>Produce</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -8503,44 +10599,44 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Prepared Coffee</t>
-        </is>
-      </c>
-      <c r="G9" s="11" t="n">
-        <v>11</v>
+          <t>Yogurt</t>
+        </is>
+      </c>
+      <c r="G9" s="54" t="n">
+        <v>21.35</v>
       </c>
       <c r="M9" t="n">
         <v>7</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Prepared Coffee</t>
-        </is>
-      </c>
-      <c r="O9" s="11" t="n">
-        <v>11</v>
+          <t>Yogurt</t>
+        </is>
+      </c>
+      <c r="O9" s="54" t="n">
+        <v>21.35</v>
       </c>
       <c r="Q9" t="n">
         <v>7</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Stonyfield Organic YoBaby Yogurt Pouch, Peach</t>
-        </is>
-      </c>
-      <c r="S9" s="11" t="n">
-        <v>7.85</v>
+          <t>Empire Kosher Ground Turkey</t>
+        </is>
+      </c>
+      <c r="S9" s="54" t="n">
+        <v>13.98</v>
       </c>
       <c r="U9" t="n">
         <v>7</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Fees &amp; Charges</t>
+          <t>Baby</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -8549,44 +10645,44 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bread</t>
-        </is>
-      </c>
-      <c r="G10" s="11" t="n">
-        <v>10.16</v>
+          <t>Fresh Vegetables</t>
+        </is>
+      </c>
+      <c r="G10" s="54" t="n">
+        <v>21.28</v>
       </c>
       <c r="M10" t="n">
         <v>8</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Bread</t>
-        </is>
-      </c>
-      <c r="O10" s="11" t="n">
-        <v>10.16</v>
+          <t>Fresh Vegetables</t>
+        </is>
+      </c>
+      <c r="O10" s="54" t="n">
+        <v>21.28</v>
       </c>
       <c r="Q10" t="n">
         <v>8</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Van's Gluten Free Blueberry Waffles</t>
-        </is>
-      </c>
-      <c r="S10" s="11" t="n">
-        <v>7.78</v>
+          <t>CeraVe Baby Healing Ointment for Diaper Rash &amp; Cracked Chafed Dry Skin for Baby + Toddler 3 oz</t>
+        </is>
+      </c>
+      <c r="S10" s="54" t="n">
+        <v>9.98</v>
       </c>
       <c r="U10" t="n">
         <v>8</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Fresh Herbs</t>
+          <t>Plant-Based Milk</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -8595,44 +10691,44 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Frozen Pizza</t>
-        </is>
-      </c>
-      <c r="G11" s="11" t="n">
-        <v>8.289999999999999</v>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="G11" s="54" t="n">
+        <v>20</v>
       </c>
       <c r="M11" t="n">
         <v>9</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Frozen Pizza</t>
-        </is>
-      </c>
-      <c r="O11" s="11" t="n">
-        <v>8.289999999999999</v>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="O11" s="54" t="n">
+        <v>20</v>
       </c>
       <c r="Q11" t="n">
         <v>9</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Sweet Loren's Gluten Free Brownie Cookie Dough</t>
-        </is>
-      </c>
-      <c r="S11" s="11" t="n">
-        <v>6.99</v>
+          <t>Chobani 20G Protein Low-Fat Greek Yogurt Drink, Strawberries and Cream 10 fl oz Bottle, 4 Pack</t>
+        </is>
+      </c>
+      <c r="S11" s="54" t="n">
+        <v>9.67</v>
       </c>
       <c r="U11" t="n">
         <v>9</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Fresh Poultry</t>
+          <t>Snacks</t>
         </is>
       </c>
       <c r="W11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -8641,44 +10737,44 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Frozen Breakfast</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="n">
-        <v>7.78</v>
+          <t>Plant-Based Milk</t>
+        </is>
+      </c>
+      <c r="G12" s="54" t="n">
+        <v>18.57</v>
       </c>
       <c r="M12" t="n">
         <v>10</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Frozen Breakfast</t>
-        </is>
-      </c>
-      <c r="O12" s="11" t="n">
-        <v>7.78</v>
+          <t>Plant-Based Milk</t>
+        </is>
+      </c>
+      <c r="O12" s="54" t="n">
+        <v>18.57</v>
       </c>
       <c r="Q12" t="n">
         <v>10</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Gluten-Free Wide Pan Bread</t>
-        </is>
-      </c>
-      <c r="S12" s="11" t="n">
-        <v>6.79</v>
+          <t>Nestle Toll House Organic Allergen Free Dark Chocolate Regular Baking Chips, Morsels for Baking, 9 oz Bag</t>
+        </is>
+      </c>
+      <c r="S12" s="54" t="n">
+        <v>8.369999999999999</v>
       </c>
       <c r="U12" t="n">
         <v>10</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Frozen Breakfast</t>
+          <t>Yogurt</t>
         </is>
       </c>
       <c r="W12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -8687,29 +10783,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Refrigerated Dough</t>
-        </is>
-      </c>
-      <c r="G13" s="11" t="n">
-        <v>6.99</v>
+          <t>Fresh Fruit</t>
+        </is>
+      </c>
+      <c r="G13" s="54" t="n">
+        <v>15.97</v>
       </c>
       <c r="M13" t="n">
         <v>11</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Refrigerated Dough</t>
-        </is>
-      </c>
-      <c r="O13" s="11" t="n">
-        <v>6.99</v>
+          <t>Fresh Fruit</t>
+        </is>
+      </c>
+      <c r="O13" s="54" t="n">
+        <v>15.97</v>
       </c>
       <c r="U13" t="n">
         <v>11</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Prepared Coffee</t>
+          <t>Bread</t>
         </is>
       </c>
       <c r="W13" t="n">
@@ -8722,29 +10818,29 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Muffins &amp; Pastries</t>
-        </is>
-      </c>
-      <c r="G14" s="11" t="n">
-        <v>5.99</v>
+          <t>Fresh Poultry</t>
+        </is>
+      </c>
+      <c r="G14" s="54" t="n">
+        <v>13.98</v>
       </c>
       <c r="M14" t="n">
         <v>12</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Muffins &amp; Pastries</t>
-        </is>
-      </c>
-      <c r="O14" s="11" t="n">
-        <v>5.99</v>
+          <t>Fresh Poultry</t>
+        </is>
+      </c>
+      <c r="O14" s="54" t="n">
+        <v>13.98</v>
       </c>
       <c r="U14" t="n">
         <v>12</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Prepared Meals</t>
+          <t>Fees &amp; Charges</t>
         </is>
       </c>
       <c r="W14" t="n">
@@ -8757,29 +10853,29 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Storage &amp; Organization</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="n">
-        <v>5.99</v>
+          <t>Prepared Coffee</t>
+        </is>
+      </c>
+      <c r="G15" s="54" t="n">
+        <v>11</v>
       </c>
       <c r="M15" t="n">
         <v>13</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Storage &amp; Organization</t>
-        </is>
-      </c>
-      <c r="O15" s="11" t="n">
-        <v>5.99</v>
+          <t>Prepared Coffee</t>
+        </is>
+      </c>
+      <c r="O15" s="54" t="n">
+        <v>11</v>
       </c>
       <c r="U15" t="n">
         <v>13</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Snack Bars</t>
+          <t>Fresh Herbs</t>
         </is>
       </c>
       <c r="W15" t="n">
@@ -8792,29 +10888,29 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Writing Supplies</t>
-        </is>
-      </c>
-      <c r="G16" s="11" t="n">
-        <v>5.99</v>
+          <t>Bread</t>
+        </is>
+      </c>
+      <c r="G16" s="54" t="n">
+        <v>10.16</v>
       </c>
       <c r="M16" t="n">
         <v>14</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Writing Supplies</t>
-        </is>
-      </c>
-      <c r="O16" s="11" t="n">
-        <v>5.99</v>
+          <t>Bread</t>
+        </is>
+      </c>
+      <c r="O16" s="54" t="n">
+        <v>10.16</v>
       </c>
       <c r="U16" t="n">
         <v>14</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Specialty Cheese</t>
+          <t>Fresh Poultry</t>
         </is>
       </c>
       <c r="W16" t="n">
@@ -8827,33 +10923,33 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fees &amp; Charges</t>
-        </is>
-      </c>
-      <c r="G17" s="11" t="n">
-        <v>5.92</v>
+          <t>Frozen Pizza</t>
+        </is>
+      </c>
+      <c r="G17" s="54" t="n">
+        <v>8.289999999999999</v>
       </c>
       <c r="M17" t="n">
         <v>15</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Fees &amp; Charges</t>
-        </is>
-      </c>
-      <c r="O17" s="11" t="n">
-        <v>5.92</v>
+          <t>Frozen Pizza</t>
+        </is>
+      </c>
+      <c r="O17" s="54" t="n">
+        <v>8.289999999999999</v>
       </c>
       <c r="U17" t="n">
         <v>15</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Crackers</t>
+          <t>Frozen Breakfast</t>
         </is>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -8862,33 +10958,33 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cream &amp; Half-and-Half</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="n">
-        <v>5.89</v>
+          <t>Frozen Breakfast</t>
+        </is>
+      </c>
+      <c r="G18" s="54" t="n">
+        <v>7.78</v>
       </c>
       <c r="M18" t="n">
         <v>16</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Cream &amp; Half-and-Half</t>
-        </is>
-      </c>
-      <c r="O18" s="11" t="n">
-        <v>5.89</v>
+          <t>Frozen Breakfast</t>
+        </is>
+      </c>
+      <c r="O18" s="54" t="n">
+        <v>7.78</v>
       </c>
       <c r="U18" t="n">
         <v>16</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Cream &amp; Half-and-Half</t>
+          <t>Prepared Coffee</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -8897,33 +10993,33 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Disposable Tableware</t>
-        </is>
-      </c>
-      <c r="G19" s="11" t="n">
-        <v>5.25</v>
+          <t>Refrigerated Dough</t>
+        </is>
+      </c>
+      <c r="G19" s="54" t="n">
+        <v>6.99</v>
       </c>
       <c r="M19" t="n">
         <v>17</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Disposable Tableware</t>
-        </is>
-      </c>
-      <c r="O19" s="11" t="n">
-        <v>5.25</v>
+          <t>Refrigerated Dough</t>
+        </is>
+      </c>
+      <c r="O19" s="54" t="n">
+        <v>6.99</v>
       </c>
       <c r="U19" t="n">
         <v>17</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Croutons</t>
+          <t>Prepared Meals</t>
         </is>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -8932,33 +11028,33 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Specialty Cheese</t>
-        </is>
-      </c>
-      <c r="G20" s="11" t="n">
-        <v>4.88</v>
+          <t>Muffins &amp; Pastries</t>
+        </is>
+      </c>
+      <c r="G20" s="54" t="n">
+        <v>5.99</v>
       </c>
       <c r="M20" t="n">
         <v>18</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Specialty Cheese</t>
-        </is>
-      </c>
-      <c r="O20" s="11" t="n">
-        <v>4.88</v>
+          <t>Muffins &amp; Pastries</t>
+        </is>
+      </c>
+      <c r="O20" s="54" t="n">
+        <v>5.99</v>
       </c>
       <c r="U20" t="n">
         <v>18</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Dips &amp; Spreads</t>
+          <t>Snack Bars</t>
         </is>
       </c>
       <c r="W20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -8967,33 +11063,33 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Snack Bars</t>
-        </is>
-      </c>
-      <c r="G21" s="11" t="n">
-        <v>3.98</v>
+          <t>Storage &amp; Organization</t>
+        </is>
+      </c>
+      <c r="G21" s="54" t="n">
+        <v>5.99</v>
       </c>
       <c r="M21" t="n">
         <v>19</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Snack Bars</t>
-        </is>
-      </c>
-      <c r="O21" s="11" t="n">
-        <v>3.98</v>
+          <t>Storage &amp; Organization</t>
+        </is>
+      </c>
+      <c r="O21" s="54" t="n">
+        <v>5.99</v>
       </c>
       <c r="U21" t="n">
         <v>19</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Disposable Tableware</t>
+          <t>Specialty Cheese</t>
         </is>
       </c>
       <c r="W21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -9002,29 +11098,29 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fresh-Cut Fruit</t>
-        </is>
-      </c>
-      <c r="G22" s="11" t="n">
-        <v>3.89</v>
+          <t>Writing Supplies</t>
+        </is>
+      </c>
+      <c r="G22" s="54" t="n">
+        <v>5.99</v>
       </c>
       <c r="M22" t="n">
         <v>20</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Fresh-Cut Fruit</t>
-        </is>
-      </c>
-      <c r="O22" s="11" t="n">
-        <v>3.89</v>
+          <t>Writing Supplies</t>
+        </is>
+      </c>
+      <c r="O22" s="54" t="n">
+        <v>5.99</v>
       </c>
       <c r="U22" t="n">
         <v>20</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Fresh-Cut Fruit</t>
+          <t>Crackers</t>
         </is>
       </c>
       <c r="W22" t="n">
@@ -9037,29 +11133,29 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Canned Beans &amp; Legumes</t>
-        </is>
-      </c>
-      <c r="G23" s="11" t="n">
-        <v>3.68</v>
+          <t>Fees &amp; Charges</t>
+        </is>
+      </c>
+      <c r="G23" s="54" t="n">
+        <v>5.92</v>
       </c>
       <c r="M23" t="n">
         <v>21</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Canned Beans &amp; Legumes</t>
-        </is>
-      </c>
-      <c r="O23" s="11" t="n">
-        <v>3.68</v>
+          <t>Fees &amp; Charges</t>
+        </is>
+      </c>
+      <c r="O23" s="54" t="n">
+        <v>5.92</v>
       </c>
       <c r="U23" t="n">
         <v>21</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Frozen Pizza</t>
+          <t>Cream &amp; Half-and-Half</t>
         </is>
       </c>
       <c r="W23" t="n">
@@ -9072,29 +11168,29 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dips &amp; Spreads</t>
-        </is>
-      </c>
-      <c r="G24" s="11" t="n">
-        <v>3.45</v>
+          <t>Cream &amp; Half-and-Half</t>
+        </is>
+      </c>
+      <c r="G24" s="54" t="n">
+        <v>5.89</v>
       </c>
       <c r="M24" t="n">
         <v>22</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Dips &amp; Spreads</t>
-        </is>
-      </c>
-      <c r="O24" s="11" t="n">
-        <v>3.45</v>
+          <t>Cream &amp; Half-and-Half</t>
+        </is>
+      </c>
+      <c r="O24" s="54" t="n">
+        <v>5.89</v>
       </c>
       <c r="U24" t="n">
         <v>22</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Jarred Vegetables</t>
+          <t>Croutons</t>
         </is>
       </c>
       <c r="W24" t="n">
@@ -9107,29 +11203,29 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jarred Vegetables</t>
-        </is>
-      </c>
-      <c r="G25" s="11" t="n">
-        <v>3.29</v>
+          <t>Disposable Tableware</t>
+        </is>
+      </c>
+      <c r="G25" s="54" t="n">
+        <v>5.25</v>
       </c>
       <c r="M25" t="n">
         <v>23</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Jarred Vegetables</t>
-        </is>
-      </c>
-      <c r="O25" s="11" t="n">
-        <v>3.29</v>
+          <t>Disposable Tableware</t>
+        </is>
+      </c>
+      <c r="O25" s="54" t="n">
+        <v>5.25</v>
       </c>
       <c r="U25" t="n">
         <v>23</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Muffins &amp; Pastries</t>
+          <t>Dips &amp; Spreads</t>
         </is>
       </c>
       <c r="W25" t="n">
@@ -9142,29 +11238,29 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pasta</t>
-        </is>
-      </c>
-      <c r="G26" s="11" t="n">
-        <v>2.99</v>
+          <t>Specialty Cheese</t>
+        </is>
+      </c>
+      <c r="G26" s="54" t="n">
+        <v>4.88</v>
       </c>
       <c r="M26" t="n">
         <v>24</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Pasta</t>
-        </is>
-      </c>
-      <c r="O26" s="11" t="n">
-        <v>2.99</v>
+          <t>Specialty Cheese</t>
+        </is>
+      </c>
+      <c r="O26" s="54" t="n">
+        <v>4.88</v>
       </c>
       <c r="U26" t="n">
         <v>24</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Pasta</t>
+          <t>Disposable Tableware</t>
         </is>
       </c>
       <c r="W26" t="n">
@@ -9177,29 +11273,29 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Salad Dressing</t>
-        </is>
-      </c>
-      <c r="G27" s="11" t="n">
-        <v>2.99</v>
+          <t>Snack Bars</t>
+        </is>
+      </c>
+      <c r="G27" s="54" t="n">
+        <v>3.98</v>
       </c>
       <c r="M27" t="n">
         <v>25</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Salad Dressing</t>
-        </is>
-      </c>
-      <c r="O27" s="11" t="n">
-        <v>2.99</v>
+          <t>Snack Bars</t>
+        </is>
+      </c>
+      <c r="O27" s="54" t="n">
+        <v>3.98</v>
       </c>
       <c r="U27" t="n">
         <v>25</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Popcorn</t>
+          <t>Fresh-Cut Fruit</t>
         </is>
       </c>
       <c r="W27" t="n">
@@ -9212,29 +11308,29 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Crackers</t>
-        </is>
-      </c>
-      <c r="G28" s="11" t="n">
-        <v>2.79</v>
+          <t>Fresh-Cut Fruit</t>
+        </is>
+      </c>
+      <c r="G28" s="54" t="n">
+        <v>3.89</v>
       </c>
       <c r="M28" t="n">
         <v>26</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Crackers</t>
-        </is>
-      </c>
-      <c r="O28" s="11" t="n">
-        <v>2.79</v>
+          <t>Fresh-Cut Fruit</t>
+        </is>
+      </c>
+      <c r="O28" s="54" t="n">
+        <v>3.89</v>
       </c>
       <c r="U28" t="n">
         <v>26</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Refrigerated Dough</t>
+          <t>Frozen Pizza</t>
         </is>
       </c>
       <c r="W28" t="n">
@@ -9247,29 +11343,29 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Popcorn</t>
-        </is>
-      </c>
-      <c r="G29" s="11" t="n">
-        <v>2.39</v>
+          <t>Canned Beans &amp; Legumes</t>
+        </is>
+      </c>
+      <c r="G29" s="54" t="n">
+        <v>3.68</v>
       </c>
       <c r="M29" t="n">
         <v>27</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Popcorn</t>
-        </is>
-      </c>
-      <c r="O29" s="11" t="n">
-        <v>2.39</v>
+          <t>Canned Beans &amp; Legumes</t>
+        </is>
+      </c>
+      <c r="O29" s="54" t="n">
+        <v>3.68</v>
       </c>
       <c r="U29" t="n">
         <v>27</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Salad Dressing</t>
+          <t>Jarred Vegetables</t>
         </is>
       </c>
       <c r="W29" t="n">
@@ -9282,29 +11378,29 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Croutons</t>
-        </is>
-      </c>
-      <c r="G30" s="11" t="n">
-        <v>1.99</v>
+          <t>Dips &amp; Spreads</t>
+        </is>
+      </c>
+      <c r="G30" s="54" t="n">
+        <v>3.45</v>
       </c>
       <c r="M30" t="n">
         <v>28</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Croutons</t>
-        </is>
-      </c>
-      <c r="O30" s="11" t="n">
-        <v>1.99</v>
+          <t>Dips &amp; Spreads</t>
+        </is>
+      </c>
+      <c r="O30" s="54" t="n">
+        <v>3.45</v>
       </c>
       <c r="U30" t="n">
         <v>28</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>Storage &amp; Organization</t>
+          <t>Meat &amp; Seafood</t>
         </is>
       </c>
       <c r="W30" t="n">
@@ -9317,32 +11413,277 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fresh Herbs</t>
-        </is>
-      </c>
-      <c r="G31" s="11" t="n">
-        <v>1.84</v>
+          <t>Jarred Vegetables</t>
+        </is>
+      </c>
+      <c r="G31" s="54" t="n">
+        <v>3.29</v>
       </c>
       <c r="M31" t="n">
         <v>29</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Fresh Herbs</t>
-        </is>
-      </c>
-      <c r="O31" s="11" t="n">
-        <v>1.84</v>
+          <t>Jarred Vegetables</t>
+        </is>
+      </c>
+      <c r="O31" s="54" t="n">
+        <v>3.29</v>
       </c>
       <c r="U31" t="n">
         <v>29</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
+          <t>Muffins &amp; Pastries</t>
+        </is>
+      </c>
+      <c r="W31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="E32" t="n">
+        <v>30</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Meat &amp; Seafood</t>
+        </is>
+      </c>
+      <c r="G32" s="54" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="M32" t="n">
+        <v>30</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Meat &amp; Seafood</t>
+        </is>
+      </c>
+      <c r="O32" s="54" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="U32" t="n">
+        <v>30</v>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Pasta</t>
+        </is>
+      </c>
+      <c r="W32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="E33" t="n">
+        <v>31</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Pasta</t>
+        </is>
+      </c>
+      <c r="G33" s="54" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="M33" t="n">
+        <v>31</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Pasta</t>
+        </is>
+      </c>
+      <c r="O33" s="54" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U33" t="n">
+        <v>31</v>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Pet</t>
+        </is>
+      </c>
+      <c r="W33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="E34" t="n">
+        <v>32</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Salad Dressing</t>
+        </is>
+      </c>
+      <c r="G34" s="54" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="M34" t="n">
+        <v>32</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Salad Dressing</t>
+        </is>
+      </c>
+      <c r="O34" s="54" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U34" t="n">
+        <v>32</v>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Popcorn</t>
+        </is>
+      </c>
+      <c r="W34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="E35" t="n">
+        <v>33</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Crackers</t>
+        </is>
+      </c>
+      <c r="G35" s="54" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="M35" t="n">
+        <v>33</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Crackers</t>
+        </is>
+      </c>
+      <c r="O35" s="54" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="U35" t="n">
+        <v>33</v>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Refrigerated Dough</t>
+        </is>
+      </c>
+      <c r="W35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="E36" t="n">
+        <v>34</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Popcorn</t>
+        </is>
+      </c>
+      <c r="G36" s="54" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="M36" t="n">
+        <v>34</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Popcorn</t>
+        </is>
+      </c>
+      <c r="O36" s="54" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="U36" t="n">
+        <v>34</v>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Salad Dressing</t>
+        </is>
+      </c>
+      <c r="W36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="E37" t="n">
+        <v>35</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Croutons</t>
+        </is>
+      </c>
+      <c r="G37" s="54" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="M37" t="n">
+        <v>35</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Croutons</t>
+        </is>
+      </c>
+      <c r="O37" s="54" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U37" t="n">
+        <v>35</v>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Storage &amp; Organization</t>
+        </is>
+      </c>
+      <c r="W37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="E38" t="n">
+        <v>36</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Fresh Herbs</t>
+        </is>
+      </c>
+      <c r="G38" s="54" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="M38" t="n">
+        <v>36</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Fresh Herbs</t>
+        </is>
+      </c>
+      <c r="O38" s="54" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U38" t="n">
+        <v>36</v>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
           <t>Writing Supplies</t>
         </is>
       </c>
-      <c r="W31" t="n">
+      <c r="W38" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9357,12 +11698,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" style="27" min="1" max="1"/>
+    <col width="16" customWidth="1" style="27" min="2" max="3"/>
+    <col width="22" customWidth="1" style="27" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9459,6 +11800,24 @@
         <v>46261.69623483796</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>walmart_aug_6_raw_ocr.json</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>46261.87458537037</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/database/shopgraph_purchase_history.xlsx
+++ b/data/database/shopgraph_purchase_history.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Imported Receipts" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Purchase History'!$A$1:$O$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Purchase History'!$A$1:$O$83</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,14 +20,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="165" formatCode="mm/dd/yyyy\ hh:mm"/>
     <numFmt numFmtId="166" formatCode="mmm\ yyyy"/>
     <numFmt numFmtId="167" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="168" formatCode="$#,##0.00"/>
-    <numFmt numFmtId="169" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="170" formatCode="mmm yyyy"/>
+    <numFmt numFmtId="169" formatCode="mmm yyyy"/>
+    <numFmt numFmtId="170" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="171" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="172" formatCode="mm/dd/yyyy hh:mm"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -263,7 +265,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -349,8 +351,10 @@
     <xf numFmtId="0" fontId="0" fillId="28" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="29" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -429,7 +433,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="13"/>
   <chart>
     <title>
       <tx>
@@ -549,7 +552,6 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -1166,7 +1168,6 @@
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -1349,7 +1350,6 @@
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -1915,7 +1915,6 @@
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -2168,7 +2167,6 @@
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="12"/>
   <chart>
     <title>
       <tx>
@@ -2408,7 +2406,6 @@
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -3471,88 +3468,94 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O76"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="27" min="1" max="1"/>
     <col width="3" customWidth="1" style="27" min="2" max="2"/>
     <col width="18" customWidth="1" style="27" min="3" max="4"/>
+    <col width="18" customWidth="1" style="27" min="4" max="4"/>
     <col width="34" customWidth="1" style="27" min="5" max="5"/>
     <col width="14" customWidth="1" style="27" min="6" max="6"/>
     <col width="16" customWidth="1" style="27" min="7" max="7"/>
     <col width="28" bestFit="1" customWidth="1" style="27" min="8" max="8"/>
     <col width="22" customWidth="1" style="27" min="9" max="9"/>
     <col width="14" customWidth="1" style="27" min="10" max="15"/>
+    <col width="14" customWidth="1" style="27" min="11" max="11"/>
+    <col width="14" customWidth="1" style="27" min="12" max="12"/>
+    <col width="14" customWidth="1" style="27" min="13" max="13"/>
+    <col width="14" customWidth="1" style="27" min="14" max="14"/>
+    <col width="14" customWidth="1" style="27" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B1" s="4" t="n"/>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="B1" s="52" t="n"/>
+      <c r="C1" s="52" t="inlineStr">
         <is>
           <t>Store</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="52" t="inlineStr">
         <is>
           <t>Six-Digit SKU</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="52" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="52" t="inlineStr">
         <is>
           <t>Tax Code</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="52" t="inlineStr">
         <is>
           <t>Store Number</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="52" t="inlineStr">
         <is>
           <t>Common Name</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="52" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="52" t="inlineStr">
         <is>
           <t>Date 1</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="52" t="inlineStr">
         <is>
           <t>Price 1</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="52" t="inlineStr">
         <is>
           <t>Date 2</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="M1" s="52" t="inlineStr">
         <is>
           <t>Price 2</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="N1" s="52" t="inlineStr">
         <is>
           <t>Date 3</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="O1" s="52" t="inlineStr">
         <is>
           <t>Price 3</t>
         </is>
@@ -5949,6 +5952,12 @@
       <c r="K51" s="1" t="n">
         <v>4.48</v>
       </c>
+      <c r="L51" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="M51" s="1" t="n">
+        <v>4.48</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1">
@@ -5996,6 +6005,12 @@
       <c r="K52" s="1" t="n">
         <v>6.96</v>
       </c>
+      <c r="L52" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="M52" s="1" t="n">
+        <v>6.96</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1">
@@ -6043,6 +6058,12 @@
       <c r="K53" s="1" t="n">
         <v>8.369999999999999</v>
       </c>
+      <c r="L53" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="M53" s="1" t="n">
+        <v>8.369999999999999</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1">
@@ -6137,6 +6158,12 @@
       <c r="K55" s="1" t="n">
         <v>23.94</v>
       </c>
+      <c r="L55" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="M55" s="1" t="n">
+        <v>23.94</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1">
@@ -6184,6 +6211,12 @@
       <c r="K56" s="1" t="n">
         <v>3.16</v>
       </c>
+      <c r="L56" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="M56" s="1" t="n">
+        <v>3.16</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1">
@@ -6231,6 +6264,12 @@
       <c r="K57" s="1" t="n">
         <v>5.82</v>
       </c>
+      <c r="L57" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="M57" s="1" t="n">
+        <v>5.82</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1">
@@ -6372,6 +6411,12 @@
       <c r="K60" s="1" t="n">
         <v>7.97</v>
       </c>
+      <c r="L60" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="M60" s="1" t="n">
+        <v>7.97</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1">
@@ -6419,6 +6464,12 @@
       <c r="K61" s="1" t="n">
         <v>5.32</v>
       </c>
+      <c r="L61" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="M61" s="1" t="n">
+        <v>5.32</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1">
@@ -6513,6 +6564,12 @@
       <c r="K63" t="n">
         <v>4.97</v>
       </c>
+      <c r="L63" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="M63" s="1" t="n">
+        <v>4.97</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1">
@@ -6560,6 +6617,12 @@
       <c r="K64" s="1" t="n">
         <v>4.97</v>
       </c>
+      <c r="L64" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="M64" s="1" t="n">
+        <v>4.97</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1">
@@ -6607,6 +6670,12 @@
       <c r="K65" s="1" t="n">
         <v>4.88</v>
       </c>
+      <c r="L65" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="M65" s="1" t="n">
+        <v>4.88</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1">
@@ -6654,6 +6723,12 @@
       <c r="K66" s="1" t="n">
         <v>9.67</v>
       </c>
+      <c r="L66" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="M66" s="1" t="n">
+        <v>9.67</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1">
@@ -6748,6 +6823,12 @@
       <c r="K68" s="1" t="n">
         <v>7.96</v>
       </c>
+      <c r="L68" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="M68" s="1" t="n">
+        <v>7.96</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1">
@@ -6795,6 +6876,12 @@
       <c r="K69" s="1" t="n">
         <v>4.97</v>
       </c>
+      <c r="L69" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="M69" s="1" t="n">
+        <v>4.97</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1">
@@ -6842,6 +6929,18 @@
       <c r="K70" s="1" t="n">
         <v>1.83</v>
       </c>
+      <c r="L70" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="M70" s="1" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="O70" s="1" t="n">
+        <v>1.83</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1">
@@ -6889,6 +6988,12 @@
       <c r="K71" s="1" t="n">
         <v>9.98</v>
       </c>
+      <c r="L71" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="M71" s="1" t="n">
+        <v>9.98</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1">
@@ -6983,6 +7088,12 @@
       <c r="K73" s="1" t="n">
         <v>3.48</v>
       </c>
+      <c r="L73" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="M73" s="1" t="n">
+        <v>3.48</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1">
@@ -7125,8 +7236,337 @@
         <v>2.77</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="1">
+        <f>SUM(K77,M77,O77)</f>
+        <v/>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>GHIRARDELLI Gluten Free Double Chocolate Brownie Mix, Gluten Free Baking Mix, Includes Chocolate Chips, 18 oz Box</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="K77" s="1" t="n">
+        <v>6.67</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1">
+        <f>SUM(K78,M78,O78)</f>
+        <v/>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Pampers Swaddlers Fragrance Free Baby Diapers Size 5, 100 Count (Select for More Options</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Baby</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="K78" s="1" t="n">
+        <v>39.77</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1">
+        <f>SUM(K79,M79,O79)</f>
+        <v/>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Chobani Oatmitk Extra Creamy 52 floz Carton 20 shopped Qty1</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Dairy</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="K79" s="1" t="n">
+        <v>4.17</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1">
+        <f>SUM(K80,M80,O80)</f>
+        <v/>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Nestle Tolt House Dark Chocolate Regular Baking Chips, 10 oz Bag 20 shopped Qty1</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="K80" s="1" t="n">
+        <v>4.96</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1">
+        <f>SUM(K81,M81,O81)</f>
+        <v/>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Applegate Natural Chicken &amp; Maple Breakfast Sausage Patties, 16 oz, GF, Resealable Bag (Frozen), About 15 Pieces per Bag</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="K81" s="1" t="n">
+        <v>11.76</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1">
+        <f>SUM(K82,M82,O82)</f>
+        <v/>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>McCormick Sea Salt Grinder, oz Bottle 20 shopped Qty1</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="K82" s="1" t="n">
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1">
+        <f>SUM(K83,M83,O83)</f>
+        <v/>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>3 hours or less</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="K83" s="1" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O74"/>
+  <autoFilter ref="A1:O83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9910,8 +10350,8 @@
     <mergeCell ref="Y59:AG62"/>
     <mergeCell ref="Y237:AG240"/>
     <mergeCell ref="S146:V146"/>
+    <mergeCell ref="S204:V204"/>
     <mergeCell ref="Y176:AG176"/>
-    <mergeCell ref="S204:V204"/>
     <mergeCell ref="S270:V270"/>
     <mergeCell ref="S151:V151"/>
     <mergeCell ref="Y182:AG182"/>
@@ -9926,11 +10366,11 @@
     <mergeCell ref="Y105:AG105"/>
     <mergeCell ref="S140:V140"/>
     <mergeCell ref="Y99:AG99"/>
+    <mergeCell ref="S246:V246"/>
+    <mergeCell ref="S47:V47"/>
+    <mergeCell ref="Y170:AG170"/>
+    <mergeCell ref="S149:V149"/>
     <mergeCell ref="S167:V167"/>
-    <mergeCell ref="S47:V47"/>
-    <mergeCell ref="S149:V149"/>
-    <mergeCell ref="Y170:AG170"/>
-    <mergeCell ref="S246:V246"/>
     <mergeCell ref="S59:V59"/>
     <mergeCell ref="S46:V46"/>
     <mergeCell ref="S248:V248"/>
@@ -10239,7 +10679,7 @@
       <c r="A3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="53" t="n">
+      <c r="B3" s="55" t="n">
         <v>46235</v>
       </c>
       <c r="C3" s="54" t="n">
@@ -11698,31 +12138,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" style="27" min="1" max="1"/>
     <col width="16" customWidth="1" style="27" min="2" max="3"/>
+    <col width="16" customWidth="1" style="27" min="3" max="3"/>
     <col width="22" customWidth="1" style="27" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Source OCR JSON</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="52" t="inlineStr">
         <is>
           <t>Store Number</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="52" t="inlineStr">
         <is>
           <t>Receipt Date</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="52" t="inlineStr">
         <is>
           <t>Imported Timestamp</t>
         </is>
@@ -11816,6 +12257,24 @@
       </c>
       <c r="D6" s="3" t="n">
         <v>46261.87458537037</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>080726_Walmart_0_raw_ocr.json</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="D7" s="56" t="n">
+        <v>46262.59873947963</v>
       </c>
     </row>
   </sheetData>

--- a/data/database/shopgraph_purchase_history.xlsx
+++ b/data/database/shopgraph_purchase_history.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Imported Receipts" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Purchase History'!$A$1:$O$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Purchase History'!$A$1:$O$99</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -27,9 +27,9 @@
     <numFmt numFmtId="167" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="168" formatCode="$#,##0.00"/>
     <numFmt numFmtId="169" formatCode="mmm yyyy"/>
-    <numFmt numFmtId="170" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="171" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="172" formatCode="mm/dd/yyyy hh:mm"/>
+    <numFmt numFmtId="170" formatCode="mm/dd/yyyy hh:mm"/>
+    <numFmt numFmtId="171" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="172" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -265,7 +265,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -354,7 +354,8 @@
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3468,7 +3469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="27" min="1" max="1"/>
@@ -7094,6 +7095,12 @@
       <c r="M73" s="1" t="n">
         <v>3.48</v>
       </c>
+      <c r="N73" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="O73" s="1" t="n">
+        <v>1.76</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1">
@@ -7141,6 +7148,12 @@
       <c r="K74" s="1" t="n">
         <v>16.92</v>
       </c>
+      <c r="L74" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="M74" s="1" t="n">
+        <v>17.72</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1">
@@ -7565,8 +7578,784 @@
         <v>5</v>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="1">
+        <f>SUM(K84,M84,O84)</f>
+        <v/>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Nature's Bakery Gluten Free Raspberry Fig Bars in Twin pack Box, 20z Each 36 shopped Qty1</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="K84" s="1" t="n">
+        <v>5.97</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1">
+        <f>SUM(K85,M85,O85)</f>
+        <v/>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Mahatma Jasmine Rice, Thai Fragrant Long Grain Rice, Gluten Free, 80 oz Bag (5 lbs</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="K85" s="1" t="n">
+        <v>6.88</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1">
+        <f>SUM(K86,M86,O86)</f>
+        <v/>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Hillshire Farm Ultra Thin Oven Roasted Turkey Breast Lunchmeat, 16 oz Plastic Tub, Refrigerated</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Meat &amp; Seafood</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="K86" s="1" t="n">
+        <v>6.48</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1">
+        <f>SUM(K87,M87,O87)</f>
+        <v/>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Hebrew National 100% Kosher Beef Franks, Hot Dogs, 10.3 oz 6 Count</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Meat &amp; Seafood</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="K87" s="1" t="n">
+        <v>5.74</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1">
+        <f>SUM(K88,M88,O88)</f>
+        <v/>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Dave's Killer Bread Organic Oats &amp; Blues Regular Size Loaf, 25 oz, USDA Organic</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="K88" s="1" t="n">
+        <v>5.98</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1">
+        <f>SUM(K89,M89,O89)</f>
+        <v/>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Birds Eye Steamfresh Sweet Peas, Frozen Vegetables, 10 oz. Bag</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Frozen</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="K89" s="1" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1">
+        <f>SUM(K90,M90,O90)</f>
+        <v/>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Cabot Creamery 4 Cheese Mexican Shredded Cheddar Cheese 2 lb (Refrigerated</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Dairy</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="K90" s="1" t="n">
+        <v>11.93</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1">
+        <f>SUM(K91,M91,O91)</f>
+        <v/>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Ziploc Brand Slider Gallon Freezer Food Storage Bags, School Supplies, with Power Shield Technology, 40 Count</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="K91" s="1" t="n">
+        <v>7.98</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1">
+        <f>SUM(K92,M92,O92)</f>
+        <v/>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Ziploc Brand Freezer Food Storage Bags, School Supplies, with Grip 'n Seal Technology, Zipper, Quart, 50 Count</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="K92" s="1" t="n">
+        <v>6.48</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1">
+        <f>SUM(K93,M93,O93)</f>
+        <v/>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Fresh Mini Cucumbers, 16 oz</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="K93" s="1" t="n">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1">
+        <f>SUM(K94,M94,O94)</f>
+        <v/>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2 pack) Yehuda Sabbath Candles,12ct</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="K94" s="1" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1">
+        <f>SUM(K95,M95,O95)</f>
+        <v/>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Fresh Yellow Squash, Each 11 weight adjusted aty1</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="K95" s="1" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="M95" s="1" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1">
+        <f>SUM(K96,M96,O96)</f>
+        <v/>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Fresh Zucchini, Each 11 weight adjusted aty1</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Zucchini</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="K96" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="M96" s="1" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1">
+        <f>SUM(K97,M97,O97)</f>
+        <v/>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Fresh Whole Red Onion, Each</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="K97" s="1" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="M97" s="1" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1">
+        <f>SUM(K98,M98,O98)</f>
+        <v/>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Fresh Tomato on the Vine, Bag (1.9 lbs/Bag Est.) 11 weight adjusted Qty1</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="K98" s="1" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1">
+        <f>SUM(K99,M99,O99)</f>
+        <v/>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Fresh Banana, Each 11 weight adjusted Qty7</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="K99" s="1" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="M99" s="1" t="n">
+        <v>1.76</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O83"/>
+  <autoFilter ref="A1:O99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12138,7 +12927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" style="27" min="1" max="1"/>
@@ -12273,8 +13062,44 @@
       <c r="C7" s="2" t="n">
         <v>46241</v>
       </c>
-      <c r="D7" s="56" t="n">
-        <v>46262.59873947963</v>
+      <c r="D7" s="57" t="n">
+        <v>46262.59873947917</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>081326_Walmart_0_raw_ocr.json</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="D8" s="57" t="n">
+        <v>46262.65887388889</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>081326_Walmart_0_B_raw_ocr.json</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="D9" s="57" t="n">
+        <v>46262.66004273877</v>
       </c>
     </row>
   </sheetData>

--- a/data/database/shopgraph_purchase_history.xlsx
+++ b/data/database/shopgraph_purchase_history.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Imported Receipts" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Purchase History'!$A$1:$O$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Purchase History'!$A$1:$S$106</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -3469,7 +3469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:S106"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="27" min="1" max="1"/>
@@ -3487,6 +3487,10 @@
     <col width="14" customWidth="1" style="27" min="13" max="13"/>
     <col width="14" customWidth="1" style="27" min="14" max="14"/>
     <col width="14" customWidth="1" style="27" min="15" max="15"/>
+    <col width="14" customWidth="1" style="27" min="16" max="16"/>
+    <col width="14" customWidth="1" style="27" min="17" max="17"/>
+    <col width="14" customWidth="1" style="27" min="18" max="18"/>
+    <col width="14" customWidth="1" style="27" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3561,10 +3565,30 @@
           <t>Price 3</t>
         </is>
       </c>
+      <c r="P1" s="52" t="inlineStr">
+        <is>
+          <t>Date 4</t>
+        </is>
+      </c>
+      <c r="Q1" s="52" t="inlineStr">
+        <is>
+          <t>Price 4</t>
+        </is>
+      </c>
+      <c r="R1" s="52" t="inlineStr">
+        <is>
+          <t>Date 5</t>
+        </is>
+      </c>
+      <c r="S1" s="52" t="inlineStr">
+        <is>
+          <t>Price 5</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1">
-        <f>SUM(K2,M2,O2)</f>
+        <f>SUM(K2,M2,O2,Q2,S2)</f>
         <v/>
       </c>
       <c r="C2" t="inlineStr">
@@ -3611,7 +3635,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1">
-        <f>SUM(K3,M3,O3)</f>
+        <f>SUM(K3,M3,O3,Q3,S3)</f>
         <v/>
       </c>
       <c r="C3" t="inlineStr">
@@ -3658,7 +3682,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1">
-        <f>SUM(K4,M4,O4)</f>
+        <f>SUM(K4,M4,O4,Q4,S4)</f>
         <v/>
       </c>
       <c r="C4" t="inlineStr">
@@ -3705,7 +3729,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1">
-        <f>SUM(K5,M5,O5)</f>
+        <f>SUM(K5,M5,O5,Q5,S5)</f>
         <v/>
       </c>
       <c r="C5" t="inlineStr">
@@ -3758,7 +3782,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1">
-        <f>SUM(K6,M6,O6)</f>
+        <f>SUM(K6,M6,O6,Q6,S6)</f>
         <v/>
       </c>
       <c r="C6" t="inlineStr">
@@ -3805,7 +3829,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1">
-        <f>SUM(K7,M7,O7)</f>
+        <f>SUM(K7,M7,O7,Q7,S7)</f>
         <v/>
       </c>
       <c r="C7" t="inlineStr">
@@ -3864,7 +3888,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1">
-        <f>SUM(K8,M8,O8)</f>
+        <f>SUM(K8,M8,O8,Q8,S8)</f>
         <v/>
       </c>
       <c r="C8" t="inlineStr">
@@ -3911,7 +3935,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1">
-        <f>SUM(K9,M9,O9)</f>
+        <f>SUM(K9,M9,O9,Q9,S9)</f>
         <v/>
       </c>
       <c r="C9" t="inlineStr">
@@ -3958,7 +3982,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1">
-        <f>SUM(K10,M10,O10)</f>
+        <f>SUM(K10,M10,O10,Q10,S10)</f>
         <v/>
       </c>
       <c r="C10" t="inlineStr">
@@ -4005,7 +4029,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1">
-        <f>SUM(K11,M11,O11)</f>
+        <f>SUM(K11,M11,O11,Q11,S11)</f>
         <v/>
       </c>
       <c r="C11" t="inlineStr">
@@ -4052,7 +4076,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1">
-        <f>SUM(K12,M12,O12)</f>
+        <f>SUM(K12,M12,O12,Q12,S12)</f>
         <v/>
       </c>
       <c r="C12" t="inlineStr">
@@ -4099,7 +4123,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1">
-        <f>SUM(K13,M13,O13)</f>
+        <f>SUM(K13,M13,O13,Q13,S13)</f>
         <v/>
       </c>
       <c r="C13" t="inlineStr">
@@ -4146,7 +4170,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1">
-        <f>SUM(K14,M14,O14)</f>
+        <f>SUM(K14,M14,O14,Q14,S14)</f>
         <v/>
       </c>
       <c r="C14" t="inlineStr">
@@ -4193,7 +4217,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1">
-        <f>SUM(K15,M15,O15)</f>
+        <f>SUM(K15,M15,O15,Q15,S15)</f>
         <v/>
       </c>
       <c r="C15" t="inlineStr">
@@ -4240,7 +4264,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1">
-        <f>SUM(K16,M16,O16)</f>
+        <f>SUM(K16,M16,O16,Q16,S16)</f>
         <v/>
       </c>
       <c r="C16" t="inlineStr">
@@ -4287,7 +4311,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1">
-        <f>SUM(K17,M17,O17)</f>
+        <f>SUM(K17,M17,O17,Q17,S17)</f>
         <v/>
       </c>
       <c r="C17" t="inlineStr">
@@ -4334,7 +4358,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1">
-        <f>SUM(K18,M18,O18)</f>
+        <f>SUM(K18,M18,O18,Q18,S18)</f>
         <v/>
       </c>
       <c r="C18" t="inlineStr">
@@ -4381,7 +4405,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1">
-        <f>SUM(K19,M19,O19)</f>
+        <f>SUM(K19,M19,O19,Q19,S19)</f>
         <v/>
       </c>
       <c r="C19" t="inlineStr">
@@ -4428,7 +4452,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1">
-        <f>SUM(K20,M20,O20)</f>
+        <f>SUM(K20,M20,O20,Q20,S20)</f>
         <v/>
       </c>
       <c r="C20" t="inlineStr">
@@ -4475,7 +4499,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1">
-        <f>SUM(K21,M21,O21)</f>
+        <f>SUM(K21,M21,O21,Q21,S21)</f>
         <v/>
       </c>
       <c r="C21" t="inlineStr">
@@ -4522,7 +4546,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1">
-        <f>SUM(K22,M22,O22)</f>
+        <f>SUM(K22,M22,O22,Q22,S22)</f>
         <v/>
       </c>
       <c r="C22" t="inlineStr">
@@ -4569,7 +4593,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1">
-        <f>SUM(K23,M23,O23)</f>
+        <f>SUM(K23,M23,O23,Q23,S23)</f>
         <v/>
       </c>
       <c r="C23" t="inlineStr">
@@ -4616,7 +4640,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1">
-        <f>SUM(K24,M24,O24)</f>
+        <f>SUM(K24,M24,O24,Q24,S24)</f>
         <v/>
       </c>
       <c r="C24" t="inlineStr">
@@ -4663,7 +4687,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1">
-        <f>SUM(K25,M25,O25)</f>
+        <f>SUM(K25,M25,O25,Q25,S25)</f>
         <v/>
       </c>
       <c r="C25" t="inlineStr">
@@ -4710,7 +4734,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1">
-        <f>SUM(K26,M26,O26)</f>
+        <f>SUM(K26,M26,O26,Q26,S26)</f>
         <v/>
       </c>
       <c r="C26" t="inlineStr">
@@ -4763,7 +4787,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1">
-        <f>SUM(K27,M27,O27)</f>
+        <f>SUM(K27,M27,O27,Q27,S27)</f>
         <v/>
       </c>
       <c r="C27" t="inlineStr">
@@ -4810,7 +4834,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1">
-        <f>SUM(K28,M28,O28)</f>
+        <f>SUM(K28,M28,O28,Q28,S28)</f>
         <v/>
       </c>
       <c r="C28" t="inlineStr">
@@ -4863,7 +4887,7 @@
     </row>
     <row r="29">
       <c r="A29" s="1">
-        <f>SUM(K29,M29,O29)</f>
+        <f>SUM(K29,M29,O29,Q29,S29)</f>
         <v/>
       </c>
       <c r="C29" t="inlineStr">
@@ -4916,7 +4940,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1">
-        <f>SUM(K30,M30,O30)</f>
+        <f>SUM(K30,M30,O30,Q30,S30)</f>
         <v/>
       </c>
       <c r="C30" t="inlineStr">
@@ -4963,7 +4987,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1">
-        <f>SUM(K31,M31,O31)</f>
+        <f>SUM(K31,M31,O31,Q31,S31)</f>
         <v/>
       </c>
       <c r="C31" t="inlineStr">
@@ -5010,7 +5034,7 @@
     </row>
     <row r="32">
       <c r="A32" s="1">
-        <f>SUM(K32,M32,O32)</f>
+        <f>SUM(K32,M32,O32,Q32,S32)</f>
         <v/>
       </c>
       <c r="C32" t="inlineStr">
@@ -5057,7 +5081,7 @@
     </row>
     <row r="33">
       <c r="A33" s="1">
-        <f>SUM(K33,M33,O33)</f>
+        <f>SUM(K33,M33,O33,Q33,S33)</f>
         <v/>
       </c>
       <c r="C33" t="inlineStr">
@@ -5104,7 +5128,7 @@
     </row>
     <row r="34">
       <c r="A34" s="1">
-        <f>SUM(K34,M34,O34)</f>
+        <f>SUM(K34,M34,O34,Q34,S34)</f>
         <v/>
       </c>
       <c r="C34" t="inlineStr">
@@ -5151,7 +5175,7 @@
     </row>
     <row r="35">
       <c r="A35" s="1">
-        <f>SUM(K35,M35,O35)</f>
+        <f>SUM(K35,M35,O35,Q35,S35)</f>
         <v/>
       </c>
       <c r="C35" t="inlineStr">
@@ -5198,7 +5222,7 @@
     </row>
     <row r="36">
       <c r="A36" s="1">
-        <f>SUM(K36,M36,O36)</f>
+        <f>SUM(K36,M36,O36,Q36,S36)</f>
         <v/>
       </c>
       <c r="C36" t="inlineStr">
@@ -5245,7 +5269,7 @@
     </row>
     <row r="37">
       <c r="A37" s="1">
-        <f>SUM(K37,M37,O37)</f>
+        <f>SUM(K37,M37,O37,Q37,S37)</f>
         <v/>
       </c>
       <c r="C37" t="inlineStr">
@@ -5292,7 +5316,7 @@
     </row>
     <row r="38">
       <c r="A38" s="1">
-        <f>SUM(K38,M38,O38)</f>
+        <f>SUM(K38,M38,O38,Q38,S38)</f>
         <v/>
       </c>
       <c r="C38" t="inlineStr">
@@ -5339,7 +5363,7 @@
     </row>
     <row r="39">
       <c r="A39" s="1">
-        <f>SUM(K39,M39,O39)</f>
+        <f>SUM(K39,M39,O39,Q39,S39)</f>
         <v/>
       </c>
       <c r="C39" t="inlineStr">
@@ -5386,7 +5410,7 @@
     </row>
     <row r="40">
       <c r="A40" s="1">
-        <f>SUM(K40,M40,O40)</f>
+        <f>SUM(K40,M40,O40,Q40,S40)</f>
         <v/>
       </c>
       <c r="C40" t="inlineStr">
@@ -5439,7 +5463,7 @@
     </row>
     <row r="41">
       <c r="A41" s="1">
-        <f>SUM(K41,M41,O41)</f>
+        <f>SUM(K41,M41,O41,Q41,S41)</f>
         <v/>
       </c>
       <c r="C41" t="inlineStr">
@@ -5486,7 +5510,7 @@
     </row>
     <row r="42">
       <c r="A42" s="1">
-        <f>SUM(K42,M42,O42)</f>
+        <f>SUM(K42,M42,O42,Q42,S42)</f>
         <v/>
       </c>
       <c r="C42" t="inlineStr">
@@ -5533,7 +5557,7 @@
     </row>
     <row r="43">
       <c r="A43" s="1">
-        <f>SUM(K43,M43,O43)</f>
+        <f>SUM(K43,M43,O43,Q43,S43)</f>
         <v/>
       </c>
       <c r="C43" t="inlineStr">
@@ -5580,7 +5604,7 @@
     </row>
     <row r="44">
       <c r="A44" s="1">
-        <f>SUM(K44,M44,O44)</f>
+        <f>SUM(K44,M44,O44,Q44,S44)</f>
         <v/>
       </c>
       <c r="C44" t="inlineStr">
@@ -5627,7 +5651,7 @@
     </row>
     <row r="45">
       <c r="A45" s="1">
-        <f>SUM(K45,M45,O45)</f>
+        <f>SUM(K45,M45,O45,Q45,S45)</f>
         <v/>
       </c>
       <c r="C45" t="inlineStr">
@@ -5674,7 +5698,7 @@
     </row>
     <row r="46">
       <c r="A46" s="1">
-        <f>SUM(K46,M46,O46)</f>
+        <f>SUM(K46,M46,O46,Q46,S46)</f>
         <v/>
       </c>
       <c r="C46" t="inlineStr">
@@ -5721,7 +5745,7 @@
     </row>
     <row r="47">
       <c r="A47" s="1">
-        <f>SUM(K47,M47,O47)</f>
+        <f>SUM(K47,M47,O47,Q47,S47)</f>
         <v/>
       </c>
       <c r="C47" t="inlineStr">
@@ -5768,7 +5792,7 @@
     </row>
     <row r="48">
       <c r="A48" s="1">
-        <f>SUM(K48,M48,O48)</f>
+        <f>SUM(K48,M48,O48,Q48,S48)</f>
         <v/>
       </c>
       <c r="C48" t="inlineStr">
@@ -5815,7 +5839,7 @@
     </row>
     <row r="49">
       <c r="A49" s="1">
-        <f>SUM(K49,M49,O49)</f>
+        <f>SUM(K49,M49,O49,Q49,S49)</f>
         <v/>
       </c>
       <c r="C49" t="inlineStr">
@@ -5862,7 +5886,7 @@
     </row>
     <row r="50">
       <c r="A50" s="1">
-        <f>SUM(K50,M50,O50)</f>
+        <f>SUM(K50,M50,O50,Q50,S50)</f>
         <v/>
       </c>
       <c r="C50" t="inlineStr">
@@ -5909,7 +5933,7 @@
     </row>
     <row r="51">
       <c r="A51" s="1">
-        <f>SUM(K51,M51,O51)</f>
+        <f>SUM(K51,M51,O51,Q51,S51)</f>
         <v/>
       </c>
       <c r="C51" t="inlineStr">
@@ -5962,7 +5986,7 @@
     </row>
     <row r="52">
       <c r="A52" s="1">
-        <f>SUM(K52,M52,O52)</f>
+        <f>SUM(K52,M52,O52,Q52,S52)</f>
         <v/>
       </c>
       <c r="C52" t="inlineStr">
@@ -6015,7 +6039,7 @@
     </row>
     <row r="53">
       <c r="A53" s="1">
-        <f>SUM(K53,M53,O53)</f>
+        <f>SUM(K53,M53,O53,Q53,S53)</f>
         <v/>
       </c>
       <c r="C53" t="inlineStr">
@@ -6068,7 +6092,7 @@
     </row>
     <row r="54">
       <c r="A54" s="1">
-        <f>SUM(K54,M54,O54)</f>
+        <f>SUM(K54,M54,O54,Q54,S54)</f>
         <v/>
       </c>
       <c r="C54" t="inlineStr">
@@ -6115,7 +6139,7 @@
     </row>
     <row r="55">
       <c r="A55" s="1">
-        <f>SUM(K55,M55,O55)</f>
+        <f>SUM(K55,M55,O55,Q55,S55)</f>
         <v/>
       </c>
       <c r="C55" t="inlineStr">
@@ -6168,7 +6192,7 @@
     </row>
     <row r="56">
       <c r="A56" s="1">
-        <f>SUM(K56,M56,O56)</f>
+        <f>SUM(K56,M56,O56,Q56,S56)</f>
         <v/>
       </c>
       <c r="C56" t="inlineStr">
@@ -6221,7 +6245,7 @@
     </row>
     <row r="57">
       <c r="A57" s="1">
-        <f>SUM(K57,M57,O57)</f>
+        <f>SUM(K57,M57,O57,Q57,S57)</f>
         <v/>
       </c>
       <c r="C57" t="inlineStr">
@@ -6274,7 +6298,7 @@
     </row>
     <row r="58">
       <c r="A58" s="1">
-        <f>SUM(K58,M58,O58)</f>
+        <f>SUM(K58,M58,O58,Q58,S58)</f>
         <v/>
       </c>
       <c r="C58" t="inlineStr">
@@ -6321,7 +6345,7 @@
     </row>
     <row r="59">
       <c r="A59" s="1">
-        <f>SUM(K59,M59,O59)</f>
+        <f>SUM(K59,M59,O59,Q59,S59)</f>
         <v/>
       </c>
       <c r="C59" t="inlineStr">
@@ -6368,7 +6392,7 @@
     </row>
     <row r="60">
       <c r="A60" s="1">
-        <f>SUM(K60,M60,O60)</f>
+        <f>SUM(K60,M60,O60,Q60,S60)</f>
         <v/>
       </c>
       <c r="C60" t="inlineStr">
@@ -6421,7 +6445,7 @@
     </row>
     <row r="61">
       <c r="A61" s="1">
-        <f>SUM(K61,M61,O61)</f>
+        <f>SUM(K61,M61,O61,Q61,S61)</f>
         <v/>
       </c>
       <c r="C61" t="inlineStr">
@@ -6474,7 +6498,7 @@
     </row>
     <row r="62">
       <c r="A62" s="1">
-        <f>SUM(K62,M62,O62)</f>
+        <f>SUM(K62,M62,O62,Q62,S62)</f>
         <v/>
       </c>
       <c r="C62" t="inlineStr">
@@ -6521,7 +6545,7 @@
     </row>
     <row r="63">
       <c r="A63" s="1">
-        <f>SUM(K63,M63,O63)</f>
+        <f>SUM(K63,M63,O63,Q63,S63)</f>
         <v/>
       </c>
       <c r="C63" t="inlineStr">
@@ -6574,7 +6598,7 @@
     </row>
     <row r="64">
       <c r="A64" s="1">
-        <f>SUM(K64,M64,O64)</f>
+        <f>SUM(K64,M64,O64,Q64,S64)</f>
         <v/>
       </c>
       <c r="C64" t="inlineStr">
@@ -6627,7 +6651,7 @@
     </row>
     <row r="65">
       <c r="A65" s="1">
-        <f>SUM(K65,M65,O65)</f>
+        <f>SUM(K65,M65,O65,Q65,S65)</f>
         <v/>
       </c>
       <c r="C65" t="inlineStr">
@@ -6680,7 +6704,7 @@
     </row>
     <row r="66">
       <c r="A66" s="1">
-        <f>SUM(K66,M66,O66)</f>
+        <f>SUM(K66,M66,O66,Q66,S66)</f>
         <v/>
       </c>
       <c r="C66" t="inlineStr">
@@ -6733,7 +6757,7 @@
     </row>
     <row r="67">
       <c r="A67" s="1">
-        <f>SUM(K67,M67,O67)</f>
+        <f>SUM(K67,M67,O67,Q67,S67)</f>
         <v/>
       </c>
       <c r="C67" t="inlineStr">
@@ -6780,7 +6804,7 @@
     </row>
     <row r="68">
       <c r="A68" s="1">
-        <f>SUM(K68,M68,O68)</f>
+        <f>SUM(K68,M68,O68,Q68,S68)</f>
         <v/>
       </c>
       <c r="C68" t="inlineStr">
@@ -6833,7 +6857,7 @@
     </row>
     <row r="69">
       <c r="A69" s="1">
-        <f>SUM(K69,M69,O69)</f>
+        <f>SUM(K69,M69,O69,Q69,S69)</f>
         <v/>
       </c>
       <c r="C69" t="inlineStr">
@@ -6886,7 +6910,7 @@
     </row>
     <row r="70">
       <c r="A70" s="1">
-        <f>SUM(K70,M70,O70)</f>
+        <f>SUM(K70,M70,O70,Q70,S70)</f>
         <v/>
       </c>
       <c r="C70" t="inlineStr">
@@ -6945,7 +6969,7 @@
     </row>
     <row r="71">
       <c r="A71" s="1">
-        <f>SUM(K71,M71,O71)</f>
+        <f>SUM(K71,M71,O71,Q71,S71)</f>
         <v/>
       </c>
       <c r="C71" t="inlineStr">
@@ -6998,7 +7022,7 @@
     </row>
     <row r="72">
       <c r="A72" s="1">
-        <f>SUM(K72,M72,O72)</f>
+        <f>SUM(K72,M72,O72,Q72,S72)</f>
         <v/>
       </c>
       <c r="C72" t="inlineStr">
@@ -7045,7 +7069,7 @@
     </row>
     <row r="73">
       <c r="A73" s="1">
-        <f>SUM(K73,M73,O73)</f>
+        <f>SUM(K73,M73,O73,Q73,S73)</f>
         <v/>
       </c>
       <c r="C73" t="inlineStr">
@@ -7101,10 +7125,22 @@
       <c r="O73" s="1" t="n">
         <v>1.76</v>
       </c>
+      <c r="P73" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="Q73" s="1" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="R73" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="S73" s="1" t="n">
+        <v>6.35</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1">
-        <f>SUM(K74,M74,O74)</f>
+        <f>SUM(K74,M74,O74,Q74,S74)</f>
         <v/>
       </c>
       <c r="C74" t="inlineStr">
@@ -7154,10 +7190,16 @@
       <c r="M74" s="1" t="n">
         <v>17.72</v>
       </c>
+      <c r="N74" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="O74" s="1" t="n">
+        <v>12.14</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1">
-        <f>SUM(K75,M75,O75)</f>
+        <f>SUM(K75,M75,O75,Q75,S75)</f>
         <v/>
       </c>
       <c r="C75" t="inlineStr">
@@ -7204,7 +7246,7 @@
     </row>
     <row r="76">
       <c r="A76" s="1">
-        <f>SUM(K76,M76,O76)</f>
+        <f>SUM(K76,M76,O76,Q76,S76)</f>
         <v/>
       </c>
       <c r="C76" t="inlineStr">
@@ -7251,7 +7293,7 @@
     </row>
     <row r="77">
       <c r="A77" s="1">
-        <f>SUM(K77,M77,O77)</f>
+        <f>SUM(K77,M77,O77,Q77,S77)</f>
         <v/>
       </c>
       <c r="C77" t="inlineStr">
@@ -7298,7 +7340,7 @@
     </row>
     <row r="78">
       <c r="A78" s="1">
-        <f>SUM(K78,M78,O78)</f>
+        <f>SUM(K78,M78,O78,Q78,S78)</f>
         <v/>
       </c>
       <c r="C78" t="inlineStr">
@@ -7345,7 +7387,7 @@
     </row>
     <row r="79">
       <c r="A79" s="1">
-        <f>SUM(K79,M79,O79)</f>
+        <f>SUM(K79,M79,O79,Q79,S79)</f>
         <v/>
       </c>
       <c r="C79" t="inlineStr">
@@ -7392,7 +7434,7 @@
     </row>
     <row r="80">
       <c r="A80" s="1">
-        <f>SUM(K80,M80,O80)</f>
+        <f>SUM(K80,M80,O80,Q80,S80)</f>
         <v/>
       </c>
       <c r="C80" t="inlineStr">
@@ -7439,7 +7481,7 @@
     </row>
     <row r="81">
       <c r="A81" s="1">
-        <f>SUM(K81,M81,O81)</f>
+        <f>SUM(K81,M81,O81,Q81,S81)</f>
         <v/>
       </c>
       <c r="C81" t="inlineStr">
@@ -7486,7 +7528,7 @@
     </row>
     <row r="82">
       <c r="A82" s="1">
-        <f>SUM(K82,M82,O82)</f>
+        <f>SUM(K82,M82,O82,Q82,S82)</f>
         <v/>
       </c>
       <c r="C82" t="inlineStr">
@@ -7533,7 +7575,7 @@
     </row>
     <row r="83">
       <c r="A83" s="1">
-        <f>SUM(K83,M83,O83)</f>
+        <f>SUM(K83,M83,O83,Q83,S83)</f>
         <v/>
       </c>
       <c r="C83" t="inlineStr">
@@ -7580,7 +7622,7 @@
     </row>
     <row r="84">
       <c r="A84" s="1">
-        <f>SUM(K84,M84,O84)</f>
+        <f>SUM(K84,M84,O84,Q84,S84)</f>
         <v/>
       </c>
       <c r="C84" t="inlineStr">
@@ -7627,7 +7669,7 @@
     </row>
     <row r="85">
       <c r="A85" s="1">
-        <f>SUM(K85,M85,O85)</f>
+        <f>SUM(K85,M85,O85,Q85,S85)</f>
         <v/>
       </c>
       <c r="C85" t="inlineStr">
@@ -7674,7 +7716,7 @@
     </row>
     <row r="86">
       <c r="A86" s="1">
-        <f>SUM(K86,M86,O86)</f>
+        <f>SUM(K86,M86,O86,Q86,S86)</f>
         <v/>
       </c>
       <c r="C86" t="inlineStr">
@@ -7721,7 +7763,7 @@
     </row>
     <row r="87">
       <c r="A87" s="1">
-        <f>SUM(K87,M87,O87)</f>
+        <f>SUM(K87,M87,O87,Q87,S87)</f>
         <v/>
       </c>
       <c r="C87" t="inlineStr">
@@ -7768,7 +7810,7 @@
     </row>
     <row r="88">
       <c r="A88" s="1">
-        <f>SUM(K88,M88,O88)</f>
+        <f>SUM(K88,M88,O88,Q88,S88)</f>
         <v/>
       </c>
       <c r="C88" t="inlineStr">
@@ -7815,7 +7857,7 @@
     </row>
     <row r="89">
       <c r="A89" s="1">
-        <f>SUM(K89,M89,O89)</f>
+        <f>SUM(K89,M89,O89,Q89,S89)</f>
         <v/>
       </c>
       <c r="C89" t="inlineStr">
@@ -7862,7 +7904,7 @@
     </row>
     <row r="90">
       <c r="A90" s="1">
-        <f>SUM(K90,M90,O90)</f>
+        <f>SUM(K90,M90,O90,Q90,S90)</f>
         <v/>
       </c>
       <c r="C90" t="inlineStr">
@@ -7909,7 +7951,7 @@
     </row>
     <row r="91">
       <c r="A91" s="1">
-        <f>SUM(K91,M91,O91)</f>
+        <f>SUM(K91,M91,O91,Q91,S91)</f>
         <v/>
       </c>
       <c r="C91" t="inlineStr">
@@ -7956,7 +7998,7 @@
     </row>
     <row r="92">
       <c r="A92" s="1">
-        <f>SUM(K92,M92,O92)</f>
+        <f>SUM(K92,M92,O92,Q92,S92)</f>
         <v/>
       </c>
       <c r="C92" t="inlineStr">
@@ -8003,7 +8045,7 @@
     </row>
     <row r="93">
       <c r="A93" s="1">
-        <f>SUM(K93,M93,O93)</f>
+        <f>SUM(K93,M93,O93,Q93,S93)</f>
         <v/>
       </c>
       <c r="C93" t="inlineStr">
@@ -8050,7 +8092,7 @@
     </row>
     <row r="94">
       <c r="A94" s="1">
-        <f>SUM(K94,M94,O94)</f>
+        <f>SUM(K94,M94,O94,Q94,S94)</f>
         <v/>
       </c>
       <c r="C94" t="inlineStr">
@@ -8097,7 +8139,7 @@
     </row>
     <row r="95">
       <c r="A95" s="1">
-        <f>SUM(K95,M95,O95)</f>
+        <f>SUM(K95,M95,O95,Q95,S95)</f>
         <v/>
       </c>
       <c r="C95" t="inlineStr">
@@ -8150,7 +8192,7 @@
     </row>
     <row r="96">
       <c r="A96" s="1">
-        <f>SUM(K96,M96,O96)</f>
+        <f>SUM(K96,M96,O96,Q96,S96)</f>
         <v/>
       </c>
       <c r="C96" t="inlineStr">
@@ -8203,7 +8245,7 @@
     </row>
     <row r="97">
       <c r="A97" s="1">
-        <f>SUM(K97,M97,O97)</f>
+        <f>SUM(K97,M97,O97,Q97,S97)</f>
         <v/>
       </c>
       <c r="C97" t="inlineStr">
@@ -8256,7 +8298,7 @@
     </row>
     <row r="98">
       <c r="A98" s="1">
-        <f>SUM(K98,M98,O98)</f>
+        <f>SUM(K98,M98,O98,Q98,S98)</f>
         <v/>
       </c>
       <c r="C98" t="inlineStr">
@@ -8303,7 +8345,7 @@
     </row>
     <row r="99">
       <c r="A99" s="1">
-        <f>SUM(K99,M99,O99)</f>
+        <f>SUM(K99,M99,O99,Q99,S99)</f>
         <v/>
       </c>
       <c r="C99" t="inlineStr">
@@ -8354,8 +8396,345 @@
         <v>1.76</v>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="1">
+        <f>SUM(K100,M100,O100,Q100,S100)</f>
+        <v/>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Command Heavy Duty Picture Hangers, Hold 20 tbs, Black, Damage-Free Hanging, 8 Pairs Adhesive Strips</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="K100" s="1" t="n">
+        <v>28.54</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1">
+        <f>SUM(K101,M101,O101,Q101,S101)</f>
+        <v/>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Dove Men+Care Antiperspirant Deodorant Stick 72-Hour Sweat &amp; Odor Protection Clean Comfort Antiperspirant For Men</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1">
+        <f>SUM(K102,M102,O102,Q102,S102)</f>
+        <v/>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Dawn Ultra 11" Puff Glassware and Dish Cleaning Brush Wand with Sponge Head</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="K102" s="1" t="n">
+        <v>4.46</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1">
+        <f>SUM(K103,M103,O103,Q103,S103)</f>
+        <v/>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Once Upon a Farm Organic Tractor Wheels Toddler Bar, Apple, Sweet Potato &amp; Spinach, 10ct</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="K103" s="1" t="n">
+        <v>9.98</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1">
+        <f>SUM(K104,M104,O104,Q104,S104)</f>
+        <v/>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Weiman Granite &amp; Stone Disinfectant Cleaner &amp; Polish, 24 floz</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Household</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="K104" s="1" t="n">
+        <v>6.24</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1">
+        <f>SUM(K105,M105,O105,Q105,S105)</f>
+        <v/>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Chobani Low-Fat Vanilla Greek Yogurt Mixed Berry On The Bottom, Hero Batch z 4PK</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="K105" s="1" t="n">
+        <v>4.67</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1">
+        <f>SUM(K106,M106,O106,Q106,S106)</f>
+        <v/>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Fresh Banana, Each 4 weight adjusted aty4</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="K106" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="M106" s="1" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O99"/>
+  <autoFilter ref="A1:S106"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12927,7 +13306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" style="27" min="1" max="1"/>
@@ -13099,7 +13478,25 @@
         <v>46247</v>
       </c>
       <c r="D9" s="57" t="n">
-        <v>46262.66004273877</v>
+        <v>46262.66004274305</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>082626_Walmart_0_raw_ocr.json</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="D10" s="57" t="n">
+        <v>46262.67645812407</v>
       </c>
     </row>
   </sheetData>

--- a/data/database/shopgraph_purchase_history.xlsx
+++ b/data/database/shopgraph_purchase_history.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/carlosgarzon/Desktop/Engineering/ShopGraph/shopping_analysis/data/database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEEC37D8-F518-234F-95EA-1217A1CCF8D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D60136-D96D-8449-A8E0-CECA70A8F933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="940" yWindow="760" windowWidth="33620" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Purchase History" sheetId="1" r:id="rId1"/>
     <sheet name="Analytics" sheetId="2" r:id="rId2"/>
-    <sheet name="_AnalyticsData" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet name="Imported Receipts" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId3"/>
+    <sheet name="_AnalyticsData" sheetId="3" state="hidden" r:id="rId4"/>
+    <sheet name="Imported Receipts" sheetId="4" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Purchase History'!$A$1:$S$122</definedName>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1634" uniqueCount="515">
   <si>
     <t>Total</t>
   </si>
@@ -659,9 +660,6 @@
     <t>Mahatma Jasmine Rice, Thai Fragrant Long Grain Rice, Gluten Free, 80 oz Bag (5 lbs</t>
   </si>
   <si>
-    <t>Pantry</t>
-  </si>
-  <si>
     <t>Hillshire Farm Ultra Thin Oven Roasted Turkey Breast Lunchmeat, 16 oz Plastic Tub, Refrigerated</t>
   </si>
   <si>
@@ -671,15 +669,9 @@
     <t>Dave's Killer Bread Organic Oats &amp; Blues Regular Size Loaf, 25 oz, USDA Organic</t>
   </si>
   <si>
-    <t>Bakery</t>
-  </si>
-  <si>
     <t>Birds Eye Steamfresh Sweet Peas, Frozen Vegetables, 10 oz. Bag</t>
   </si>
   <si>
-    <t>Frozen</t>
-  </si>
-  <si>
     <t>Cabot Creamery 4 Cheese Mexican Shredded Cheddar Cheese 2 lb (Refrigerated</t>
   </si>
   <si>
@@ -725,9 +717,6 @@
     <t>Weiman Granite &amp; Stone Disinfectant Cleaner &amp; Polish, 24 floz</t>
   </si>
   <si>
-    <t>Household</t>
-  </si>
-  <si>
     <t>Chobani Low-Fat Vanilla Greek Yogurt Mixed Berry On The Bottom, Hero Batch z 4PK</t>
   </si>
   <si>
@@ -1263,6 +1252,339 @@
   </si>
   <si>
     <t>082826_Publix_120_raw_ocr.json</t>
+  </si>
+  <si>
+    <t>Baby Care</t>
+  </si>
+  <si>
+    <t>Honest Company Conditioning Detangler</t>
+  </si>
+  <si>
+    <t>Hair Care</t>
+  </si>
+  <si>
+    <t>Nestle Toll House Dark Chocolate Baking Chips</t>
+  </si>
+  <si>
+    <t>Baking Ingredients</t>
+  </si>
+  <si>
+    <t>Baking Mixes</t>
+  </si>
+  <si>
+    <t>Purina Tidy Cats With Glade</t>
+  </si>
+  <si>
+    <t>Lawry's Garlic Salt</t>
+  </si>
+  <si>
+    <t>Seasonings &amp; Spices</t>
+  </si>
+  <si>
+    <t>Huggies Natural Care Baby Wipes</t>
+  </si>
+  <si>
+    <t>Pampers Swaddlers Size 5</t>
+  </si>
+  <si>
+    <t>Chobani Oatmilk Extra Creamy</t>
+  </si>
+  <si>
+    <t>Chobani Extra Creamy Oatmilk</t>
+  </si>
+  <si>
+    <t>Fairlife Chocolate Milk</t>
+  </si>
+  <si>
+    <t>Milk</t>
+  </si>
+  <si>
+    <t>Dove Sensitive Skin Body Wash</t>
+  </si>
+  <si>
+    <t>Great Value Large White Eggs</t>
+  </si>
+  <si>
+    <t>Eggs</t>
+  </si>
+  <si>
+    <t>Chobani 20G Protein Greek Yogurt Drink</t>
+  </si>
+  <si>
+    <t>McCormick Sea Salt Grinder</t>
+  </si>
+  <si>
+    <t>Mandarin Oranges</t>
+  </si>
+  <si>
+    <t>Fresh Banana</t>
+  </si>
+  <si>
+    <t>CeraVe Baby Healing Ointment</t>
+  </si>
+  <si>
+    <t>Driver Tip</t>
+  </si>
+  <si>
+    <t>Express Delivery Fee</t>
+  </si>
+  <si>
+    <t>Price Adjustment</t>
+  </si>
+  <si>
+    <t>Chobani Oatmitk Extra Creamy</t>
+  </si>
+  <si>
+    <t>Applegate Chicken &amp; Maple Breakfast Sausage</t>
+  </si>
+  <si>
+    <t>Frozen Meat</t>
+  </si>
+  <si>
+    <t>Nature's Bakery GF Raspberry Fig Bars</t>
+  </si>
+  <si>
+    <t>Nature's Bakery Gluten-Free Raspberry Fig Bars</t>
+  </si>
+  <si>
+    <t>Mahatma Jasmine Rice</t>
+  </si>
+  <si>
+    <t>Rice &amp; Grains</t>
+  </si>
+  <si>
+    <t>Hillshire Farm Oven Roasted Turkey Breast</t>
+  </si>
+  <si>
+    <t>Deli Meat</t>
+  </si>
+  <si>
+    <t>Hebrew National Beef Franks</t>
+  </si>
+  <si>
+    <t>Hot Dogs &amp; Sausages</t>
+  </si>
+  <si>
+    <t>Dave's Killer Bread Oats &amp; Blues</t>
+  </si>
+  <si>
+    <t>Birds Eye Steamfresh Sweet Peas</t>
+  </si>
+  <si>
+    <t>Frozen Vegetables</t>
+  </si>
+  <si>
+    <t>Cabot Mexican Shredded Cheese</t>
+  </si>
+  <si>
+    <t>Cheese</t>
+  </si>
+  <si>
+    <t>Ziploc Slider Gallon Freezer Bags</t>
+  </si>
+  <si>
+    <t>Ziploc Gallon Freezer Bags</t>
+  </si>
+  <si>
+    <t>Food Storage</t>
+  </si>
+  <si>
+    <t>Ziploc Quart Freezer Bags</t>
+  </si>
+  <si>
+    <t>Fresh Mini Cucumbers</t>
+  </si>
+  <si>
+    <t>Mini Cucumbers</t>
+  </si>
+  <si>
+    <t>Yehuda Sabbath Candles</t>
+  </si>
+  <si>
+    <t>Fresh Yellow Squash</t>
+  </si>
+  <si>
+    <t>Fresh Whole Red Onion</t>
+  </si>
+  <si>
+    <t>Red Onion</t>
+  </si>
+  <si>
+    <t>Fresh Tomato on the Vine</t>
+  </si>
+  <si>
+    <t>Tomatoes on the Vine</t>
+  </si>
+  <si>
+    <t>Command Heavy Duty Picture Hangers</t>
+  </si>
+  <si>
+    <t>Home Improvement</t>
+  </si>
+  <si>
+    <t>Dove Men+Care Antiperspirant</t>
+  </si>
+  <si>
+    <t>Dawn Dish Cleaning Brush Wand</t>
+  </si>
+  <si>
+    <t>Once Upon a Farm Tractor Wheels Toddler Bar</t>
+  </si>
+  <si>
+    <t>Baby &amp; Toddler Food</t>
+  </si>
+  <si>
+    <t>Chobani Vanilla Greek Yogurt Mixed Berry</t>
+  </si>
+  <si>
+    <t>Chobani Vanilla Mixed Berry Greek Yogurt</t>
+  </si>
+  <si>
+    <t>Jif No Sugar Added Creamy Peanut Butter</t>
+  </si>
+  <si>
+    <t>Peanut Butter</t>
+  </si>
+  <si>
+    <t>King Arthur Gluten-Free Pancake Mix</t>
+  </si>
+  <si>
+    <t>Green Beans</t>
+  </si>
+  <si>
+    <t>Cholula Cremosa Cilantro Lime Sauce</t>
+  </si>
+  <si>
+    <t>Sauces &amp; Condiments</t>
+  </si>
+  <si>
+    <t>McCormick Everything Bagel Seasoning</t>
+  </si>
+  <si>
+    <t>Banza White Cheddar Shells</t>
+  </si>
+  <si>
+    <t>Annie's Gluten-Free Deluxe Shells &amp; Cheddar</t>
+  </si>
+  <si>
+    <t>GreenWise Keta Salmon Fillet</t>
+  </si>
+  <si>
+    <t>Fresh Seafood</t>
+  </si>
+  <si>
+    <t>Daiya Mexican Blend Shreds</t>
+  </si>
+  <si>
+    <t>Plant-Based Cheese</t>
+  </si>
+  <si>
+    <t>Taylor Farms Chopped Caesar Salad Kit</t>
+  </si>
+  <si>
+    <t>Salad Kits</t>
+  </si>
+  <si>
+    <t>Taylor Farms Everything Chopped Salad Kit</t>
+  </si>
+  <si>
+    <t>Safety 1st Soft Grip Brush &amp; Comb</t>
+  </si>
+  <si>
+    <t>Nestle Toll House Allergen Free Dark Chocolate Baking Chips</t>
+  </si>
+  <si>
+    <t>Nestle Toll House Allergen-Free Dark Chocolate Baking Chips</t>
+  </si>
+  <si>
+    <t>GHIRARDELLI Gluten Free Double Chocolate Brownie Mix</t>
+  </si>
+  <si>
+    <t>Ghirardelli Gluten-Free Double Chocolate Brownie Mix</t>
+  </si>
+  <si>
+    <t>Purina Tidy Cats Clumping Cat Litter</t>
+  </si>
+  <si>
+    <t>Cat Litter</t>
+  </si>
+  <si>
+    <t>Huggies Natural Care Sensitive Baby Wipes</t>
+  </si>
+  <si>
+    <t>Pampers Swaddlers Size 5 Diapers</t>
+  </si>
+  <si>
+    <t>Desitin Maximum Strength Diaper Rash Cream</t>
+  </si>
+  <si>
+    <t>fairlife Chocolate Ultra Filtered Milk</t>
+  </si>
+  <si>
+    <t>Dove Sensitive Skin Body Wash...</t>
+  </si>
+  <si>
+    <t>Body Wash</t>
+  </si>
+  <si>
+    <t>Great Value Large White Eggs 36 Count</t>
+  </si>
+  <si>
+    <t>Chobani Protein Greek Yogurt Drink, Strawberries &amp; Cream</t>
+  </si>
+  <si>
+    <t>Fresh Mandarin Oranges, 5 lb Bag</t>
+  </si>
+  <si>
+    <t>Fresh Pink Lady Apples, 3 lb Bag</t>
+  </si>
+  <si>
+    <t>Nestle Tolt House Dark Chocolate Baking Chips</t>
+  </si>
+  <si>
+    <t>Applegate Chicken &amp; Maple Breakfast Sausage Patties</t>
+  </si>
+  <si>
+    <t>Hillshire Farm Oven Roasted Turkey Breast Lunchmeat</t>
+  </si>
+  <si>
+    <t>Hebrew National Kosher Beef Franks</t>
+  </si>
+  <si>
+    <t>Judaica</t>
+  </si>
+  <si>
+    <t>Fresh Zucchini</t>
+  </si>
+  <si>
+    <t>Dove Men+Care Antiperspirant Deodorant</t>
+  </si>
+  <si>
+    <t>Deodorant</t>
+  </si>
+  <si>
+    <t>Dishwashing Supplies</t>
+  </si>
+  <si>
+    <t>Once Upon a Farm Tractor Wheels Toddler Bars</t>
+  </si>
+  <si>
+    <t>Weiman Granite &amp; Stone Cleaner &amp; Polish</t>
+  </si>
+  <si>
+    <t>Household Cleaners</t>
+  </si>
+  <si>
+    <t>Ruby Sensation Potato Nibbles</t>
+  </si>
+  <si>
+    <t>Macaroni &amp; Cheese</t>
+  </si>
+  <si>
+    <t>Häagen-Dazs Blackberry Ice Cream</t>
+  </si>
+  <si>
+    <t>Ice Cream</t>
   </si>
 </sst>
 </file>
@@ -1498,6 +1820,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr lang="en-US"/>
               <a:t>Monthly Spending</a:t>
             </a:r>
           </a:p>
@@ -1603,6 +1926,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-US"/>
                   <a:t>Month Number</a:t>
                 </a:r>
               </a:p>
@@ -1639,6 +1963,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-US"/>
                   <a:t>Spending ($)</a:t>
                 </a:r>
               </a:p>
@@ -1684,6 +2009,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr lang="en-US"/>
               <a:t>Spending by Category</a:t>
             </a:r>
           </a:p>
@@ -2764,6 +3090,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-US"/>
                   <a:t>Spending ($)</a:t>
                 </a:r>
               </a:p>
@@ -2800,6 +3127,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-US"/>
                   <a:t>Number</a:t>
                 </a:r>
               </a:p>
@@ -2845,6 +3173,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr lang="en-US"/>
               <a:t>Spending by Store</a:t>
             </a:r>
           </a:p>
@@ -3088,6 +3417,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-US"/>
                   <a:t>Spending ($)</a:t>
                 </a:r>
               </a:p>
@@ -3124,6 +3454,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-US"/>
                   <a:t>Number</a:t>
                 </a:r>
               </a:p>
@@ -6824,7 +7155,7 @@
     <col min="5" max="5" width="34" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="28" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22" customWidth="1"/>
     <col min="10" max="19" width="14" customWidth="1"/>
   </cols>
@@ -8566,10 +8897,10 @@
         <v>167</v>
       </c>
       <c r="H51" t="s">
-        <v>19</v>
+        <v>482</v>
       </c>
       <c r="I51" t="s">
-        <v>19</v>
+        <v>404</v>
       </c>
       <c r="J51" s="2">
         <v>46240</v>
@@ -8605,10 +8936,10 @@
         <v>167</v>
       </c>
       <c r="H52" t="s">
-        <v>19</v>
+        <v>405</v>
       </c>
       <c r="I52" t="s">
-        <v>169</v>
+        <v>406</v>
       </c>
       <c r="J52" s="2">
         <v>46240</v>
@@ -8644,10 +8975,10 @@
         <v>167</v>
       </c>
       <c r="H53" t="s">
-        <v>19</v>
+        <v>484</v>
       </c>
       <c r="I53" t="s">
-        <v>171</v>
+        <v>408</v>
       </c>
       <c r="J53" s="2">
         <v>46240</v>
@@ -8683,10 +9014,10 @@
         <v>167</v>
       </c>
       <c r="H54" t="s">
-        <v>19</v>
+        <v>486</v>
       </c>
       <c r="I54" t="s">
-        <v>171</v>
+        <v>409</v>
       </c>
       <c r="J54" s="2">
         <v>46240</v>
@@ -8716,10 +9047,10 @@
         <v>167</v>
       </c>
       <c r="H55" t="s">
-        <v>19</v>
+        <v>487</v>
       </c>
       <c r="I55" t="s">
-        <v>174</v>
+        <v>488</v>
       </c>
       <c r="J55" s="2">
         <v>46240</v>
@@ -8755,10 +9086,10 @@
         <v>167</v>
       </c>
       <c r="H56" t="s">
-        <v>19</v>
+        <v>411</v>
       </c>
       <c r="I56" t="s">
-        <v>176</v>
+        <v>412</v>
       </c>
       <c r="J56" s="2">
         <v>46240</v>
@@ -8794,10 +9125,10 @@
         <v>167</v>
       </c>
       <c r="H57" t="s">
-        <v>19</v>
+        <v>413</v>
       </c>
       <c r="I57" t="s">
-        <v>178</v>
+        <v>404</v>
       </c>
       <c r="J57" s="2">
         <v>46240</v>
@@ -8833,10 +9164,10 @@
         <v>167</v>
       </c>
       <c r="H58" t="s">
-        <v>19</v>
+        <v>490</v>
       </c>
       <c r="I58" t="s">
-        <v>178</v>
+        <v>404</v>
       </c>
       <c r="J58" s="2">
         <v>46240</v>
@@ -8866,10 +9197,10 @@
         <v>167</v>
       </c>
       <c r="H59" t="s">
-        <v>19</v>
+        <v>416</v>
       </c>
       <c r="I59" t="s">
-        <v>169</v>
+        <v>37</v>
       </c>
       <c r="J59" s="2">
         <v>46240</v>
@@ -8899,10 +9230,10 @@
         <v>167</v>
       </c>
       <c r="H60" t="s">
-        <v>19</v>
+        <v>491</v>
       </c>
       <c r="I60" t="s">
-        <v>169</v>
+        <v>404</v>
       </c>
       <c r="J60" s="2">
         <v>46240</v>
@@ -8938,10 +9269,10 @@
         <v>167</v>
       </c>
       <c r="H61" t="s">
-        <v>19</v>
+        <v>417</v>
       </c>
       <c r="I61" t="s">
-        <v>169</v>
+        <v>418</v>
       </c>
       <c r="J61" s="2">
         <v>46240</v>
@@ -8977,10 +9308,10 @@
         <v>167</v>
       </c>
       <c r="H62" t="s">
-        <v>19</v>
+        <v>407</v>
       </c>
       <c r="I62" t="s">
-        <v>171</v>
+        <v>408</v>
       </c>
       <c r="J62" s="2">
         <v>46240</v>
@@ -9010,10 +9341,10 @@
         <v>167</v>
       </c>
       <c r="H63" t="s">
-        <v>19</v>
+        <v>419</v>
       </c>
       <c r="I63" t="s">
-        <v>19</v>
+        <v>494</v>
       </c>
       <c r="J63" s="2">
         <v>46240</v>
@@ -9049,10 +9380,10 @@
         <v>167</v>
       </c>
       <c r="H64" t="s">
-        <v>19</v>
+        <v>419</v>
       </c>
       <c r="I64" t="s">
-        <v>19</v>
+        <v>494</v>
       </c>
       <c r="J64" s="2">
         <v>46240</v>
@@ -9088,10 +9419,10 @@
         <v>167</v>
       </c>
       <c r="H65" t="s">
-        <v>19</v>
+        <v>420</v>
       </c>
       <c r="I65" t="s">
-        <v>19</v>
+        <v>421</v>
       </c>
       <c r="J65" s="2">
         <v>46240</v>
@@ -9127,10 +9458,10 @@
         <v>167</v>
       </c>
       <c r="H66" t="s">
-        <v>19</v>
+        <v>496</v>
       </c>
       <c r="I66" t="s">
-        <v>188</v>
+        <v>24</v>
       </c>
       <c r="J66" s="2">
         <v>46240</v>
@@ -9166,10 +9497,10 @@
         <v>167</v>
       </c>
       <c r="H67" t="s">
-        <v>19</v>
+        <v>423</v>
       </c>
       <c r="I67" t="s">
-        <v>19</v>
+        <v>412</v>
       </c>
       <c r="J67" s="2">
         <v>46240</v>
@@ -9199,10 +9530,10 @@
         <v>167</v>
       </c>
       <c r="H68" t="s">
-        <v>19</v>
+        <v>424</v>
       </c>
       <c r="I68" t="s">
-        <v>188</v>
+        <v>71</v>
       </c>
       <c r="J68" s="2">
         <v>46240</v>
@@ -9238,10 +9569,10 @@
         <v>167</v>
       </c>
       <c r="H69" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="I69" t="s">
-        <v>188</v>
+        <v>71</v>
       </c>
       <c r="J69" s="2">
         <v>46240</v>
@@ -9277,10 +9608,10 @@
         <v>167</v>
       </c>
       <c r="H70" t="s">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="I70" t="s">
-        <v>188</v>
+        <v>71</v>
       </c>
       <c r="J70" s="2">
         <v>46240</v>
@@ -9322,10 +9653,10 @@
         <v>167</v>
       </c>
       <c r="H71" t="s">
-        <v>19</v>
+        <v>426</v>
       </c>
       <c r="I71" t="s">
-        <v>178</v>
+        <v>404</v>
       </c>
       <c r="J71" s="2">
         <v>46240</v>
@@ -9361,10 +9692,10 @@
         <v>167</v>
       </c>
       <c r="H72" t="s">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="I72" t="s">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="J72" s="2">
         <v>46240</v>
@@ -9394,10 +9725,10 @@
         <v>167</v>
       </c>
       <c r="H73" t="s">
-        <v>19</v>
+        <v>162</v>
       </c>
       <c r="I73" t="s">
-        <v>19</v>
+        <v>163</v>
       </c>
       <c r="J73" s="2">
         <v>46240</v>
@@ -9451,10 +9782,10 @@
         <v>167</v>
       </c>
       <c r="H74" t="s">
-        <v>19</v>
+        <v>427</v>
       </c>
       <c r="I74" t="s">
-        <v>19</v>
+        <v>163</v>
       </c>
       <c r="J74" s="2">
         <v>46240</v>
@@ -9496,10 +9827,10 @@
         <v>167</v>
       </c>
       <c r="H75" t="s">
-        <v>19</v>
+        <v>428</v>
       </c>
       <c r="I75" t="s">
-        <v>19</v>
+        <v>163</v>
       </c>
       <c r="J75" s="2">
         <v>46240</v>
@@ -9529,10 +9860,10 @@
         <v>167</v>
       </c>
       <c r="H76" t="s">
-        <v>19</v>
+        <v>429</v>
       </c>
       <c r="I76" t="s">
-        <v>19</v>
+        <v>163</v>
       </c>
       <c r="J76" s="2">
         <v>46240</v>
@@ -9562,10 +9893,10 @@
         <v>167</v>
       </c>
       <c r="H77" t="s">
-        <v>19</v>
+        <v>486</v>
       </c>
       <c r="I77" t="s">
-        <v>171</v>
+        <v>409</v>
       </c>
       <c r="J77" s="2">
         <v>46241</v>
@@ -9595,10 +9926,10 @@
         <v>167</v>
       </c>
       <c r="H78" t="s">
-        <v>19</v>
+        <v>490</v>
       </c>
       <c r="I78" t="s">
-        <v>178</v>
+        <v>404</v>
       </c>
       <c r="J78" s="2">
         <v>46241</v>
@@ -9628,10 +9959,10 @@
         <v>167</v>
       </c>
       <c r="H79" t="s">
-        <v>19</v>
+        <v>416</v>
       </c>
       <c r="I79" t="s">
-        <v>169</v>
+        <v>37</v>
       </c>
       <c r="J79" s="2">
         <v>46241</v>
@@ -9661,10 +9992,10 @@
         <v>167</v>
       </c>
       <c r="H80" t="s">
-        <v>19</v>
+        <v>407</v>
       </c>
       <c r="I80" t="s">
-        <v>171</v>
+        <v>408</v>
       </c>
       <c r="J80" s="2">
         <v>46241</v>
@@ -9694,10 +10025,10 @@
         <v>167</v>
       </c>
       <c r="H81" t="s">
-        <v>19</v>
+        <v>431</v>
       </c>
       <c r="I81" t="s">
-        <v>188</v>
+        <v>432</v>
       </c>
       <c r="J81" s="2">
         <v>46241</v>
@@ -9727,10 +10058,10 @@
         <v>167</v>
       </c>
       <c r="H82" t="s">
-        <v>19</v>
+        <v>423</v>
       </c>
       <c r="I82" t="s">
-        <v>19</v>
+        <v>412</v>
       </c>
       <c r="J82" s="2">
         <v>46241</v>
@@ -9760,10 +10091,10 @@
         <v>167</v>
       </c>
       <c r="H83" t="s">
-        <v>19</v>
+        <v>428</v>
       </c>
       <c r="I83" t="s">
-        <v>19</v>
+        <v>163</v>
       </c>
       <c r="J83" s="2">
         <v>46241</v>
@@ -9793,10 +10124,10 @@
         <v>167</v>
       </c>
       <c r="H84" t="s">
-        <v>19</v>
+        <v>434</v>
       </c>
       <c r="I84" t="s">
-        <v>188</v>
+        <v>93</v>
       </c>
       <c r="J84" s="2">
         <v>46247</v>
@@ -9826,10 +10157,10 @@
         <v>167</v>
       </c>
       <c r="H85" t="s">
-        <v>19</v>
+        <v>435</v>
       </c>
       <c r="I85" t="s">
-        <v>206</v>
+        <v>436</v>
       </c>
       <c r="J85" s="2">
         <v>46247</v>
@@ -9850,7 +10181,7 @@
         <v>19</v>
       </c>
       <c r="E86" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F86" t="s">
         <v>19</v>
@@ -9859,10 +10190,10 @@
         <v>167</v>
       </c>
       <c r="H86" t="s">
-        <v>19</v>
+        <v>437</v>
       </c>
       <c r="I86" t="s">
-        <v>176</v>
+        <v>438</v>
       </c>
       <c r="J86" s="2">
         <v>46247</v>
@@ -9883,7 +10214,7 @@
         <v>19</v>
       </c>
       <c r="E87" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F87" t="s">
         <v>19</v>
@@ -9892,10 +10223,10 @@
         <v>167</v>
       </c>
       <c r="H87" t="s">
-        <v>19</v>
+        <v>439</v>
       </c>
       <c r="I87" t="s">
-        <v>176</v>
+        <v>440</v>
       </c>
       <c r="J87" s="2">
         <v>46247</v>
@@ -9916,7 +10247,7 @@
         <v>19</v>
       </c>
       <c r="E88" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F88" t="s">
         <v>19</v>
@@ -9925,10 +10256,10 @@
         <v>167</v>
       </c>
       <c r="H88" t="s">
-        <v>19</v>
+        <v>441</v>
       </c>
       <c r="I88" t="s">
-        <v>210</v>
+        <v>46</v>
       </c>
       <c r="J88" s="2">
         <v>46247</v>
@@ -9949,7 +10280,7 @@
         <v>19</v>
       </c>
       <c r="E89" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F89" t="s">
         <v>19</v>
@@ -9958,10 +10289,10 @@
         <v>167</v>
       </c>
       <c r="H89" t="s">
-        <v>19</v>
+        <v>442</v>
       </c>
       <c r="I89" t="s">
-        <v>212</v>
+        <v>443</v>
       </c>
       <c r="J89" s="2">
         <v>46247</v>
@@ -9982,7 +10313,7 @@
         <v>19</v>
       </c>
       <c r="E90" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F90" t="s">
         <v>19</v>
@@ -9991,10 +10322,10 @@
         <v>167</v>
       </c>
       <c r="H90" t="s">
-        <v>19</v>
+        <v>444</v>
       </c>
       <c r="I90" t="s">
-        <v>169</v>
+        <v>445</v>
       </c>
       <c r="J90" s="2">
         <v>46247</v>
@@ -10015,7 +10346,7 @@
         <v>19</v>
       </c>
       <c r="E91" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F91" t="s">
         <v>19</v>
@@ -10024,10 +10355,10 @@
         <v>167</v>
       </c>
       <c r="H91" t="s">
-        <v>19</v>
+        <v>447</v>
       </c>
       <c r="I91" t="s">
-        <v>19</v>
+        <v>448</v>
       </c>
       <c r="J91" s="2">
         <v>46247</v>
@@ -10048,7 +10379,7 @@
         <v>19</v>
       </c>
       <c r="E92" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F92" t="s">
         <v>19</v>
@@ -10057,10 +10388,10 @@
         <v>167</v>
       </c>
       <c r="H92" t="s">
-        <v>19</v>
+        <v>449</v>
       </c>
       <c r="I92" t="s">
-        <v>19</v>
+        <v>448</v>
       </c>
       <c r="J92" s="2">
         <v>46247</v>
@@ -10081,7 +10412,7 @@
         <v>19</v>
       </c>
       <c r="E93" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F93" t="s">
         <v>19</v>
@@ -10090,10 +10421,10 @@
         <v>167</v>
       </c>
       <c r="H93" t="s">
-        <v>19</v>
+        <v>451</v>
       </c>
       <c r="I93" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="J93" s="2">
         <v>46247</v>
@@ -10114,7 +10445,7 @@
         <v>19</v>
       </c>
       <c r="E94" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F94" t="s">
         <v>161</v>
@@ -10123,10 +10454,10 @@
         <v>167</v>
       </c>
       <c r="H94" t="s">
-        <v>19</v>
+        <v>452</v>
       </c>
       <c r="I94" t="s">
-        <v>19</v>
+        <v>503</v>
       </c>
       <c r="J94" s="2">
         <v>46247</v>
@@ -10147,7 +10478,7 @@
         <v>19</v>
       </c>
       <c r="E95" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F95" t="s">
         <v>19</v>
@@ -10156,10 +10487,10 @@
         <v>167</v>
       </c>
       <c r="H95" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="I95" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="J95" s="2">
         <v>46247</v>
@@ -10186,7 +10517,7 @@
         <v>19</v>
       </c>
       <c r="E96" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F96" t="s">
         <v>19</v>
@@ -10198,7 +10529,7 @@
         <v>48</v>
       </c>
       <c r="I96" t="s">
-        <v>188</v>
+        <v>49</v>
       </c>
       <c r="J96" s="2">
         <v>46247</v>
@@ -10225,7 +10556,7 @@
         <v>19</v>
       </c>
       <c r="E97" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F97" t="s">
         <v>19</v>
@@ -10234,10 +10565,10 @@
         <v>167</v>
       </c>
       <c r="H97" t="s">
-        <v>19</v>
+        <v>455</v>
       </c>
       <c r="I97" t="s">
-        <v>188</v>
+        <v>49</v>
       </c>
       <c r="J97" s="2">
         <v>46247</v>
@@ -10264,7 +10595,7 @@
         <v>19</v>
       </c>
       <c r="E98" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F98" t="s">
         <v>19</v>
@@ -10273,10 +10604,10 @@
         <v>167</v>
       </c>
       <c r="H98" t="s">
-        <v>19</v>
+        <v>457</v>
       </c>
       <c r="I98" t="s">
-        <v>188</v>
+        <v>49</v>
       </c>
       <c r="J98" s="2">
         <v>46247</v>
@@ -10297,7 +10628,7 @@
         <v>19</v>
       </c>
       <c r="E99" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F99" t="s">
         <v>19</v>
@@ -10306,10 +10637,10 @@
         <v>167</v>
       </c>
       <c r="H99" t="s">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="I99" t="s">
-        <v>188</v>
+        <v>71</v>
       </c>
       <c r="J99" s="2">
         <v>46247</v>
@@ -10336,7 +10667,7 @@
         <v>19</v>
       </c>
       <c r="E100" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F100" t="s">
         <v>19</v>
@@ -10345,10 +10676,10 @@
         <v>167</v>
       </c>
       <c r="H100" t="s">
-        <v>19</v>
+        <v>458</v>
       </c>
       <c r="I100" t="s">
-        <v>19</v>
+        <v>459</v>
       </c>
       <c r="J100" s="2">
         <v>46260</v>
@@ -10369,7 +10700,7 @@
         <v>19</v>
       </c>
       <c r="E101" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F101" t="s">
         <v>19</v>
@@ -10378,10 +10709,10 @@
         <v>167</v>
       </c>
       <c r="H101" t="s">
-        <v>19</v>
+        <v>460</v>
       </c>
       <c r="I101" t="s">
-        <v>19</v>
+        <v>506</v>
       </c>
       <c r="J101" s="2">
         <v>46260</v>
@@ -10402,7 +10733,7 @@
         <v>19</v>
       </c>
       <c r="E102" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F102" t="s">
         <v>19</v>
@@ -10411,10 +10742,10 @@
         <v>167</v>
       </c>
       <c r="H102" t="s">
-        <v>19</v>
+        <v>461</v>
       </c>
       <c r="I102" t="s">
-        <v>19</v>
+        <v>507</v>
       </c>
       <c r="J102" s="2">
         <v>46260</v>
@@ -10435,7 +10766,7 @@
         <v>19</v>
       </c>
       <c r="E103" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F103" t="s">
         <v>19</v>
@@ -10444,10 +10775,10 @@
         <v>167</v>
       </c>
       <c r="H103" t="s">
-        <v>19</v>
+        <v>508</v>
       </c>
       <c r="I103" t="s">
-        <v>188</v>
+        <v>463</v>
       </c>
       <c r="J103" s="2">
         <v>46260</v>
@@ -10468,7 +10799,7 @@
         <v>19</v>
       </c>
       <c r="E104" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F104" t="s">
         <v>19</v>
@@ -10477,10 +10808,10 @@
         <v>167</v>
       </c>
       <c r="H104" t="s">
-        <v>19</v>
+        <v>509</v>
       </c>
       <c r="I104" t="s">
-        <v>228</v>
+        <v>510</v>
       </c>
       <c r="J104" s="2">
         <v>46260</v>
@@ -10501,7 +10832,7 @@
         <v>19</v>
       </c>
       <c r="E105" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F105" t="s">
         <v>19</v>
@@ -10510,10 +10841,10 @@
         <v>167</v>
       </c>
       <c r="H105" t="s">
-        <v>19</v>
+        <v>465</v>
       </c>
       <c r="I105" t="s">
-        <v>188</v>
+        <v>24</v>
       </c>
       <c r="J105" s="2">
         <v>46260</v>
@@ -10534,7 +10865,7 @@
         <v>19</v>
       </c>
       <c r="E106" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F106" t="s">
         <v>19</v>
@@ -10543,10 +10874,10 @@
         <v>167</v>
       </c>
       <c r="H106" t="s">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="I106" t="s">
-        <v>188</v>
+        <v>71</v>
       </c>
       <c r="J106" s="2">
         <v>46260</v>
@@ -10573,19 +10904,19 @@
         <v>19</v>
       </c>
       <c r="E107" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="F107" t="s">
         <v>21</v>
       </c>
       <c r="G107" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H107" t="s">
-        <v>19</v>
+        <v>466</v>
       </c>
       <c r="I107" t="s">
-        <v>169</v>
+        <v>467</v>
       </c>
       <c r="J107" s="2">
         <v>46262</v>
@@ -10606,19 +10937,19 @@
         <v>19</v>
       </c>
       <c r="E108" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F108" t="s">
         <v>21</v>
       </c>
       <c r="G108" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H108" t="s">
-        <v>19</v>
+        <v>468</v>
       </c>
       <c r="I108" t="s">
-        <v>19</v>
+        <v>409</v>
       </c>
       <c r="J108" s="2">
         <v>46262</v>
@@ -10639,19 +10970,19 @@
         <v>19</v>
       </c>
       <c r="E109" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="F109" t="s">
         <v>21</v>
       </c>
       <c r="G109" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H109" t="s">
-        <v>19</v>
+        <v>469</v>
       </c>
       <c r="I109" t="s">
-        <v>206</v>
+        <v>49</v>
       </c>
       <c r="J109" s="2">
         <v>46262</v>
@@ -10672,19 +11003,19 @@
         <v>19</v>
       </c>
       <c r="E110" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F110" t="s">
         <v>21</v>
       </c>
       <c r="G110" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H110" t="s">
-        <v>235</v>
+        <v>511</v>
       </c>
       <c r="I110" t="s">
-        <v>188</v>
+        <v>49</v>
       </c>
       <c r="J110" s="2">
         <v>46262</v>
@@ -10705,19 +11036,19 @@
         <v>19</v>
       </c>
       <c r="E111" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="F111" t="s">
         <v>21</v>
       </c>
       <c r="G111" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H111" t="s">
-        <v>19</v>
+        <v>470</v>
       </c>
       <c r="I111" t="s">
-        <v>19</v>
+        <v>471</v>
       </c>
       <c r="J111" s="2">
         <v>46262</v>
@@ -10738,19 +11069,19 @@
         <v>19</v>
       </c>
       <c r="E112" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="F112" t="s">
         <v>21</v>
       </c>
       <c r="G112" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H112" t="s">
-        <v>19</v>
+        <v>472</v>
       </c>
       <c r="I112" t="s">
-        <v>19</v>
+        <v>412</v>
       </c>
       <c r="J112" s="2">
         <v>46262</v>
@@ -10771,19 +11102,19 @@
         <v>19</v>
       </c>
       <c r="E113" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F113" t="s">
         <v>21</v>
       </c>
       <c r="G113" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H113" t="s">
-        <v>19</v>
+        <v>473</v>
       </c>
       <c r="I113" t="s">
-        <v>19</v>
+        <v>512</v>
       </c>
       <c r="J113" s="2">
         <v>46262</v>
@@ -10804,19 +11135,19 @@
         <v>19</v>
       </c>
       <c r="E114" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="F114" t="s">
         <v>21</v>
       </c>
       <c r="G114" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H114" t="s">
-        <v>19</v>
+        <v>473</v>
       </c>
       <c r="I114" t="s">
-        <v>19</v>
+        <v>512</v>
       </c>
       <c r="J114" s="2">
         <v>46262</v>
@@ -10837,19 +11168,19 @@
         <v>19</v>
       </c>
       <c r="E115" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="F115" t="s">
         <v>21</v>
       </c>
       <c r="G115" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H115" t="s">
-        <v>19</v>
+        <v>474</v>
       </c>
       <c r="I115" t="s">
-        <v>19</v>
+        <v>512</v>
       </c>
       <c r="J115" s="2">
         <v>46262</v>
@@ -10870,19 +11201,19 @@
         <v>19</v>
       </c>
       <c r="E116" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F116" t="s">
         <v>21</v>
       </c>
       <c r="G116" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H116" t="s">
-        <v>19</v>
+        <v>474</v>
       </c>
       <c r="I116" t="s">
-        <v>19</v>
+        <v>512</v>
       </c>
       <c r="J116" s="2">
         <v>46262</v>
@@ -10903,19 +11234,19 @@
         <v>19</v>
       </c>
       <c r="E117" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F117" t="s">
         <v>21</v>
       </c>
       <c r="G117" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H117" t="s">
-        <v>19</v>
+        <v>475</v>
       </c>
       <c r="I117" t="s">
-        <v>176</v>
+        <v>476</v>
       </c>
       <c r="J117" s="2">
         <v>46262</v>
@@ -10942,13 +11273,13 @@
         <v>19</v>
       </c>
       <c r="G118" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H118" t="s">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="I118" t="s">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="J118" s="2">
         <v>46262</v>
@@ -10969,19 +11300,19 @@
         <v>19</v>
       </c>
       <c r="E119" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F119" t="s">
         <v>21</v>
       </c>
       <c r="G119" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H119" t="s">
-        <v>19</v>
+        <v>477</v>
       </c>
       <c r="I119" t="s">
-        <v>206</v>
+        <v>478</v>
       </c>
       <c r="J119" s="2">
         <v>46262</v>
@@ -11008,19 +11339,19 @@
         <v>19</v>
       </c>
       <c r="E120" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="F120" t="s">
         <v>19</v>
       </c>
       <c r="G120" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H120" t="s">
-        <v>19</v>
+        <v>479</v>
       </c>
       <c r="I120" t="s">
-        <v>19</v>
+        <v>480</v>
       </c>
       <c r="J120" s="2">
         <v>46262</v>
@@ -11041,19 +11372,19 @@
         <v>19</v>
       </c>
       <c r="E121" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="F121" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="G121" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H121" t="s">
-        <v>19</v>
+        <v>481</v>
       </c>
       <c r="I121" t="s">
-        <v>19</v>
+        <v>480</v>
       </c>
       <c r="J121" s="2">
         <v>46262</v>
@@ -11074,19 +11405,19 @@
         <v>19</v>
       </c>
       <c r="E122" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="F122" t="s">
         <v>161</v>
       </c>
       <c r="G122" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H122" t="s">
-        <v>247</v>
+        <v>513</v>
       </c>
       <c r="I122" t="s">
-        <v>188</v>
+        <v>514</v>
       </c>
       <c r="J122" s="2">
         <v>46262</v>
@@ -11113,13 +11444,13 @@
         <v>19</v>
       </c>
       <c r="G123" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H123" t="s">
-        <v>19</v>
+        <v>162</v>
       </c>
       <c r="I123" t="s">
-        <v>19</v>
+        <v>163</v>
       </c>
       <c r="J123" s="2">
         <v>46262</v>
@@ -11140,19 +11471,19 @@
         <v>19</v>
       </c>
       <c r="E124" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="F124" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="G124" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H124" t="s">
-        <v>19</v>
+        <v>481</v>
       </c>
       <c r="I124" t="s">
-        <v>19</v>
+        <v>480</v>
       </c>
       <c r="J124" s="2">
         <v>46262</v>
@@ -11226,7 +11557,7 @@
   <sheetData>
     <row r="1" spans="1:33" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="29" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B1" s="27"/>
       <c r="C1" s="27"/>
@@ -11298,19 +11629,19 @@
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="T4" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z4" s="7" t="s">
         <v>249</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="T4" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="Z4" s="7" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="5" spans="1:33" ht="16" x14ac:dyDescent="0.2">
@@ -11321,7 +11652,7 @@
         <v>82</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="T5" s="9">
         <v>5</v>
@@ -11332,7 +11663,7 @@
     </row>
     <row r="8" spans="1:33" ht="16" x14ac:dyDescent="0.2">
       <c r="Q8" s="30" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="R8" s="27"/>
       <c r="S8" s="27"/>
@@ -11341,7 +11672,7 @@
       <c r="V8" s="27"/>
       <c r="W8" s="27"/>
       <c r="Y8" s="30" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="Z8" s="27"/>
       <c r="AA8" s="27"/>
@@ -11355,13 +11686,13 @@
     <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="Q9" s="10"/>
       <c r="R9" s="10" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="S9" s="10" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="W9" s="10" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10" spans="1:33" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -11370,16 +11701,16 @@
         <v>1</v>
       </c>
       <c r="S10" s="26" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="T10" s="27"/>
       <c r="U10" s="27"/>
       <c r="V10" s="27"/>
       <c r="W10" s="6" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="Y10" s="28" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="Z10" s="27"/>
       <c r="AA10" s="27"/>
@@ -11392,7 +11723,7 @@
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="Y11" s="26" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="Z11" s="27"/>
       <c r="AA11" s="27"/>
@@ -11438,7 +11769,7 @@
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="Y16" s="28" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="Z16" s="27"/>
       <c r="AA16" s="27"/>
@@ -11451,7 +11782,7 @@
     </row>
     <row r="17" spans="25:33" x14ac:dyDescent="0.2">
       <c r="Y17" s="26" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="Z17" s="27"/>
       <c r="AA17" s="27"/>
@@ -11497,7 +11828,7 @@
     </row>
     <row r="22" spans="25:33" x14ac:dyDescent="0.2">
       <c r="Y22" s="28" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="Z22" s="27"/>
       <c r="AA22" s="27"/>
@@ -11510,7 +11841,7 @@
     </row>
     <row r="23" spans="25:33" x14ac:dyDescent="0.2">
       <c r="Y23" s="26" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="Z23" s="27"/>
       <c r="AA23" s="27"/>
@@ -11556,7 +11887,7 @@
     </row>
     <row r="28" spans="25:33" x14ac:dyDescent="0.2">
       <c r="Y28" s="28" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="Z28" s="27"/>
       <c r="AA28" s="27"/>
@@ -11569,7 +11900,7 @@
     </row>
     <row r="29" spans="25:33" x14ac:dyDescent="0.2">
       <c r="Y29" s="26" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="Z29" s="27"/>
       <c r="AA29" s="27"/>
@@ -11615,7 +11946,7 @@
     </row>
     <row r="44" spans="17:33" ht="16" x14ac:dyDescent="0.2">
       <c r="Q44" s="30" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="R44" s="27"/>
       <c r="S44" s="27"/>
@@ -11624,7 +11955,7 @@
       <c r="V44" s="27"/>
       <c r="W44" s="27"/>
       <c r="Y44" s="30" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="Z44" s="27"/>
       <c r="AA44" s="27"/>
@@ -11638,13 +11969,13 @@
     <row r="45" spans="17:33" x14ac:dyDescent="0.2">
       <c r="Q45" s="10"/>
       <c r="R45" s="10" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="S45" s="10" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="W45" s="10" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="46" spans="17:33" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -11659,10 +11990,10 @@
       <c r="U46" s="27"/>
       <c r="V46" s="27"/>
       <c r="W46" s="6" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="Y46" s="28" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="Z46" s="27"/>
       <c r="AA46" s="27"/>
@@ -11679,16 +12010,16 @@
         <v>2</v>
       </c>
       <c r="S47" s="26" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="T47" s="27"/>
       <c r="U47" s="27"/>
       <c r="V47" s="27"/>
       <c r="W47" s="6" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="Y47" s="26" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="Z47" s="27"/>
       <c r="AA47" s="27"/>
@@ -11711,7 +12042,7 @@
       <c r="U48" s="27"/>
       <c r="V48" s="27"/>
       <c r="W48" s="6" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="Y48" s="27"/>
       <c r="Z48" s="27"/>
@@ -11735,7 +12066,7 @@
       <c r="U49" s="27"/>
       <c r="V49" s="27"/>
       <c r="W49" s="6" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Y49" s="27"/>
       <c r="Z49" s="27"/>
@@ -11759,7 +12090,7 @@
       <c r="U50" s="27"/>
       <c r="V50" s="27"/>
       <c r="W50" s="6" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="Y50" s="27"/>
       <c r="Z50" s="27"/>
@@ -11783,7 +12114,7 @@
       <c r="U51" s="27"/>
       <c r="V51" s="27"/>
       <c r="W51" s="6" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="52" spans="17:33" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -11798,10 +12129,10 @@
       <c r="U52" s="27"/>
       <c r="V52" s="27"/>
       <c r="W52" s="6" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="Y52" s="28" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="Z52" s="27"/>
       <c r="AA52" s="27"/>
@@ -11824,10 +12155,10 @@
       <c r="U53" s="27"/>
       <c r="V53" s="27"/>
       <c r="W53" s="6" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="Y53" s="26" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="Z53" s="27"/>
       <c r="AA53" s="27"/>
@@ -11850,7 +12181,7 @@
       <c r="U54" s="27"/>
       <c r="V54" s="27"/>
       <c r="W54" s="6" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="Y54" s="27"/>
       <c r="Z54" s="27"/>
@@ -11874,7 +12205,7 @@
       <c r="U55" s="27"/>
       <c r="V55" s="27"/>
       <c r="W55" s="6" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="Y55" s="27"/>
       <c r="Z55" s="27"/>
@@ -11898,7 +12229,7 @@
       <c r="U56" s="27"/>
       <c r="V56" s="27"/>
       <c r="W56" s="6" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="Y56" s="27"/>
       <c r="Z56" s="27"/>
@@ -11922,7 +12253,7 @@
       <c r="U57" s="27"/>
       <c r="V57" s="27"/>
       <c r="W57" s="6" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="58" spans="17:33" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -11937,10 +12268,10 @@
       <c r="U58" s="27"/>
       <c r="V58" s="27"/>
       <c r="W58" s="6" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="Y58" s="28" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="Z58" s="27"/>
       <c r="AA58" s="27"/>
@@ -11963,10 +12294,10 @@
       <c r="U59" s="27"/>
       <c r="V59" s="27"/>
       <c r="W59" s="6" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="Y59" s="26" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="Z59" s="27"/>
       <c r="AA59" s="27"/>
@@ -11989,7 +12320,7 @@
       <c r="U60" s="27"/>
       <c r="V60" s="27"/>
       <c r="W60" s="6" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="Y60" s="27"/>
       <c r="Z60" s="27"/>
@@ -12013,7 +12344,7 @@
       <c r="U61" s="27"/>
       <c r="V61" s="27"/>
       <c r="W61" s="6" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="Y61" s="27"/>
       <c r="Z61" s="27"/>
@@ -12037,7 +12368,7 @@
       <c r="U62" s="27"/>
       <c r="V62" s="27"/>
       <c r="W62" s="6" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="Y62" s="27"/>
       <c r="Z62" s="27"/>
@@ -12061,7 +12392,7 @@
       <c r="U63" s="27"/>
       <c r="V63" s="27"/>
       <c r="W63" s="6" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="64" spans="17:33" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -12076,7 +12407,7 @@
       <c r="U64" s="27"/>
       <c r="V64" s="27"/>
       <c r="W64" s="6" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="65" spans="17:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -12091,7 +12422,7 @@
       <c r="U65" s="27"/>
       <c r="V65" s="27"/>
       <c r="W65" s="6" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="66" spans="17:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -12106,7 +12437,7 @@
       <c r="U66" s="27"/>
       <c r="V66" s="27"/>
       <c r="W66" s="6" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="67" spans="17:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -12121,7 +12452,7 @@
       <c r="U67" s="27"/>
       <c r="V67" s="27"/>
       <c r="W67" s="6" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="68" spans="17:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -12136,7 +12467,7 @@
       <c r="U68" s="27"/>
       <c r="V68" s="27"/>
       <c r="W68" s="6" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="69" spans="17:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -12151,7 +12482,7 @@
       <c r="U69" s="27"/>
       <c r="V69" s="27"/>
       <c r="W69" s="6" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="70" spans="17:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -12166,7 +12497,7 @@
       <c r="U70" s="27"/>
       <c r="V70" s="27"/>
       <c r="W70" s="6" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="71" spans="17:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -12181,7 +12512,7 @@
       <c r="U71" s="27"/>
       <c r="V71" s="27"/>
       <c r="W71" s="6" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="72" spans="17:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -12196,7 +12527,7 @@
       <c r="U72" s="27"/>
       <c r="V72" s="27"/>
       <c r="W72" s="6" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="73" spans="17:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -12211,7 +12542,7 @@
       <c r="U73" s="27"/>
       <c r="V73" s="27"/>
       <c r="W73" s="6" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="74" spans="17:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -12226,7 +12557,7 @@
       <c r="U74" s="27"/>
       <c r="V74" s="27"/>
       <c r="W74" s="6" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="75" spans="17:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -12241,7 +12572,7 @@
       <c r="U75" s="27"/>
       <c r="V75" s="27"/>
       <c r="W75" s="6" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="76" spans="17:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -12256,7 +12587,7 @@
       <c r="U76" s="27"/>
       <c r="V76" s="27"/>
       <c r="W76" s="6" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="77" spans="17:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -12271,7 +12602,7 @@
       <c r="U77" s="27"/>
       <c r="V77" s="27"/>
       <c r="W77" s="6" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="78" spans="17:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -12286,7 +12617,7 @@
       <c r="U78" s="27"/>
       <c r="V78" s="27"/>
       <c r="W78" s="6" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="79" spans="17:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -12301,7 +12632,7 @@
       <c r="U79" s="27"/>
       <c r="V79" s="27"/>
       <c r="W79" s="6" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="80" spans="17:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -12316,7 +12647,7 @@
       <c r="U80" s="27"/>
       <c r="V80" s="27"/>
       <c r="W80" s="6" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="81" spans="17:33" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -12331,12 +12662,12 @@
       <c r="U81" s="27"/>
       <c r="V81" s="27"/>
       <c r="W81" s="6" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="85" spans="17:33" ht="16" x14ac:dyDescent="0.2">
       <c r="Q85" s="30" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="R85" s="27"/>
       <c r="S85" s="27"/>
@@ -12345,7 +12676,7 @@
       <c r="V85" s="27"/>
       <c r="W85" s="27"/>
       <c r="Y85" s="30" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="Z85" s="27"/>
       <c r="AA85" s="27"/>
@@ -12359,13 +12690,13 @@
     <row r="86" spans="17:33" x14ac:dyDescent="0.2">
       <c r="Q86" s="10"/>
       <c r="R86" s="10" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="S86" s="10" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="W86" s="10" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="87" spans="17:33" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -12380,10 +12711,10 @@
       <c r="U87" s="27"/>
       <c r="V87" s="27"/>
       <c r="W87" s="6" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="Y87" s="28" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="Z87" s="27"/>
       <c r="AA87" s="27"/>
@@ -12406,10 +12737,10 @@
       <c r="U88" s="27"/>
       <c r="V88" s="27"/>
       <c r="W88" s="6" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="Y88" s="26" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="Z88" s="27"/>
       <c r="AA88" s="27"/>
@@ -12432,7 +12763,7 @@
       <c r="U89" s="27"/>
       <c r="V89" s="27"/>
       <c r="W89" s="6" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="Y89" s="27"/>
       <c r="Z89" s="27"/>
@@ -12456,7 +12787,7 @@
       <c r="U90" s="27"/>
       <c r="V90" s="27"/>
       <c r="W90" s="6" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="Y90" s="27"/>
       <c r="Z90" s="27"/>
@@ -12480,7 +12811,7 @@
       <c r="U91" s="27"/>
       <c r="V91" s="27"/>
       <c r="W91" s="6" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="Y91" s="27"/>
       <c r="Z91" s="27"/>
@@ -12494,7 +12825,7 @@
     </row>
     <row r="93" spans="17:33" x14ac:dyDescent="0.2">
       <c r="Y93" s="28" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="Z93" s="27"/>
       <c r="AA93" s="27"/>
@@ -12507,7 +12838,7 @@
     </row>
     <row r="94" spans="17:33" x14ac:dyDescent="0.2">
       <c r="Y94" s="26" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Z94" s="27"/>
       <c r="AA94" s="27"/>
@@ -12553,7 +12884,7 @@
     </row>
     <row r="99" spans="25:33" x14ac:dyDescent="0.2">
       <c r="Y99" s="28" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="Z99" s="27"/>
       <c r="AA99" s="27"/>
@@ -12566,7 +12897,7 @@
     </row>
     <row r="100" spans="25:33" x14ac:dyDescent="0.2">
       <c r="Y100" s="26" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="Z100" s="27"/>
       <c r="AA100" s="27"/>
@@ -12612,7 +12943,7 @@
     </row>
     <row r="105" spans="25:33" x14ac:dyDescent="0.2">
       <c r="Y105" s="28" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="Z105" s="27"/>
       <c r="AA105" s="27"/>
@@ -12625,7 +12956,7 @@
     </row>
     <row r="106" spans="25:33" x14ac:dyDescent="0.2">
       <c r="Y106" s="26" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="Z106" s="27"/>
       <c r="AA106" s="27"/>
@@ -12671,7 +13002,7 @@
     </row>
     <row r="121" spans="17:33" ht="16" x14ac:dyDescent="0.2">
       <c r="Q121" s="30" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="R121" s="27"/>
       <c r="S121" s="27"/>
@@ -12680,7 +13011,7 @@
       <c r="V121" s="27"/>
       <c r="W121" s="27"/>
       <c r="Y121" s="30" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="Z121" s="27"/>
       <c r="AA121" s="27"/>
@@ -12694,13 +13025,13 @@
     <row r="122" spans="17:33" x14ac:dyDescent="0.2">
       <c r="Q122" s="10"/>
       <c r="R122" s="10" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="S122" s="10" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="W122" s="10" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="123" spans="17:33" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -12715,10 +13046,10 @@
       <c r="U123" s="27"/>
       <c r="V123" s="27"/>
       <c r="W123" s="6" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="Y123" s="28" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="Z123" s="27"/>
       <c r="AA123" s="27"/>
@@ -12735,16 +13066,16 @@
         <v>2</v>
       </c>
       <c r="S124" s="26" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="T124" s="27"/>
       <c r="U124" s="27"/>
       <c r="V124" s="27"/>
       <c r="W124" s="6" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="Y124" s="26" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="Z124" s="27"/>
       <c r="AA124" s="27"/>
@@ -12767,7 +13098,7 @@
       <c r="U125" s="27"/>
       <c r="V125" s="27"/>
       <c r="W125" s="6" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="Y125" s="27"/>
       <c r="Z125" s="27"/>
@@ -12791,7 +13122,7 @@
       <c r="U126" s="27"/>
       <c r="V126" s="27"/>
       <c r="W126" s="6" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="Y126" s="27"/>
       <c r="Z126" s="27"/>
@@ -12815,7 +13146,7 @@
       <c r="U127" s="27"/>
       <c r="V127" s="27"/>
       <c r="W127" s="6" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="Y127" s="27"/>
       <c r="Z127" s="27"/>
@@ -12839,7 +13170,7 @@
       <c r="U128" s="27"/>
       <c r="V128" s="27"/>
       <c r="W128" s="6" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="129" spans="17:33" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -12854,10 +13185,10 @@
       <c r="U129" s="27"/>
       <c r="V129" s="27"/>
       <c r="W129" s="6" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="Y129" s="28" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="Z129" s="27"/>
       <c r="AA129" s="27"/>
@@ -12880,10 +13211,10 @@
       <c r="U130" s="27"/>
       <c r="V130" s="27"/>
       <c r="W130" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="Y130" s="26" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="Z130" s="27"/>
       <c r="AA130" s="27"/>
@@ -12906,7 +13237,7 @@
       <c r="U131" s="27"/>
       <c r="V131" s="27"/>
       <c r="W131" s="6" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="Y131" s="27"/>
       <c r="Z131" s="27"/>
@@ -12930,7 +13261,7 @@
       <c r="U132" s="27"/>
       <c r="V132" s="27"/>
       <c r="W132" s="6" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="Y132" s="27"/>
       <c r="Z132" s="27"/>
@@ -12954,7 +13285,7 @@
       <c r="U133" s="27"/>
       <c r="V133" s="27"/>
       <c r="W133" s="6" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="Y133" s="27"/>
       <c r="Z133" s="27"/>
@@ -12978,7 +13309,7 @@
       <c r="U134" s="27"/>
       <c r="V134" s="27"/>
       <c r="W134" s="6" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="135" spans="17:33" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -12993,10 +13324,10 @@
       <c r="U135" s="27"/>
       <c r="V135" s="27"/>
       <c r="W135" s="6" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="Y135" s="28" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="Z135" s="27"/>
       <c r="AA135" s="27"/>
@@ -13019,10 +13350,10 @@
       <c r="U136" s="27"/>
       <c r="V136" s="27"/>
       <c r="W136" s="6" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="Y136" s="26" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="Z136" s="27"/>
       <c r="AA136" s="27"/>
@@ -13045,7 +13376,7 @@
       <c r="U137" s="27"/>
       <c r="V137" s="27"/>
       <c r="W137" s="6" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="Y137" s="27"/>
       <c r="Z137" s="27"/>
@@ -13069,7 +13400,7 @@
       <c r="U138" s="27"/>
       <c r="V138" s="27"/>
       <c r="W138" s="6" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="Y138" s="27"/>
       <c r="Z138" s="27"/>
@@ -13093,7 +13424,7 @@
       <c r="U139" s="27"/>
       <c r="V139" s="27"/>
       <c r="W139" s="6" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="Y139" s="27"/>
       <c r="Z139" s="27"/>
@@ -13117,7 +13448,7 @@
       <c r="U140" s="27"/>
       <c r="V140" s="27"/>
       <c r="W140" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="141" spans="17:33" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -13132,10 +13463,10 @@
       <c r="U141" s="27"/>
       <c r="V141" s="27"/>
       <c r="W141" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="Y141" s="28" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="Z141" s="27"/>
       <c r="AA141" s="27"/>
@@ -13158,10 +13489,10 @@
       <c r="U142" s="27"/>
       <c r="V142" s="27"/>
       <c r="W142" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="Y142" s="26" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="Z142" s="27"/>
       <c r="AA142" s="27"/>
@@ -13184,7 +13515,7 @@
       <c r="U143" s="27"/>
       <c r="V143" s="27"/>
       <c r="W143" s="6" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="Y143" s="27"/>
       <c r="Z143" s="27"/>
@@ -13208,7 +13539,7 @@
       <c r="U144" s="27"/>
       <c r="V144" s="27"/>
       <c r="W144" s="6" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="Y144" s="27"/>
       <c r="Z144" s="27"/>
@@ -13232,7 +13563,7 @@
       <c r="U145" s="27"/>
       <c r="V145" s="27"/>
       <c r="W145" s="6" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="Y145" s="27"/>
       <c r="Z145" s="27"/>
@@ -13256,7 +13587,7 @@
       <c r="U146" s="27"/>
       <c r="V146" s="27"/>
       <c r="W146" s="6" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="147" spans="17:33" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -13271,7 +13602,7 @@
       <c r="U147" s="27"/>
       <c r="V147" s="27"/>
       <c r="W147" s="6" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="148" spans="17:33" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -13286,7 +13617,7 @@
       <c r="U148" s="27"/>
       <c r="V148" s="27"/>
       <c r="W148" s="6" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="149" spans="17:33" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -13301,7 +13632,7 @@
       <c r="U149" s="27"/>
       <c r="V149" s="27"/>
       <c r="W149" s="6" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="150" spans="17:33" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -13316,7 +13647,7 @@
       <c r="U150" s="27"/>
       <c r="V150" s="27"/>
       <c r="W150" s="6" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="151" spans="17:33" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -13331,7 +13662,7 @@
       <c r="U151" s="27"/>
       <c r="V151" s="27"/>
       <c r="W151" s="6" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="152" spans="17:33" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -13346,7 +13677,7 @@
       <c r="U152" s="27"/>
       <c r="V152" s="27"/>
       <c r="W152" s="6" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="153" spans="17:33" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -13361,7 +13692,7 @@
       <c r="U153" s="27"/>
       <c r="V153" s="27"/>
       <c r="W153" s="6" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="154" spans="17:33" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -13376,7 +13707,7 @@
       <c r="U154" s="27"/>
       <c r="V154" s="27"/>
       <c r="W154" s="6" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="155" spans="17:33" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -13391,7 +13722,7 @@
       <c r="U155" s="27"/>
       <c r="V155" s="27"/>
       <c r="W155" s="6" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
     <row r="156" spans="17:33" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -13406,7 +13737,7 @@
       <c r="U156" s="27"/>
       <c r="V156" s="27"/>
       <c r="W156" s="6" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
     </row>
     <row r="157" spans="17:33" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -13421,7 +13752,7 @@
       <c r="U157" s="27"/>
       <c r="V157" s="27"/>
       <c r="W157" s="6" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="158" spans="17:33" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -13436,12 +13767,12 @@
       <c r="U158" s="27"/>
       <c r="V158" s="27"/>
       <c r="W158" s="6" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="162" spans="17:33" ht="16" x14ac:dyDescent="0.2">
       <c r="Q162" s="30" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="R162" s="27"/>
       <c r="S162" s="27"/>
@@ -13450,7 +13781,7 @@
       <c r="V162" s="27"/>
       <c r="W162" s="27"/>
       <c r="Y162" s="30" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="Z162" s="27"/>
       <c r="AA162" s="27"/>
@@ -13464,13 +13795,13 @@
     <row r="163" spans="17:33" x14ac:dyDescent="0.2">
       <c r="Q163" s="10"/>
       <c r="R163" s="10" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="S163" s="10" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="W163" s="10" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="164" spans="17:33" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -13485,10 +13816,10 @@
       <c r="U164" s="27"/>
       <c r="V164" s="27"/>
       <c r="W164" s="6" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="Y164" s="28" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="Z164" s="27"/>
       <c r="AA164" s="27"/>
@@ -13511,10 +13842,10 @@
       <c r="U165" s="27"/>
       <c r="V165" s="27"/>
       <c r="W165" s="6" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="Y165" s="26" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="Z165" s="27"/>
       <c r="AA165" s="27"/>
@@ -13537,7 +13868,7 @@
       <c r="U166" s="27"/>
       <c r="V166" s="27"/>
       <c r="W166" s="6" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="Y166" s="27"/>
       <c r="Z166" s="27"/>
@@ -13561,7 +13892,7 @@
       <c r="U167" s="27"/>
       <c r="V167" s="27"/>
       <c r="W167" s="6" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="Y167" s="27"/>
       <c r="Z167" s="27"/>
@@ -13585,7 +13916,7 @@
       <c r="U168" s="27"/>
       <c r="V168" s="27"/>
       <c r="W168" s="6" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="Y168" s="27"/>
       <c r="Z168" s="27"/>
@@ -13609,7 +13940,7 @@
       <c r="U169" s="27"/>
       <c r="V169" s="27"/>
       <c r="W169" s="6" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="170" spans="17:33" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -13624,10 +13955,10 @@
       <c r="U170" s="27"/>
       <c r="V170" s="27"/>
       <c r="W170" s="6" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="Y170" s="28" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="Z170" s="27"/>
       <c r="AA170" s="27"/>
@@ -13650,10 +13981,10 @@
       <c r="U171" s="27"/>
       <c r="V171" s="27"/>
       <c r="W171" s="6" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="Y171" s="26" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="Z171" s="27"/>
       <c r="AA171" s="27"/>
@@ -13676,7 +14007,7 @@
       <c r="U172" s="27"/>
       <c r="V172" s="27"/>
       <c r="W172" s="6" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="Y172" s="27"/>
       <c r="Z172" s="27"/>
@@ -13700,7 +14031,7 @@
       <c r="U173" s="27"/>
       <c r="V173" s="27"/>
       <c r="W173" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="Y173" s="27"/>
       <c r="Z173" s="27"/>
@@ -13725,7 +14056,7 @@
     </row>
     <row r="176" spans="17:33" x14ac:dyDescent="0.2">
       <c r="Y176" s="28" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="Z176" s="27"/>
       <c r="AA176" s="27"/>
@@ -13738,7 +14069,7 @@
     </row>
     <row r="177" spans="25:33" x14ac:dyDescent="0.2">
       <c r="Y177" s="26" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="Z177" s="27"/>
       <c r="AA177" s="27"/>
@@ -13784,7 +14115,7 @@
     </row>
     <row r="182" spans="25:33" x14ac:dyDescent="0.2">
       <c r="Y182" s="28" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="Z182" s="27"/>
       <c r="AA182" s="27"/>
@@ -13797,7 +14128,7 @@
     </row>
     <row r="183" spans="25:33" x14ac:dyDescent="0.2">
       <c r="Y183" s="26" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="Z183" s="27"/>
       <c r="AA183" s="27"/>
@@ -13843,7 +14174,7 @@
     </row>
     <row r="198" spans="17:33" ht="16" x14ac:dyDescent="0.2">
       <c r="Q198" s="30" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="R198" s="27"/>
       <c r="S198" s="27"/>
@@ -13852,7 +14183,7 @@
       <c r="V198" s="27"/>
       <c r="W198" s="27"/>
       <c r="Y198" s="30" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="Z198" s="27"/>
       <c r="AA198" s="27"/>
@@ -13866,13 +14197,13 @@
     <row r="199" spans="17:33" x14ac:dyDescent="0.2">
       <c r="Q199" s="10"/>
       <c r="R199" s="10" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="S199" s="10" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="W199" s="10" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="200" spans="17:33" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -13887,10 +14218,10 @@
       <c r="U200" s="27"/>
       <c r="V200" s="27"/>
       <c r="W200" s="6" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="Y200" s="28" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="Z200" s="27"/>
       <c r="AA200" s="27"/>
@@ -13913,10 +14244,10 @@
       <c r="U201" s="27"/>
       <c r="V201" s="27"/>
       <c r="W201" s="6" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="Y201" s="26" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="Z201" s="27"/>
       <c r="AA201" s="27"/>
@@ -13939,7 +14270,7 @@
       <c r="U202" s="27"/>
       <c r="V202" s="27"/>
       <c r="W202" s="6" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="Y202" s="27"/>
       <c r="Z202" s="27"/>
@@ -13963,7 +14294,7 @@
       <c r="U203" s="27"/>
       <c r="V203" s="27"/>
       <c r="W203" s="6" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="Y203" s="27"/>
       <c r="Z203" s="27"/>
@@ -13987,7 +14318,7 @@
       <c r="U204" s="27"/>
       <c r="V204" s="27"/>
       <c r="W204" s="6" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="Y204" s="27"/>
       <c r="Z204" s="27"/>
@@ -14005,18 +14336,18 @@
         <v>1</v>
       </c>
       <c r="S205" s="26" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="T205" s="27"/>
       <c r="U205" s="27"/>
       <c r="V205" s="27"/>
       <c r="W205" s="6" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="206" spans="17:33" x14ac:dyDescent="0.2">
       <c r="Y206" s="28" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="Z206" s="27"/>
       <c r="AA206" s="27"/>
@@ -14029,7 +14360,7 @@
     </row>
     <row r="207" spans="17:33" x14ac:dyDescent="0.2">
       <c r="Y207" s="26" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="Z207" s="27"/>
       <c r="AA207" s="27"/>
@@ -14075,7 +14406,7 @@
     </row>
     <row r="212" spans="25:33" x14ac:dyDescent="0.2">
       <c r="Y212" s="28" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="Z212" s="27"/>
       <c r="AA212" s="27"/>
@@ -14088,7 +14419,7 @@
     </row>
     <row r="213" spans="25:33" x14ac:dyDescent="0.2">
       <c r="Y213" s="26" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="Z213" s="27"/>
       <c r="AA213" s="27"/>
@@ -14134,7 +14465,7 @@
     </row>
     <row r="218" spans="25:33" x14ac:dyDescent="0.2">
       <c r="Y218" s="28" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="Z218" s="27"/>
       <c r="AA218" s="27"/>
@@ -14147,7 +14478,7 @@
     </row>
     <row r="219" spans="25:33" x14ac:dyDescent="0.2">
       <c r="Y219" s="26" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="Z219" s="27"/>
       <c r="AA219" s="27"/>
@@ -14193,7 +14524,7 @@
     </row>
     <row r="234" spans="17:33" ht="16" x14ac:dyDescent="0.2">
       <c r="Q234" s="30" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="R234" s="27"/>
       <c r="S234" s="27"/>
@@ -14202,7 +14533,7 @@
       <c r="V234" s="27"/>
       <c r="W234" s="27"/>
       <c r="Y234" s="30" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="Z234" s="27"/>
       <c r="AA234" s="27"/>
@@ -14216,13 +14547,13 @@
     <row r="235" spans="17:33" x14ac:dyDescent="0.2">
       <c r="Q235" s="10"/>
       <c r="R235" s="10" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="S235" s="10" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="W235" s="10" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="236" spans="17:33" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -14231,16 +14562,16 @@
         <v>1</v>
       </c>
       <c r="S236" s="26" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="T236" s="27"/>
       <c r="U236" s="27"/>
       <c r="V236" s="27"/>
       <c r="W236" s="6" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="Y236" s="28" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="Z236" s="27"/>
       <c r="AA236" s="27"/>
@@ -14263,10 +14594,10 @@
       <c r="U237" s="27"/>
       <c r="V237" s="27"/>
       <c r="W237" s="6" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="Y237" s="26" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="Z237" s="27"/>
       <c r="AA237" s="27"/>
@@ -14289,7 +14620,7 @@
       <c r="U238" s="27"/>
       <c r="V238" s="27"/>
       <c r="W238" s="6" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="Y238" s="27"/>
       <c r="Z238" s="27"/>
@@ -14313,7 +14644,7 @@
       <c r="U239" s="27"/>
       <c r="V239" s="27"/>
       <c r="W239" s="6" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="Y239" s="27"/>
       <c r="Z239" s="27"/>
@@ -14337,7 +14668,7 @@
       <c r="U240" s="27"/>
       <c r="V240" s="27"/>
       <c r="W240" s="6" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="Y240" s="27"/>
       <c r="Z240" s="27"/>
@@ -14361,7 +14692,7 @@
       <c r="U241" s="27"/>
       <c r="V241" s="27"/>
       <c r="W241" s="6" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="242" spans="17:33" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -14376,10 +14707,10 @@
       <c r="U242" s="27"/>
       <c r="V242" s="27"/>
       <c r="W242" s="6" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="Y242" s="28" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="Z242" s="27"/>
       <c r="AA242" s="27"/>
@@ -14402,10 +14733,10 @@
       <c r="U243" s="27"/>
       <c r="V243" s="27"/>
       <c r="W243" s="6" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="Y243" s="26" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="Z243" s="27"/>
       <c r="AA243" s="27"/>
@@ -14428,7 +14759,7 @@
       <c r="U244" s="27"/>
       <c r="V244" s="27"/>
       <c r="W244" s="6" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="Y244" s="27"/>
       <c r="Z244" s="27"/>
@@ -14452,7 +14783,7 @@
       <c r="U245" s="27"/>
       <c r="V245" s="27"/>
       <c r="W245" s="6" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="Y245" s="27"/>
       <c r="Z245" s="27"/>
@@ -14476,7 +14807,7 @@
       <c r="U246" s="27"/>
       <c r="V246" s="27"/>
       <c r="W246" s="6" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="Y246" s="27"/>
       <c r="Z246" s="27"/>
@@ -14500,7 +14831,7 @@
       <c r="U247" s="27"/>
       <c r="V247" s="27"/>
       <c r="W247" s="6" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="248" spans="17:33" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -14515,10 +14846,10 @@
       <c r="U248" s="27"/>
       <c r="V248" s="27"/>
       <c r="W248" s="6" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="Y248" s="28" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="Z248" s="27"/>
       <c r="AA248" s="27"/>
@@ -14541,10 +14872,10 @@
       <c r="U249" s="27"/>
       <c r="V249" s="27"/>
       <c r="W249" s="6" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="Y249" s="26" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="Z249" s="27"/>
       <c r="AA249" s="27"/>
@@ -14567,7 +14898,7 @@
       <c r="U250" s="27"/>
       <c r="V250" s="27"/>
       <c r="W250" s="6" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="Y250" s="27"/>
       <c r="Z250" s="27"/>
@@ -14591,7 +14922,7 @@
       <c r="U251" s="27"/>
       <c r="V251" s="27"/>
       <c r="W251" s="6" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="Y251" s="27"/>
       <c r="Z251" s="27"/>
@@ -14615,7 +14946,7 @@
       <c r="U252" s="27"/>
       <c r="V252" s="27"/>
       <c r="W252" s="6" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="Y252" s="27"/>
       <c r="Z252" s="27"/>
@@ -14639,7 +14970,7 @@
       <c r="U253" s="27"/>
       <c r="V253" s="27"/>
       <c r="W253" s="6" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="254" spans="17:33" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -14654,7 +14985,7 @@
       <c r="U254" s="27"/>
       <c r="V254" s="27"/>
       <c r="W254" s="6" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="255" spans="17:33" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -14669,7 +15000,7 @@
       <c r="U255" s="27"/>
       <c r="V255" s="27"/>
       <c r="W255" s="6" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="256" spans="17:33" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -14684,7 +15015,7 @@
       <c r="U256" s="27"/>
       <c r="V256" s="27"/>
       <c r="W256" s="6" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="257" spans="17:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -14699,7 +15030,7 @@
       <c r="U257" s="27"/>
       <c r="V257" s="27"/>
       <c r="W257" s="6" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="258" spans="17:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -14714,7 +15045,7 @@
       <c r="U258" s="27"/>
       <c r="V258" s="27"/>
       <c r="W258" s="6" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="259" spans="17:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -14729,7 +15060,7 @@
       <c r="U259" s="27"/>
       <c r="V259" s="27"/>
       <c r="W259" s="6" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="260" spans="17:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -14744,7 +15075,7 @@
       <c r="U260" s="27"/>
       <c r="V260" s="27"/>
       <c r="W260" s="6" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="261" spans="17:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -14759,7 +15090,7 @@
       <c r="U261" s="27"/>
       <c r="V261" s="27"/>
       <c r="W261" s="6" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="262" spans="17:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -14774,7 +15105,7 @@
       <c r="U262" s="27"/>
       <c r="V262" s="27"/>
       <c r="W262" s="6" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="263" spans="17:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -14789,7 +15120,7 @@
       <c r="U263" s="27"/>
       <c r="V263" s="27"/>
       <c r="W263" s="6" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="264" spans="17:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -14804,7 +15135,7 @@
       <c r="U264" s="27"/>
       <c r="V264" s="27"/>
       <c r="W264" s="6" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="265" spans="17:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -14819,7 +15150,7 @@
       <c r="U265" s="27"/>
       <c r="V265" s="27"/>
       <c r="W265" s="6" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="266" spans="17:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -14834,7 +15165,7 @@
       <c r="U266" s="27"/>
       <c r="V266" s="27"/>
       <c r="W266" s="6" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="267" spans="17:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -14849,7 +15180,7 @@
       <c r="U267" s="27"/>
       <c r="V267" s="27"/>
       <c r="W267" s="6" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="268" spans="17:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -14864,7 +15195,7 @@
       <c r="U268" s="27"/>
       <c r="V268" s="27"/>
       <c r="W268" s="6" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="269" spans="17:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -14879,7 +15210,7 @@
       <c r="U269" s="27"/>
       <c r="V269" s="27"/>
       <c r="W269" s="6" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="270" spans="17:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -14894,7 +15225,7 @@
       <c r="U270" s="27"/>
       <c r="V270" s="27"/>
       <c r="W270" s="6" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="271" spans="17:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -14909,7 +15240,7 @@
       <c r="U271" s="27"/>
       <c r="V271" s="27"/>
       <c r="W271" s="6" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -15118,105 +15449,1156 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6F49D47-447C-6742-9605-E99AAA6E1415}">
+  <dimension ref="C1:F74"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="45.33203125" customWidth="1"/>
+    <col min="5" max="5" width="38.5" customWidth="1"/>
+    <col min="6" max="6" width="34.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C1">
+        <v>51</v>
+      </c>
+      <c r="D1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E1" t="s">
+        <v>482</v>
+      </c>
+      <c r="F1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="2" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C2">
+        <v>52</v>
+      </c>
+      <c r="D2" t="s">
+        <v>405</v>
+      </c>
+      <c r="E2" t="s">
+        <v>405</v>
+      </c>
+      <c r="F2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="3" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C3">
+        <v>53</v>
+      </c>
+      <c r="D3" t="s">
+        <v>483</v>
+      </c>
+      <c r="E3" t="s">
+        <v>484</v>
+      </c>
+      <c r="F3" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="4" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C4">
+        <v>54</v>
+      </c>
+      <c r="D4" t="s">
+        <v>485</v>
+      </c>
+      <c r="E4" t="s">
+        <v>486</v>
+      </c>
+      <c r="F4" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="5" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C5">
+        <v>55</v>
+      </c>
+      <c r="D5" t="s">
+        <v>410</v>
+      </c>
+      <c r="E5" t="s">
+        <v>487</v>
+      </c>
+      <c r="F5" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="6" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C6">
+        <v>56</v>
+      </c>
+      <c r="D6" t="s">
+        <v>411</v>
+      </c>
+      <c r="E6" t="s">
+        <v>411</v>
+      </c>
+      <c r="F6" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="7" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C7">
+        <v>57</v>
+      </c>
+      <c r="D7" t="s">
+        <v>489</v>
+      </c>
+      <c r="E7" t="s">
+        <v>413</v>
+      </c>
+      <c r="F7" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="8" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C8">
+        <v>58</v>
+      </c>
+      <c r="D8" t="s">
+        <v>414</v>
+      </c>
+      <c r="E8" t="s">
+        <v>490</v>
+      </c>
+      <c r="F8" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="9" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C9">
+        <v>59</v>
+      </c>
+      <c r="D9" t="s">
+        <v>415</v>
+      </c>
+      <c r="E9" t="s">
+        <v>416</v>
+      </c>
+      <c r="F9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C10">
+        <v>60</v>
+      </c>
+      <c r="D10" t="s">
+        <v>491</v>
+      </c>
+      <c r="E10" t="s">
+        <v>491</v>
+      </c>
+      <c r="F10" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="11" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C11">
+        <v>61</v>
+      </c>
+      <c r="D11" t="s">
+        <v>492</v>
+      </c>
+      <c r="E11" t="s">
+        <v>417</v>
+      </c>
+      <c r="F11" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="12" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C12">
+        <v>62</v>
+      </c>
+      <c r="D12" t="s">
+        <v>407</v>
+      </c>
+      <c r="E12" t="s">
+        <v>407</v>
+      </c>
+      <c r="F12" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="13" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C13">
+        <v>63</v>
+      </c>
+      <c r="D13" t="s">
+        <v>493</v>
+      </c>
+      <c r="E13" t="s">
+        <v>419</v>
+      </c>
+      <c r="F13" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="14" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C14">
+        <v>64</v>
+      </c>
+      <c r="D14" t="s">
+        <v>185</v>
+      </c>
+      <c r="E14" t="s">
+        <v>419</v>
+      </c>
+      <c r="F14" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="15" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C15">
+        <v>65</v>
+      </c>
+      <c r="D15" t="s">
+        <v>495</v>
+      </c>
+      <c r="E15" t="s">
+        <v>420</v>
+      </c>
+      <c r="F15" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="16" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C16">
+        <v>66</v>
+      </c>
+      <c r="D16" t="s">
+        <v>422</v>
+      </c>
+      <c r="E16" t="s">
+        <v>496</v>
+      </c>
+      <c r="F16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C17">
+        <v>67</v>
+      </c>
+      <c r="D17" t="s">
+        <v>423</v>
+      </c>
+      <c r="E17" t="s">
+        <v>423</v>
+      </c>
+      <c r="F17" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="18" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C18">
+        <v>68</v>
+      </c>
+      <c r="D18" t="s">
+        <v>497</v>
+      </c>
+      <c r="E18" t="s">
+        <v>424</v>
+      </c>
+      <c r="F18" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C19">
+        <v>69</v>
+      </c>
+      <c r="D19" t="s">
+        <v>498</v>
+      </c>
+      <c r="E19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F19" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C20">
+        <v>70</v>
+      </c>
+      <c r="D20" t="s">
+        <v>425</v>
+      </c>
+      <c r="E20" t="s">
+        <v>90</v>
+      </c>
+      <c r="F20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C21">
+        <v>71</v>
+      </c>
+      <c r="D21" t="s">
+        <v>426</v>
+      </c>
+      <c r="E21" t="s">
+        <v>426</v>
+      </c>
+      <c r="F21" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="22" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C22">
+        <v>72</v>
+      </c>
+      <c r="D22" t="s">
+        <v>425</v>
+      </c>
+      <c r="E22" t="s">
+        <v>90</v>
+      </c>
+      <c r="F22" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C23">
+        <v>73</v>
+      </c>
+      <c r="D23" t="s">
+        <v>162</v>
+      </c>
+      <c r="E23" t="s">
+        <v>162</v>
+      </c>
+      <c r="F23" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="24" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C24">
+        <v>74</v>
+      </c>
+      <c r="D24" t="s">
+        <v>194</v>
+      </c>
+      <c r="E24" t="s">
+        <v>427</v>
+      </c>
+      <c r="F24" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="25" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C25">
+        <v>75</v>
+      </c>
+      <c r="D25" t="s">
+        <v>195</v>
+      </c>
+      <c r="E25" t="s">
+        <v>428</v>
+      </c>
+      <c r="F25" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="26" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C26">
+        <v>76</v>
+      </c>
+      <c r="D26" t="s">
+        <v>196</v>
+      </c>
+      <c r="E26" t="s">
+        <v>429</v>
+      </c>
+      <c r="F26" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="27" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C27">
+        <v>77</v>
+      </c>
+      <c r="D27" t="s">
+        <v>485</v>
+      </c>
+      <c r="E27" t="s">
+        <v>486</v>
+      </c>
+      <c r="F27" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="28" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C28">
+        <v>78</v>
+      </c>
+      <c r="D28" t="s">
+        <v>414</v>
+      </c>
+      <c r="E28" t="s">
+        <v>490</v>
+      </c>
+      <c r="F28" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="29" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C29">
+        <v>79</v>
+      </c>
+      <c r="D29" t="s">
+        <v>430</v>
+      </c>
+      <c r="E29" t="s">
+        <v>416</v>
+      </c>
+      <c r="F29" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C30">
+        <v>80</v>
+      </c>
+      <c r="D30" t="s">
+        <v>499</v>
+      </c>
+      <c r="E30" t="s">
+        <v>407</v>
+      </c>
+      <c r="F30" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="31" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C31">
+        <v>81</v>
+      </c>
+      <c r="D31" t="s">
+        <v>500</v>
+      </c>
+      <c r="E31" t="s">
+        <v>431</v>
+      </c>
+      <c r="F31" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="32" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C32">
+        <v>82</v>
+      </c>
+      <c r="D32" t="s">
+        <v>423</v>
+      </c>
+      <c r="E32" t="s">
+        <v>423</v>
+      </c>
+      <c r="F32" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="33" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C33">
+        <v>83</v>
+      </c>
+      <c r="D33" t="s">
+        <v>203</v>
+      </c>
+      <c r="E33" t="s">
+        <v>428</v>
+      </c>
+      <c r="F33" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="34" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C34">
+        <v>84</v>
+      </c>
+      <c r="D34" t="s">
+        <v>433</v>
+      </c>
+      <c r="E34" t="s">
+        <v>434</v>
+      </c>
+      <c r="F34" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C35">
+        <v>85</v>
+      </c>
+      <c r="D35" t="s">
+        <v>435</v>
+      </c>
+      <c r="E35" t="s">
+        <v>435</v>
+      </c>
+      <c r="F35" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="36" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C36">
+        <v>86</v>
+      </c>
+      <c r="D36" t="s">
+        <v>501</v>
+      </c>
+      <c r="E36" t="s">
+        <v>437</v>
+      </c>
+      <c r="F36" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="37" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C37">
+        <v>87</v>
+      </c>
+      <c r="D37" t="s">
+        <v>502</v>
+      </c>
+      <c r="E37" t="s">
+        <v>439</v>
+      </c>
+      <c r="F37" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="38" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C38">
+        <v>88</v>
+      </c>
+      <c r="D38" t="s">
+        <v>441</v>
+      </c>
+      <c r="E38" t="s">
+        <v>441</v>
+      </c>
+      <c r="F38" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C39">
+        <v>89</v>
+      </c>
+      <c r="D39" t="s">
+        <v>442</v>
+      </c>
+      <c r="E39" t="s">
+        <v>442</v>
+      </c>
+      <c r="F39" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="40" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C40">
+        <v>90</v>
+      </c>
+      <c r="D40" t="s">
+        <v>444</v>
+      </c>
+      <c r="E40" t="s">
+        <v>444</v>
+      </c>
+      <c r="F40" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="41" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C41">
+        <v>91</v>
+      </c>
+      <c r="D41" t="s">
+        <v>446</v>
+      </c>
+      <c r="E41" t="s">
+        <v>447</v>
+      </c>
+      <c r="F41" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="42" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C42">
+        <v>92</v>
+      </c>
+      <c r="D42" t="s">
+        <v>449</v>
+      </c>
+      <c r="E42" t="s">
+        <v>449</v>
+      </c>
+      <c r="F42" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="43" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C43">
+        <v>93</v>
+      </c>
+      <c r="D43" t="s">
+        <v>450</v>
+      </c>
+      <c r="E43" t="s">
+        <v>451</v>
+      </c>
+      <c r="F43" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="44" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C44">
+        <v>94</v>
+      </c>
+      <c r="D44" t="s">
+        <v>452</v>
+      </c>
+      <c r="E44" t="s">
+        <v>452</v>
+      </c>
+      <c r="F44" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="45" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C45">
+        <v>95</v>
+      </c>
+      <c r="D45" t="s">
+        <v>453</v>
+      </c>
+      <c r="E45" t="s">
+        <v>51</v>
+      </c>
+      <c r="F45" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="46" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C46">
+        <v>96</v>
+      </c>
+      <c r="D46" t="s">
+        <v>504</v>
+      </c>
+      <c r="E46" t="s">
+        <v>48</v>
+      </c>
+      <c r="F46" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="47" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C47">
+        <v>97</v>
+      </c>
+      <c r="D47" t="s">
+        <v>454</v>
+      </c>
+      <c r="E47" t="s">
+        <v>455</v>
+      </c>
+      <c r="F47" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="48" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C48">
+        <v>98</v>
+      </c>
+      <c r="D48" t="s">
+        <v>456</v>
+      </c>
+      <c r="E48" t="s">
+        <v>457</v>
+      </c>
+      <c r="F48" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C49">
+        <v>99</v>
+      </c>
+      <c r="D49" t="s">
+        <v>425</v>
+      </c>
+      <c r="E49" t="s">
+        <v>90</v>
+      </c>
+      <c r="F49" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="50" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C50">
+        <v>100</v>
+      </c>
+      <c r="D50" t="s">
+        <v>458</v>
+      </c>
+      <c r="E50" t="s">
+        <v>458</v>
+      </c>
+      <c r="F50" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="51" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C51">
+        <v>101</v>
+      </c>
+      <c r="D51" t="s">
+        <v>505</v>
+      </c>
+      <c r="E51" t="s">
+        <v>460</v>
+      </c>
+      <c r="F51" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="52" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C52">
+        <v>102</v>
+      </c>
+      <c r="D52" t="s">
+        <v>461</v>
+      </c>
+      <c r="E52" t="s">
+        <v>461</v>
+      </c>
+      <c r="F52" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="53" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C53">
+        <v>103</v>
+      </c>
+      <c r="D53" t="s">
+        <v>462</v>
+      </c>
+      <c r="E53" t="s">
+        <v>508</v>
+      </c>
+      <c r="F53" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="54" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C54">
+        <v>104</v>
+      </c>
+      <c r="D54" t="s">
+        <v>509</v>
+      </c>
+      <c r="E54" t="s">
+        <v>509</v>
+      </c>
+      <c r="F54" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="55" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C55">
+        <v>105</v>
+      </c>
+      <c r="D55" t="s">
+        <v>464</v>
+      </c>
+      <c r="E55" t="s">
+        <v>465</v>
+      </c>
+      <c r="F55" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="56" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C56">
+        <v>106</v>
+      </c>
+      <c r="D56" t="s">
+        <v>425</v>
+      </c>
+      <c r="E56" t="s">
+        <v>90</v>
+      </c>
+      <c r="F56" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="57" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C57">
+        <v>107</v>
+      </c>
+      <c r="D57" t="s">
+        <v>227</v>
+      </c>
+      <c r="E57" t="s">
+        <v>466</v>
+      </c>
+      <c r="F57" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="58" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C58">
+        <v>108</v>
+      </c>
+      <c r="D58" t="s">
+        <v>229</v>
+      </c>
+      <c r="E58" t="s">
+        <v>468</v>
+      </c>
+      <c r="F58" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="59" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C59">
+        <v>109</v>
+      </c>
+      <c r="D59" t="s">
+        <v>230</v>
+      </c>
+      <c r="E59" t="s">
+        <v>469</v>
+      </c>
+      <c r="F59" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="60" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C60">
+        <v>110</v>
+      </c>
+      <c r="D60" t="s">
+        <v>231</v>
+      </c>
+      <c r="E60" t="s">
+        <v>511</v>
+      </c>
+      <c r="F60" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="61" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C61">
+        <v>111</v>
+      </c>
+      <c r="D61" t="s">
+        <v>232</v>
+      </c>
+      <c r="E61" t="s">
+        <v>470</v>
+      </c>
+      <c r="F61" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="62" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C62">
+        <v>112</v>
+      </c>
+      <c r="D62" t="s">
+        <v>233</v>
+      </c>
+      <c r="E62" t="s">
+        <v>472</v>
+      </c>
+      <c r="F62" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="63" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C63">
+        <v>113</v>
+      </c>
+      <c r="D63" t="s">
+        <v>234</v>
+      </c>
+      <c r="E63" t="s">
+        <v>473</v>
+      </c>
+      <c r="F63" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="64" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C64">
+        <v>114</v>
+      </c>
+      <c r="D64" t="s">
+        <v>235</v>
+      </c>
+      <c r="E64" t="s">
+        <v>473</v>
+      </c>
+      <c r="F64" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="65" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C65">
+        <v>115</v>
+      </c>
+      <c r="D65" t="s">
+        <v>236</v>
+      </c>
+      <c r="E65" t="s">
+        <v>474</v>
+      </c>
+      <c r="F65" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="66" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C66">
+        <v>116</v>
+      </c>
+      <c r="D66" t="s">
+        <v>237</v>
+      </c>
+      <c r="E66" t="s">
+        <v>474</v>
+      </c>
+      <c r="F66" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="67" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C67">
+        <v>117</v>
+      </c>
+      <c r="D67" t="s">
+        <v>238</v>
+      </c>
+      <c r="E67" t="s">
+        <v>475</v>
+      </c>
+      <c r="F67" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="68" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C68">
+        <v>118</v>
+      </c>
+      <c r="D68" t="s">
+        <v>90</v>
+      </c>
+      <c r="E68" t="s">
+        <v>90</v>
+      </c>
+      <c r="F68" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="69" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C69">
+        <v>119</v>
+      </c>
+      <c r="D69" t="s">
+        <v>239</v>
+      </c>
+      <c r="E69" t="s">
+        <v>477</v>
+      </c>
+      <c r="F69" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="70" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C70">
+        <v>120</v>
+      </c>
+      <c r="D70" t="s">
+        <v>240</v>
+      </c>
+      <c r="E70" t="s">
+        <v>479</v>
+      </c>
+      <c r="F70" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="71" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C71">
+        <v>121</v>
+      </c>
+      <c r="D71" t="s">
+        <v>241</v>
+      </c>
+      <c r="E71" t="s">
+        <v>481</v>
+      </c>
+      <c r="F71" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="72" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C72">
+        <v>122</v>
+      </c>
+      <c r="D72" t="s">
+        <v>243</v>
+      </c>
+      <c r="E72" t="s">
+        <v>513</v>
+      </c>
+      <c r="F72" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="73" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C73">
+        <v>123</v>
+      </c>
+      <c r="D73" t="s">
+        <v>162</v>
+      </c>
+      <c r="E73" t="s">
+        <v>162</v>
+      </c>
+      <c r="F73" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="74" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C74">
+        <v>124</v>
+      </c>
+      <c r="D74" t="s">
+        <v>241</v>
+      </c>
+      <c r="E74" t="s">
+        <v>481</v>
+      </c>
+      <c r="F74" t="s">
+        <v>480</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AD38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
+        <v>379</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>380</v>
+      </c>
+      <c r="I1" s="25" t="s">
+        <v>381</v>
+      </c>
+      <c r="M1" s="25" t="s">
+        <v>382</v>
+      </c>
+      <c r="Q1" s="25" t="s">
         <v>383</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="U1" s="25" t="s">
         <v>384</v>
       </c>
-      <c r="I1" s="25" t="s">
+      <c r="Y1" s="25" t="s">
         <v>385</v>
-      </c>
-      <c r="M1" s="25" t="s">
-        <v>386</v>
-      </c>
-      <c r="Q1" s="25" t="s">
-        <v>387</v>
-      </c>
-      <c r="U1" s="25" t="s">
-        <v>388</v>
-      </c>
-      <c r="Y1" s="25" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="25" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="F2" s="25" t="s">
         <v>7</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="J2" s="25" t="s">
         <v>1</v>
       </c>
       <c r="K2" s="25" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="M2" s="25" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="N2" s="25" t="s">
         <v>7</v>
       </c>
       <c r="O2" s="25" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="Q2" s="25" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="R2" s="25" t="s">
         <v>3</v>
       </c>
       <c r="S2" s="25" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="U2" s="25" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="V2" s="25" t="s">
         <v>7</v>
       </c>
       <c r="W2" s="25" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="Y2" s="25" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="Z2" s="25" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="AA2" s="25" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="AB2" s="25" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="AC2" s="25" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="AD2" s="25" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.2">
@@ -15269,7 +16651,7 @@
         <v>1</v>
       </c>
       <c r="V3" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="W3">
         <v>10</v>
@@ -15298,7 +16680,7 @@
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="G4" s="5">
         <v>53.49</v>
@@ -15316,7 +16698,7 @@
         <v>2</v>
       </c>
       <c r="N4" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="O4" s="5">
         <v>53.49</v>
@@ -16430,7 +17812,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -16442,21 +17824,21 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B1" s="25" t="s">
         <v>5</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="D1" s="25" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
@@ -16470,7 +17852,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B3" t="s">
         <v>44</v>
@@ -16484,7 +17866,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B4" t="s">
         <v>139</v>
@@ -16498,7 +17880,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
@@ -16512,7 +17894,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B6" t="s">
         <v>167</v>
@@ -16526,7 +17908,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B7" t="s">
         <v>167</v>
@@ -16540,7 +17922,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="B8" t="s">
         <v>167</v>
@@ -16554,7 +17936,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B9" t="s">
         <v>167</v>
@@ -16568,7 +17950,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B10" t="s">
         <v>167</v>
@@ -16582,10 +17964,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B11" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C11" s="2">
         <v>46262</v>

--- a/data/database/shopgraph_purchase_history.xlsx
+++ b/data/database/shopgraph_purchase_history.xlsx
@@ -14,8 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_AnalyticsData" sheetId="6" state="hidden" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Imported Receipts" sheetId="7" state="hidden" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BP w1_Aug 26" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BP w1_sep 26" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BP 9_26w1 26" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Purchase History'!$A$1:$S$146</definedName>
@@ -3426,899 +3425,6 @@
 
 <file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Budget vs Category Spending</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="stacked"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'BP w1_Aug 26'!AH1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="5B9BD5"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="5B9BD5"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AG$2:$AG$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AH$2:$AH$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'BP w1_Aug 26'!AI1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="ED7D31"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="ED7D31"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <dLbls>
-            <dLbl>
-              <idx val="1"/>
-              <dLblPos val="ctr"/>
-              <showSerName val="1"/>
-            </dLbl>
-          </dLbls>
-          <cat>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AG$2:$AG$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AI$2:$AI$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'BP w1_Aug 26'!AJ1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="70AD47"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="70AD47"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <dLbls>
-            <dLbl>
-              <idx val="1"/>
-              <dLblPos val="ctr"/>
-              <showSerName val="1"/>
-            </dLbl>
-          </dLbls>
-          <cat>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AG$2:$AG$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AJ$2:$AJ$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="3"/>
-          <order val="3"/>
-          <tx>
-            <strRef>
-              <f>'BP w1_Aug 26'!AK1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="A5A5A5"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="A5A5A5"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <dLbls>
-            <dLbl>
-              <idx val="1"/>
-              <dLblPos val="ctr"/>
-              <showSerName val="1"/>
-            </dLbl>
-          </dLbls>
-          <cat>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AG$2:$AG$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AK$2:$AK$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="4"/>
-          <order val="4"/>
-          <tx>
-            <strRef>
-              <f>'BP w1_Aug 26'!AL1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="FFC000"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="FFC000"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <dLbls>
-            <dLbl>
-              <idx val="1"/>
-              <dLblPos val="ctr"/>
-              <showSerName val="1"/>
-            </dLbl>
-          </dLbls>
-          <cat>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AG$2:$AG$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AL$2:$AL$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="5"/>
-          <order val="5"/>
-          <tx>
-            <strRef>
-              <f>'BP w1_Aug 26'!AM1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="4472C4"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <dLbls>
-            <dLbl>
-              <idx val="1"/>
-              <dLblPos val="ctr"/>
-              <showSerName val="1"/>
-            </dLbl>
-          </dLbls>
-          <cat>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AG$2:$AG$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AM$2:$AM$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="6"/>
-          <order val="6"/>
-          <tx>
-            <strRef>
-              <f>'BP w1_Aug 26'!AN1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="255E91"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="255E91"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <dLbls>
-            <dLbl>
-              <idx val="1"/>
-              <dLblPos val="ctr"/>
-              <showSerName val="1"/>
-            </dLbl>
-          </dLbls>
-          <cat>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AG$2:$AG$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AN$2:$AN$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="7"/>
-          <order val="7"/>
-          <tx>
-            <strRef>
-              <f>'BP w1_Aug 26'!AO1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="9E480E"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="9E480E"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <dLbls>
-            <dLbl>
-              <idx val="1"/>
-              <dLblPos val="ctr"/>
-              <showSerName val="1"/>
-            </dLbl>
-          </dLbls>
-          <cat>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AG$2:$AG$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AO$2:$AO$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="8"/>
-          <order val="8"/>
-          <tx>
-            <strRef>
-              <f>'BP w1_Aug 26'!AP1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="636363"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="636363"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <dLbls>
-            <dLbl>
-              <idx val="1"/>
-              <dLblPos val="ctr"/>
-              <showSerName val="1"/>
-            </dLbl>
-          </dLbls>
-          <cat>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AG$2:$AG$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AP$2:$AP$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="9"/>
-          <order val="9"/>
-          <tx>
-            <strRef>
-              <f>'BP w1_Aug 26'!AQ1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="997300"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="997300"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <dLbls>
-            <dLbl>
-              <idx val="1"/>
-              <dLblPos val="ctr"/>
-              <showSerName val="1"/>
-            </dLbl>
-          </dLbls>
-          <cat>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AG$2:$AG$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AQ$2:$AQ$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="10"/>
-          <order val="10"/>
-          <tx>
-            <strRef>
-              <f>'BP w1_Aug 26'!AR1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="264478"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="264478"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <dLbls>
-            <dLbl>
-              <idx val="1"/>
-              <dLblPos val="ctr"/>
-              <showSerName val="1"/>
-            </dLbl>
-          </dLbls>
-          <cat>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AG$2:$AG$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AR$2:$AR$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="11"/>
-          <order val="11"/>
-          <tx>
-            <strRef>
-              <f>'BP w1_Aug 26'!AS1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="43682B"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="43682B"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <dLbls>
-            <dLbl>
-              <idx val="1"/>
-              <dLblPos val="ctr"/>
-              <showSerName val="1"/>
-            </dLbl>
-          </dLbls>
-          <cat>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AG$2:$AG$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AS$2:$AS$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="12"/>
-          <order val="12"/>
-          <tx>
-            <strRef>
-              <f>'BP w1_Aug 26'!AT1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="8064A2"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="8064A2"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <dLbls>
-            <dLbl>
-              <idx val="1"/>
-              <dLblPos val="ctr"/>
-              <showSerName val="1"/>
-            </dLbl>
-          </dLbls>
-          <cat>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AG$2:$AG$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AT$2:$AT$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="13"/>
-          <order val="13"/>
-          <tx>
-            <strRef>
-              <f>'BP w1_Aug 26'!AU1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4BACC6"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="4BACC6"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <dLbls>
-            <dLbl>
-              <idx val="1"/>
-              <dLblPos val="ctr"/>
-              <showSerName val="1"/>
-            </dLbl>
-          </dLbls>
-          <cat>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AG$2:$AG$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AU$2:$AU$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="14"/>
-          <order val="14"/>
-          <tx>
-            <strRef>
-              <f>'BP w1_Aug 26'!AV1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="F79646"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="F79646"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <dLbls>
-            <dLbl>
-              <idx val="1"/>
-              <dLblPos val="ctr"/>
-              <showSerName val="1"/>
-            </dLbl>
-          </dLbls>
-          <cat>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AG$2:$AG$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AV$2:$AV$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="15"/>
-          <order val="15"/>
-          <tx>
-            <strRef>
-              <f>'BP w1_Aug 26'!AW1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="92A9CF"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="92A9CF"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <dLbls>
-            <dLbl>
-              <idx val="1"/>
-              <dLblPos val="ctr"/>
-              <showSerName val="1"/>
-            </dLbl>
-          </dLbls>
-          <cat>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AG$2:$AG$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AW$2:$AW$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="16"/>
-          <order val="16"/>
-          <tx>
-            <strRef>
-              <f>'BP w1_Aug 26'!AX1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="95B3D7"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="95B3D7"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <dLbls>
-            <dLbl>
-              <idx val="1"/>
-              <dLblPos val="ctr"/>
-              <showSerName val="1"/>
-            </dLbl>
-          </dLbls>
-          <cat>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AG$2:$AG$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AX$2:$AX$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="17"/>
-          <order val="17"/>
-          <tx>
-            <strRef>
-              <f>'BP w1_Aug 26'!AY1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="C0504D"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="C0504D"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <dLbls>
-            <dLbl>
-              <idx val="1"/>
-              <dLblPos val="ctr"/>
-              <showSerName val="1"/>
-            </dLbl>
-          </dLbls>
-          <cat>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AG$2:$AG$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AY$2:$AY$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="18"/>
-          <order val="18"/>
-          <tx>
-            <strRef>
-              <f>'BP w1_Aug 26'!AZ1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="9BBB59"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="9BBB59"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <dLbls>
-            <dLbl>
-              <idx val="1"/>
-              <dLblPos val="ctr"/>
-              <showSerName val="1"/>
-            </dLbl>
-          </dLbls>
-          <cat>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AG$2:$AG$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AZ$2:$AZ$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="19"/>
-          <order val="19"/>
-          <tx>
-            <strRef>
-              <f>'BP w1_Aug 26'!BA1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="7F7F7F"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="7F7F7F"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <dLbls>
-            <dLbl>
-              <idx val="1"/>
-              <dLblPos val="ctr"/>
-              <showSerName val="1"/>
-            </dLbl>
-          </dLbls>
-          <cat>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AG$2:$AG$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'BP w1_Aug 26'!$BA$2:$BA$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="20"/>
-          <order val="20"/>
-          <tx>
-            <strRef>
-              <f>'BP w1_Aug 26'!BB1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="806000"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="806000"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <dLbls>
-            <dLbl>
-              <idx val="1"/>
-              <dLblPos val="ctr"/>
-              <showSerName val="1"/>
-            </dLbl>
-          </dLbls>
-          <cat>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AG$2:$AG$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'BP w1_Aug 26'!$BB$2:$BB$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="21"/>
-          <order val="21"/>
-          <tx>
-            <strRef>
-              <f>'BP w1_Aug 26'!BC1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="ED7D31"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="ED7D31"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <dLbls>
-            <dLbl>
-              <idx val="1"/>
-              <dLblPos val="ctr"/>
-              <showSerName val="1"/>
-            </dLbl>
-          </dLbls>
-          <cat>
-            <numRef>
-              <f>'BP w1_Aug 26'!$AG$2:$AG$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'BP w1_Aug 26'!$BC$2:$BC$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="70"/>
-        <overlap val="100"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>None</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Amount ($)</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
     <title>
@@ -4345,7 +3451,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'BP w1_sep 26'!AH1</f>
+              <f>'BP 9_26w1 26'!AH1</f>
             </strRef>
           </tx>
           <spPr>
@@ -4361,12 +3467,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'BP w1_sep 26'!$AG$2:$AG$3</f>
+              <f>'BP 9_26w1 26'!$AG$2:$AG$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'BP w1_sep 26'!$AH$2:$AH$3</f>
+              <f>'BP 9_26w1 26'!$AH$2:$AH$3</f>
             </numRef>
           </val>
         </ser>
@@ -4375,7 +3481,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'BP w1_sep 26'!AI1</f>
+              <f>'BP 9_26w1 26'!AI1</f>
             </strRef>
           </tx>
           <spPr>
@@ -4398,12 +3504,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'BP w1_sep 26'!$AG$2:$AG$3</f>
+              <f>'BP 9_26w1 26'!$AG$2:$AG$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'BP w1_sep 26'!$AI$2:$AI$3</f>
+              <f>'BP 9_26w1 26'!$AI$2:$AI$3</f>
             </numRef>
           </val>
         </ser>
@@ -4412,7 +3518,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'BP w1_sep 26'!AJ1</f>
+              <f>'BP 9_26w1 26'!AJ1</f>
             </strRef>
           </tx>
           <spPr>
@@ -4435,12 +3541,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'BP w1_sep 26'!$AG$2:$AG$3</f>
+              <f>'BP 9_26w1 26'!$AG$2:$AG$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'BP w1_sep 26'!$AJ$2:$AJ$3</f>
+              <f>'BP 9_26w1 26'!$AJ$2:$AJ$3</f>
             </numRef>
           </val>
         </ser>
@@ -4449,7 +3555,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'BP w1_sep 26'!AK1</f>
+              <f>'BP 9_26w1 26'!AK1</f>
             </strRef>
           </tx>
           <spPr>
@@ -4472,12 +3578,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'BP w1_sep 26'!$AG$2:$AG$3</f>
+              <f>'BP 9_26w1 26'!$AG$2:$AG$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'BP w1_sep 26'!$AK$2:$AK$3</f>
+              <f>'BP 9_26w1 26'!$AK$2:$AK$3</f>
             </numRef>
           </val>
         </ser>
@@ -4486,7 +3592,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'BP w1_sep 26'!AL1</f>
+              <f>'BP 9_26w1 26'!AL1</f>
             </strRef>
           </tx>
           <spPr>
@@ -4509,12 +3615,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'BP w1_sep 26'!$AG$2:$AG$3</f>
+              <f>'BP 9_26w1 26'!$AG$2:$AG$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'BP w1_sep 26'!$AL$2:$AL$3</f>
+              <f>'BP 9_26w1 26'!$AL$2:$AL$3</f>
             </numRef>
           </val>
         </ser>
@@ -4523,7 +3629,7 @@
           <order val="5"/>
           <tx>
             <strRef>
-              <f>'BP w1_sep 26'!AM1</f>
+              <f>'BP 9_26w1 26'!AM1</f>
             </strRef>
           </tx>
           <spPr>
@@ -4546,12 +3652,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'BP w1_sep 26'!$AG$2:$AG$3</f>
+              <f>'BP 9_26w1 26'!$AG$2:$AG$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'BP w1_sep 26'!$AM$2:$AM$3</f>
+              <f>'BP 9_26w1 26'!$AM$2:$AM$3</f>
             </numRef>
           </val>
         </ser>
@@ -4560,7 +3666,7 @@
           <order val="6"/>
           <tx>
             <strRef>
-              <f>'BP w1_sep 26'!AN1</f>
+              <f>'BP 9_26w1 26'!AN1</f>
             </strRef>
           </tx>
           <spPr>
@@ -4583,12 +3689,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'BP w1_sep 26'!$AG$2:$AG$3</f>
+              <f>'BP 9_26w1 26'!$AG$2:$AG$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'BP w1_sep 26'!$AN$2:$AN$3</f>
+              <f>'BP 9_26w1 26'!$AN$2:$AN$3</f>
             </numRef>
           </val>
         </ser>
@@ -4597,7 +3703,7 @@
           <order val="7"/>
           <tx>
             <strRef>
-              <f>'BP w1_sep 26'!AO1</f>
+              <f>'BP 9_26w1 26'!AO1</f>
             </strRef>
           </tx>
           <spPr>
@@ -4620,12 +3726,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'BP w1_sep 26'!$AG$2:$AG$3</f>
+              <f>'BP 9_26w1 26'!$AG$2:$AG$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'BP w1_sep 26'!$AO$2:$AO$3</f>
+              <f>'BP 9_26w1 26'!$AO$2:$AO$3</f>
             </numRef>
           </val>
         </ser>
@@ -4634,7 +3740,7 @@
           <order val="8"/>
           <tx>
             <strRef>
-              <f>'BP w1_sep 26'!AP1</f>
+              <f>'BP 9_26w1 26'!AP1</f>
             </strRef>
           </tx>
           <spPr>
@@ -4657,12 +3763,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'BP w1_sep 26'!$AG$2:$AG$3</f>
+              <f>'BP 9_26w1 26'!$AG$2:$AG$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'BP w1_sep 26'!$AP$2:$AP$3</f>
+              <f>'BP 9_26w1 26'!$AP$2:$AP$3</f>
             </numRef>
           </val>
         </ser>
@@ -4671,7 +3777,7 @@
           <order val="9"/>
           <tx>
             <strRef>
-              <f>'BP w1_sep 26'!AQ1</f>
+              <f>'BP 9_26w1 26'!AQ1</f>
             </strRef>
           </tx>
           <spPr>
@@ -4694,12 +3800,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'BP w1_sep 26'!$AG$2:$AG$3</f>
+              <f>'BP 9_26w1 26'!$AG$2:$AG$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'BP w1_sep 26'!$AQ$2:$AQ$3</f>
+              <f>'BP 9_26w1 26'!$AQ$2:$AQ$3</f>
             </numRef>
           </val>
         </ser>
@@ -4708,7 +3814,7 @@
           <order val="10"/>
           <tx>
             <strRef>
-              <f>'BP w1_sep 26'!AR1</f>
+              <f>'BP 9_26w1 26'!AR1</f>
             </strRef>
           </tx>
           <spPr>
@@ -4731,12 +3837,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'BP w1_sep 26'!$AG$2:$AG$3</f>
+              <f>'BP 9_26w1 26'!$AG$2:$AG$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'BP w1_sep 26'!$AR$2:$AR$3</f>
+              <f>'BP 9_26w1 26'!$AR$2:$AR$3</f>
             </numRef>
           </val>
         </ser>
@@ -4745,7 +3851,7 @@
           <order val="11"/>
           <tx>
             <strRef>
-              <f>'BP w1_sep 26'!AS1</f>
+              <f>'BP 9_26w1 26'!AS1</f>
             </strRef>
           </tx>
           <spPr>
@@ -4768,12 +3874,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'BP w1_sep 26'!$AG$2:$AG$3</f>
+              <f>'BP 9_26w1 26'!$AG$2:$AG$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'BP w1_sep 26'!$AS$2:$AS$3</f>
+              <f>'BP 9_26w1 26'!$AS$2:$AS$3</f>
             </numRef>
           </val>
         </ser>
@@ -4782,7 +3888,7 @@
           <order val="12"/>
           <tx>
             <strRef>
-              <f>'BP w1_sep 26'!AT1</f>
+              <f>'BP 9_26w1 26'!AT1</f>
             </strRef>
           </tx>
           <spPr>
@@ -4805,12 +3911,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'BP w1_sep 26'!$AG$2:$AG$3</f>
+              <f>'BP 9_26w1 26'!$AG$2:$AG$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'BP w1_sep 26'!$AT$2:$AT$3</f>
+              <f>'BP 9_26w1 26'!$AT$2:$AT$3</f>
             </numRef>
           </val>
         </ser>
@@ -4819,7 +3925,7 @@
           <order val="13"/>
           <tx>
             <strRef>
-              <f>'BP w1_sep 26'!AU1</f>
+              <f>'BP 9_26w1 26'!AU1</f>
             </strRef>
           </tx>
           <spPr>
@@ -4842,12 +3948,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'BP w1_sep 26'!$AG$2:$AG$3</f>
+              <f>'BP 9_26w1 26'!$AG$2:$AG$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'BP w1_sep 26'!$AU$2:$AU$3</f>
+              <f>'BP 9_26w1 26'!$AU$2:$AU$3</f>
             </numRef>
           </val>
         </ser>
@@ -4856,7 +3962,7 @@
           <order val="14"/>
           <tx>
             <strRef>
-              <f>'BP w1_sep 26'!AV1</f>
+              <f>'BP 9_26w1 26'!AV1</f>
             </strRef>
           </tx>
           <spPr>
@@ -4879,12 +3985,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'BP w1_sep 26'!$AG$2:$AG$3</f>
+              <f>'BP 9_26w1 26'!$AG$2:$AG$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'BP w1_sep 26'!$AV$2:$AV$3</f>
+              <f>'BP 9_26w1 26'!$AV$2:$AV$3</f>
             </numRef>
           </val>
         </ser>
@@ -4893,7 +3999,7 @@
           <order val="15"/>
           <tx>
             <strRef>
-              <f>'BP w1_sep 26'!AW1</f>
+              <f>'BP 9_26w1 26'!AW1</f>
             </strRef>
           </tx>
           <spPr>
@@ -4916,12 +4022,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'BP w1_sep 26'!$AG$2:$AG$3</f>
+              <f>'BP 9_26w1 26'!$AG$2:$AG$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'BP w1_sep 26'!$AW$2:$AW$3</f>
+              <f>'BP 9_26w1 26'!$AW$2:$AW$3</f>
             </numRef>
           </val>
         </ser>
@@ -4930,7 +4036,7 @@
           <order val="16"/>
           <tx>
             <strRef>
-              <f>'BP w1_sep 26'!AX1</f>
+              <f>'BP 9_26w1 26'!AX1</f>
             </strRef>
           </tx>
           <spPr>
@@ -4953,12 +4059,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'BP w1_sep 26'!$AG$2:$AG$3</f>
+              <f>'BP 9_26w1 26'!$AG$2:$AG$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'BP w1_sep 26'!$AX$2:$AX$3</f>
+              <f>'BP 9_26w1 26'!$AX$2:$AX$3</f>
             </numRef>
           </val>
         </ser>
@@ -4967,7 +4073,7 @@
           <order val="17"/>
           <tx>
             <strRef>
-              <f>'BP w1_sep 26'!AY1</f>
+              <f>'BP 9_26w1 26'!AY1</f>
             </strRef>
           </tx>
           <spPr>
@@ -4990,12 +4096,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'BP w1_sep 26'!$AG$2:$AG$3</f>
+              <f>'BP 9_26w1 26'!$AG$2:$AG$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'BP w1_sep 26'!$AY$2:$AY$3</f>
+              <f>'BP 9_26w1 26'!$AY$2:$AY$3</f>
             </numRef>
           </val>
         </ser>
@@ -5004,7 +4110,7 @@
           <order val="18"/>
           <tx>
             <strRef>
-              <f>'BP w1_sep 26'!AZ1</f>
+              <f>'BP 9_26w1 26'!AZ1</f>
             </strRef>
           </tx>
           <spPr>
@@ -5027,12 +4133,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'BP w1_sep 26'!$AG$2:$AG$3</f>
+              <f>'BP 9_26w1 26'!$AG$2:$AG$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'BP w1_sep 26'!$AZ$2:$AZ$3</f>
+              <f>'BP 9_26w1 26'!$AZ$2:$AZ$3</f>
             </numRef>
           </val>
         </ser>
@@ -5041,7 +4147,7 @@
           <order val="19"/>
           <tx>
             <strRef>
-              <f>'BP w1_sep 26'!BA1</f>
+              <f>'BP 9_26w1 26'!BA1</f>
             </strRef>
           </tx>
           <spPr>
@@ -5064,12 +4170,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'BP w1_sep 26'!$AG$2:$AG$3</f>
+              <f>'BP 9_26w1 26'!$AG$2:$AG$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'BP w1_sep 26'!$BA$2:$BA$3</f>
+              <f>'BP 9_26w1 26'!$BA$2:$BA$3</f>
             </numRef>
           </val>
         </ser>
@@ -5078,7 +4184,7 @@
           <order val="20"/>
           <tx>
             <strRef>
-              <f>'BP w1_sep 26'!BB1</f>
+              <f>'BP 9_26w1 26'!BB1</f>
             </strRef>
           </tx>
           <spPr>
@@ -5101,12 +4207,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'BP w1_sep 26'!$AG$2:$AG$3</f>
+              <f>'BP 9_26w1 26'!$AG$2:$AG$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'BP w1_sep 26'!$BB$2:$BB$3</f>
+              <f>'BP 9_26w1 26'!$BB$2:$BB$3</f>
             </numRef>
           </val>
         </ser>
@@ -5115,7 +4221,7 @@
           <order val="21"/>
           <tx>
             <strRef>
-              <f>'BP w1_sep 26'!BC1</f>
+              <f>'BP 9_26w1 26'!BC1</f>
             </strRef>
           </tx>
           <spPr>
@@ -5138,12 +4244,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'BP w1_sep 26'!$AG$2:$AG$3</f>
+              <f>'BP 9_26w1 26'!$AG$2:$AG$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'BP w1_sep 26'!$BC$2:$BC$3</f>
+              <f>'BP 9_26w1 26'!$BC$2:$BC$3</f>
             </numRef>
           </val>
         </ser>
@@ -11994,33 +11100,6 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>17</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6480000" cy="4680000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -19523,872 +18602,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:BC49"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="38" customWidth="1" style="84" min="1" max="1"/>
-    <col width="48" customWidth="1" style="84" min="2" max="2"/>
-    <col width="6" customWidth="1" style="84" min="10" max="10"/>
-    <col width="28" customWidth="1" style="84" min="11" max="11"/>
-    <col width="14" customWidth="1" style="84" min="12" max="12"/>
-    <col width="16" customWidth="1" style="84" min="28" max="28"/>
-    <col width="16" customWidth="1" style="84" min="29" max="29"/>
-    <col width="16" customWidth="1" style="84" min="30" max="30"/>
-    <col width="16" customWidth="1" style="84" min="31" max="31"/>
-    <col width="16" customWidth="1" style="84" min="32" max="32"/>
-    <col width="16" customWidth="1" style="84" min="33" max="33"/>
-    <col width="16" customWidth="1" style="84" min="34" max="34"/>
-    <col width="16" customWidth="1" style="84" min="35" max="35"/>
-    <col width="16" customWidth="1" style="84" min="36" max="36"/>
-    <col width="16" customWidth="1" style="84" min="37" max="37"/>
-    <col width="16" customWidth="1" style="84" min="38" max="38"/>
-    <col width="16" customWidth="1" style="84" min="39" max="39"/>
-    <col width="16" customWidth="1" style="84" min="40" max="40"/>
-    <col width="16" customWidth="1" style="84" min="41" max="41"/>
-    <col width="16" customWidth="1" style="84" min="42" max="42"/>
-    <col width="16" customWidth="1" style="84" min="43" max="43"/>
-    <col width="16" customWidth="1" style="84" min="44" max="44"/>
-    <col width="16" customWidth="1" style="84" min="45" max="45"/>
-    <col width="16" customWidth="1" style="84" min="46" max="46"/>
-    <col width="16" customWidth="1" style="84" min="47" max="47"/>
-    <col width="16" customWidth="1" style="84" min="48" max="48"/>
-    <col width="16" customWidth="1" style="84" min="49" max="49"/>
-    <col width="16" customWidth="1" style="84" min="50" max="50"/>
-    <col width="16" customWidth="1" style="84" min="51" max="51"/>
-    <col width="16" customWidth="1" style="84" min="52" max="52"/>
-    <col width="16" customWidth="1" style="84" min="53" max="53"/>
-    <col width="16" customWidth="1" style="84" min="54" max="54"/>
-    <col width="16" customWidth="1" style="84" min="55" max="55"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="106" t="inlineStr">
-        <is>
-          <t>w1_sep</t>
-        </is>
-      </c>
-      <c r="AB1" s="107" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="AC1" s="107" t="inlineStr">
-        <is>
-          <t>Ideal Remaining Budget</t>
-        </is>
-      </c>
-      <c r="AD1" s="107" t="inlineStr">
-        <is>
-          <t>Actual Remaining Budget</t>
-        </is>
-      </c>
-      <c r="AE1" s="107" t="inlineStr">
-        <is>
-          <t>Cumulative Spending</t>
-        </is>
-      </c>
-      <c r="AG1" s="107" t="inlineStr">
-        <is>
-          <t>Comparison</t>
-        </is>
-      </c>
-      <c r="AH1" s="107" t="inlineStr">
-        <is>
-          <t>Budget</t>
-        </is>
-      </c>
-      <c r="AI1" s="107" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ1" s="107" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK1" s="107" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL1" s="107" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AM1" s="107" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AN1" s="107" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AO1" s="107" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AP1" s="107" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AQ1" s="107" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AR1" s="107" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AS1" s="107" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AT1" s="107" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AU1" s="107" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AV1" s="107" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AW1" s="107" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AX1" s="107" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AY1" s="107" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AZ1" s="107" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="BA1" s="107" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BB1" s="107" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="BC1" s="107" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="AB2" s="2" t="n">
-        <v>46264</v>
-      </c>
-      <c r="AC2" s="132" t="n">
-        <v>230</v>
-      </c>
-      <c r="AD2" s="132" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE2" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>Budget</t>
-        </is>
-      </c>
-      <c r="AH2" s="132" t="n">
-        <v>230</v>
-      </c>
-      <c r="AI2" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC2" s="132" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="109" t="inlineStr">
-        <is>
-          <t>Budget Plan</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>w1_sep</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="n">
-        <v>46265</v>
-      </c>
-      <c r="AC3" s="132" t="n">
-        <v>191.6666666666667</v>
-      </c>
-      <c r="AD3" s="132" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE3" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>Spent</t>
-        </is>
-      </c>
-      <c r="AH3" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" s="132" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="AK3" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" s="132" t="n">
-        <v>26.16</v>
-      </c>
-      <c r="AM3" s="132" t="n">
-        <v>29.75</v>
-      </c>
-      <c r="AN3" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" s="132" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AP3" s="132" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="AQ3" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" s="132" t="n">
-        <v>18.57</v>
-      </c>
-      <c r="AW3" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" s="132" t="n">
-        <v>18.76</v>
-      </c>
-      <c r="AZ3" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" s="132" t="n">
-        <v>7.19</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="109" t="inlineStr">
-        <is>
-          <t>Start Date</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>46264</v>
-      </c>
-      <c r="AB4" s="2" t="n">
-        <v>46266</v>
-      </c>
-      <c r="AC4" s="132" t="n">
-        <v>153.3333333333333</v>
-      </c>
-      <c r="AD4" s="132" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE4" s="132" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="109" t="inlineStr">
-        <is>
-          <t>End Date</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>46270</v>
-      </c>
-      <c r="AB5" s="2" t="n">
-        <v>46267</v>
-      </c>
-      <c r="AC5" s="132" t="n">
-        <v>115</v>
-      </c>
-      <c r="AD5" s="132" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE5" s="132" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="109" t="inlineStr">
-        <is>
-          <t>Category Scope</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>All Categories</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>46268</v>
-      </c>
-      <c r="AC6" s="132" t="n">
-        <v>76.66666666666667</v>
-      </c>
-      <c r="AD6" s="132" t="n">
-        <v>68.00999999999999</v>
-      </c>
-      <c r="AE6" s="132" t="n">
-        <v>161.99</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="109" t="inlineStr">
-        <is>
-          <t>Categories</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>All Categories</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="n">
-        <v>46269</v>
-      </c>
-      <c r="AC7" s="132" t="n">
-        <v>38.33333333333332</v>
-      </c>
-      <c r="AD7" s="132" t="n">
-        <v>68.00999999999999</v>
-      </c>
-      <c r="AE7" s="132" t="n">
-        <v>161.99</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="109" t="inlineStr">
-        <is>
-          <t>Budget</t>
-        </is>
-      </c>
-      <c r="B8" s="132" t="n">
-        <v>230</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>46270</v>
-      </c>
-      <c r="AC8" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="132" t="n">
-        <v>68.00999999999999</v>
-      </c>
-      <c r="AE8" s="132" t="n">
-        <v>161.99</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="109" t="inlineStr">
-        <is>
-          <t>Total Spent</t>
-        </is>
-      </c>
-      <c r="B9" s="132" t="n">
-        <v>161.99</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="109" t="inlineStr">
-        <is>
-          <t>Remaining Budget</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>68.00999999999999</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="109" t="inlineStr">
-        <is>
-          <t>Relevant Date</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>46268</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="109" t="inlineStr">
-        <is>
-          <t>Ideal Spending Through Relevant Date</t>
-        </is>
-      </c>
-      <c r="B12" s="132" t="n">
-        <v>153.3333333333333</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="109" t="inlineStr">
-        <is>
-          <t>Actual Spending Through Relevant Date</t>
-        </is>
-      </c>
-      <c r="B13" s="132" t="n">
-        <v>161.99</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="109" t="inlineStr">
-        <is>
-          <t>Ahead / Behind Budget</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Behind by $8.66</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="110" t="inlineStr">
-        <is>
-          <t>Budget vs Category Spending</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="J18" s="111" t="inlineStr">
-        <is>
-          <t>Category Key</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="J19" s="107" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="K19" s="107" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="L19" s="107" t="inlineStr">
-        <is>
-          <t>Spent</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="J20" s="112" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Baby Care</t>
-        </is>
-      </c>
-      <c r="L20" s="132" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="J21" s="113" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Bakery</t>
-        </is>
-      </c>
-      <c r="L21" s="132" t="n">
-        <v>6.79</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="J22" s="114" t="n">
-        <v>3</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Condiments &amp; Seasonings</t>
-        </is>
-      </c>
-      <c r="L22" s="132" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="J23" s="115" t="n">
-        <v>4</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Dairy</t>
-        </is>
-      </c>
-      <c r="L23" s="132" t="n">
-        <v>26.16</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="J24" s="116" t="n">
-        <v>5</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Dessert</t>
-        </is>
-      </c>
-      <c r="L24" s="132" t="n">
-        <v>29.75</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="J25" s="117" t="n">
-        <v>6</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Eggs</t>
-        </is>
-      </c>
-      <c r="L25" s="132" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="J26" s="118" t="n">
-        <v>7</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Fees</t>
-        </is>
-      </c>
-      <c r="L26" s="132" t="n">
-        <v>1.87</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="J27" s="119" t="n">
-        <v>8</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Fish</t>
-        </is>
-      </c>
-      <c r="L27" s="132" t="n">
-        <v>52.9</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="J28" s="120" t="n">
-        <v>9</v>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Frozen</t>
-        </is>
-      </c>
-      <c r="L28" s="132" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="J29" s="121" t="n">
-        <v>10</v>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Frozen Food</t>
-        </is>
-      </c>
-      <c r="L29" s="132" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="J30" s="122" t="n">
-        <v>11</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Home Improvement</t>
-        </is>
-      </c>
-      <c r="L30" s="132" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="J31" s="123" t="n">
-        <v>12</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Meat</t>
-        </is>
-      </c>
-      <c r="L31" s="132" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="J32" s="124" t="n">
-        <v>13</v>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Office Supplies</t>
-        </is>
-      </c>
-      <c r="L32" s="132" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="J33" s="125" t="n">
-        <v>14</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Pantry</t>
-        </is>
-      </c>
-      <c r="L33" s="132" t="n">
-        <v>18.57</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="J34" s="126" t="n">
-        <v>15</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Pets</t>
-        </is>
-      </c>
-      <c r="L34" s="132" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="J35" s="127" t="n">
-        <v>16</v>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Prepared Eating</t>
-        </is>
-      </c>
-      <c r="L35" s="132" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="J36" s="128" t="n">
-        <v>17</v>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Produce</t>
-        </is>
-      </c>
-      <c r="L36" s="132" t="n">
-        <v>18.76</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="J37" s="129" t="n">
-        <v>18</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Self Care</t>
-        </is>
-      </c>
-      <c r="L37" s="132" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="J38" s="130" t="n">
-        <v>19</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Toiletries, Cleaning and Disposables</t>
-        </is>
-      </c>
-      <c r="L38" s="132" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="J39" s="131" t="n">
-        <v>20</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Torah</t>
-        </is>
-      </c>
-      <c r="L39" s="132" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="J40" s="112" t="n">
-        <v>21</v>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Wine</t>
-        </is>
-      </c>
-      <c r="L40" s="132" t="n">
-        <v>7.19</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="83" t="inlineStr">
-        <is>
-          <t>Interpretation: the chart has exactly two bars. Budget is the full configured Budget Plan amount. Spent is one stacked bar; each colored segment is the amount spent in one Category through the Relevant Date. The number inside a segment matches the Category Key on the right.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48"/>
-    <row r="49"/>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="J18:L18"/>
-    <mergeCell ref="A47:H49"/>
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -26682,9 +24895,9 @@
     </row>
   </sheetData>
   <mergeCells count="281">
+    <mergeCell ref="S118:V118"/>
+    <mergeCell ref="Y113:AG113"/>
     <mergeCell ref="S207:V207"/>
-    <mergeCell ref="Y113:AG113"/>
-    <mergeCell ref="S118:V118"/>
     <mergeCell ref="S158:V158"/>
     <mergeCell ref="S329:V329"/>
     <mergeCell ref="S210:V210"/>
@@ -33276,7 +31489,7 @@
     <row r="1">
       <c r="A1" s="106" t="inlineStr">
         <is>
-          <t>w1_Aug</t>
+          <t>9_26w1</t>
         </is>
       </c>
       <c r="AB1" s="107" t="inlineStr">
@@ -33417,13 +31630,13 @@
     </row>
     <row r="2">
       <c r="AB2" s="2" t="n">
-        <v>46264</v>
+        <v>46266</v>
       </c>
       <c r="AC2" s="132" t="n">
-        <v>280</v>
+        <v>233</v>
       </c>
       <c r="AD2" s="132" t="n">
-        <v>280</v>
+        <v>233</v>
       </c>
       <c r="AE2" s="132" t="n">
         <v>0</v>
@@ -33434,7 +31647,7 @@
         </is>
       </c>
       <c r="AH2" s="132" t="n">
-        <v>280</v>
+        <v>233</v>
       </c>
       <c r="AI2" s="132" t="n">
         <v>0</v>
@@ -33508,17 +31721,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>w1_Aug</t>
+          <t>9_26w1</t>
         </is>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="AC3" s="132" t="n">
-        <v>233.3333333333333</v>
+        <v>174.75</v>
       </c>
       <c r="AD3" s="132" t="n">
-        <v>280</v>
+        <v>233</v>
       </c>
       <c r="AE3" s="132" t="n">
         <v>0</v>
@@ -33602,19 +31815,19 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46264</v>
+        <v>46266</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="AC4" s="132" t="n">
-        <v>186.6666666666667</v>
+        <v>116.5</v>
       </c>
       <c r="AD4" s="132" t="n">
-        <v>280</v>
+        <v>71.00999999999999</v>
       </c>
       <c r="AE4" s="132" t="n">
-        <v>0</v>
+        <v>161.99</v>
       </c>
     </row>
     <row r="5">
@@ -33627,16 +31840,16 @@
         <v>46270</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="AC5" s="132" t="n">
-        <v>140</v>
+        <v>58.25</v>
       </c>
       <c r="AD5" s="132" t="n">
-        <v>280</v>
+        <v>71.00999999999999</v>
       </c>
       <c r="AE5" s="132" t="n">
-        <v>0</v>
+        <v>161.99</v>
       </c>
     </row>
     <row r="6">
@@ -33651,13 +31864,13 @@
         </is>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>46268</v>
+        <v>46270</v>
       </c>
       <c r="AC6" s="132" t="n">
-        <v>93.33333333333334</v>
+        <v>0</v>
       </c>
       <c r="AD6" s="132" t="n">
-        <v>118.01</v>
+        <v>71.00999999999999</v>
       </c>
       <c r="AE6" s="132" t="n">
         <v>161.99</v>
@@ -33674,18 +31887,6 @@
           <t>All Categories</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="n">
-        <v>46269</v>
-      </c>
-      <c r="AC7" s="132" t="n">
-        <v>46.66666666666666</v>
-      </c>
-      <c r="AD7" s="132" t="n">
-        <v>118.01</v>
-      </c>
-      <c r="AE7" s="132" t="n">
-        <v>161.99</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="109" t="inlineStr">
@@ -33694,19 +31895,7 @@
         </is>
       </c>
       <c r="B8" s="132" t="n">
-        <v>280</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>46270</v>
-      </c>
-      <c r="AC8" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="132" t="n">
-        <v>118.01</v>
-      </c>
-      <c r="AE8" s="132" t="n">
-        <v>161.99</v>
+        <v>233</v>
       </c>
     </row>
     <row r="9">
@@ -33726,7 +31915,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>118.01</v>
+        <v>71.00999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -33736,7 +31925,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46268</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="12">
@@ -33746,7 +31935,7 @@
         </is>
       </c>
       <c r="B12" s="132" t="n">
-        <v>186.6666666666667</v>
+        <v>233</v>
       </c>
     </row>
     <row r="13">
@@ -33767,7 +31956,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ahead by $24.68</t>
+          <t>Ahead by $71.01</t>
         </is>
       </c>
     </row>
